--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0535c04d39f14a07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Red904a60920644e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf75f6ac41e984c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R79bf4eeac3344af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R80b4e1d92f114724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R8db4cef7d68c4e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8db76da38b9e4e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6a394c190c1b45e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rc08491ecee6147c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R7cedd2f9392c40ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R39ccb643969546e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R485449992f34496d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +36,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,6 +73,11 @@
         <x:fgColor rgb="FFDBEAFE"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -94,7 +99,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -141,6 +146,9 @@
     <x:xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -149,8 +157,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D10" headerRowCount="1">
-  <x:autoFilter ref="A1:D10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D9" headerRowCount="1">
+  <x:autoFilter ref="A1:D9"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -162,8 +170,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E15" headerRowCount="1">
-  <x:autoFilter ref="A1:E15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E16" headerRowCount="1">
+  <x:autoFilter ref="A1:E16"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -176,14 +184,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:E17" headerRowCount="1">
-  <x:autoFilter ref="A1:E17"/>
-  <x:tableColumns count="5">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:F17" headerRowCount="1">
+  <x:autoFilter ref="A1:F17"/>
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
     <x:tableColumn id="3" name="Task"/>
     <x:tableColumn id="4" name="Dependency"/>
     <x:tableColumn id="5" name="Acceptance Criteria"/>
+    <x:tableColumn id="6" name="Status"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -203,8 +212,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D14" headerRowCount="1">
-  <x:autoFilter ref="A1:D14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D11" headerRowCount="1">
+  <x:autoFilter ref="A1:D11"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -377,10 +386,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="21.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
@@ -413,120 +422,106 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>Working branch</x:v>
+        <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>develop</x:v>
+        <x:v>feature/payment-method-metadata</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Planning docs are created after merging feature/payment-provider-config.</x:v>
+        <x:v>Implements payment method/provider metadata exposure.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
-        <x:v>Feature merge commit</x:v>
+        <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>0fda13c</x:v>
+        <x:v>b949678</x:v>
       </x:c>
       <x:c r="C4" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>merge: payment provider config foundation.</x:v>
+        <x:v>docs: add project completion plan.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="str">
-        <x:v>Test status</x:v>
+        <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>Pending final validation</x:v>
+        <x:v>feat: expose payment method metadata</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Run ./mvnw.cmd test before publishing.</x:v>
+        <x:v>Commit hash is created after final validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="str">
-        <x:v>Diff hygiene</x:v>
+        <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Pending final validation</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Pending</x:v>
+        <x:v>./mvnw.cmd test: pass 237 tests</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Run git diff --check before publishing.</x:v>
+        <x:v>Full test suite passed on 2026-06-11.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
-        <x:v>CodeRabbit CLI</x:v>
+        <x:v>Diff hygiene</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Pending availability check</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>Pending</x:v>
+        <x:v>git diff --check: pass</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Record unavailable if coderabbit command is not installed.</x:v>
+        <x:v>No whitespace errors.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
-        <x:v>Publish develop</x:v>
+        <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>Pending push to origin/develop</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>Pending</x:v>
+        <x:v>CodeRabbit CLI unavailable; local diff review completed</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>Push only after validation and main merge flow.</x:v>
+        <x:v>`coderabbit` command not found in this environment.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
-        <x:v>Publish main</x:v>
+        <x:v>Local config</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>Pending merge and push to origin/main</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>Pending</x:v>
+        <x:v>src/main/resources/application.yml</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Merge develop into main with no force push.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="7" t="str">
-        <x:v>Local config</x:v>
-      </x:c>
-      <x:c r="B10" s="7" t="str">
-        <x:v>src/main/resources/application.yml</x:v>
-      </x:c>
-      <x:c r="C10" s="9" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="str">
         <x:v>Keep environment-specific local changes uncommitted.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec3a9a3a9134d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e14806739346c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -536,10 +531,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="47.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="41.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="48.75" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="47.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
@@ -731,76 +726,93 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="7" t="str">
-        <x:v>Rating</x:v>
+        <x:v>Payment</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Create rating, status, public driver ratings</x:v>
+        <x:v>Payment method/provider metadata exposure</x:v>
       </x:c>
       <x:c r="C12" s="7" t="str">
-        <x:v>/api/v1/ratings and driver rating endpoints</x:v>
+        <x:v>/api/v1/payments/methods</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>Prevents duplicate trip ratings.</x:v>
+        <x:v>FE can render CASH/MOMO/VNPAY availability from backend; only enabled methods are accepted for booking.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="7" t="str">
-        <x:v>Notification</x:v>
+        <x:v>Rating</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>Inbox, mark read, FCM token/channel/sender cleanup</x:v>
+        <x:v>Create rating, status, public driver ratings</x:v>
       </x:c>
       <x:c r="C13" s="7" t="str">
-        <x:v>/api/v1/notifications and FCM token endpoints</x:v>
+        <x:v>/api/v1/ratings and driver rating endpoints</x:v>
       </x:c>
       <x:c r="D13" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>In-app, WS, and FCM paths are prepared.</x:v>
+        <x:v>Prevents duplicate trip ratings.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="7" t="str">
-        <x:v>Admin</x:v>
+        <x:v>Notification</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>Driver approval, trip list, dashboard</x:v>
+        <x:v>Inbox, mark read, FCM token/channel/sender cleanup</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
-        <x:v>/api/v1/admin/drivers, /trips, /dashboard</x:v>
+        <x:v>/api/v1/notifications and FCM token endpoints</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>Operational admin views can be built.</x:v>
+        <x:v>In-app, WS, and FCM paths are prepared.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="7" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+      <x:c r="B15" s="7" t="str">
+        <x:v>Driver approval, trip list, dashboard</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>/api/v1/admin/drivers, /trips, /dashboard</x:v>
+      </x:c>
+      <x:c r="D15" s="9" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="str">
+        <x:v>Operational admin views can be built.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="7" t="str">
         <x:v>Docs</x:v>
       </x:c>
-      <x:c r="B15" s="7" t="str">
+      <x:c r="B16" s="7" t="str">
         <x:v>Implementation log and integration plan</x:v>
       </x:c>
-      <x:c r="C15" s="7" t="str">
+      <x:c r="C16" s="7" t="str">
         <x:v>docs/implementation-log.md, integrate-plan.md</x:v>
       </x:c>
-      <x:c r="D15" s="9" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="E15" s="7" t="str">
+      <x:c r="D16" s="9" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47451df5c9c24107"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R618e484efdc64011"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -810,10 +822,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="41.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="57.5" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25.5" customHeight="1">
@@ -832,6 +845,9 @@
       <x:c r="E1" s="4" t="str">
         <x:v>Acceptance Criteria</x:v>
       </x:c>
+      <x:c r="F1" s="4" t="str">
+        <x:v>Status</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="13" t="str">
@@ -849,10 +865,13 @@
       <x:c r="E2" s="7" t="str">
         <x:v>Checkout returns real redirect/deeplink and sandbox success/failure updates payment/trip state.</x:v>
       </x:c>
+      <x:c r="F2" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="13" t="str">
-        <x:v>P0</x:v>
+      <x:c r="A3" s="9" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
         <x:v>Payment methods</x:v>
@@ -861,10 +880,13 @@
         <x:v>Expose supported payment methods/provider metadata to FE.</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Provider enabled flags and config.</x:v>
+        <x:v>Provider enabled flags, registry support, booking guard.</x:v>
       </x:c>
       <x:c r="E3" s="7" t="str">
-        <x:v>FE can render CASH/MoMo/VNPay availability without hardcoding.</x:v>
+        <x:v>GET /api/v1/payments/methods returns CASH/MOMO/VNPAY metadata and booking rejects disabled methods.</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str">
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -883,6 +905,9 @@
       <x:c r="E4" s="7" t="str">
         <x:v>Invalid/replayed callbacks are rejected; valid callbacks are idempotent.</x:v>
       </x:c>
+      <x:c r="F4" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="13" t="str">
@@ -900,6 +925,9 @@
       <x:c r="E5" s="7" t="str">
         <x:v>Success, failure, cancel, and duplicate callbacks map to internal states with tests.</x:v>
       </x:c>
+      <x:c r="F5" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="13" t="str">
@@ -917,6 +945,9 @@
       <x:c r="E6" s="7" t="str">
         <x:v>Estimates and final fare use real route distance/time with fallback handling.</x:v>
       </x:c>
+      <x:c r="F6" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -934,6 +965,9 @@
       <x:c r="E7" s="7" t="str">
         <x:v>Stale drivers become unavailable for matching without manual offline action.</x:v>
       </x:c>
+      <x:c r="F7" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -951,6 +985,9 @@
       <x:c r="E8" s="7" t="str">
         <x:v>FCM works in staging/prod without committed credentials.</x:v>
       </x:c>
+      <x:c r="F8" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -968,6 +1005,9 @@
       <x:c r="E9" s="7" t="str">
         <x:v>Auth, booking, matching, tracking, payment, notification, and admin flows run in CI.</x:v>
       </x:c>
+      <x:c r="F9" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -985,6 +1025,9 @@
       <x:c r="E10" s="7" t="str">
         <x:v>Production defaults are explicit, observable, and safe.</x:v>
       </x:c>
+      <x:c r="F10" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -1002,6 +1045,9 @@
       <x:c r="E11" s="7" t="str">
         <x:v>Schema changes are reproducible and documented per release.</x:v>
       </x:c>
+      <x:c r="F11" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="15" t="str">
@@ -1019,6 +1065,9 @@
       <x:c r="E12" s="7" t="str">
         <x:v>Drivers upload files; admins view secure document URLs.</x:v>
       </x:c>
+      <x:c r="F12" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="15" t="str">
@@ -1036,6 +1085,9 @@
       <x:c r="E13" s="7" t="str">
         <x:v>Only trip participants can send/subscribe to messages.</x:v>
       </x:c>
+      <x:c r="F13" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="15" t="str">
@@ -1053,6 +1105,9 @@
       <x:c r="E14" s="7" t="str">
         <x:v>Scheduled ride dispatch starts at configured lead time.</x:v>
       </x:c>
+      <x:c r="F14" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="15" t="str">
@@ -1070,6 +1125,9 @@
       <x:c r="E15" s="7" t="str">
         <x:v>Estimate includes transparent surge multiplier breakdown.</x:v>
       </x:c>
+      <x:c r="F15" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="15" t="str">
@@ -1087,6 +1145,9 @@
       <x:c r="E16" s="7" t="str">
         <x:v>Bookings outside service zones are handled according to policy.</x:v>
       </x:c>
+      <x:c r="F16" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="15" t="str">
@@ -1104,11 +1165,14 @@
       <x:c r="E17" s="7" t="str">
         <x:v>Admin can inspect demand, revenue, cancellation, and utilization trends.</x:v>
       </x:c>
+      <x:c r="F17" s="13" t="str">
+        <x:v>Open</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d7a1d0e6dea42f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646faffcdc754c50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1145,7 +1209,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo/VNPay providers, signatures, provider metadata, sandbox tests.</x:v>
+        <x:v>MoMo/VNPay providers, signatures, provider metadata refinement, sandbox tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Online sandbox payment can be completed and reconciled.</x:v>
@@ -1224,7 +1288,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3a552d005214ec4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d132a2237a94b0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1311,13 +1375,13 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="str">
-        <x:v>Admin driver approval</x:v>
+        <x:v>Fare estimate</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>/api/v1/admin/drivers/pending and approval endpoint</x:v>
+        <x:v>/api/v1/bookings/estimate</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Review pending drivers and approve/reject with reason.</x:v>
+        <x:v>Show estimate before passenger confirms booking.</x:v>
       </x:c>
       <x:c r="D6" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -1325,13 +1389,13 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
-        <x:v>Fare estimate</x:v>
+        <x:v>Payment methods</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>/api/v1/bookings/estimate</x:v>
+        <x:v>/api/v1/payments/methods</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Show estimate before passenger confirms booking.</x:v>
+        <x:v>Render payment method options from backend; allow only enabled methods.</x:v>
       </x:c>
       <x:c r="D7" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -1339,27 +1403,27 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
-        <x:v>Booking</x:v>
+        <x:v>Payment checkout</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>/api/v1/bookings</x:v>
+        <x:v>/api/v1/payments/trips/{tripId}, /checkout</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Create booking, show matching progress, cancel where allowed.</x:v>
-      </x:c>
-      <x:c r="D8" s="17" t="str">
-        <x:v>Ready for FE</x:v>
+        <x:v>Support CASH now; handle online redirect only after provider implementation is enabled.</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="str">
-        <x:v>Driver offers</x:v>
+        <x:v>Rating</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>Driver offer APIs and user-specific WebSocket notifications</x:v>
+        <x:v>/api/v1/ratings and rating status/list endpoints</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Show offer countdown and accept/reject actions.</x:v>
+        <x:v>Prompt after completed trip and hide form after rating exists.</x:v>
       </x:c>
       <x:c r="D9" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -1367,13 +1431,13 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="7" t="str">
-        <x:v>Trip tracking</x:v>
+        <x:v>Notifications</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Trip topic WS and tracking REST fallback</x:v>
+        <x:v>/api/v1/notifications, FCM token endpoints, WS notification channel</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Subscribe to live driver location; poll fallback after reconnect.</x:v>
+        <x:v>Register FCM token, show inbox/badge, mark read.</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -1381,64 +1445,22 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
-        <x:v>Payment</x:v>
+        <x:v>Admin trips/dashboard</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}, /checkout</x:v>
+        <x:v>/api/v1/admin/trips, /api/v1/admin/dashboard</x:v>
       </x:c>
       <x:c r="C11" s="7" t="str">
-        <x:v>Support CASH now; show online options only after provider metadata exists.</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>Partial</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="7" t="str">
-        <x:v>Rating</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="str">
-        <x:v>/api/v1/ratings and rating status/list endpoints</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="str">
-        <x:v>Prompt after completed trip and hide form after rating exists.</x:v>
-      </x:c>
-      <x:c r="D12" s="17" t="str">
-        <x:v>Ready for FE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="7" t="str">
-        <x:v>Notifications</x:v>
-      </x:c>
-      <x:c r="B13" s="7" t="str">
-        <x:v>/api/v1/notifications, FCM token endpoints, WS notification channel</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>Register FCM token, show inbox/badge, mark read.</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="str">
-        <x:v>Ready for FE</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="7" t="str">
-        <x:v>Admin trips/dashboard</x:v>
-      </x:c>
-      <x:c r="B14" s="7" t="str">
-        <x:v>/api/v1/admin/trips, /api/v1/admin/dashboard</x:v>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
         <x:v>Build operational dashboard and trip filter screens.</x:v>
       </x:c>
-      <x:c r="D14" s="17" t="str">
+      <x:c r="D11" s="17" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re62c65febfe74279"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77410121b8749fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1475,9 +1497,9 @@
         <x:v>MoMo/VNPay cannot safely launch in production yet.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP and complete sandbox provider implementation first.</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
+        <x:v>Metadata endpoint keeps online methods disabled until real providers are registered and configured.</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
@@ -1491,7 +1513,7 @@
       <x:c r="C3" s="7" t="str">
         <x:v>Implement provider-specific signature checks and idempotency.</x:v>
       </x:c>
-      <x:c r="D3" s="11" t="str">
+      <x:c r="D3" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
@@ -1505,7 +1527,7 @@
       <x:c r="C4" s="7" t="str">
         <x:v>Integrate a real route provider before real-money launch.</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
+      <x:c r="D4" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
@@ -1519,7 +1541,7 @@
       <x:c r="C5" s="7" t="str">
         <x:v>Add heartbeat/timeout before broad driver testing.</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
+      <x:c r="D5" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
@@ -1533,7 +1555,7 @@
       <x:c r="C6" s="7" t="str">
         <x:v>Use env-specific secret store and never commit credentials.</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
+      <x:c r="D6" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
@@ -1547,14 +1569,14 @@
       <x:c r="C7" s="7" t="str">
         <x:v>Add integration/E2E tests and CI before release candidate.</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
+      <x:c r="D7" s="13" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb68cdca964e4594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d4350f539f44f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8db76da38b9e4e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6a394c190c1b45e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rc08491ecee6147c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R7cedd2f9392c40ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R39ccb643969546e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R485449992f34496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R760251edc6834613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rbde37c39f0414397"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R4cedf16314a84180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4da94adb7b6a4fa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb02229f155674d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rbfdd667964d34de0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,7 +36,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +78,21 @@
         <x:fgColor rgb="FFDCFCE7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -99,7 +114,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -147,6 +162,18 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -425,13 +452,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/payment-method-metadata</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="str">
+        <x:v>feature/vnpay-checkout-provider</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Implements payment method/provider metadata exposure.</x:v>
+        <x:v>Implements VNPAY signed checkout URL provider.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -439,13 +466,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>b949678</x:v>
-      </x:c>
-      <x:c r="C4" s="9" t="str">
+        <x:v>develop after merge payment metadata</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>docs: add project completion plan.</x:v>
+        <x:v>feature/payment-method-metadata is merged into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -453,9 +480,9 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: expose payment method metadata</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="str">
+        <x:v>feat: add vnpay checkout provider</x:v>
+      </x:c>
+      <x:c r="C5" s="19" t="str">
         <x:v>Pending</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
@@ -467,9 +494,9 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 237 tests</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
+        <x:v>./mvnw.cmd test: pass 241 tests</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
@@ -483,7 +510,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="C7" s="22" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
@@ -497,7 +524,7 @@
       <x:c r="B8" s="7" t="str">
         <x:v>CodeRabbit CLI unavailable; local diff review completed</x:v>
       </x:c>
-      <x:c r="C8" s="18" t="str">
+      <x:c r="C8" s="22" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
@@ -521,7 +548,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e14806739346c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ffbe8db29944565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,10 +836,27 @@
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="7" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>VNPAY signed checkout URL provider</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="str">
+        <x:v>/api/v1/payments/trips/{tripId}/checkout</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>Creates VNPAY redirect URL with sorted query params and HMAC-SHA512 signature when provider config is enabled.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R618e484efdc64011"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8325d52898e34940"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -857,16 +901,16 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Implement real MoMo and VNPay providers.</x:v>
+        <x:v>Complete MoMo provider and finish VNPAY callback/webhook handling; VNPAY signed checkout URL provider is partially implemented.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Sandbox merchant accounts, provider specs, callback URLs.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Checkout returns real redirect/deeplink and sandbox success/failure updates payment/trip state.</x:v>
-      </x:c>
-      <x:c r="F2" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Online checkout returns real redirect/deeplink; sandbox success/failure updates GoRide payment/trip state; failed/cancelled payments persist correctly.</x:v>
+      </x:c>
+      <x:c r="F2" s="19" t="str">
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1172,7 +1216,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R646faffcdc754c50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62a37d98f1e4433a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1288,7 +1332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d132a2237a94b0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3cf67e12fc469e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1409,9 +1453,9 @@
         <x:v>/api/v1/payments/trips/{tripId}, /checkout</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Support CASH now; handle online redirect only after provider implementation is enabled.</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
+        <x:v>Support CASH now; VNPAY can open checkoutUrl when metadata enabled; MoMo remains disabled until provider implementation exists.</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
@@ -1460,7 +1504,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77410121b8749fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f63e5d998ab4b7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1576,7 +1620,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1d4350f539f44f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab17cc11ed0544d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R760251edc6834613"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rbde37c39f0414397"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R4cedf16314a84180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4da94adb7b6a4fa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb02229f155674d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rbfdd667964d34de0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R171f1adb0e38420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc974d927bd5c4ad8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf43e06d36b4f415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re6bbd1dac0a14adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Raf4d4ac069f24a57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R60099595f3214ccb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -438,13 +438,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="C2" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok project planning snapshot.</x:v>
+        <x:v>Asia/Bangkok status after VNPAY webhook/IPN verification.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -452,13 +452,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/vnpay-checkout-provider</x:v>
+        <x:v>feature/vnpay-webhook-verification</x:v>
       </x:c>
       <x:c r="C3" s="20" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Implements VNPAY signed checkout URL provider.</x:v>
+        <x:v>Verifies VNPAY callbacks and returns provider-compatible IPN responses.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -466,13 +466,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge payment metadata</x:v>
+        <x:v>develop after merge vnpay checkout provider</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/payment-method-metadata is merged into develop.</x:v>
+        <x:v>feature/vnpay-checkout-provider is merged into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -480,13 +480,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add vnpay checkout provider</x:v>
+        <x:v>feat: verify vnpay webhook callbacks</x:v>
       </x:c>
       <x:c r="C5" s="19" t="str">
-        <x:v>Pending</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Commit hash is created after final validation.</x:v>
+        <x:v>Feature commit created on the review branch.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -494,13 +494,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 241 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 249 tests</x:v>
       </x:c>
       <x:c r="C6" s="22" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full test suite passed on 2026-06-11.</x:v>
+        <x:v>Full test suite passed on 2026-06-13.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -514,7 +514,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors.</x:v>
+        <x:v>No whitespace errors on 2026-06-13.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -548,7 +548,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ffbe8db29944565"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95cdfc6e256742ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -847,16 +847,33 @@
         <x:v>/api/v1/payments/trips/{tripId}/checkout</x:v>
       </x:c>
       <x:c r="D18" s="19" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
         <x:v>Creates VNPAY redirect URL with sorted query params and HMAC-SHA512 signature when provider config is enabled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>VNPAY signature-verified webhook and IPN response</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>/api/v1/payments/providers/vnpay/webhook</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>GET/POST callbacks verify signature, merchant and amount; GET IPN returns RspCode/Message and duplicate success does not repeat completion workflow.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8325d52898e34940"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ebdaa2c68274f9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -901,13 +918,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Complete MoMo provider and finish VNPAY callback/webhook handling; VNPAY signed checkout URL provider is partially implemented.</x:v>
+        <x:v>Complete MoMo provider; finish VNPAY sandbox/E2E validation against a real merchant callback flow.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Sandbox merchant accounts, provider specs, callback URLs.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Online checkout returns real redirect/deeplink; sandbox success/failure updates GoRide payment/trip state; failed/cancelled payments persist correctly.</x:v>
+        <x:v>Online checkout returns real redirect/deeplink; VNPAY IPN RspCode handling is accepted by sandbox; failed/cancelled payments persist correctly.</x:v>
       </x:c>
       <x:c r="F2" s="19" t="str">
         <x:v>Partial</x:v>
@@ -941,16 +958,16 @@
         <x:v>Webhook security</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Verify provider signatures and request freshness.</x:v>
+        <x:v>Add MoMo signature verification and provider request freshness/replay checks; VNPAY vnp_SecureHash verification is implemented.</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>Provider secret keys and canonical algorithms.</x:v>
+        <x:v>Provider secret keys, canonical algorithms, reliable provider timestamp/nonce policy.</x:v>
       </x:c>
       <x:c r="E4" s="7" t="str">
-        <x:v>Invalid/replayed callbacks are rejected; valid callbacks are idempotent.</x:v>
+        <x:v>Invalid signatures are rejected; replay/expired callbacks are rejected where provider data supports it; valid callbacks are idempotent.</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -961,16 +978,16 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Parse MoMo/VNPay sandbox callback payloads.</x:v>
+        <x:v>Complete MoMo callback parsing and run VNPAY sandbox account callback tests; VNPAY success/fail unit mapping is implemented.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Sandbox callback examples.</x:v>
+        <x:v>Sandbox callback examples and merchant test accounts.</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Success, failure, cancel, and duplicate callbacks map to internal states with tests.</x:v>
+        <x:v>Sandbox success/failure/refund-like statuses map to internal payment states with tests.</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1216,7 +1233,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62a37d98f1e4433a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6c6569c150d499d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1253,7 +1270,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo/VNPay providers, signatures, provider metadata refinement, sandbox tests.</x:v>
+        <x:v>MoMo checkout/webhook, VNPAY sandbox E2E callback validation, webhook replay/freshness policy, sandbox tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Online sandbox payment can be completed and reconciled.</x:v>
@@ -1332,7 +1349,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3cf67e12fc469e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88127b6e948b47fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1447,13 +1464,13 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="str">
-        <x:v>Payment checkout</x:v>
+        <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}, /checkout</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/vnpay/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Support CASH now; VNPAY can open checkoutUrl when metadata enabled; MoMo remains disabled until provider implementation exists.</x:v>
+        <x:v>Open VNPAY checkoutUrl only when enabled; after redirect refresh payment detail. The provider calls GET IPN and receives raw RspCode/Message.</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
         <x:v>Partial</x:v>
@@ -1504,7 +1521,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f63e5d998ab4b7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5adadb2c86a94318"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1535,30 +1552,30 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Online payment providers are foundations only.</x:v>
+        <x:v>Online payment providers are not production-complete.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>MoMo/VNPay cannot safely launch in production yet.</x:v>
+        <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Metadata endpoint keeps online methods disabled until real providers are registered and configured.</x:v>
+        <x:v>Keep CASH as MVP; expose VNPAY only when backend metadata says enabled and provider env is configured.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>Webhook signatures are incomplete.</x:v>
+        <x:v>Webhook protection is partial by provider.</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>Payment state could be spoofed if public callback URL is exposed.</x:v>
+        <x:v>MoMo is not implemented and replay/freshness checks are still open.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Implement provider-specific signature checks and idempotency.</x:v>
+        <x:v>Keep VNPAY signature checks enabled; add MoMo verification and replay policy before public launch.</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1620,7 +1637,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab17cc11ed0544d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3861fe69ab284e8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R171f1adb0e38420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc974d927bd5c4ad8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf43e06d36b4f415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re6bbd1dac0a14adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Raf4d4ac069f24a57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R60099595f3214ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9206f0a8766a4b35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R27eb6afd36cf4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R24bbe3f0d1d64a0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5162a06a419e4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6a9e0a7e49b34698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R65673dcaab2548ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,8 +35,26 @@
       <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF173D2B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF5A4400"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7A1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +111,21 @@
         <x:fgColor rgb="FFDCFCE7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7F5E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1BF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFADBD8"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -114,7 +147,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -174,6 +207,32 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -440,11 +499,11 @@
       <x:c r="B2" s="7" t="str">
         <x:v>2026-06-13</x:v>
       </x:c>
-      <x:c r="C2" s="9" t="str">
+      <x:c r="C2" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after VNPAY webhook/IPN verification.</x:v>
+        <x:v>Asia/Bangkok status after MoMo create-payment checkout implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -452,13 +511,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/vnpay-webhook-verification</x:v>
-      </x:c>
-      <x:c r="C3" s="20" t="str">
-        <x:v>Done</x:v>
+        <x:v>feature/momo-checkout-provider</x:v>
+      </x:c>
+      <x:c r="C3" s="28" t="str">
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Verifies VNPAY callbacks and returns provider-compatible IPN responses.</x:v>
+        <x:v>Adds signed MoMo checkout creation; IPN/webhook remains a later commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -466,13 +525,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge vnpay checkout provider</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="str">
+        <x:v>develop after merge vnpay webhook verification</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/vnpay-checkout-provider is merged into develop.</x:v>
+        <x:v>feature/vnpay-webhook-verification is merged into develop at 04c2606.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -480,13 +539,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: verify vnpay webhook callbacks</x:v>
-      </x:c>
-      <x:c r="C5" s="19" t="str">
+        <x:v>feat: add momo checkout provider</x:v>
+      </x:c>
+      <x:c r="C5" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Feature commit created on the review branch.</x:v>
+        <x:v>Feature commit created on feature/momo-checkout-provider; waiting for user review before merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -494,9 +553,9 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 249 tests</x:v>
-      </x:c>
-      <x:c r="C6" s="22" t="str">
+        <x:v>./mvnw.cmd test: pass 262 tests</x:v>
+      </x:c>
+      <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
@@ -510,7 +569,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="22" t="str">
+      <x:c r="C7" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
@@ -522,13 +581,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>CodeRabbit CLI unavailable; local diff review completed</x:v>
-      </x:c>
-      <x:c r="C8" s="22" t="str">
-        <x:v>Done</x:v>
+        <x:v>CodeRabbit CLI blocked by install policy</x:v>
+      </x:c>
+      <x:c r="C8" s="32" t="str">
+        <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>`coderabbit` command not found in this environment.</x:v>
+        <x:v>CLI is missing; the environment rejected execution of the official downloaded installer script.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -548,7 +607,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95cdfc6e256742ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6229fda8cb34095"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -748,7 +807,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>CASH works; online provider foundation exists.</x:v>
+        <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -765,7 +824,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>FE can render CASH/MOMO/VNPAY availability from backend; only enabled methods are accepted for booking.</x:v>
+        <x:v>FE can render CASH/MOMO/VNPAY availability; online methods require provider registration, enabled config, and provider-specific required fields.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -836,6 +895,23 @@
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>MoMo signed create-payment checkout provider</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>/api/v1/payments/trips/{tripId}/checkout</x:v>
+      </x:c>
+      <x:c r="D17" s="24" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E17" s="29" t="str">
+        <x:v>Creates captureWallet checkout with stable IDs, HMAC-SHA256 verification, 30-second timeouts, and validated payUrl. MoMo IPN remains open.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18">
       <x:c r="A18" s="7" t="str">
         <x:v>Payment</x:v>
@@ -873,7 +949,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ebdaa2c68274f9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3bb175b411640ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -918,13 +994,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Complete MoMo provider; finish VNPAY sandbox/E2E validation against a real merchant callback flow.</x:v>
+        <x:v>Complete MoMo IPN/webhook and payment completion; run MoMo/VNPAY sandbox E2E against real merchant callback flows.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Sandbox merchant accounts, provider specs, callback URLs.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Online checkout returns real redirect/deeplink; VNPAY IPN RspCode handling is accepted by sandbox; failed/cancelled payments persist correctly.</x:v>
+        <x:v>Both online providers return usable checkout URLs; sandbox success/failure updates and reconciles internal payment/trip state.</x:v>
       </x:c>
       <x:c r="F2" s="19" t="str">
         <x:v>Partial</x:v>
@@ -958,7 +1034,7 @@
         <x:v>Webhook security</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Add MoMo signature verification and provider request freshness/replay checks; VNPAY vnp_SecureHash verification is implemented.</x:v>
+        <x:v>Add MoMo IPN signature verification and provider request freshness/replay checks; VNPAY callbacks and MoMo create-response signatures are verified.</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
         <x:v>Provider secret keys, canonical algorithms, reliable provider timestamp/nonce policy.</x:v>
@@ -978,7 +1054,7 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Complete MoMo callback parsing and run VNPAY sandbox account callback tests; VNPAY success/fail unit mapping is implemented.</x:v>
+        <x:v>Implement MoMo callback parsing and run MoMo/VNPAY sandbox account callback tests.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
         <x:v>Sandbox callback examples and merchant test accounts.</x:v>
@@ -1233,7 +1309,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6c6569c150d499d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b74e505a226409f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1263,17 +1339,17 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="7" t="str">
+      <x:c r="A2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo checkout/webhook, VNPAY sandbox E2E callback validation, webhook replay/freshness policy, sandbox tests.</x:v>
+        <x:v>MoMo IPN/webhook and payment completion, MoMo/VNPAY sandbox E2E validation, replay/freshness policy, sandbox tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Online sandbox payment can be completed and reconciled.</x:v>
+        <x:v>Online sandbox payment can be completed and reconciled for both providers.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1349,7 +1425,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88127b6e948b47fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495211bf0f144ee4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1467,10 +1543,10 @@
         <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/vnpay/webhook</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Open VNPAY checkoutUrl only when enabled; after redirect refresh payment detail. The provider calls GET IPN and receives raw RspCode/Message.</x:v>
+        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled. VNPAY callback completion is available; keep MoMo operationally disabled until IPN/payment completion is implemented.</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
         <x:v>Partial</x:v>
@@ -1521,7 +1597,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5adadb2c86a94318"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4660a59c850942ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1558,7 +1634,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP; expose VNPAY only when backend metadata says enabled and provider env is configured.</x:v>
+        <x:v>Keep CASH as MVP; expose online methods only when metadata is enabled and the complete callback flow is configured.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1569,10 +1645,10 @@
         <x:v>Webhook protection is partial by provider.</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>MoMo is not implemented and replay/freshness checks are still open.</x:v>
+        <x:v>MoMo create-response verification exists, but MoMo IPN and replay/freshness checks remain open.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Keep VNPAY signature checks enabled; add MoMo verification and replay policy before public launch.</x:v>
+        <x:v>Keep VNPAY signature checks enabled; add MoMo IPN verification and replay policy before public launch.</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1637,7 +1713,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3861fe69ab284e8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ffcd74c347d41e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9206f0a8766a4b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R27eb6afd36cf4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R24bbe3f0d1d64a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5162a06a419e4218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6a9e0a7e49b34698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R65673dcaab2548ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R590f80a96ac943ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R175eb2ea204440be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R866ef1ac720a4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rff68d1dd98b44933"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R01c594fcf8214e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R25de32ece85f4d1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -53,8 +53,14 @@
       <x:color rgb="FF7A1F1F"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF166534"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="15">
+  <x:fills count="20">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -124,6 +130,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFADBD8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7F5E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1BF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD7F5E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFADBD8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -147,7 +178,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -234,6 +265,45 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -256,8 +326,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E16" headerRowCount="1">
-  <x:autoFilter ref="A1:E16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E17" headerRowCount="1">
+  <x:autoFilter ref="A1:E17"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -499,11 +569,11 @@
       <x:c r="B2" s="7" t="str">
         <x:v>2026-06-13</x:v>
       </x:c>
-      <x:c r="C2" s="26" t="str">
+      <x:c r="C2" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after MoMo create-payment checkout implementation.</x:v>
+        <x:v>Asia/Bangkok status after MoMo IPN verification and payment completion implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -511,13 +581,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/momo-checkout-provider</x:v>
-      </x:c>
-      <x:c r="C3" s="28" t="str">
+        <x:v>feature/momo-webhook-verification</x:v>
+      </x:c>
+      <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds signed MoMo checkout creation; IPN/webhook remains a later commit.</x:v>
+        <x:v>Adds signed MoMo IPN handling and provider-compatible HTTP 204 acknowledgement.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -525,13 +595,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge vnpay webhook verification</x:v>
-      </x:c>
-      <x:c r="C4" s="26" t="str">
+        <x:v>develop after merge momo checkout provider</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/vnpay-webhook-verification is merged into develop at 04c2606.</x:v>
+        <x:v>feature/momo-checkout-provider is merged into develop at d04d3c4.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -539,13 +609,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add momo checkout provider</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str">
+        <x:v>feat: verify momo webhook callbacks</x:v>
+      </x:c>
+      <x:c r="C5" s="45" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Feature commit created on feature/momo-checkout-provider; waiting for user review before merge.</x:v>
+        <x:v>Committed on feature branch and awaiting user review before merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -553,9 +623,9 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 262 tests</x:v>
-      </x:c>
-      <x:c r="C6" s="26" t="str">
+        <x:v>./mvnw.cmd test: pass 275 tests</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
@@ -569,7 +639,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="26" t="str">
+      <x:c r="C7" s="39" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
@@ -583,11 +653,11 @@
       <x:c r="B8" s="7" t="str">
         <x:v>CodeRabbit CLI blocked by install policy</x:v>
       </x:c>
-      <x:c r="C8" s="32" t="str">
+      <x:c r="C8" s="41" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>CLI is missing; the environment rejected execution of the official downloaded installer script.</x:v>
+        <x:v>CLI is missing and the environment security policy disallows executing the official downloaded installer script.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -607,7 +677,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6229fda8cb34095"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2dc7995d464ebc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -895,21 +965,21 @@
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="34" customHeight="1">
+    <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Payment</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>MoMo signed create-payment checkout provider</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}/checkout</x:v>
-      </x:c>
-      <x:c r="D17" s="24" t="str">
+        <x:v>MoMo signed checkout and signature-verified IPN</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="str">
+        <x:v>/api/v1/payments/trips/{tripId}/checkout, /api/v1/payments/providers/momo/webhook</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E17" s="29" t="str">
-        <x:v>Creates captureWallet checkout with stable IDs, HMAC-SHA256 verification, 30-second timeouts, and validated payUrl. MoMo IPN remains open.</x:v>
+        <x:v>Creates verified captureWallet checkout; POST IPN verifies HMAC/payment data, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -949,7 +1019,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3bb175b411640ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6535938f1656491e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -994,13 +1064,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Complete MoMo IPN/webhook and payment completion; run MoMo/VNPAY sandbox E2E against real merchant callback flows.</x:v>
+        <x:v>Run MoMo/VNPAY sandbox E2E against real merchant callback flows.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Sandbox merchant accounts, provider specs, callback URLs.</x:v>
+        <x:v>Sandbox merchant accounts, callback URLs, provider test apps.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Both online providers return usable checkout URLs; sandbox success/failure updates and reconciles internal payment/trip state.</x:v>
+        <x:v>Real sandbox success/failure callbacks reconcile internal payment/trip state for both providers.</x:v>
       </x:c>
       <x:c r="F2" s="19" t="str">
         <x:v>Partial</x:v>
@@ -1034,13 +1104,13 @@
         <x:v>Webhook security</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Add MoMo IPN signature verification and provider request freshness/replay checks; VNPAY callbacks and MoMo create-response signatures are verified.</x:v>
+        <x:v>Define provider freshness policy beyond signature verification, pessimistic locking and transaction-reference idempotency.</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>Provider secret keys, canonical algorithms, reliable provider timestamp/nonce policy.</x:v>
+        <x:v>Reliable provider retry/freshness guarantees and optional callback event store.</x:v>
       </x:c>
       <x:c r="E4" s="7" t="str">
-        <x:v>Invalid signatures are rejected; replay/expired callbacks are rejected where provider data supports it; valid callbacks are idempotent.</x:v>
+        <x:v>Stale/conflicting callbacks are rejected without blocking legitimate provider retries.</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1054,13 +1124,13 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Implement MoMo callback parsing and run MoMo/VNPAY sandbox account callback tests.</x:v>
+        <x:v>Run MoMo/VNPAY sandbox account callback tests; unit signature and state mapping are implemented.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
         <x:v>Sandbox callback examples and merchant test accounts.</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Sandbox success/failure/refund-like statuses map to internal payment states with tests.</x:v>
+        <x:v>Real gateway acknowledgements and success/failure states match provider expectations.</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1309,7 +1379,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b74e505a226409f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3628c62fdc6040cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1346,7 +1416,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo IPN/webhook and payment completion, MoMo/VNPAY sandbox E2E validation, replay/freshness policy, sandbox tests.</x:v>
+        <x:v>MoMo/VNPAY sandbox E2E validation, replay/freshness policy, and real merchant callback tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Online sandbox payment can be completed and reconciled for both providers.</x:v>
@@ -1425,7 +1495,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R495211bf0f144ee4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c16027a7264720"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1546,7 +1616,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled. VNPAY callback completion is available; keep MoMo operationally disabled until IPN/payment completion is implemented.</x:v>
+        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled, then refresh payment detail after redirect. Signed provider callbacks update final state; MoMo IPN is backend-only and returns HTTP 204.</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
         <x:v>Partial</x:v>
@@ -1597,7 +1667,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4660a59c850942ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc66c7c28087c4a3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1634,7 +1704,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP; expose online methods only when metadata is enabled and the complete callback flow is configured.</x:v>
+        <x:v>Keep CASH as MVP; enable online methods first in sandbox and only after full callback/UAT validation.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1642,13 +1712,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>Webhook protection is partial by provider.</x:v>
+        <x:v>Webhook freshness policy is incomplete.</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>MoMo create-response verification exists, but MoMo IPN and replay/freshness checks remain open.</x:v>
+        <x:v>Both provider signatures and duplicate handling exist, but there is no explicit stale-callback window or event ledger.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Keep VNPAY signature checks enabled; add MoMo IPN verification and replay policy before public launch.</x:v>
+        <x:v>Keep locking and transaction-reference checks; define a provider-safe freshness/replay policy before launch.</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1713,7 +1783,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ffcd74c347d41e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8271f8e742014069"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R590f80a96ac943ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R175eb2ea204440be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R866ef1ac720a4610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rff68d1dd98b44933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R01c594fcf8214e88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R25de32ece85f4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1a166888ef9b418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc7048eef6d734448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R611f22b44bbf42f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rc91bf201f0a344a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb973a24dccdd4baa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R8a5ae8d3e942411d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,14 @@
       <x:color rgb="FF166534"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF991B1B"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="20">
+  <x:fills count="23">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -155,6 +161,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEE2E2"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -178,7 +199,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="64">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -303,6 +324,56 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -573,7 +644,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after MoMo IPN verification and payment completion implementation.</x:v>
+        <x:v>Asia/Bangkok status after payment webhook freshness and replay policy implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -581,13 +652,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/momo-webhook-verification</x:v>
+        <x:v>feature/payment-webhook-freshness</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds signed MoMo IPN handling and provider-compatible HTTP 204 acknowledgement.</x:v>
+        <x:v>Adds configurable signed callback age/future-skew validation for MoMo and VNPAY.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -595,13 +666,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge momo checkout provider</x:v>
+        <x:v>develop after merge momo webhook verification</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/momo-checkout-provider is merged into develop at d04d3c4.</x:v>
+        <x:v>feature/momo-webhook-verification is merged into develop at a1537a8.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -609,9 +680,9 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: verify momo webhook callbacks</x:v>
-      </x:c>
-      <x:c r="C5" s="45" t="str">
+        <x:v>feat: enforce payment webhook freshness</x:v>
+      </x:c>
+      <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
@@ -623,13 +694,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 275 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 288 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full test suite passed on 2026-06-13.</x:v>
+        <x:v>Targeted payment suite passed 56 tests; full suite passed on 2026-06-13.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -639,7 +710,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="39" t="str">
+      <x:c r="C7" s="59" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
@@ -653,7 +724,7 @@
       <x:c r="B8" s="7" t="str">
         <x:v>CodeRabbit CLI blocked by install policy</x:v>
       </x:c>
-      <x:c r="C8" s="41" t="str">
+      <x:c r="C8" s="63" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
@@ -677,7 +748,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f2dc7995d464ebc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ee95334eb87454d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -979,7 +1050,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E17" s="29" t="str">
-        <x:v>Creates verified captureWallet checkout; POST IPN verifies HMAC/payment data, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
+        <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1013,13 +1084,30 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>GET/POST callbacks verify signature, merchant and amount; GET IPN returns RspCode/Message and duplicate success does not repeat completion workflow.</x:v>
+        <x:v>GET/POST callbacks verify signature, merchant, amount and pay date freshness; duplicate success does not repeat completion workflow.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="55" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B20" s="55" t="str">
+        <x:v>Configurable webhook freshness and replay policy</x:v>
+      </x:c>
+      <x:c r="C20" s="55" t="str">
+        <x:v>MoMo responseTime and VNPAY vnp_PayDate</x:v>
+      </x:c>
+      <x:c r="D20" s="54" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E20" s="55" t="str">
+        <x:v>Rejects stale/future signed callbacks while allowing stale idempotent terminal retries with the same provider transaction reference.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6535938f1656491e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a7a73691dc2406d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1097,23 +1185,23 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="13" t="str">
-        <x:v>P0</x:v>
+      <x:c r="A4" s="53" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
         <x:v>Webhook security</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Define provider freshness policy beyond signature verification, pessimistic locking and transaction-reference idempotency.</x:v>
+        <x:v>Enforce provider freshness policy beyond signature verification, locking and transaction-reference idempotency.</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>Reliable provider retry/freshness guarantees and optional callback event store.</x:v>
+        <x:v>Signed MoMo responseTime and VNPAY vnp_PayDate.</x:v>
       </x:c>
       <x:c r="E4" s="7" t="str">
-        <x:v>Stale/conflicting callbacks are rejected without blocking legitimate provider retries.</x:v>
-      </x:c>
-      <x:c r="F4" s="13" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Stale/future callbacks are rejected while matching terminal retries remain idempotent.</x:v>
+      </x:c>
+      <x:c r="F4" s="53" t="str">
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1379,7 +1467,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3628c62fdc6040cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05886745988e4459"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1416,7 +1504,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo/VNPAY sandbox E2E validation, replay/freshness policy, and real merchant callback tests.</x:v>
+        <x:v>MoMo/VNPAY sandbox E2E validation, provider-specific freshness-window tuning, and real merchant callback tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Online sandbox payment can be completed and reconciled for both providers.</x:v>
@@ -1495,7 +1583,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c16027a7264720"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778ce2b527064f40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1616,7 +1704,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled, then refresh payment detail after redirect. Signed provider callbacks update final state; MoMo IPN is backend-only and returns HTTP 204.</x:v>
+        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled, then refresh payment detail after redirect. Signed callbacks enforce timestamp freshness; MoMo IPN remains backend-only and returns HTTP 204.</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
         <x:v>Partial</x:v>
@@ -1667,7 +1755,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc66c7c28087c4a3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra747999c1c914834"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1712,13 +1800,13 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>Webhook freshness policy is incomplete.</x:v>
+        <x:v>Webhook freshness defaults need sandbox calibration.</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>Both provider signatures and duplicate handling exist, but there is no explicit stale-callback window or event ledger.</x:v>
+        <x:v>The configurable 24-hour age and 5-minute future-skew defaults have not been validated against real merchant retries.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Keep locking and transaction-reference checks; define a provider-safe freshness/replay policy before launch.</x:v>
+        <x:v>Run sandbox/UAT callbacks and tune each provider window without weakening signature or transaction-reference checks.</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1783,7 +1871,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8271f8e742014069"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65318273d0454e70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1a166888ef9b418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc7048eef6d734448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R611f22b44bbf42f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rc91bf201f0a344a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb973a24dccdd4baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R8a5ae8d3e942411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf6340e191bf84115"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd289642e12524df5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R20c73695fc574067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R85a11ec042314881"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rdcc8fb4bbe2744d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R1eb84ad667214c94"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -66,7 +66,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="23">
+  <x:fills count="26">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -161,6 +161,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEE2E2"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -199,7 +214,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="64">
+  <x:cellXfs count="77">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -374,6 +389,45 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="24" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -397,8 +451,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E17" headerRowCount="1">
-  <x:autoFilter ref="A1:E17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E18" headerRowCount="1">
+  <x:autoFilter ref="A1:E18"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -644,7 +698,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after payment webhook freshness and replay policy implementation.</x:v>
+        <x:v>Asia/Bangkok status after OSRM-compatible routing provider implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -652,13 +706,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/payment-webhook-freshness</x:v>
+        <x:v>feature/real-distance-provider</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds configurable signed callback age/future-skew validation for MoMo and VNPAY.</x:v>
+        <x:v>Adds routed distance/duration with configurable Haversine fallback.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -666,13 +720,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge momo webhook verification</x:v>
+        <x:v>develop after merge payment webhook freshness</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/momo-webhook-verification is merged into develop at a1537a8.</x:v>
+        <x:v>feature/payment-webhook-freshness is merged into develop at 88d5fb0.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -680,7 +734,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: enforce payment webhook freshness</x:v>
+        <x:v>feat: add real distance routing provider</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
@@ -694,13 +748,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 288 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 297 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted payment suite passed 56 tests; full suite passed on 2026-06-13.</x:v>
+        <x:v>Targeted routing suite passed 20 tests; full suite passed on 2026-06-13.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -710,7 +764,7 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="59" t="str">
+      <x:c r="C7" s="75" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
@@ -724,7 +778,7 @@
       <x:c r="B8" s="7" t="str">
         <x:v>CodeRabbit CLI blocked by install policy</x:v>
       </x:c>
-      <x:c r="C8" s="63" t="str">
+      <x:c r="C8" s="76" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
@@ -748,7 +802,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ee95334eb87454d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd2e554e85dd46fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1053,21 +1107,21 @@
         <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="7" t="str">
-        <x:v>Payment</x:v>
-      </x:c>
-      <x:c r="B18" s="7" t="str">
-        <x:v>VNPAY signed checkout URL provider</x:v>
-      </x:c>
-      <x:c r="C18" s="7" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}/checkout</x:v>
-      </x:c>
-      <x:c r="D18" s="19" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="E18" s="7" t="str">
-        <x:v>Creates VNPAY redirect URL with sorted query params and HMAC-SHA512 signature when provider config is enabled.</x:v>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="71" t="str">
+        <x:v>Routing</x:v>
+      </x:c>
+      <x:c r="B18" s="71" t="str">
+        <x:v>OSRM-compatible distance and duration provider</x:v>
+      </x:c>
+      <x:c r="C18" s="71" t="str">
+        <x:v>/api/v1/bookings/estimate and booking creation</x:v>
+      </x:c>
+      <x:c r="D18" s="70" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E18" s="71" t="str">
+        <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1104,10 +1158,17 @@
         <x:v>Rejects stale/future signed callbacks while allowing stale idempotent terminal retries with the same provider transaction reference.</x:v>
       </x:c>
     </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a7a73691dc2406d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93446dd21ad4d0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1225,23 +1286,23 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="13" t="str">
-        <x:v>P0</x:v>
+      <x:c r="A6" s="70" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>Maps/distance</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Replace MockDistanceService with real routing provider.</x:v>
+        <x:v>Replace MockDistanceService with an OSRM-compatible routing provider.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Google Maps, Mapbox, HERE, or equivalent key.</x:v>
+        <x:v>Controlled OSRM-compatible endpoint for production UAT.</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
-        <x:v>Estimates and final fare use real route distance/time with fallback handling.</x:v>
-      </x:c>
-      <x:c r="F6" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Estimate/create booking use routed distance/time; provider failures follow configured fallback behavior.</x:v>
+      </x:c>
+      <x:c r="F6" s="70" t="str">
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1467,7 +1528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05886745988e4459"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e163e7579d74014"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1518,10 +1579,10 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Distance/maps provider, route estimates, fallback behavior.</x:v>
+        <x:v>OSRM-compatible routing implemented; production endpoint UAT, fallback monitoring, and timeout tuning remain.</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Fare estimates are based on real route distance/time.</x:v>
+        <x:v>Controlled routing endpoint returns stable estimates and fallback rate is operationally acceptable.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1583,7 +1644,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778ce2b527064f40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b448a7a8b8a4a91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1676,7 +1737,7 @@
         <x:v>/api/v1/bookings/estimate</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Show estimate before passenger confirms booking.</x:v>
+        <x:v>Show backend distance/duration/fare estimate before booking. FE never calls OSRM directly; preserve pickup/dropoff and retry on ROUTING_PROVIDER_ERROR.</x:v>
       </x:c>
       <x:c r="D6" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -1755,7 +1816,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra747999c1c914834"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94066c3ca104587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1814,16 +1875,16 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="str">
-        <x:v>Mock distance provider remains active.</x:v>
+        <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Fare estimates can be inaccurate.</x:v>
+        <x:v>Real routing is implemented, but endpoint capacity, timeout, and fallback frequency are not validated in UAT.</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Integrate a real route provider before real-money launch.</x:v>
+        <x:v>Use a controlled OSRM-compatible endpoint, monitor fallback warnings, and tune profile/timeout before launch.</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1871,7 +1932,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65318273d0454e70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc079c692101a466d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf6340e191bf84115"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd289642e12524df5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R20c73695fc574067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R85a11ec042314881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rdcc8fb4bbe2744d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R1eb84ad667214c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R527a9a7d5a7b401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R60543c4c23af42db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Ra185e9f044414b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Raf4c98b0e7594c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rca720317247f40ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Re4c553bdd1994913"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -65,8 +65,19 @@
       <x:color rgb="FF991B1B"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1E3A8A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="26">
+  <x:fills count="29">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -193,8 +204,23 @@
         <x:fgColor rgb="FFFEE2E2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFBFE3F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="3">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -210,11 +236,25 @@
         <x:color rgb="FFE5E7EB"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD1D5DB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="92">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -428,6 +468,45 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -692,13 +771,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-14</x:v>
       </x:c>
       <x:c r="C2" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after OSRM-compatible routing provider implementation.</x:v>
+        <x:v>Asia/Bangkok status after driver heartbeat/offline timeout implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -706,13 +785,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/real-distance-provider</x:v>
+        <x:v>feature/driver-heartbeat-timeout</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds routed distance/duration with configurable Haversine fallback.</x:v>
+        <x:v>Adds heartbeat TTL refresh and scheduled stale-driver database cleanup.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -720,13 +799,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge payment webhook freshness</x:v>
+        <x:v>develop after merge real distance routing provider</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/payment-webhook-freshness is merged into develop at 88d5fb0.</x:v>
+        <x:v>feature/real-distance-provider is merged into develop at 241f153.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -734,7 +813,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add real distance routing provider</x:v>
+        <x:v>feat: add driver heartbeat timeout</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
@@ -748,13 +827,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 297 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 309 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted routing suite passed 20 tests; full suite passed on 2026-06-13.</x:v>
+        <x:v>Targeted heartbeat suite passed 24 tests; full suite passed on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -768,7 +847,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-13.</x:v>
+        <x:v>No whitespace errors on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -802,7 +881,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd2e554e85dd46fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465199961ec04139"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1159,16 +1238,26 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="48" customHeight="1">
-      <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
-      <x:c r="E21"/>
+      <x:c r="A21" s="81" t="str">
+        <x:v>Driver</x:v>
+      </x:c>
+      <x:c r="B21" s="81" t="str">
+        <x:v>Heartbeat and automatic offline timeout</x:v>
+      </x:c>
+      <x:c r="C21" s="81" t="str">
+        <x:v>POST /api/v1/drivers/me/heartbeat</x:v>
+      </x:c>
+      <x:c r="D21" s="84" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E21" s="81" t="str">
+        <x:v>Refreshes GEO/meta/status TTL without overwriting BUSY; scheduled batch marks stale database profiles offline.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93446dd21ad4d0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99764ef9bc9043d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1306,8 +1395,8 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>P1</x:v>
+      <x:c r="A7" s="88" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>Driver availability</x:v>
@@ -1321,8 +1410,8 @@
       <x:c r="E7" s="7" t="str">
         <x:v>Stale drivers become unavailable for matching without manual offline action.</x:v>
       </x:c>
-      <x:c r="F7" s="13" t="str">
-        <x:v>Open</x:v>
+      <x:c r="F7" s="88" t="str">
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1528,7 +1617,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e163e7579d74014"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd699bf0f253d4aa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1593,10 +1682,10 @@
         <x:v>Driver availability reliability</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Heartbeat endpoint/job, stale-driver timeout, matching tests.</x:v>
+        <x:v>Heartbeat API, Redis TTL refresh and scheduled database offline timeout implemented; production interval tuning remains.</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>Unavailable drivers are not offered new trips.</x:v>
+        <x:v>Stale drivers are excluded from matching and database online state is cleaned in configured batches.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1644,7 +1733,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b448a7a8b8a4a91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13279ad3692a4ba0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1813,10 +1902,24 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="81" t="str">
+        <x:v>Driver availability</x:v>
+      </x:c>
+      <x:c r="B12" s="81" t="str">
+        <x:v>PATCH /api/v1/drivers/me/status, POST /api/v1/drivers/me/heartbeat</x:v>
+      </x:c>
+      <x:c r="C12" s="81" t="str">
+        <x:v>After going online, send current coordinates every 20 seconds before expiresAt; on DRIVER_NOT_AVAILABLE stop heartbeat and require online action again.</x:v>
+      </x:c>
+      <x:c r="D12" s="91" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94066c3ca104587"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf991adade244162"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1889,16 +1992,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="str">
-        <x:v>No driver heartbeat yet.</x:v>
+        <x:v>Heartbeat intervals are not production-calibrated.</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>Matching may send offers to stale online drivers.</x:v>
+        <x:v>Aggressive intervals may cause reconnect churn; loose intervals delay database cleanup.</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Add heartbeat/timeout before broad driver testing.</x:v>
+        <x:v>Start with 20-second client heartbeat and 60-second timeout, then tune using staging disconnect and scheduler metrics.</x:v>
       </x:c>
       <x:c r="D5" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1932,7 +2035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc079c692101a466d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ab4e4b84b464782"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R527a9a7d5a7b401c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R60543c4c23af42db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Ra185e9f044414b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Raf4c98b0e7594c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rca720317247f40ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Re4c553bdd1994913"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R21dff57954ef45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R63105dc6b7d74271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rb69b97b013d2402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R47b3c572fdba47aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R341f6e36c46746dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R02c5fcb1e6c04ed3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="29">
+  <x:fills count="30">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -217,6 +217,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD1FAE5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -254,7 +259,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="92">
+  <x:cellXfs count="96">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -507,6 +512,18 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -777,7 +794,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after driver heartbeat/offline timeout implementation.</x:v>
+        <x:v>Asia/Bangkok status after Firebase production credential setup.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -785,13 +802,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/driver-heartbeat-timeout</x:v>
+        <x:v>feature/firebase-production-config</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds heartbeat TTL refresh and scheduled stale-driver database cleanup.</x:v>
+        <x:v>Adds ADC/service-account loading and fail-fast Firebase startup validation.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -799,13 +816,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge real distance routing provider</x:v>
+        <x:v>develop after merge driver heartbeat timeout</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/real-distance-provider is merged into develop at 241f153.</x:v>
+        <x:v>feature/driver-heartbeat-timeout is merged into develop at e57955c.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -813,7 +830,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add driver heartbeat timeout</x:v>
+        <x:v>feat: add firebase production config</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
@@ -827,13 +844,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 309 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 311 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted heartbeat suite passed 24 tests; full suite passed on 2026-06-14.</x:v>
+        <x:v>Targeted Firebase suite passed 16 tests; full suite passed on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -881,7 +898,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R465199961ec04139"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6174fce87c8b4d54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1123,7 +1140,7 @@
         <x:v>Notification</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>Inbox, mark read, FCM token/channel/sender cleanup</x:v>
+        <x:v>Inbox, FCM token/sender, ADC credentials and startup validation</x:v>
       </x:c>
       <x:c r="C14" s="7" t="str">
         <x:v>/api/v1/notifications and FCM token endpoints</x:v>
@@ -1132,7 +1149,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>In-app, WS, and FCM paths are prepared.</x:v>
+        <x:v>FCM stays disabled by default; enabled deployments use ADC or mounted service-account file and fail startup clearly when credentials are invalid.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1257,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99764ef9bc9043d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R777750f6f56f47a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1415,23 +1432,23 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>P1</x:v>
+      <x:c r="A8" s="95" t="str">
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>Firebase</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Finalize production Firebase service account secret loading.</x:v>
+        <x:v>Finalize production Firebase credential loading.</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>Secure secret store and env profiles.</x:v>
+        <x:v>ADC/workload identity or securely mounted credential file.</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>FCM works in staging/prod without committed credentials.</x:v>
-      </x:c>
-      <x:c r="F8" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>FCM starts without committed credentials and missing/invalid credentials fail startup clearly.</x:v>
+      </x:c>
+      <x:c r="F8" s="95" t="str">
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1617,7 +1634,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd699bf0f253d4aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6574553ad5ce4c1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1696,10 +1713,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secrets, env profiles, CORS/rate limits, observability, DB release strategy.</x:v>
+        <x:v>Firebase ADC/secret loading and fail-fast validation implemented; env profiles, CORS/rate limits, observability and DB release strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging deployment can run with safe production-like config.</x:v>
+        <x:v>Staging deployment can load Firebase identity securely and expose safe production-like config.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1733,7 +1750,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13279ad3692a4ba0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621e29160e5b49e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1919,7 +1936,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf991adade244162"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8cde2afa7104f85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2006,16 +2023,16 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="str">
-        <x:v>Production secrets not finalized.</x:v>
+        <x:v>Firebase identity still needs staging UAT.</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Deployments may fail or require unsafe manual credential handling.</x:v>
+        <x:v>Credential loading is ready, but the real workload identity or secret mount has not been exercised here.</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Use env-specific secret store and never commit credentials.</x:v>
+        <x:v>Prefer ADC/attached identity; otherwise mount credentials outside the image and verify startup plus one staging push.</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2035,7 +2052,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ab4e4b84b464782"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f81280a63094d52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R21dff57954ef45e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R63105dc6b7d74271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rb69b97b013d2402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R47b3c572fdba47aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R341f6e36c46746dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R02c5fcb1e6c04ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R44f4c2dc6ac043a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd5b32919659e4263"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R2aa728cdcc084dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5219e942e13042be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R7dc26b6c7ccc47d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R983ea5c32a1a4e1d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -547,8 +547,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E18" headerRowCount="1">
-  <x:autoFilter ref="A1:E18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E19" headerRowCount="1">
+  <x:autoFilter ref="A1:E19"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -794,7 +794,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after Firebase production credential setup.</x:v>
+        <x:v>Asia/Bangkok status after auth integration test implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -802,13 +802,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/firebase-production-config</x:v>
+        <x:v>feature/auth-integration-tests</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds ADC/service-account loading and fail-fast Firebase startup validation.</x:v>
+        <x:v>Adds Docker-backed PostGIS/Redis integration foundation and full auth HTTP flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -816,13 +816,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge driver heartbeat timeout</x:v>
+        <x:v>develop after merge Firebase production config</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/driver-heartbeat-timeout is merged into develop at e57955c.</x:v>
+        <x:v>feature/firebase-production-config is merged into develop at c0ad35f.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -830,13 +830,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add firebase production config</x:v>
+        <x:v>test: add auth integration flow</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Committed on feature branch and awaiting user review before merge.</x:v>
+        <x:v>Committed on feature/auth-integration-tests; awaiting user review before merge to develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -844,13 +844,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 311 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 312 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted Firebase suite passed 16 tests; full suite passed on 2026-06-14.</x:v>
+        <x:v>Targeted auth integration test passed 1 test; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -898,7 +898,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6174fce87c8b4d54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52a0d74b3f0240bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1220,21 +1220,21 @@
         <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>Payment</x:v>
-      </x:c>
-      <x:c r="B19" t="str">
-        <x:v>VNPAY signature-verified webhook and IPN response</x:v>
-      </x:c>
-      <x:c r="C19" t="str">
-        <x:v>/api/v1/payments/providers/vnpay/webhook</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
-        <x:v>GET/POST callbacks verify signature, merchant, amount and pay date freshness; duplicate success does not repeat completion workflow.</x:v>
+    <x:row r="19" ht="46" customHeight="1">
+      <x:c r="A19" s="29" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B19" s="29" t="str">
+        <x:v>Testcontainers PostGIS/Redis auth integration flow</x:v>
+      </x:c>
+      <x:c r="C19" s="29" t="str">
+        <x:v>AuthFlowIntegrationTests</x:v>
+      </x:c>
+      <x:c r="D19" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E19" s="29" t="str">
+        <x:v>Runs register, JWT-protected request, refresh rotation, logout revocation, and duplicate-phone rejection through HTTP, JPA, and Redis.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="48" customHeight="1">
@@ -1274,7 +1274,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R777750f6f56f47a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5085f2087c6d40fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1459,16 +1459,16 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Add integration/E2E coverage for critical flows.</x:v>
+        <x:v>Auth integration is covered; add booking, matching, trip lifecycle, tracking, payment, notification, and admin integration flows.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Testcontainers or stable local test profile.</x:v>
+        <x:v>Existing Testcontainers PostGIS/Redis base and Docker-enabled CI.</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>Auth, booking, matching, tracking, payment, notification, and admin flows run in CI.</x:v>
+        <x:v>Remaining critical passenger/driver/admin flows run in CI against database/Redis-compatible services.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1634,7 +1634,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6574553ad5ce4c1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4267f04c18474c12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1727,10 +1727,10 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Integration/E2E tests and CI validation.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation and auth HTTP flow implemented; booking/matching/tracking/payment/admin flows and CI validation remain.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Passenger/driver/admin happy paths pass in CI.</x:v>
+        <x:v>All critical passenger/driver/admin happy paths pass in CI.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1750,7 +1750,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621e29160e5b49e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf91f462014b74b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1936,7 +1936,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8cde2afa7104f85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R529540f2bd1144a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="str">
-        <x:v>Integration coverage is limited.</x:v>
+        <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Cross-module regressions may slip through.</x:v>
+        <x:v>Auth runs through HTTP/JWT/JPA/Redis, but cross-module booking, matching, tracking and payment regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Add integration/E2E tests and CI before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for remaining critical flows and run the suite in CI before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f81280a63094d52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4874d70655dd4dd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R44f4c2dc6ac043a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd5b32919659e4263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R2aa728cdcc084dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5219e942e13042be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R7dc26b6c7ccc47d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R983ea5c32a1a4e1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb54e2fcf05f342a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rb137c826fe434f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R854ff96a3adb4f4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R63e2fcb677524c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0b85f967489846c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R2140e55323d744e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -259,7 +259,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="96">
+  <x:cellXfs count="99">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -524,6 +524,15 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -547,8 +556,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E19" headerRowCount="1">
-  <x:autoFilter ref="A1:E19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E20" headerRowCount="1">
+  <x:autoFilter ref="A1:E20"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -561,8 +570,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:F17" headerRowCount="1">
-  <x:autoFilter ref="A1:F17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:F18" headerRowCount="1">
+  <x:autoFilter ref="A1:F18"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
@@ -589,8 +598,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D11" headerRowCount="1">
-  <x:autoFilter ref="A1:D11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D12" headerRowCount="1">
+  <x:autoFilter ref="A1:D12"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -794,7 +803,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after auth integration test implementation.</x:v>
+        <x:v>Asia/Bangkok status after driver trip routing implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -802,13 +811,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/auth-integration-tests</x:v>
+        <x:v>feature/driver-trip-routing</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds Docker-backed PostGIS/Redis integration foundation and full auth HTTP flow.</x:v>
+        <x:v>Connects accepted trips to pickup/dropoff GeoJSON navigation for the assigned driver.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -816,13 +825,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge Firebase production config</x:v>
+        <x:v>develop after merge auth integration tests</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/firebase-production-config is merged into develop at c0ad35f.</x:v>
+        <x:v>feature/auth-integration-tests is merged into develop at 08ec166.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -830,13 +839,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: add auth integration flow</x:v>
+        <x:v>feat: add driver trip routing</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Committed on feature/auth-integration-tests; awaiting user review before merge to develop.</x:v>
+        <x:v>Prepared on feature branch for user review before merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -844,13 +853,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 312 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 321 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted auth integration test passed 1 test; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
+        <x:v>Targeted routing suite passed 15 tests; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -898,7 +907,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52a0d74b3f0240bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec28f73966c4bbf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -914,7 +923,7 @@
     <x:col min="5" max="5" width="47.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Module</x:v>
       </x:c>
@@ -931,7 +940,7 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="7" t="str">
         <x:v>Auth/JWT</x:v>
       </x:c>
@@ -948,7 +957,7 @@
         <x:v>Ready for FE auth session flow.</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>User</x:v>
       </x:c>
@@ -965,7 +974,7 @@
         <x:v>Supports profile page and admin account management.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Driver</x:v>
       </x:c>
@@ -982,7 +991,7 @@
         <x:v>Redis availability is integrated with matching.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Pricing</x:v>
       </x:c>
@@ -999,7 +1008,7 @@
         <x:v>Static configurable pricing is in place.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Booking</x:v>
       </x:c>
@@ -1016,7 +1025,7 @@
         <x:v>Passenger booking flow is wired to trip/matching.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Trip lifecycle</x:v>
       </x:c>
@@ -1033,7 +1042,7 @@
         <x:v>Final fare can use tracking history.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>Matching</x:v>
       </x:c>
@@ -1050,7 +1059,7 @@
         <x:v>Uses Redis GEO/availability data.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>WebSocket</x:v>
       </x:c>
@@ -1067,7 +1076,7 @@
         <x:v>Trip subscriptions are protected.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Tracking</x:v>
       </x:c>
@@ -1084,7 +1093,7 @@
         <x:v>Latest location stored in Redis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1101,7 +1110,7 @@
         <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1118,7 +1127,7 @@
         <x:v>FE can render CASH/MOMO/VNPAY availability; online methods require provider registration, enabled config, and provider-specific required fields.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="str">
         <x:v>Rating</x:v>
       </x:c>
@@ -1135,7 +1144,7 @@
         <x:v>Prevents duplicate trip ratings.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="str">
         <x:v>Notification</x:v>
       </x:c>
@@ -1152,7 +1161,7 @@
         <x:v>FCM stays disabled by default; enabled deployments use ADC or mounted service-account file and fail startup clearly when credentials are invalid.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="7" t="str">
         <x:v>Admin</x:v>
       </x:c>
@@ -1169,7 +1178,7 @@
         <x:v>Operational admin views can be built.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="7" t="str">
         <x:v>Docs</x:v>
       </x:c>
@@ -1186,11 +1195,11 @@
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" t="str">
+    <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A17" s="29" t="str">
         <x:v>Payment</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="29" t="str">
         <x:v>MoMo signed checkout and signature-verified IPN</x:v>
       </x:c>
       <x:c r="C17" s="29" t="str">
@@ -1203,7 +1212,7 @@
         <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="48" customHeight="1">
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" s="71" t="str">
         <x:v>Routing</x:v>
       </x:c>
@@ -1213,14 +1222,14 @@
       <x:c r="C18" s="71" t="str">
         <x:v>/api/v1/bookings/estimate and booking creation</x:v>
       </x:c>
-      <x:c r="D18" s="70" t="str">
+      <x:c r="D18" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E18" s="71" t="str">
         <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="46" customHeight="1">
+    <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A19" s="29" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1237,24 +1246,24 @@
         <x:v>Runs register, JWT-protected request, refresh rotation, logout revocation, and duplicate-phone rejection through HTTP, JPA, and Redis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="48" customHeight="1">
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" s="55" t="str">
-        <x:v>Payment</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="B20" s="55" t="str">
-        <x:v>Configurable webhook freshness and replay policy</x:v>
+        <x:v>Assigned-driver pickup/dropoff GeoJSON navigation</x:v>
       </x:c>
       <x:c r="C20" s="55" t="str">
-        <x:v>MoMo responseTime and VNPAY vnp_PayDate</x:v>
-      </x:c>
-      <x:c r="D20" s="54" t="str">
+        <x:v>POST /api/v1/drivers/trips/{tripId}/route</x:v>
+      </x:c>
+      <x:c r="D20" s="97" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E20" s="55" t="str">
-        <x:v>Rejects stale/future signed callbacks while allowing stale idempotent terminal retries with the same provider transaction reference.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="48" customHeight="1">
+        <x:v>Validates assigned driver and trip status; returns destination, distance/duration, GeoJSON LineString, and OSRM maneuver steps.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A21" s="81" t="str">
         <x:v>Driver</x:v>
       </x:c>
@@ -1274,7 +1283,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5085f2087c6d40fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0a1f793a7994f94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1291,7 +1300,7 @@
     <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Priority</x:v>
       </x:c>
@@ -1311,7 +1320,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A2" s="13" t="str">
         <x:v>P0</x:v>
       </x:c>
@@ -1327,11 +1336,11 @@
       <x:c r="E2" s="7" t="str">
         <x:v>Real sandbox success/failure callbacks reconcile internal payment/trip state for both providers.</x:v>
       </x:c>
-      <x:c r="F2" s="19" t="str">
+      <x:c r="F2" s="11" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1351,8 +1360,8 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="53" t="str">
+    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A4" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
@@ -1367,11 +1376,11 @@
       <x:c r="E4" s="7" t="str">
         <x:v>Stale/future callbacks are rejected while matching terminal retries remain idempotent.</x:v>
       </x:c>
-      <x:c r="F4" s="53" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="F4" s="96" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A5" s="13" t="str">
         <x:v>P0</x:v>
       </x:c>
@@ -1391,8 +1400,8 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="70" t="str">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A6" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
@@ -1407,11 +1416,11 @@
       <x:c r="E6" s="7" t="str">
         <x:v>Estimate/create booking use routed distance/time; provider failures follow configured fallback behavior.</x:v>
       </x:c>
-      <x:c r="F6" s="70" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="F6" s="96" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A7" s="88" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1431,8 +1440,8 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="95" t="str">
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="88" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
@@ -1447,11 +1456,11 @@
       <x:c r="E8" s="7" t="str">
         <x:v>FCM starts without committed credentials and missing/invalid credentials fail startup clearly.</x:v>
       </x:c>
-      <x:c r="F8" s="95" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="F8" s="88" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -1471,7 +1480,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="11" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -1491,7 +1500,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -1511,7 +1520,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1531,7 +1540,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1551,7 +1560,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1571,7 +1580,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1591,7 +1600,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1611,7 +1620,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="15" t="str">
         <x:v>P2</x:v>
       </x:c>
@@ -1629,12 +1638,32 @@
       </x:c>
       <x:c r="F17" s="13" t="str">
         <x:v>Open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A18" s="29" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B18" s="29" t="str">
+        <x:v>Routing UAT</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="str">
+        <x:v>Validate driver navigation against a controlled production/self-hosted routing endpoint and add request-rate controls.</x:v>
+      </x:c>
+      <x:c r="D18" s="29" t="str">
+        <x:v>OSRM-compatible endpoint, staging GPS routes, metrics/rate-limit policy.</x:v>
+      </x:c>
+      <x:c r="E18" s="29" t="str">
+        <x:v>Vietnam routes are accurate enough, latency/error rate is measured, and FE re-route requests are debounced or rate-limited.</x:v>
+      </x:c>
+      <x:c r="F18" s="29" t="str">
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4267f04c18474c12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdba446d6b5c942d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1685,10 +1714,10 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>OSRM-compatible routing implemented; production endpoint UAT, fallback monitoring, and timeout tuning remain.</x:v>
+        <x:v>Fare estimation and assigned-driver pickup/dropoff GeoJSON routing implemented; production endpoint UAT, request-rate control, monitoring, and timeout tuning remain.</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Controlled routing endpoint returns stable estimates and fallback rate is operationally acceptable.</x:v>
+        <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1750,7 +1779,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf91f462014b74b15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf8a4117e94d4c30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1765,7 +1794,7 @@
     <x:col min="4" max="4" width="18.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Screen / Flow</x:v>
       </x:c>
@@ -1779,7 +1808,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="7" t="str">
         <x:v>Auth</x:v>
       </x:c>
@@ -1793,7 +1822,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>Passenger profile</x:v>
       </x:c>
@@ -1807,7 +1836,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Driver onboarding</x:v>
       </x:c>
@@ -1821,7 +1850,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Admin users</x:v>
       </x:c>
@@ -1835,7 +1864,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Fare estimate</x:v>
       </x:c>
@@ -1849,7 +1878,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Payment methods</x:v>
       </x:c>
@@ -1863,7 +1892,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>Payment checkout/callback</x:v>
       </x:c>
@@ -1873,11 +1902,11 @@
       <x:c r="C8" s="7" t="str">
         <x:v>Open VNPAY or MoMo checkoutUrl only when enabled, then refresh payment detail after redirect. Signed callbacks enforce timestamp freshness; MoMo IPN remains backend-only and returns HTTP 204.</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="str">
+      <x:c r="D8" s="11" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>Rating</x:v>
       </x:c>
@@ -1891,7 +1920,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Notifications</x:v>
       </x:c>
@@ -1905,7 +1934,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>Admin trips/dashboard</x:v>
       </x:c>
@@ -1919,24 +1948,24 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="54" customHeight="1">
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A12" s="81" t="str">
-        <x:v>Driver availability</x:v>
+        <x:v>Driver navigation</x:v>
       </x:c>
       <x:c r="B12" s="81" t="str">
-        <x:v>PATCH /api/v1/drivers/me/status, POST /api/v1/drivers/me/heartbeat</x:v>
+        <x:v>POST /api/v1/drivers/trips/{tripId}/route</x:v>
       </x:c>
       <x:c r="C12" s="81" t="str">
-        <x:v>After going online, send current coordinates every 20 seconds before expiresAt; on DRIVER_NOT_AVAILABLE stop heartbeat and require online action again.</x:v>
-      </x:c>
-      <x:c r="D12" s="91" t="str">
+        <x:v>Send current GPS; draw GeoJSON LineString to pickup while ACCEPTED and dropoff after ARRIVED; debounce re-route and handle provider fallback to external maps.</x:v>
+      </x:c>
+      <x:c r="D12" s="98" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R529540f2bd1144a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78219074b9514d6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1998,10 +2027,10 @@
         <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Real routing is implemented, but endpoint capacity, timeout, and fallback frequency are not validated in UAT.</x:v>
+        <x:v>Fare estimates and driver navigation geometry are implemented, but endpoint capacity, request rate, latency, and Vietnamese road quality are not validated.</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Use a controlled OSRM-compatible endpoint, monitor fallback warnings, and tune profile/timeout before launch.</x:v>
+        <x:v>Use a controlled OSRM-compatible endpoint, debounce/re-route on FE, add rate/latency metrics, and tune profile/timeout before launch.</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2052,7 +2081,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4874d70655dd4dd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9b5d1ccbc2347d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb54e2fcf05f342a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rb137c826fe434f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R854ff96a3adb4f4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R63e2fcb677524c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0b85f967489846c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R2140e55323d744e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e8845e835d040ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Reefbbcf261624a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R44134915cee8493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R8d370c4d8d3b44f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb13f6da7960d40f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R92c8a5af51434031"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -556,8 +556,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E20" headerRowCount="1">
-  <x:autoFilter ref="A1:E20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E22" headerRowCount="1">
+  <x:autoFilter ref="A1:E22"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -803,7 +803,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after driver trip routing implementation.</x:v>
+        <x:v>Asia/Bangkok status after booking/matching/routing integration coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -811,13 +811,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/driver-trip-routing</x:v>
+        <x:v>feature/booking-matching-routing-integration</x:v>
       </x:c>
       <x:c r="C3" s="34" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Connects accepted trips to pickup/dropoff GeoJSON navigation for the assigned driver.</x:v>
+        <x:v>Adds a full backend integration flow from passenger booking through driver pickup/dropoff routing.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -825,13 +825,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge auth integration tests</x:v>
+        <x:v>develop after merge driver trip routing</x:v>
       </x:c>
       <x:c r="C4" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/auth-integration-tests is merged into develop at 08ec166.</x:v>
+        <x:v>feature/driver-trip-routing is merged into develop at fe3b5a0.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -839,7 +839,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add driver trip routing</x:v>
+        <x:v>test: cover booking matching routing flow</x:v>
       </x:c>
       <x:c r="C5" s="59" t="str">
         <x:v>Done</x:v>
@@ -853,13 +853,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 321 tests</x:v>
+        <x:v>./mvnw.cmd test: pass 322 tests</x:v>
       </x:c>
       <x:c r="C6" s="33" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted routing suite passed 15 tests; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
+        <x:v>Targeted integration flow passed 1 test; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -907,7 +907,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec28f73966c4bbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21b0e6fb533a4bd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1280,10 +1280,27 @@
         <x:v>Refreshes GEO/meta/status TTL without overwriting BUSY; scheduled batch marks stale database profiles offline.</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="29" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B22" s="29" t="str">
+        <x:v>Booking, matching and driver routing integration flow</x:v>
+      </x:c>
+      <x:c r="C22" s="29" t="str">
+        <x:v>BookingMatchingRoutingIntegrationTests</x:v>
+      </x:c>
+      <x:c r="D22" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E22" s="29" t="str">
+        <x:v>Runs booking creation, Redis offer matching, driver acceptance, pickup route, arrival transition, and dropoff route through HTTP/JWT/PostGIS/Redis with a local OSRM boundary.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0a1f793a7994f94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a19cfea7f0f4822"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1468,7 +1485,7 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Auth integration is covered; add booking, matching, trip lifecycle, tracking, payment, notification, and admin integration flows.</x:v>
+        <x:v>Auth and booking/matching/pickup-dropoff routing are covered; add trip completion, tracking, payment, notification, and admin integration flows.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>Existing Testcontainers PostGIS/Redis base and Docker-enabled CI.</x:v>
@@ -1663,7 +1680,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdba446d6b5c942d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad75a1f8589541aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1756,7 +1773,7 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation and auth HTTP flow implemented; booking/matching/tracking/payment/admin flows and CI validation remain.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth flow, and booking-to-matching-to-pickup/dropoff-routing flow implemented; trip completion, tracking, payment, notification, admin, and CI validation remain.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
         <x:v>All critical passenger/driver/admin happy paths pass in CI.</x:v>
@@ -1779,7 +1796,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf8a4117e94d4c30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2178eb9cd64bac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1965,7 +1982,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78219074b9514d6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d1082e4b6f4576"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2069,7 +2086,7 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth runs through HTTP/JWT/JPA/Redis, but cross-module booking, matching, tracking and payment regressions may still slip through.</x:v>
+        <x:v>Auth and booking/matching/driver-routing run through HTTP/JWT/JPA/Redis, but trip completion, tracking, payment, notification, and admin regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
         <x:v>Reuse the Testcontainers base for remaining critical flows and run the suite in CI before release candidate.</x:v>
@@ -2081,7 +2098,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9b5d1ccbc2347d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3b4d5e076849d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e8845e835d040ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Reefbbcf261624a34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R44134915cee8493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R8d370c4d8d3b44f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb13f6da7960d40f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R92c8a5af51434031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb178b21690d44858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rbea20fe0be874dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R278317da9d7a4113"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R290b3dad0e6a45d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6a3ebd042be0467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R1bcec3ea7b6f478a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -259,7 +259,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="99">
+  <x:cellXfs count="100">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -533,6 +533,9 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -556,8 +559,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E22" headerRowCount="1">
-  <x:autoFilter ref="A1:E22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E23" headerRowCount="1">
+  <x:autoFilter ref="A1:E23"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -598,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D12" headerRowCount="1">
-  <x:autoFilter ref="A1:D12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D13" headerRowCount="1">
+  <x:autoFilter ref="A1:D13"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -611,8 +614,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D7" headerRowCount="1">
-  <x:autoFilter ref="A1:D7"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D8" headerRowCount="1">
+  <x:autoFilter ref="A1:D8"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -797,13 +800,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-14</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="str">
+        <x:v>2026-06-15</x:v>
+      </x:c>
+      <x:c r="C2" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after booking/matching/routing integration coverage.</x:v>
+        <x:v>Asia/Bangkok status after request tracing logging implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -811,13 +814,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/booking-matching-routing-integration</x:v>
-      </x:c>
-      <x:c r="C3" s="34" t="str">
+        <x:v>feature/request-tracing-logging</x:v>
+      </x:c>
+      <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds a full backend integration flow from passenger booking through driver pickup/dropoff routing.</x:v>
+        <x:v>Adds safe HTTP correlation IDs, centralized exception logging, and FE-visible request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -825,13 +828,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge driver trip routing</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="str">
+        <x:v>develop after merge booking matching routing integration</x:v>
+      </x:c>
+      <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/driver-trip-routing is merged into develop at fe3b5a0.</x:v>
+        <x:v>feature/booking-matching-routing-integration is merged into develop at 1fbe893.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -839,27 +842,27 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: cover booking matching routing flow</x:v>
-      </x:c>
-      <x:c r="C5" s="59" t="str">
+        <x:v>feat: add request tracing logs</x:v>
+      </x:c>
+      <x:c r="C5" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
         <x:v>Prepared on feature branch for user review before merge.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>./mvnw.cmd test: pass 322 tests</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>Done</x:v>
+        <x:v>Related auth/logging/WebSocket/driver/matching/tracking tests: pass 57</x:v>
+      </x:c>
+      <x:c r="C6" s="26" t="str">
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Targeted integration flow passed 1 test; full suite passed with 0 failures and 0 errors on 2026-06-14.</x:v>
+        <x:v>Full suite previously passed 325 tests; Docker-backed full integration rerun is pending.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -869,11 +872,11 @@
       <x:c r="B7" s="7" t="str">
         <x:v>git diff --check: pass</x:v>
       </x:c>
-      <x:c r="C7" s="75" t="str">
+      <x:c r="C7" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-14.</x:v>
+        <x:v>No whitespace errors on 2026-06-15.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -883,7 +886,7 @@
       <x:c r="B8" s="7" t="str">
         <x:v>CodeRabbit CLI blocked by install policy</x:v>
       </x:c>
-      <x:c r="C8" s="76" t="str">
+      <x:c r="C8" s="99" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
@@ -904,10 +907,24 @@
         <x:v>Keep environment-specific local changes uncommitted.</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="42" customHeight="1">
+      <x:c r="A10" s="29" t="str">
+        <x:v>Booking flow hotfix</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>SockJS compatibility and initial no-driver transition</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>/ws supports SockJS; /ws-native preserves native STOMP; initial no-candidate booking remains SEARCHING; driver online/heartbeat retries matching; driver approach location is broadcast from ACCEPTED.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21b0e6fb533a4bd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc8ead2c793140f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1297,10 +1314,78 @@
         <x:v>Runs booking creation, Redis offer matching, driver acceptance, pickup route, arrival transition, and dropoff route through HTTP/JWT/PostGIS/Redis with a local OSRM boundary.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="48" customHeight="1">
+      <x:c r="A23" s="29" t="str">
+        <x:v>Observability</x:v>
+      </x:c>
+      <x:c r="B23" s="29" t="str">
+        <x:v>HTTP request correlation and centralized error logging</x:v>
+      </x:c>
+      <x:c r="C23" s="29" t="str">
+        <x:v>X-Request-Id on all REST endpoints</x:v>
+      </x:c>
+      <x:c r="D23" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E23" s="29" t="str">
+        <x:v>Returns request ID in header/error body; logs method, path, status, duration, error code, and 5xx stack traces without bodies or secrets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" customHeight="1">
+      <x:c r="A24" s="29" t="str">
+        <x:v>WebSocket</x:v>
+      </x:c>
+      <x:c r="B24" s="29" t="str">
+        <x:v>SockJS and native STOMP endpoint compatibility</x:v>
+      </x:c>
+      <x:c r="C24" s="29" t="str">
+        <x:v>/ws (SockJS), /ws-native (native)</x:v>
+      </x:c>
+      <x:c r="D24" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E24" s="29" t="str">
+        <x:v>GET /ws/info is served by SockJS while native clients retain a dedicated endpoint.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="29" t="str">
+        <x:v>Matching</x:v>
+      </x:c>
+      <x:c r="B25" s="29" t="str">
+        <x:v>Rematch searching trips when drivers become available</x:v>
+      </x:c>
+      <x:c r="C25" s="29" t="str">
+        <x:v>DriverAvailableEvent, SearchingTripMatchingService</x:v>
+      </x:c>
+      <x:c r="D25" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E25" s="29" t="str">
+        <x:v>Initial no-candidate booking remains SEARCHING; driver online/heartbeat retries unmatched searching trips and dispatches offer when a candidate is available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="54" customHeight="1">
+      <x:c r="A26" s="29" t="str">
+        <x:v>Tracking</x:v>
+      </x:c>
+      <x:c r="B26" s="29" t="str">
+        <x:v>Driver approach location before trip start</x:v>
+      </x:c>
+      <x:c r="C26" s="29" t="str">
+        <x:v>/app/driver.location, /topic/trip/{tripId}/location, REST fallback</x:v>
+      </x:c>
+      <x:c r="D26" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E26" s="29" t="str">
+        <x:v>ACCEPTED/ARRIVED locations are cached and broadcast for passenger approach view; only IN_PROGRESS locations are persisted to history for fare distance.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a19cfea7f0f4822"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54cf372465004fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1505,16 +1590,16 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Add CORS/rate limits/observability/health readiness review.</x:v>
+        <x:v>Request correlation and centralized error logging are done; add log shipping, metrics/tracing backend, CORS/rate limits, and health/readiness review.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Deployment platform policy.</x:v>
+        <x:v>Deployment platform and centralized observability service.</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>Production defaults are explicit, observable, and safe.</x:v>
+        <x:v>Logs are searchable across instances and production defaults are explicit, observable, and safe.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -1680,7 +1765,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad75a1f8589541aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fe82c5745784003"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1759,10 +1844,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase ADC/secret loading and fail-fast validation implemented; env profiles, CORS/rate limits, observability and DB release strategy remain.</x:v>
+        <x:v>Firebase secure credential loading plus HTTP request correlation and centralized application error logging implemented; log aggregation, metrics/tracing, env profiles, CORS/rate limits, health/readiness, and DB release strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging deployment can load Firebase identity securely and expose safe production-like config.</x:v>
+        <x:v>Staging loads secrets safely and operators can trace failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1796,7 +1881,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a2178eb9cd64bac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6d1aef4d734116"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1979,10 +2064,52 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="29" t="str">
+        <x:v>Error/support flow</x:v>
+      </x:c>
+      <x:c r="B13" s="29" t="str">
+        <x:v>All REST endpoints; X-Request-Id response header and error body</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="str">
+        <x:v>Generate a safe request ID per call; retain requestId, endpoint, time, and error.code when reporting failures.</x:v>
+      </x:c>
+      <x:c r="D13" s="29" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="29" t="str">
+        <x:v>Realtime connection</x:v>
+      </x:c>
+      <x:c r="B14" s="29" t="str">
+        <x:v>/ws (SockJS) or /ws-native (native STOMP)</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="str">
+        <x:v>Use SockJS(http://host/ws) or brokerURL ws://host/ws-native; send JWT in STOMP CONNECT headers.</x:v>
+      </x:c>
+      <x:c r="D14" s="29" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="29" t="str">
+        <x:v>Passenger matching/tracking</x:v>
+      </x:c>
+      <x:c r="B15" s="29" t="str">
+        <x:v>Trip status topic and GET /api/v1/tracking/trips/{tripId}/driver-location</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="str">
+        <x:v>Handle SEARCHING as waiting-for-driver; once assigned, subscribe/poll location during ACCEPTED, ARRIVED, and IN_PROGRESS. Driver approach location is realtime before trip start.</x:v>
+      </x:c>
+      <x:c r="D15" s="29" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9d1082e4b6f4576"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13cb91387ec64110"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2095,10 +2222,24 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="29" t="str">
+        <x:v>Logs are local to each application instance.</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>Request IDs make failures searchable, but logs can be lost or fragmented across replicas.</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>Ship stdout logs centrally and configure retention, search, and alert rules before scaling production.</x:v>
+      </x:c>
+      <x:c r="D8" s="29" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree3b4d5e076849d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04db9770200f4644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb178b21690d44858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rbea20fe0be874dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R278317da9d7a4113"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R290b3dad0e6a45d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6a3ebd042be0467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R1bcec3ea7b6f478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc606ab51791a4560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R79bd1997dd3a429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R67f75508512e43cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1be34619412b405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rfae4fb413eab4c88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R39489430ea4e4254"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -921,10 +921,24 @@
         <x:v>/ws supports SockJS; /ws-native preserves native STOMP; initial no-candidate booking remains SEARCHING; driver online/heartbeat retries matching; driver approach location is broadcast from ACCEPTED.</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Payment readiness diagnostics</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>GET /api/v1/payments/providers/readiness</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Admin/devops can verify MoMo/VNPAY registered/enabled/configured state before sandbox UAT; payment suite passes 65 tests.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc8ead2c793140f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f20a25bd57e48c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1382,10 +1396,27 @@
         <x:v>ACCEPTED/ARRIVED locations are cached and broadcast for passenger approach view; only IN_PROGRESS locations are persisted to history for fare distance.</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Payment provider sandbox readiness diagnostics</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>/api/v1/payments/providers/readiness</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Reports providerRegistered, checkoutReady, webhookReady, sandboxReady and missingRequirements without exposing secrets.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54cf372465004fba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428f72410ee04bdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1430,13 +1461,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Run MoMo/VNPAY sandbox E2E against real merchant callback flows.</x:v>
+        <x:v>Run MoMo/VNPAY sandbox E2E against real merchant callback flows after readiness endpoint reports sandboxReady=true.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Sandbox merchant accounts, callback URLs, provider test apps.</x:v>
+        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Real sandbox success/failure callbacks reconcile internal payment/trip state for both providers.</x:v>
+        <x:v>Both online providers report sandboxReady=true, return usable checkout URLs, and real sandbox success/failure callbacks reconcile internal payment/trip state.</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>Partial</x:v>
@@ -1765,7 +1796,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fe82c5745784003"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cdb77003be42c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1802,10 +1833,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>MoMo/VNPAY sandbox E2E validation, provider-specific freshness-window tuning, and real merchant callback tests.</x:v>
+        <x:v>Readiness diagnostics implemented; next run MoMo/VNPAY sandbox E2E validation, provider-specific freshness-window tuning, and real merchant callback tests.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Online sandbox payment can be completed and reconciled for both providers.</x:v>
+        <x:v>Both providers report sandboxReady=true and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1881,7 +1912,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad6d1aef4d734116"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ad8a28effd4756"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2106,10 +2137,24 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Admin payment readiness</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>/api/v1/payments/providers/readiness</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Show MoMo/VNPAY readiness before UAT; expose missingRequirements to admins/devops, never to passenger checkout UI.</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Ready for admin FE</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13cb91387ec64110"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fdbbff37560466b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2146,7 +2191,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP; enable online methods first in sandbox and only after full callback/UAT validation.</x:v>
+        <x:v>Use /api/v1/payments/providers/readiness to confirm sandboxReady=true, keep CASH as MVP, then enable online methods only after checkout and callback UAT succeeds.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2239,7 +2284,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04db9770200f4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc71a0c80bc65424a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc606ab51791a4560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R79bd1997dd3a429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R67f75508512e43cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1be34619412b405f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rfae4fb413eab4c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R39489430ea4e4254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0ec63208b22c4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R4d06fea12b534da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R679d7a380c5b456f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R772f468dc8f34475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0e8b4acb5ba04f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rfffc1861dc7a4cb2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,8 +546,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D9" headerRowCount="1">
-  <x:autoFilter ref="A1:D9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D10" headerRowCount="1">
+  <x:autoFilter ref="A1:D10"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -559,8 +559,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E23" headerRowCount="1">
-  <x:autoFilter ref="A1:E23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E24" headerRowCount="1">
+  <x:autoFilter ref="A1:E24"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D13" headerRowCount="1">
-  <x:autoFilter ref="A1:D13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D14" headerRowCount="1">
+  <x:autoFilter ref="A1:D14"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -800,13 +800,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after request tracing logging implementation.</x:v>
+        <x:v>Asia/Bangkok status after payment sandbox webhook contract coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -814,13 +814,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/request-tracing-logging</x:v>
+        <x:v>feature/payment-sandbox-callback-uat-support</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds safe HTTP correlation IDs, centralized exception logging, and FE-visible request IDs.</x:v>
+        <x:v>Adds service-level signed MoMo/VNPAY callback coverage and injectable webhook clock for sandbox UAT support.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -828,13 +828,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge booking matching routing integration</x:v>
+        <x:v>develop after merge payment provider readiness diagnostics</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/booking-matching-routing-integration is merged into develop at 1fbe893.</x:v>
+        <x:v>feature/payment-provider-sandbox-e2e is merged into develop at efaa8c8.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -842,10 +842,10 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add request tracing logs</x:v>
+        <x:v>test: add payment sandbox webhook contract coverage</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
         <x:v>Prepared on feature branch for user review before merge.</x:v>
@@ -856,13 +856,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Related auth/logging/WebSocket/driver/matching/tracking tests: pass 57</x:v>
+        <x:v>Full mvnw.cmd test: pass 337; targeted suite: pass 41</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full suite previously passed 325 tests; Docker-backed full integration rerun is pending.</x:v>
+        <x:v>Full suite includes Testcontainers PostGIS/Redis integration tests on 2026-06-23.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -876,7 +876,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-15.</x:v>
+        <x:v>No whitespace errors on 2026-06-23; LF/CRLF warnings only.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -884,13 +884,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>CodeRabbit CLI blocked by install policy</x:v>
+        <x:v>CodeRabbit CLI blocked on Windows installer</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>CLI is missing and the environment security policy disallows executing the official downloaded installer script.</x:v>
+        <x:v>CLI missing; official installer via Git Bash reports unsupported OS mingw64_nt-10.0-26200.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -909,16 +909,16 @@
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="29" t="str">
-        <x:v>Booking flow hotfix</x:v>
+        <x:v>Payment sandbox webhook contracts</x:v>
       </x:c>
       <x:c r="B10" s="29" t="str">
-        <x:v>SockJS compatibility and initial no-driver transition</x:v>
+        <x:v>Service-level signed MoMo/VNPAY callback coverage</x:v>
       </x:c>
       <x:c r="C10" s="29" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D10" s="29" t="str">
-        <x:v>/ws supports SockJS; /ws-native preserves native STOMP; initial no-candidate booking remains SEARCHING; driver online/heartbeat retries matching; driver approach location is broadcast from ACCEPTED.</x:v>
+        <x:v>PaymentWebhookService now uses an injectable clock; targeted webhook/provider suite passes 41 tests. Real merchant sandbox callback UAT remains open.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -938,7 +938,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f20a25bd57e48c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R255fe247adb64dad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1347,19 +1347,19 @@
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
       <x:c r="A24" s="29" t="str">
-        <x:v>WebSocket</x:v>
+        <x:v>Payment</x:v>
       </x:c>
       <x:c r="B24" s="29" t="str">
-        <x:v>SockJS and native STOMP endpoint compatibility</x:v>
+        <x:v>Payment sandbox webhook contract coverage</x:v>
       </x:c>
       <x:c r="C24" s="29" t="str">
-        <x:v>/ws (SockJS), /ws-native (native)</x:v>
+        <x:v>PaymentWebhookService + MoMo/VNPAY provider webhooks</x:v>
       </x:c>
       <x:c r="D24" s="29" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E24" s="29" t="str">
-        <x:v>GET /ws/info is served by SockJS while native clients retain a dedicated endpoint.</x:v>
+        <x:v>Covers signed MoMo success, signed VNPAY failure, and stale callback rejection through the service dispatch layer.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -1416,7 +1416,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R428f72410ee04bdd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ba63553999c429a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1461,13 +1461,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Run MoMo/VNPAY sandbox E2E against real merchant callback flows after readiness endpoint reports sandboxReady=true.</x:v>
+        <x:v>Finish real MoMo/VNPAY sandbox merchant UAT; backend readiness and service-level signed callback contract coverage are in place.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Both online providers report sandboxReady=true, return usable checkout URLs, and real sandbox success/failure callbacks reconcile internal payment/trip state.</x:v>
+        <x:v>Both providers return usable checkout URLs and real sandbox success/failure callbacks reconcile internal payment/trip state. Current backend contract tests do not replace provider-hosted callback UAT.</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>Partial</x:v>
@@ -1521,13 +1521,13 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Run MoMo/VNPAY sandbox account callback tests; unit signature and state mapping are implemented.</x:v>
+        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs; service-level success/failure/stale callback coverage is implemented.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
         <x:v>Sandbox callback examples and merchant test accounts.</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Real gateway acknowledgements and success/failure states match provider expectations.</x:v>
+        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; signed sandbox payloads map to internal payment states.</x:v>
       </x:c>
       <x:c r="F5" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1796,7 +1796,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8cdb77003be42c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eaa3e2fb062406f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1833,7 +1833,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Readiness diagnostics implemented; next run MoMo/VNPAY sandbox E2E validation, provider-specific freshness-window tuning, and real merchant callback tests.</x:v>
+        <x:v>Readiness diagnostics and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT and tune freshness windows if needed.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
         <x:v>Both providers report sandboxReady=true and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
@@ -1912,7 +1912,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66ad8a28effd4756"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R471771500ab04c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2111,16 +2111,16 @@
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="29" t="str">
-        <x:v>Realtime connection</x:v>
+        <x:v>Payment sandbox UAT handoff</x:v>
       </x:c>
       <x:c r="B14" s="29" t="str">
-        <x:v>/ws (SockJS) or /ws-native (native STOMP)</x:v>
+        <x:v>GET /api/v1/payments/providers/readiness plus provider webhook callbacks</x:v>
       </x:c>
       <x:c r="C14" s="29" t="str">
-        <x:v>Use SockJS(http://host/ws) or brokerURL ws://host/ws-native; send JWT in STOMP CONNECT headers.</x:v>
+        <x:v>Before exposing MoMo/VNPAY to testers, confirm sandboxReady=true, create checkout, complete/cancel in provider sandbox, then refresh payment detail after redirect/callback.</x:v>
       </x:c>
       <x:c r="D14" s="29" t="str">
-        <x:v>Ready for FE</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -2154,7 +2154,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fdbbff37560466b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0f6278e7d14571"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2191,7 +2191,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Use /api/v1/payments/providers/readiness to confirm sandboxReady=true, keep CASH as MVP, then enable online methods only after checkout and callback UAT succeeds.</x:v>
+        <x:v>Keep CASH as MVP. Use readiness endpoint and service-level signed callback tests before UAT, then enable MoMo/VNPAY only after real sandbox callback validation.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2205,7 +2205,7 @@
         <x:v>The configurable 24-hour age and 5-minute future-skew defaults have not been validated against real merchant retries.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Run sandbox/UAT callbacks and tune each provider window without weakening signature or transaction-reference checks.</x:v>
+        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox before tuning provider-specific freshness windows.</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2284,7 +2284,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc71a0c80bc65424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R074de670bfc74e38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R0ec63208b22c4381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R4d06fea12b534da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R679d7a380c5b456f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R772f468dc8f34475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0e8b4acb5ba04f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rfffc1861dc7a4cb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R81fc3726428e4dfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc58f2596643049f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R72359b078dee4361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rbfee929caec9448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R42a328107e8e49b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd8633e9db23b4524"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,8 +546,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D10" headerRowCount="1">
-  <x:autoFilter ref="A1:D10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D11" headerRowCount="1">
+  <x:autoFilter ref="A1:D11"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -559,8 +559,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E24" headerRowCount="1">
-  <x:autoFilter ref="A1:E24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E25" headerRowCount="1">
+  <x:autoFilter ref="A1:E25"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -601,8 +601,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D14" headerRowCount="1">
-  <x:autoFilter ref="A1:D14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D15" headerRowCount="1">
+  <x:autoFilter ref="A1:D15"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -800,13 +800,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after payment sandbox webhook contract coverage.</x:v>
+        <x:v>Asia/Bangkok status after trip completion, tracking fallback and cash payment integration coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -814,13 +814,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/payment-sandbox-callback-uat-support</x:v>
+        <x:v>feature/trip-completion-payment-integration</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds service-level signed MoMo/VNPAY callback coverage and injectable webhook clock for sandbox UAT support.</x:v>
+        <x:v>Adds Testcontainers coverage for booking -&gt; matching -&gt; trip completion -&gt; tracking fallback -&gt; CASH payment confirmation.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -828,13 +828,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge payment provider readiness diagnostics</x:v>
+        <x:v>develop after merge payment sandbox webhook contract coverage</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/payment-provider-sandbox-e2e is merged into develop at efaa8c8.</x:v>
+        <x:v>feature/payment-sandbox-callback-uat-support is merged into develop at e541e80.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -842,7 +842,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: add payment sandbox webhook contract coverage</x:v>
+        <x:v>test: cover trip completion payment integration</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -851,21 +851,21 @@
         <x:v>Prepared on feature branch for user review before merge.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="42" customHeight="1">
+    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Full mvnw.cmd test: pass 337; targeted suite: pass 41</x:v>
+        <x:v>Full mvnw.cmd test: pass 338; targeted BookingMatchingRoutingIntegrationTests: pass 2</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full suite includes Testcontainers PostGIS/Redis integration tests on 2026-06-23.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Full suite and targeted Testcontainers PostGIS/Redis integration flow passed on 2026-06-24.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Diff hygiene</x:v>
       </x:c>
@@ -876,7 +876,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-23; LF/CRLF warnings only.</x:v>
+        <x:v>No whitespace errors on 2026-06-24; LF/CRLF warnings only.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -907,7 +907,7 @@
         <x:v>Keep environment-specific local changes uncommitted.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="42" customHeight="1">
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
         <x:v>Payment sandbox webhook contracts</x:v>
       </x:c>
@@ -915,30 +915,44 @@
         <x:v>Service-level signed MoMo/VNPAY callback coverage</x:v>
       </x:c>
       <x:c r="C10" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>Merged into develop at e541e80. Real merchant sandbox callback UAT remains open.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A11" s="29" t="str">
+        <x:v>Payment readiness diagnostics</x:v>
+      </x:c>
+      <x:c r="B11" s="29" t="str">
+        <x:v>GET /api/v1/payments/providers/readiness</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="str">
+        <x:v>Merged into develop before the current integration coverage feature.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A12" s="29" t="str">
+        <x:v>Trip completion/payment integration</x:v>
+      </x:c>
+      <x:c r="B12" s="29" t="str">
+        <x:v>BookingMatchingRoutingIntegrationTests end-to-end coverage</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="str">
         <x:v>In review</x:v>
       </x:c>
-      <x:c r="D10" s="29" t="str">
-        <x:v>PaymentWebhookService now uses an injectable clock; targeted webhook/provider suite passes 41 tests. Real merchant sandbox callback UAT remains open.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str">
-        <x:v>Payment readiness diagnostics</x:v>
-      </x:c>
-      <x:c r="B11" t="str">
-        <x:v>GET /api/v1/payments/providers/readiness</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>In review</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>Admin/devops can verify MoMo/VNPAY registered/enabled/configured state before sandbox UAT; payment suite passes 65 tests.</x:v>
+      <x:c r="D12" s="29" t="str">
+        <x:v>Covers final fare, latest location REST fallback, payment detail, CASH checkout, payment-confirm and post-payment driver heartbeat.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R255fe247adb64dad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R627e8da021bb4466"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1345,7 +1359,7 @@
         <x:v>Returns request ID in header/error body; logs method, path, status, duration, error code, and 5xx stack traces without bodies or secrets.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="36" customHeight="1">
+    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A24" s="29" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1356,13 +1370,13 @@
         <x:v>PaymentWebhookService + MoMo/VNPAY provider webhooks</x:v>
       </x:c>
       <x:c r="D24" s="29" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E24" s="29" t="str">
         <x:v>Covers signed MoMo success, signed VNPAY failure, and stale callback rejection through the service dispatch layer.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="54" customHeight="1">
+    <x:row r="25" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A25" s="29" t="str">
         <x:v>Matching</x:v>
       </x:c>
@@ -1379,7 +1393,7 @@
         <x:v>Initial no-candidate booking remains SEARCHING; driver online/heartbeat retries unmatched searching trips and dispatches offer when a candidate is available.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="54" customHeight="1">
+    <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" s="29" t="str">
         <x:v>Tracking</x:v>
       </x:c>
@@ -1396,27 +1410,44 @@
         <x:v>ACCEPTED/ARRIVED locations are cached and broadcast for passenger approach view; only IN_PROGRESS locations are persisted to history for fare distance.</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
+    <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A27" s="29" t="str">
         <x:v>Payment</x:v>
       </x:c>
-      <x:c r="B27" t="str">
+      <x:c r="B27" s="29" t="str">
         <x:v>Payment provider sandbox readiness diagnostics</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C27" s="29" t="str">
         <x:v>/api/v1/payments/providers/readiness</x:v>
       </x:c>
-      <x:c r="D27" t="str">
+      <x:c r="D27" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E27" s="29" t="str">
+        <x:v>Reports providerRegistered, checkoutReady, webhookReady, sandboxReady and missingRequirements without exposing secrets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A28" s="29" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B28" s="29" t="str">
+        <x:v>Trip completion, tracking fallback and cash payment integration flow</x:v>
+      </x:c>
+      <x:c r="C28" s="29" t="str">
+        <x:v>BookingMatchingRoutingIntegrationTests</x:v>
+      </x:c>
+      <x:c r="D28" s="29" t="str">
         <x:v>In review</x:v>
       </x:c>
-      <x:c r="E27" t="str">
-        <x:v>Reports providerRegistered, checkoutReady, webhookReady, sandboxReady and missingRequirements without exposing secrets.</x:v>
+      <x:c r="E28" s="29" t="str">
+        <x:v>Runs booking, matching, driver accept/arrived/start/complete, tracking REST fallback, final fare, payment detail/checkout, cash confirmation and driver heartbeat through Testcontainers.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ba63553999c429a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R366cfe1aefac4290"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1601,13 +1632,13 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Auth and booking/matching/pickup-dropoff routing are covered; add trip completion, tracking, payment, notification, and admin integration flows.</x:v>
+        <x:v>Auth, booking/matching/pickup-dropoff routing, trip completion, tracking fallback and cash payment confirmation are covered; add notification, admin and provider sandbox E2E flows.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Existing Testcontainers PostGIS/Redis base and Docker-enabled CI.</x:v>
+        <x:v>Existing Testcontainers PostGIS/Redis base, sandbox merchant accounts and Docker-enabled CI.</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>Remaining critical passenger/driver/admin flows run in CI against database/Redis-compatible services.</x:v>
+        <x:v>Remaining notification/admin/provider sandbox happy paths run in CI against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1796,7 +1827,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3eaa3e2fb062406f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54fcd4a3d8940aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1889,10 +1920,10 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth flow, and booking-to-matching-to-pickup/dropoff-routing flow implemented; trip completion, tracking, payment, notification, admin, and CI validation remain.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth flow, booking-to-matching-to-pickup/dropoff-routing flow, trip completion, tracking fallback and cash payment confirmation are implemented; notification, admin, provider sandbox E2E and CI validation remain.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>All critical passenger/driver/admin happy paths pass in CI.</x:v>
+        <x:v>All critical passenger/driver/admin happy paths pass in CI, including provider sandbox callback UAT before online payment launch.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1912,7 +1943,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R471771500ab04c36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7c6935f8ffb41de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2033,7 +2064,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>Open VNPAY or MoMo checkoutUrl only when enabled, then refresh payment detail after redirect. Signed callbacks enforce timestamp freshness; MoMo IPN remains backend-only and returns HTTP 204.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Open VNPAY/MoMo checkoutUrl only when enabled, then refresh payment detail after redirect/callback.</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>Partial</x:v>
@@ -2109,7 +2140,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="42" customHeight="1">
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" s="29" t="str">
         <x:v>Payment sandbox UAT handoff</x:v>
       </x:c>
@@ -2123,7 +2154,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="54" customHeight="1">
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" s="29" t="str">
         <x:v>Passenger matching/tracking</x:v>
       </x:c>
@@ -2137,24 +2168,44 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str">
+    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A16" s="29" t="str">
+        <x:v>Trip completion and cash payment</x:v>
+      </x:c>
+      <x:c r="B16" s="29" t="str">
+        <x:v>/api/v1/bookings/{tripId}, /api/v1/payments/trips/{tripId}, /checkout, PATCH /api/v1/drivers/trips/{tripId}/payment-confirm</x:v>
+      </x:c>
+      <x:c r="C16" s="29" t="str">
+        <x:v>After driver completes trip, refresh trip detail for finalFare/completedAt, load payment detail, show CASH confirmation to driver, then refresh payment status and allow driver heartbeat/available screen.</x:v>
+      </x:c>
+      <x:c r="D16" s="29" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A17" s="29" t="str">
         <x:v>Admin payment readiness</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B17" s="29" t="str">
         <x:v>/api/v1/payments/providers/readiness</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C17" s="29" t="str">
         <x:v>Show MoMo/VNPAY readiness before UAT; expose missingRequirements to admins/devops, never to passenger checkout UI.</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D17" s="29" t="str">
         <x:v>Ready for admin FE</x:v>
       </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0f6278e7d14571"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e8bed9904bf4a34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2253,12 +2304,12 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth and booking/matching/driver-routing run through HTTP/JWT/JPA/Redis, but trip completion, tracking, payment, notification, and admin regressions may still slip through.</x:v>
+        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback and cash payment confirmation run through HTTP/JWT/JPA/Redis, but notification, admin and real provider sandbox regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
         <x:v>Reuse the Testcontainers base for remaining critical flows and run the suite in CI before release candidate.</x:v>
@@ -2284,7 +2335,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R074de670bfc74e38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b6255b230f64476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R81fc3726428e4dfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc58f2596643049f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R72359b078dee4361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rbfee929caec9448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R42a328107e8e49b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd8633e9db23b4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R013b411e4ed6411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R92065a9921b4434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R38e0f5aeae434d24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5dd4aacccdc94c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R225002c572d84a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R3357b4d1ccc146d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -800,13 +800,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after trip completion, tracking fallback and cash payment integration coverage.</x:v>
+        <x:v>Asia/Bangkok status after driver-offer cancellation dismiss fix.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -820,7 +820,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds Testcontainers coverage for booking -&gt; matching -&gt; trip completion -&gt; tracking fallback -&gt; CASH payment confirmation.</x:v>
+        <x:v>Adds targeted fix for passenger cancellation while driver offer popup is active.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -842,7 +842,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: cover trip completion payment integration</x:v>
+        <x:v>fix: dismiss driver offer on passenger cancellation</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -856,13 +856,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Full mvnw.cmd test: pass 338; targeted BookingMatchingRoutingIntegrationTests: pass 2</x:v>
+        <x:v>Targeted BookingServiceTests, BookingCancelledMatchingListenerTests, WebSocketDriverOfferNotifierTests: pass 15</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full suite and targeted Testcontainers PostGIS/Redis integration flow passed on 2026-06-24.</x:v>
+        <x:v>Booking cancel now publishes an event; matching listener clears Redis offer state and sends driver dismiss payload.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -949,10 +949,24 @@
         <x:v>Covers final fare, latest location REST fallback, payment detail, CASH checkout, payment-confirm and post-payment driver heartbeat.</x:v>
       </x:c>
     </x:row>
+    <x:row r="13" ht="28.5" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Driver offer cancel dismiss</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>BookingCancelledEvent + DISMISS payload</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>Cancel clears Redis offer lock and closes driver modal.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R627e8da021bb4466"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45fef0a3eb464b70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1101,7 +1115,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>Uses Redis GEO/availability data.</x:v>
+        <x:v>Uses Redis GEO/availability data; passenger cancellation clears active matching state/driver lock and sends TRIP_CANCELLED/DISMISS to the offered driver.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -1444,10 +1458,27 @@
         <x:v>Runs booking, matching, driver accept/arrived/start/complete, tracking REST fallback, final fare, payment detail/checkout, cash confirmation and driver heartbeat through Testcontainers.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="31.5" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>Matching</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>Cancel dismisses active driver offer</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>/api/v1/bookings/{tripId}/cancel; /user/queue/trip-requests</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>Event clears Redis offer lock and sends TRIP_CANCELLED/DISMISS.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R366cfe1aefac4290"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad36a86350434232"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1827,7 +1858,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf54fcd4a3d8940aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d5105b16a0641bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1943,7 +1974,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7c6935f8ffb41de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d091303ad074681"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2196,16 +2227,22 @@
         <x:v>Ready for admin FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
-      <x:c r="C18"/>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>Driver offer cancellation</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>/user/queue/trip-requests</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>On TRIP_CANCELLED/DISMISS: close modal, stop countdown.</x:v>
+      </x:c>
       <x:c r="D18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e8bed9904bf4a34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde52c32fbb4f4a01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2335,7 +2372,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b6255b230f64476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cc70020e3454109"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R013b411e4ed6411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R92065a9921b4434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R38e0f5aeae434d24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5dd4aacccdc94c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R225002c572d84a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R3357b4d1ccc146d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5fd3599022cd41de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Re8bcaf5d8e8a4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R196717a01c0b4870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R9d847a2c73d44dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R52ce0ec341854e6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd46d69023da746dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -806,7 +806,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after driver-offer cancellation dismiss fix.</x:v>
+        <x:v>Asia/Bangkok status after notification flow integration coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -842,7 +842,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>fix: dismiss driver offer on passenger cancellation</x:v>
+        <x:v>test: cover notification flow integration</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -856,13 +856,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted BookingServiceTests, BookingCancelledMatchingListenerTests, WebSocketDriverOfferNotifierTests: pass 15</x:v>
+        <x:v>Targeted NotificationFlowIntegrationTests: pass 1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Booking cancel now publishes an event; matching listener clears Redis offer state and sends driver dismiss payload.</x:v>
+        <x:v>Covers FCM token Redis CRUD plus notification inbox list/mark-read through HTTP/JWT/JPA/Redis.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -963,10 +963,24 @@
         <x:v>Cancel clears Redis offer lock and closes driver modal.</x:v>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Notification integration</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>NotificationFlowIntegrationTests</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>FCM token CRUD + inbox mark-read via HTTP/JWT/JPA/Redis.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45fef0a3eb464b70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92703f85df8b4434"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1475,10 +1489,27 @@
         <x:v>Event clears Redis offer lock and sends TRIP_CANCELLED/DISMISS.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Notification inbox + FCM token flow</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>NotificationFlowIntegrationTests</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>Registers user, verifies Redis token CRUD, lists inbox, marks read.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad36a86350434232"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e914371405c4f2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1663,13 +1694,13 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Auth, booking/matching/pickup-dropoff routing, trip completion, tracking fallback and cash payment confirmation are covered; add notification, admin and provider sandbox E2E flows.</x:v>
+        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation and notification inbox/FCM token flow are covered; add admin and provider sandbox E2E flows.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>Existing Testcontainers PostGIS/Redis base, sandbox merchant accounts and Docker-enabled CI.</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>Remaining notification/admin/provider sandbox happy paths run in CI against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
+        <x:v>Remaining admin/provider sandbox happy paths run in CI against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1858,7 +1889,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d5105b16a0641bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2dc4bb2e37b4670"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1951,7 +1982,7 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth flow, booking-to-matching-to-pickup/dropoff-routing flow, trip completion, tracking fallback and cash payment confirmation are implemented; notification, admin, provider sandbox E2E and CI validation remain.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment and notification inbox/FCM token flows are implemented; admin, provider sandbox E2E and CI validation remain.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
         <x:v>All critical passenger/driver/admin happy paths pass in CI, including provider sandbox callback UAT before online payment launch.</x:v>
@@ -1974,7 +2005,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d091303ad074681"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc76591213ae94f00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2242,7 +2273,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde52c32fbb4f4a01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1357b97083d4d9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2346,10 +2377,10 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback and cash payment confirmation run through HTTP/JWT/JPA/Redis, but notification, admin and real provider sandbox regressions may still slip through.</x:v>
+        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation and notification inbox/FCM token flow run through HTTP/JWT/JPA/Redis, but admin/provider sandbox regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Reuse the Testcontainers base for remaining critical flows and run the suite in CI before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for remaining admin/provider flows and run the suite in CI before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2372,7 +2403,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cc70020e3454109"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0ae8735d2c24dca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5fd3599022cd41de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Re8bcaf5d8e8a4e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R196717a01c0b4870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R9d847a2c73d44dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R52ce0ec341854e6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd46d69023da746dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re8c446cef92542a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R2937c11b9ad04bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R5c5bb6ea52a94415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R2c834ed96bbc4cdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3e0ecef5094f4c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R7b3b8d43972240a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -806,7 +806,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after notification flow integration coverage.</x:v>
+        <x:v>Asia/Bangkok status after admin flow integration coverage.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -842,7 +842,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: cover notification flow integration</x:v>
+        <x:v>test: cover admin flow integration</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -856,13 +856,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted NotificationFlowIntegrationTests: pass 1</x:v>
+        <x:v>Targeted AdminFlowIntegrationTests, AdminTripServiceTests: pass 4</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Covers FCM token Redis CRUD plus notification inbox list/mark-read through HTTP/JWT/JPA/Redis.</x:v>
+        <x:v>Covers admin RBAC, driver approval, pricing, trip list/dashboard and Postgres-safe trip filters.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -977,10 +977,24 @@
         <x:v>FCM token CRUD + inbox mark-read via HTTP/JWT/JPA/Redis.</x:v>
       </x:c>
     </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Admin integration</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>AdminFlowIntegrationTests</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>Admin RBAC, driver approval, pricing, trips, dashboard via HTTP/JWT/JPA/PostGIS.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92703f85df8b4434"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1d4ae1b518a4391"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1506,10 +1520,27 @@
         <x:v>Registers user, verifies Redis token CRUD, lists inbox, marks read.</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Admin flow integration coverage</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>AdminFlowIntegrationTests, AdminTripServiceTests</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>Covers forbidden passenger access, pending driver approval, pricing CRUD, admin trips and dashboard.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e914371405c4f2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R558e2c58cc134141"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1694,13 +1725,13 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation and notification inbox/FCM token flow are covered; add admin and provider sandbox E2E flows.</x:v>
+        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow and admin flow are covered; add provider sandbox E2E flow and CI wiring.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
         <x:v>Existing Testcontainers PostGIS/Redis base, sandbox merchant accounts and Docker-enabled CI.</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>Remaining admin/provider sandbox happy paths run in CI against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
+        <x:v>Provider sandbox happy paths run in CI/staging against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
       </x:c>
       <x:c r="F9" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1889,7 +1920,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2dc4bb2e37b4670"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47f5b73a9d484596"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1982,7 +2013,7 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment and notification inbox/FCM token flows are implemented; admin, provider sandbox E2E and CI validation remain.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token and admin flows are implemented; provider sandbox E2E and CI validation remain.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
         <x:v>All critical passenger/driver/admin happy paths pass in CI, including provider sandbox callback UAT before online payment launch.</x:v>
@@ -2005,7 +2036,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc76591213ae94f00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R931ef9a135db4d35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2273,7 +2304,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1357b97083d4d9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc25ba0dfc46a42fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2377,10 +2408,10 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation and notification inbox/FCM token flow run through HTTP/JWT/JPA/Redis, but admin/provider sandbox regressions may still slip through.</x:v>
+        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, but real provider sandbox regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Reuse the Testcontainers base for remaining admin/provider flows and run the suite in CI before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for provider flows and run the suite in CI before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2403,7 +2434,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0ae8735d2c24dca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde7564c26a874e47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re8c446cef92542a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R2937c11b9ad04bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R5c5bb6ea52a94415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R2c834ed96bbc4cdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3e0ecef5094f4c2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R7b3b8d43972240a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R438d768804b2486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R3f8c476c38f14694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R012ddb567a3f4296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf3c73ad5e14c4b27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rf146f1e5dcd149b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb826df2b66bc4f1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -76,8 +76,13 @@
       <x:color rgb="FF1E3A8A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="30">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -222,6 +227,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -259,7 +269,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="100">
+  <x:cellXfs count="103">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -537,6 +547,11 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -800,13 +815,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after admin flow integration coverage.</x:v>
+        <x:v>Asia/Bangkok status after backend CI wiring commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -842,7 +857,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>test: cover admin flow integration</x:v>
+        <x:v>ci: run backend tests on github actions</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -856,13 +871,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted AdminFlowIntegrationTests, AdminTripServiceTests: pass 4</x:v>
+        <x:v>Backend CI workflow added; GitHub will run ./mvnw test after push</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Covers admin RBAC, driver approval, pricing, trip list/dashboard and Postgres-safe trip filters.</x:v>
+        <x:v>Workflow uses Java 17 and Docker-enabled ubuntu-latest runner for Testcontainers.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -876,7 +891,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-24; LF/CRLF warnings only.</x:v>
+        <x:v>No whitespace errors on 2026-06-27; LF/CRLF warnings only.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -994,7 +1009,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1d4ae1b518a4391"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d25de66817482e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1537,10 +1552,27 @@
         <x:v>Covers forbidden passenger access, pending driver approval, pricing CRUD, admin trips and dashboard.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="102" t="str">
+        <x:v>Testing</x:v>
+      </x:c>
+      <x:c r="B32" s="102" t="str">
+        <x:v>Backend CI workflow for Maven/Testcontainers suite</x:v>
+      </x:c>
+      <x:c r="C32" s="102" t="str">
+        <x:v>.github/workflows/backend-ci.yml</x:v>
+      </x:c>
+      <x:c r="D32" s="102" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E32" s="102" t="str">
+        <x:v>Runs on push to main/develop/feature branches and PRs to main/develop using Java 17, Maven cache, Docker check and ./mvnw test.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R558e2c58cc134141"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9705d35f33194f49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1725,10 +1757,10 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="7" t="str">
-        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow and admin flow are covered; add provider sandbox E2E flow and CI wiring.</x:v>
+        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow, admin flow and CI wiring are covered; add provider sandbox E2E flow.</x:v>
       </x:c>
       <x:c r="D9" s="7" t="str">
-        <x:v>Existing Testcontainers PostGIS/Redis base, sandbox merchant accounts and Docker-enabled CI.</x:v>
+        <x:v>Existing Testcontainers PostGIS/Redis base and sandbox merchant accounts.</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
         <x:v>Provider sandbox happy paths run in CI/staging against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
@@ -1920,7 +1952,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47f5b73a9d484596"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56b44fdf52c14a44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2013,10 +2045,10 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token and admin flows are implemented; provider sandbox E2E and CI validation remain.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token, admin flows and backend CI workflow are implemented; provider sandbox E2E remains.</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>All critical passenger/driver/admin happy paths pass in CI, including provider sandbox callback UAT before online payment launch.</x:v>
+        <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2036,7 +2068,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R931ef9a135db4d35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc83b901bc847a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2304,7 +2336,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc25ba0dfc46a42fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a323e3cb9d64351"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2408,10 +2440,10 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, but real provider sandbox regressions may still slip through.</x:v>
+        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, and GitHub Actions runs the suite on pushes/PRs; real provider sandbox regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Reuse the Testcontainers base for provider flows and run the suite in CI before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for provider flows and validate real gateway callbacks before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2434,7 +2466,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde7564c26a874e47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5efc45a1814c4bda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R438d768804b2486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R3f8c476c38f14694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R012ddb567a3f4296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf3c73ad5e14c4b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rf146f1e5dcd149b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb826df2b66bc4f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1d9667f3f6074464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rf52f14c6c4b14190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rd1911013ec95441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1143699c8e764121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6ece9f546aa5467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R57d401bdadf14551"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -81,8 +81,13 @@
       <x:color rgb="FF000000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="31">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -227,6 +232,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -269,7 +279,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="103">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -551,6 +561,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -821,7 +836,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after backend CI wiring commit.</x:v>
+        <x:v>Asia/Bangkok status after health/readiness endpoint commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -829,13 +844,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/trip-completion-payment-integration</x:v>
+        <x:v>feature/production-health-readiness</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds targeted fix for passenger cancellation while driver offer popup is active.</x:v>
+        <x:v>Adds public Actuator health/liveness/readiness/info endpoints for deployment probes.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -843,13 +858,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge payment sandbox webhook contract coverage</x:v>
+        <x:v>develop after merge trip completion payment integration</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/payment-sandbox-callback-uat-support is merged into develop at e541e80.</x:v>
+        <x:v>feature/trip-completion-payment-integration is merged into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -857,7 +872,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>ci: run backend tests on github actions</x:v>
+        <x:v>feat: add actuator health readiness endpoints</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -871,13 +886,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Backend CI workflow added; GitHub will run ./mvnw test after push</x:v>
+        <x:v>Targeted HealthReadinessIntegrationTests: pass 1</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Workflow uses Java 17 and Docker-enabled ubuntu-latest runner for Testcontainers.</x:v>
+        <x:v>Verifies public health/liveness/readiness/info with Testcontainers PostGIS/Redis.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -1009,7 +1024,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d25de66817482e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1391df5db7b4421"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1569,10 +1584,27 @@
         <x:v>Runs on push to main/develop/feature branches and PRs to main/develop using Java 17, Maven cache, Docker check and ./mvnw test.</x:v>
       </x:c>
     </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="105" t="str">
+        <x:v>Operations</x:v>
+      </x:c>
+      <x:c r="B33" s="105" t="str">
+        <x:v>Actuator health, liveness, readiness and info endpoints</x:v>
+      </x:c>
+      <x:c r="C33" s="105" t="str">
+        <x:v>/actuator/health, /actuator/health/liveness, /actuator/health/readiness, /actuator/info</x:v>
+      </x:c>
+      <x:c r="D33" s="105" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E33" s="105" t="str">
+        <x:v>Endpoints are public; readiness includes readinessState, db and redis; liveness includes livenessState only; health details are hidden.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9705d35f33194f49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34134567bba0452f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1777,13 +1809,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Request correlation and centralized error logging are done; add log shipping, metrics/tracing backend, CORS/rate limits, and health/readiness review.</x:v>
+        <x:v>Request correlation, centralized error logging and Actuator health/readiness endpoints are done; add log shipping, metrics/tracing backend, CORS policy and rate limits.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
         <x:v>Deployment platform and centralized observability service.</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>Logs are searchable across instances and production defaults are explicit, observable, and safe.</x:v>
+        <x:v>Logs and metrics are searchable across instances; CORS/rate limits are explicit; probes feed deployment dashboards and alerts.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1952,7 +1984,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56b44fdf52c14a44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e55b0c55834dcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2031,10 +2063,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading plus HTTP request correlation and centralized application error logging implemented; log aggregation, metrics/tracing, env profiles, CORS/rate limits, health/readiness, and DB release strategy remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging and Actuator health/readiness endpoints implemented; log aggregation, metrics/tracing, env profiles, CORS/rate limits and release SQL strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely and operators can trace failures across instances using request IDs.</x:v>
+        <x:v>Staging loads secrets safely, probes report app/dependency readiness, and operators can trace failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2068,7 +2100,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc83b901bc847a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb164047c4b04212"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2336,7 +2368,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a323e3cb9d64351"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505bc655133541e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2454,10 +2486,10 @@
         <x:v>Logs are local to each application instance.</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>Request IDs make failures searchable, but logs can be lost or fragmented across replicas.</x:v>
+        <x:v>Request IDs and health probes make failures easier to detect, but logs can still be lost or fragmented across replicas.</x:v>
       </x:c>
       <x:c r="C8" s="29" t="str">
-        <x:v>Ship stdout logs centrally and configure retention, search, and alert rules before scaling production.</x:v>
+        <x:v>Ship stdout logs centrally and configure retention, search, alerting plus health-probe dashboards before scaling production.</x:v>
       </x:c>
       <x:c r="D8" s="29" t="str">
         <x:v>Open</x:v>
@@ -2466,7 +2498,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5efc45a1814c4bda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b3d2c7d0aac4069"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R1d9667f3f6074464"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rf52f14c6c4b14190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rd1911013ec95441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1143699c8e764121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6ece9f546aa5467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R57d401bdadf14551"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R41da13adc58d4b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6cba1ebf27c94745"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf1da7d04057b4fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rc937914a62ac4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R2129985a485a4451"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R9cc6c473c68c4c24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -86,8 +86,13 @@
       <x:color rgb="FF000000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="32">
+  <x:fills count="33">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -232,6 +237,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD1FAE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -279,7 +289,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="106">
+  <x:cellXfs count="109">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -566,6 +576,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="11" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -830,13 +845,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after health/readiness endpoint commit.</x:v>
+        <x:v>Asia/Bangkok status after configurable CORS policy commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -872,7 +887,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add actuator health readiness endpoints</x:v>
+        <x:v>feat: add configurable cors policy</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -886,13 +901,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted HealthReadinessIntegrationTests: pass 1</x:v>
+        <x:v>Targeted SecurityCorsIntegrationTests: pass 3</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Verifies public health/liveness/readiness/info with Testcontainers PostGIS/Redis.</x:v>
+        <x:v>Verifies allowed preflight, exposed X-Request-Id and rejected disallowed origins.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -906,7 +921,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-27; LF/CRLF warnings only.</x:v>
+        <x:v>No whitespace errors on 2026-06-28; LF/CRLF warnings only.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1024,7 +1039,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1391df5db7b4421"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66462247166e4468"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1601,10 +1616,27 @@
         <x:v>Endpoints are public; readiness includes readinessState, db and redis; liveness includes livenessState only; health details are hidden.</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="108" t="str">
+        <x:v>Security</x:v>
+      </x:c>
+      <x:c r="B34" s="108" t="str">
+        <x:v>Configurable CORS allowlist for web FE/admin clients</x:v>
+      </x:c>
+      <x:c r="C34" s="108" t="str">
+        <x:v>CORS preflight, all REST endpoints, X-Request-Id response header</x:v>
+      </x:c>
+      <x:c r="D34" s="108" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E34" s="108" t="str">
+        <x:v>Defaults allow common localhost origins; production can override origins/patterns, methods, headers, exposed headers, credentials and max-age via env vars.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34134567bba0452f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re55e443c0f044919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1809,13 +1841,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Request correlation, centralized error logging and Actuator health/readiness endpoints are done; add log shipping, metrics/tracing backend, CORS policy and rate limits.</x:v>
+        <x:v>Request correlation, centralized error logging, configurable CORS allowlist and Actuator health/readiness endpoints are done; add log shipping, metrics/tracing backend and rate limits.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
         <x:v>Deployment platform and centralized observability service.</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>Logs and metrics are searchable across instances; CORS/rate limits are explicit; probes feed deployment dashboards and alerts.</x:v>
+        <x:v>Logs and metrics are searchable across instances; rate limits are explicit; probes feed deployment dashboards and alerts.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>Partial</x:v>
@@ -1984,7 +2016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9e55b0c55834dcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77db58a517fb4bd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2063,10 +2095,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging and Actuator health/readiness endpoints implemented; log aggregation, metrics/tracing, env profiles, CORS/rate limits and release SQL strategy remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist and Actuator health/readiness endpoints implemented; log aggregation, metrics/tracing, env profiles, rate limits and release SQL strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely, probes report app/dependency readiness, and operators can trace failures across instances using request IDs.</x:v>
+        <x:v>Staging loads secrets safely, FE browser origins are explicitly allowlisted, probes report app/dependency readiness, and operators can trace failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2100,7 +2132,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb164047c4b04212"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R448ffa1663dd4aec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2368,7 +2400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505bc655133541e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0fe08c069042fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2486,7 +2518,7 @@
         <x:v>Logs are local to each application instance.</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>Request IDs and health probes make failures easier to detect, but logs can still be lost or fragmented across replicas.</x:v>
+        <x:v>Request IDs, CORS allowlist and health probes make failures easier to detect and reproduce, but logs can still be lost or fragmented across replicas.</x:v>
       </x:c>
       <x:c r="C8" s="29" t="str">
         <x:v>Ship stdout logs centrally and configure retention, search, alerting plus health-probe dashboards before scaling production.</x:v>
@@ -2498,7 +2530,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b3d2c7d0aac4069"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500f9f463bad4704"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R41da13adc58d4b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6cba1ebf27c94745"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf1da7d04057b4fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rc937914a62ac4f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R2129985a485a4451"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R9cc6c473c68c4c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re50ebbdda9554789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc18594cd5a9c4a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rcc25dcaadd3748a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R862d8e6a552241e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0a51bdf960384f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R395dd2a898184d52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E25" headerRowCount="1">
-  <x:autoFilter ref="A1:E25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E26" headerRowCount="1">
+  <x:autoFilter ref="A1:E26"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -646,8 +646,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D15" headerRowCount="1">
-  <x:autoFilter ref="A1:D15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D16" headerRowCount="1">
+  <x:autoFilter ref="A1:D16"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -659,8 +659,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D8" headerRowCount="1">
-  <x:autoFilter ref="A1:D8"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D9" headerRowCount="1">
+  <x:autoFilter ref="A1:D9"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -851,7 +851,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after configurable CORS policy commit.</x:v>
+        <x:v>Asia/Bangkok status after API rate limiting commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -859,13 +859,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/production-health-readiness</x:v>
+        <x:v>feature/rate-limit-policy</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds public Actuator health/liveness/readiness/info endpoints for deployment probes.</x:v>
+        <x:v>Adds configurable in-memory token-bucket REST API rate limiting and FE 429 contract.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -873,13 +873,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge trip completion payment integration</x:v>
+        <x:v>develop after merge production health readiness</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/trip-completion-payment-integration is merged into develop.</x:v>
+        <x:v>feature/production-health-readiness is merged into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -887,7 +887,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add configurable cors policy</x:v>
+        <x:v>feat: add api rate limiting</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -901,13 +901,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted SecurityCorsIntegrationTests: pass 3</x:v>
+        <x:v>Targeted RateLimitFilterIntegrationTests, SecurityCorsIntegrationTests: pass 5</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Verifies allowed preflight, exposed X-Request-Id and rejected disallowed origins.</x:v>
+        <x:v>Verifies login throttle, actuator exclusion, allowed preflight, exposed headers and rejected origins.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -921,7 +921,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-28; LF/CRLF warnings only.</x:v>
+        <x:v>No whitespace errors on 2026-06-28; LF/CRLF warnings only if Git reports line-ending normalization.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1039,7 +1039,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66462247166e4468"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68200b1fef154c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1482,19 +1482,19 @@
     </x:row>
     <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" s="29" t="str">
-        <x:v>Tracking</x:v>
+        <x:v>Security/Operations</x:v>
       </x:c>
       <x:c r="B26" s="29" t="str">
-        <x:v>Driver approach location before trip start</x:v>
+        <x:v>In-memory API rate limiting policy</x:v>
       </x:c>
       <x:c r="C26" s="29" t="str">
-        <x:v>/app/driver.location, /topic/trip/{tripId}/location, REST fallback</x:v>
+        <x:v>All REST endpoints; Retry-After and X-RateLimit-* headers</x:v>
       </x:c>
       <x:c r="D26" s="29" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E26" s="29" t="str">
-        <x:v>ACCEPTED/ARRIVED locations are cached and broadcast for passenger approach view; only IN_PROGRESS locations are persisted to history for fare distance.</x:v>
+        <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -1636,7 +1636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re55e443c0f044919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6d98dfc1fa4ef1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1841,13 +1841,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Request correlation, centralized error logging, configurable CORS allowlist and Actuator health/readiness endpoints are done; add log shipping, metrics/tracing backend and rate limits.</x:v>
+        <x:v>Request correlation, centralized error logging, configurable CORS, health/readiness and basic rate limiting are implemented; add centralized log shipping plus metrics/tracing backend.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Deployment platform and centralized observability service.</x:v>
+        <x:v>Deployment platform and centralized observability stack.</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>Logs and metrics are searchable across instances; rate limits are explicit; probes feed deployment dashboards and alerts.</x:v>
+        <x:v>Logs, metrics, traces and rate-limit events are searchable across instances; dashboards and alerts cover health, 5xx and throttling.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2016,7 +2016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77db58a517fb4bd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51421859768d455b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2095,10 +2095,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist and Actuator health/readiness endpoints implemented; log aggregation, metrics/tracing, env profiles, rate limits and release SQL strategy remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness and basic API rate limiting implemented; log aggregation, metrics/tracing, env profiles and release SQL strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely, FE browser origins are explicitly allowlisted, probes report app/dependency readiness, and operators can trace failures across instances using request IDs.</x:v>
+        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, and operators can trace failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2132,7 +2132,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R448ffa1663dd4aec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc59f1cff69d4ce5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2359,13 +2359,13 @@
     </x:row>
     <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" s="29" t="str">
-        <x:v>Trip completion and cash payment</x:v>
+        <x:v>Rate limit handling</x:v>
       </x:c>
       <x:c r="B16" s="29" t="str">
-        <x:v>/api/v1/bookings/{tripId}, /api/v1/payments/trips/{tripId}, /checkout, PATCH /api/v1/drivers/trips/{tripId}/payment-confirm</x:v>
+        <x:v>All REST endpoints except configured diagnostics/docs/WebSocket paths; Retry-After and X-RateLimit-* headers</x:v>
       </x:c>
       <x:c r="C16" s="29" t="str">
-        <x:v>After driver completes trip, refresh trip detail for finalFare/completedAt, load payment detail, show CASH confirmation to driver, then refresh payment status and allow driver heartbeat/available screen.</x:v>
+        <x:v>On HTTP 429/RATE_LIMIT_EXCEEDED, stop immediate retries, disable the action temporarily, schedule retry after Retry-After and keep requestId for support.</x:v>
       </x:c>
       <x:c r="D16" s="29" t="str">
         <x:v>Ready for FE</x:v>
@@ -2400,7 +2400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0fe08c069042fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89ea3897d6484e30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2513,24 +2513,38 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="48" customHeight="1">
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="29" t="str">
-        <x:v>Logs are local to each application instance.</x:v>
+        <x:v>Logs and rate-limit state are local to each application instance.</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>Request IDs, CORS allowlist and health probes make failures easier to detect and reproduce, but logs can still be lost or fragmented across replicas.</x:v>
+        <x:v>Request IDs, CORS allowlist, health probes and 429 throttling improve diagnosis, but logs and in-memory buckets can still be fragmented across replicas.</x:v>
       </x:c>
       <x:c r="C8" s="29" t="str">
-        <x:v>Ship stdout logs centrally and configure retention, search, alerting plus health-probe dashboards before scaling production.</x:v>
+        <x:v>Ship stdout logs centrally; add retention/search/alerts plus health and throttling dashboards. Move rate-limit buckets to Redis or edge gateway before strict global quotas.</x:v>
       </x:c>
       <x:c r="D8" s="29" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A9" s="29" t="str">
+        <x:v>In-memory rate limiting is per application instance.</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>Multiple replicas each keep their own token buckets, so total traffic allowed may exceed the configured per-instance limit.</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>Use conservative MVP defaults now; move bucket state to Redis or enforce limits at the API gateway if production needs global quotas.</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="str">
         <x:v>Open</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500f9f463bad4704"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d0b539ffb942a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Re50ebbdda9554789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc18594cd5a9c4a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rcc25dcaadd3748a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R862d8e6a552241e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R0a51bdf960384f8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R395dd2a898184d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R47569b77483e4db9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rce4cd944e94c432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R0c1bc6a646e5410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rece4762285094798"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rff16fe6e0ca543af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R8de81beb204d4a14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E26" headerRowCount="1">
-  <x:autoFilter ref="A1:E26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E27" headerRowCount="1">
+  <x:autoFilter ref="A1:E27"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -646,8 +646,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D16" headerRowCount="1">
-  <x:autoFilter ref="A1:D16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D17" headerRowCount="1">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -659,8 +659,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D9" headerRowCount="1">
-  <x:autoFilter ref="A1:D9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D10" headerRowCount="1">
+  <x:autoFilter ref="A1:D10"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -851,7 +851,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after API rate limiting commit.</x:v>
+        <x:v>Asia/Bangkok status after Prometheus observability metrics commit.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -859,13 +859,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/rate-limit-policy</x:v>
+        <x:v>feature/observability-metrics</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds configurable in-memory token-bucket REST API rate limiting and FE 429 contract.</x:v>
+        <x:v>Adds Prometheus scrape endpoint plus custom rate-limit metrics.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -873,13 +873,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge production health readiness</x:v>
+        <x:v>develop after merge api rate limiting</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/production-health-readiness is merged into develop.</x:v>
+        <x:v>feature/rate-limit-policy is merged into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -887,7 +887,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add api rate limiting</x:v>
+        <x:v>feat: add prometheus observability metrics</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -901,13 +901,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Targeted RateLimitFilterIntegrationTests, SecurityCorsIntegrationTests: pass 5</x:v>
+        <x:v>Full ./mvnw.cmd test: pass 350</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Verifies login throttle, actuator exclusion, allowed preflight, exposed headers and rejected origins.</x:v>
+        <x:v>Full suite passed on 2026-06-28; observability test covers actuator discovery, Prometheus scrape and custom rate-limit metrics.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -1039,7 +1039,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68200b1fef154c2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R101ffe5b03ad42ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1499,19 +1499,19 @@
     </x:row>
     <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A27" s="29" t="str">
-        <x:v>Payment</x:v>
+        <x:v>Operations</x:v>
       </x:c>
       <x:c r="B27" s="29" t="str">
-        <x:v>Payment provider sandbox readiness diagnostics</x:v>
+        <x:v>Prometheus observability metrics</x:v>
       </x:c>
       <x:c r="C27" s="29" t="str">
-        <x:v>/api/v1/payments/providers/readiness</x:v>
+        <x:v>/actuator/metrics, /actuator/prometheus, goride.rate.limit.*</x:v>
       </x:c>
       <x:c r="D27" s="29" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E27" s="29" t="str">
-        <x:v>Reports providerRegistered, checkoutReady, webhookReady, sandboxReady and missingRequirements without exposing secrets.</x:v>
+        <x:v>Exposes standard HTTP metrics, common application tag, request histogram config, and custom rate-limit allowed/rejected counters plus bucket gauge.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="52.79999923706055" hidden="0" customHeight="1">
@@ -1636,7 +1636,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6d98dfc1fa4ef1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda93a29957524d34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1841,13 +1841,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Request correlation, centralized error logging, configurable CORS, health/readiness and basic rate limiting are implemented; add centralized log shipping plus metrics/tracing backend.</x:v>
+        <x:v>Request correlation, centralized error logging, configurable CORS, health/readiness, basic rate limiting and Prometheus metrics are implemented; add centralized log shipping plus distributed tracing backend.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
-        <x:v>Deployment platform and centralized observability stack.</x:v>
+        <x:v>Deployment platform, log aggregation and tracing/observability stack.</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>Logs, metrics, traces and rate-limit events are searchable across instances; dashboards and alerts cover health, 5xx and throttling.</x:v>
+        <x:v>Logs, metrics and traces are correlated across instances; dashboards and alerts cover health, latency, 5xx, throttling and dependency readiness.</x:v>
       </x:c>
       <x:c r="F10" s="13" t="str">
         <x:v>Partial</x:v>
@@ -2016,7 +2016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51421859768d455b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78c2e2ef768d49b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2095,10 +2095,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness and basic API rate limiting implemented; log aggregation, metrics/tracing, env profiles and release SQL strategy remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting and Prometheus metrics implemented; log aggregation, distributed tracing, env profiles and release SQL strategy remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, and operators can trace failures across instances using request IDs.</x:v>
+        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, and operators can correlate failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2132,7 +2132,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc59f1cff69d4ce5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cda3a78f5bb4262"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2373,16 +2373,16 @@
     </x:row>
     <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A17" s="29" t="str">
-        <x:v>Admin payment readiness</x:v>
+        <x:v>Observability smoke</x:v>
       </x:c>
       <x:c r="B17" s="29" t="str">
-        <x:v>/api/v1/payments/providers/readiness</x:v>
+        <x:v>/actuator, /actuator/metrics, /actuator/prometheus</x:v>
       </x:c>
       <x:c r="C17" s="29" t="str">
-        <x:v>Show MoMo/VNPAY readiness before UAT; expose missingRequirements to admins/devops, never to passenger checkout UI.</x:v>
+        <x:v>Devops scrapes Prometheus and checks http.server.requests, goride.rate.limit.requests and goride.rate.limit.buckets; keep endpoints behind trusted network controls in production.</x:v>
       </x:c>
       <x:c r="D17" s="29" t="str">
-        <x:v>Ready for admin FE</x:v>
+        <x:v>Ready for devops</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
@@ -2400,7 +2400,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89ea3897d6484e30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9caf7624bf90456e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2515,13 +2515,13 @@
     </x:row>
     <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A8" s="29" t="str">
-        <x:v>Logs and rate-limit state are local to each application instance.</x:v>
+        <x:v>Logs and metrics are still per-instance until deployment wiring is added.</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>Request IDs, CORS allowlist, health probes and 429 throttling improve diagnosis, but logs and in-memory buckets can still be fragmented across replicas.</x:v>
+        <x:v>Request IDs, health probes, Prometheus metrics and 429 throttling improve diagnosis, but logs/metrics can still be fragmented across replicas.</x:v>
       </x:c>
       <x:c r="C8" s="29" t="str">
-        <x:v>Ship stdout logs centrally; add retention/search/alerts plus health and throttling dashboards. Move rate-limit buckets to Redis or edge gateway before strict global quotas.</x:v>
+        <x:v>Ship stdout logs centrally, scrape each instance from Prometheus or the platform collector, and add retention/search/alert dashboards before production scaling.</x:v>
       </x:c>
       <x:c r="D8" s="29" t="str">
         <x:v>Open</x:v>
@@ -2541,10 +2541,24 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" ht="72" customHeight="1">
+      <x:c r="A10" s="29" t="str">
+        <x:v>Prometheus endpoint exposure needs network controls.</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>Metrics can reveal route names, status patterns and operational load if exposed directly to the public internet.</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>Expose actuator metrics only on a trusted network, behind gateway rules or via platform scrape integration; keep auth/network policy outside app-level local dev defaults.</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99d0b539ffb942a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refeebf71fa424451"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R47569b77483e4db9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rce4cd944e94c432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R0c1bc6a646e5410d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rece4762285094798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rff16fe6e0ca543af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R8de81beb204d4a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6d69c56f828b4204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R48178d1a0fd04284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R62d87e41330e464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R2a9c917b75224b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rbc6b5d3751804d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf4509ff9c6bb4f22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,13 +820,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="37.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="41" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="7.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="111.37999725341797" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Field</x:v>
       </x:c>
@@ -840,54 +840,54 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="7" t="str">
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after Prometheus observability metrics commit.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+        <x:v>Asia/Bangkok status after payment sandbox UAT harness implementation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/observability-metrics</x:v>
+        <x:v>feature/payment-sandbox-uat-harness</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds Prometheus scrape endpoint plus custom rate-limit metrics.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>Adds admin/devops UAT checklist endpoint for online payment sandbox validation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge api rate limiting</x:v>
+        <x:v>develop after merge prometheus observability metrics</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/rate-limit-policy is merged into develop.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>feature/observability-metrics is merged into develop; OTLP tracing branch is held unmerged.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add prometheus observability metrics</x:v>
+        <x:v>feat: add payment sandbox uat harness</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -896,18 +896,18 @@
         <x:v>Prepared on feature branch for user review before merge.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Full ./mvnw.cmd test: pass 350</x:v>
+        <x:v>Full ./mvnw.cmd test: pass 354</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full suite passed on 2026-06-28; observability test covers actuator discovery, Prometheus scrape and custom rate-limit metrics.</x:v>
+        <x:v>Full suite passed on 2026-06-30; targeted PaymentControllerTests and PaymentSandboxUatPlanServiceTests passed 8 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -921,24 +921,24 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>No whitespace errors on 2026-06-28; LF/CRLF warnings only if Git reports line-ending normalization.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Pass on 2026-06-30; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>CodeRabbit CLI blocked on Windows installer</x:v>
+        <x:v>CodeRabbit CLI missing; remote installer rejected by approval policy</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>CLI missing; official installer via Git Bash reports unsupported OS mingw64_nt-10.0-26200.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>coderabbit is not in PATH; installer execution was rejected because it would install third-party software on the user machine without explicit approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="str">
         <x:v>Local config</x:v>
       </x:c>
@@ -952,94 +952,94 @@
         <x:v>Keep environment-specific local changes uncommitted.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
+        <x:v>Payment sandbox UAT harness</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>Admin endpoint reports prerequisites, provider status, callback URLs, missing requirements, FE actions and backend checks without exposing secrets.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="29" t="str">
         <x:v>Payment sandbox webhook contracts</x:v>
       </x:c>
-      <x:c r="B10" s="29" t="str">
+      <x:c r="B11" s="29" t="str">
         <x:v>Service-level signed MoMo/VNPAY callback coverage</x:v>
       </x:c>
-      <x:c r="C10" s="29" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="D10" s="29" t="str">
-        <x:v>Merged into develop at e541e80. Real merchant sandbox callback UAT remains open.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A11" s="29" t="str">
+      <x:c r="C11" s="29" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="str">
+        <x:v>Real merchant sandbox callback UAT remains open.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="29" t="str">
         <x:v>Payment readiness diagnostics</x:v>
       </x:c>
-      <x:c r="B11" s="29" t="str">
+      <x:c r="B12" s="29" t="str">
         <x:v>GET /api/v1/payments/providers/readiness</x:v>
       </x:c>
-      <x:c r="C11" s="29" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="D11" s="29" t="str">
-        <x:v>Merged into develop before the current integration coverage feature.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A12" s="29" t="str">
-        <x:v>Trip completion/payment integration</x:v>
-      </x:c>
-      <x:c r="B12" s="29" t="str">
-        <x:v>BookingMatchingRoutingIntegrationTests end-to-end coverage</x:v>
-      </x:c>
       <x:c r="C12" s="29" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="29" t="str">
-        <x:v>Covers final fare, latest location REST fallback, payment detail, CASH checkout, payment-confirm and post-payment driver heartbeat.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="28.5" customHeight="1">
+        <x:v>Readiness stays the gate for enabled/sandboxReady online providers.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
-        <x:v>Driver offer cancel dismiss</x:v>
+        <x:v>Prometheus observability metrics</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>BookingCancelledEvent + DISMISS payload</x:v>
+        <x:v>/actuator/prometheus and goride.rate.limit.*</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>Cancel clears Redis offer lock and closes driver modal.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>Merged into develop before this feature branch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
-        <x:v>Notification integration</x:v>
+        <x:v>OTLP tracing config</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>NotificationFlowIntegrationTests</x:v>
+        <x:v>feature/otlp-tracing-config</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>In review</x:v>
+        <x:v>Held</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>FCM token CRUD + inbox mark-read via HTTP/JWT/JPA/Redis.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>Implemented on a separate branch but intentionally not merged into develop yet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
-        <x:v>Admin integration</x:v>
+        <x:v>Real merchant sandbox UAT</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>AdminFlowIntegrationTests</x:v>
+        <x:v>MoMo/VNPAY provider-hosted checkout/callback</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>In review</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>Admin RBAC, driver approval, pricing, trips, dashboard via HTTP/JWT/JPA/PostGIS.</x:v>
+        <x:v>Backend harness is ready; external sandbox accounts and public callback URLs are still required.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R101ffe5b03ad42ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95087947067b4cb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1048,11 +1048,11 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="41.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="48.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="47.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="66.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="138.3800048828125" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -1106,7 +1106,7 @@
         <x:v>Supports profile page and admin account management.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Driver</x:v>
       </x:c>
@@ -1123,7 +1123,7 @@
         <x:v>Redis availability is integrated with matching.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Pricing</x:v>
       </x:c>
@@ -1157,7 +1157,7 @@
         <x:v>Passenger booking flow is wired to trip/matching.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Trip lifecycle</x:v>
       </x:c>
@@ -1225,7 +1225,7 @@
         <x:v>Latest location stored in Redis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1242,7 +1242,7 @@
         <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1276,7 +1276,7 @@
         <x:v>Prevents duplicate trip ratings.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="7" t="str">
         <x:v>Notification</x:v>
       </x:c>
@@ -1327,7 +1327,7 @@
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="29" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1344,7 +1344,7 @@
         <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="71" t="str">
         <x:v>Routing</x:v>
       </x:c>
@@ -1361,7 +1361,7 @@
         <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="29" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1378,7 +1378,7 @@
         <x:v>Runs register, JWT-protected request, refresh rotation, logout revocation, and duplicate-phone rejection through HTTP, JPA, and Redis.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="55" t="str">
         <x:v>Routing</x:v>
       </x:c>
@@ -1395,7 +1395,7 @@
         <x:v>Validates assigned driver and trip status; returns destination, distance/duration, GeoJSON LineString, and OSRM maneuver steps.</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="81" t="str">
         <x:v>Driver</x:v>
       </x:c>
@@ -1412,7 +1412,7 @@
         <x:v>Refreshes GEO/meta/status TTL without overwriting BUSY; scheduled batch marks stale database profiles offline.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="54" customHeight="1">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="29" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1429,7 +1429,7 @@
         <x:v>Runs booking creation, Redis offer matching, driver acceptance, pickup route, arrival transition, and dropoff route through HTTP/JWT/PostGIS/Redis with a local OSRM boundary.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="48" customHeight="1">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="29" t="str">
         <x:v>Observability</x:v>
       </x:c>
@@ -1446,7 +1446,7 @@
         <x:v>Returns request ID in header/error body; logs method, path, status, duration, error code, and 5xx stack traces without bodies or secrets.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="29" t="str">
         <x:v>Payment</x:v>
       </x:c>
@@ -1463,7 +1463,7 @@
         <x:v>Covers signed MoMo success, signed VNPAY failure, and stale callback rejection through the service dispatch layer.</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="29" t="str">
         <x:v>Matching</x:v>
       </x:c>
@@ -1480,7 +1480,7 @@
         <x:v>Initial no-candidate booking remains SEARCHING; driver online/heartbeat retries unmatched searching trips and dispatches offer when a candidate is available.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="29" t="str">
         <x:v>Security/Operations</x:v>
       </x:c>
@@ -1491,13 +1491,13 @@
         <x:v>All REST endpoints; Retry-After and X-RateLimit-* headers</x:v>
       </x:c>
       <x:c r="D26" s="29" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E26" s="29" t="str">
-        <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
+        <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds. Merged before current branch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="29" t="str">
         <x:v>Operations</x:v>
       </x:c>
@@ -1508,13 +1508,13 @@
         <x:v>/actuator/metrics, /actuator/prometheus, goride.rate.limit.*</x:v>
       </x:c>
       <x:c r="D27" s="29" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E27" s="29" t="str">
-        <x:v>Exposes standard HTTP metrics, common application tag, request histogram config, and custom rate-limit allowed/rejected counters plus bucket gauge.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="52.79999923706055" hidden="0" customHeight="1">
+        <x:v>Exposes standard HTTP metrics, common application tag, request histogram config, and custom rate-limit allowed/rejected counters plus bucket gauge. Merged into develop.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="29" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1531,7 +1531,7 @@
         <x:v>Runs booking, matching, driver accept/arrived/start/complete, tracking REST fallback, final fare, payment detail/checkout, cash confirmation and driver heartbeat through Testcontainers.</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="31.5" customHeight="1">
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Matching</x:v>
       </x:c>
@@ -1548,7 +1548,7 @@
         <x:v>Event clears Redis offer lock and sends TRIP_CANCELLED/DISMISS.</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1565,7 +1565,7 @@
         <x:v>Registers user, verifies Redis token CRUD, lists inbox, marks read.</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1582,7 +1582,7 @@
         <x:v>Covers forbidden passenger access, pending driver approval, pricing CRUD, admin trips and dashboard.</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="102" t="str">
         <x:v>Testing</x:v>
       </x:c>
@@ -1599,7 +1599,7 @@
         <x:v>Runs on push to main/develop/feature branches and PRs to main/develop using Java 17, Maven cache, Docker check and ./mvnw test.</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="105" t="str">
         <x:v>Operations</x:v>
       </x:c>
@@ -1616,7 +1616,7 @@
         <x:v>Endpoints are public; readiness includes readinessState, db and redis; liveness includes livenessState only; health details are hidden.</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="108" t="str">
         <x:v>Security</x:v>
       </x:c>
@@ -1631,12 +1631,29 @@
       </x:c>
       <x:c r="E34" s="108" t="str">
         <x:v>Defaults allow common localhost origins; production can override origins/patterns, methods, headers, exposed headers, credentials and max-age via env vars.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Payment sandbox UAT harness</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements, FE actions and backend checks; real merchant sandbox UAT remains open.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda93a29957524d34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc466dce3424b4905"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1645,12 +1662,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21.25" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="45" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="57.5" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="154.1300048828125" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="79.62999725341797" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="156.1300048828125" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="7.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -1673,7 +1690,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="13" t="str">
         <x:v>P0</x:v>
       </x:c>
@@ -1681,19 +1698,19 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Finish real MoMo/VNPAY sandbox merchant UAT; backend readiness and service-level signed callback contract coverage are in place.</x:v>
+        <x:v>Finish real MoMo/VNPAY sandbox merchant UAT; backend readiness, sandbox UAT plan and service-level signed callback contract coverage are in place.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint.</x:v>
+        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint and UAT plan endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Both providers return usable checkout URLs and real sandbox success/failure callbacks reconcile internal payment/trip state. Current backend contract tests do not replace provider-hosted callback UAT.</x:v>
+        <x:v>Both providers return usable checkout URLs and real sandbox success/failure callbacks reconcile internal payment/trip state. Current backend harness/contract tests do not replace provider-hosted callback UAT.</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="9" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1713,7 +1730,7 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1733,7 +1750,7 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="13" t="str">
         <x:v>P0</x:v>
       </x:c>
@@ -1741,10 +1758,10 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs; service-level success/failure/stale callback coverage is implemented.</x:v>
+        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs; service-level success/failure/stale callback coverage and admin UAT plan are implemented.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Sandbox callback examples and merchant test accounts.</x:v>
+        <x:v>Sandbox callback examples, merchant test accounts and public HTTPS backend URL.</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
         <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; signed sandbox payloads map to internal payment states.</x:v>
@@ -1753,7 +1770,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="96" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1773,7 +1790,7 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="88" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1793,7 +1810,7 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="88" t="str">
         <x:v>Done</x:v>
       </x:c>
@@ -1813,7 +1830,7 @@
         <x:v>Done</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="11" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -1853,7 +1870,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="11" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -1993,7 +2010,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="29" t="str">
         <x:v>P1</x:v>
       </x:c>
@@ -2016,7 +2033,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78c2e2ef768d49b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8c5ecacd0b488d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2025,13 +2042,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="221.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="174.3800048828125" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Phase</x:v>
       </x:c>
@@ -2045,7 +2062,7 @@
         <x:v>Exit Criteria</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="7" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2053,13 +2070,13 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Readiness diagnostics and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT and tune freshness windows if needed.</x:v>
+        <x:v>Readiness diagnostics, admin sandbox UAT plan and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT and tune freshness windows if needed.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Both providers report sandboxReady=true and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+        <x:v>Both providers report sandboxReady=true, UAT plan shows READY_FOR_SANDBOX_UAT, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>2</x:v>
       </x:c>
@@ -2073,7 +2090,7 @@
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>3</x:v>
       </x:c>
@@ -2087,7 +2104,7 @@
         <x:v>Stale drivers are excluded from matching and database online state is cleaned in configured batches.</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>4</x:v>
       </x:c>
@@ -2101,7 +2118,7 @@
         <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, and operators can correlate failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>5</x:v>
       </x:c>
@@ -2115,7 +2132,7 @@
         <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>6</x:v>
       </x:c>
@@ -2132,7 +2149,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cda3a78f5bb4262"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1107ea2189fe4f2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2141,10 +2158,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="27.5" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="53.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="58.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="147.8800048828125" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="205.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.380000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -2217,7 +2234,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Fare estimate</x:v>
       </x:c>
@@ -2245,15 +2262,15 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>/api/v1/payments/methods, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Open VNPAY/MoMo checkoutUrl only when enabled, then refresh payment detail after redirect/callback.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Use readiness/UAT plan before exposing VNPAY/MoMo, open checkoutUrl only when enabled, then refresh payment detail after redirect/callback.</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
         <x:v>Partial</x:v>
@@ -2301,7 +2318,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="81" t="str">
         <x:v>Driver navigation</x:v>
       </x:c>
@@ -2315,7 +2332,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="29" t="str">
         <x:v>Error/support flow</x:v>
       </x:c>
@@ -2329,21 +2346,21 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="29" t="str">
         <x:v>Payment sandbox UAT handoff</x:v>
       </x:c>
       <x:c r="B14" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/readiness plus provider webhook callbacks</x:v>
+        <x:v>GET /api/v1/payments/providers/readiness, GET /api/v1/payments/providers/sandbox-uat-plan plus provider webhook callbacks</x:v>
       </x:c>
       <x:c r="C14" s="29" t="str">
-        <x:v>Before exposing MoMo/VNPAY to testers, confirm sandboxReady=true, create checkout, complete/cancel in provider sandbox, then refresh payment detail after redirect/callback.</x:v>
+        <x:v>Before exposing MoMo/VNPAY to testers, confirm sandboxReady=true and UAT plan status READY_FOR_SANDBOX_UAT, register the returned webhook/IPN URL with the provider, create checkout, complete/cancel in sandbox, then refresh payment detail after redirect/callback.</x:v>
       </x:c>
       <x:c r="D14" s="29" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="29" t="str">
         <x:v>Passenger matching/tracking</x:v>
       </x:c>
@@ -2357,7 +2374,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="29" t="str">
         <x:v>Rate limit handling</x:v>
       </x:c>
@@ -2371,7 +2388,7 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="29" t="str">
         <x:v>Observability smoke</x:v>
       </x:c>
@@ -2385,7 +2402,7 @@
         <x:v>Ready for devops</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Driver offer cancellation</x:v>
       </x:c>
@@ -2395,12 +2412,14 @@
       <x:c r="C18" t="str">
         <x:v>On TRIP_CANCELLED/DISMISS: close modal, stop countdown.</x:v>
       </x:c>
-      <x:c r="D18"/>
+      <x:c r="D18" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9caf7624bf90456e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b291a9a9d404cd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2409,13 +2428,13 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="45" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="45" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="57.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="53.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="215.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="136.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="25.5" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="4" t="str">
         <x:v>Risk</x:v>
       </x:c>
@@ -2429,7 +2448,7 @@
         <x:v>Status</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="7" t="str">
         <x:v>Online payment providers are not production-complete.</x:v>
       </x:c>
@@ -2437,13 +2456,13 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP. Use readiness endpoint and service-level signed callback tests before UAT, then enable MoMo/VNPAY only after real sandbox callback validation.</x:v>
+        <x:v>Keep CASH as MVP. Use readiness endpoint, sandbox UAT plan and service-level signed callback tests before UAT, then enable MoMo/VNPAY only after real sandbox callback validation.</x:v>
       </x:c>
       <x:c r="D2" s="13" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>Webhook freshness defaults need sandbox calibration.</x:v>
       </x:c>
@@ -2457,7 +2476,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
@@ -2471,7 +2490,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Heartbeat intervals are not production-calibrated.</x:v>
       </x:c>
@@ -2485,7 +2504,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="str">
         <x:v>Firebase identity still needs staging UAT.</x:v>
       </x:c>
@@ -2499,7 +2518,7 @@
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="52.79999923706055" hidden="0" customHeight="1">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="str">
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
@@ -2507,13 +2526,13 @@
         <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, and GitHub Actions runs the suite on pushes/PRs; real provider sandbox regressions may still slip through.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Reuse the Testcontainers base for provider flows and validate real gateway callbacks before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for provider flows, use the sandbox UAT plan as the handoff checklist, and validate real gateway callbacks before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
         <x:v>Partial</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="29" t="str">
         <x:v>Logs and metrics are still per-instance until deployment wiring is added.</x:v>
       </x:c>
@@ -2527,7 +2546,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="39.599998474121094" hidden="0" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="29" t="str">
         <x:v>In-memory rate limiting is per application instance.</x:v>
       </x:c>
@@ -2541,7 +2560,7 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
         <x:v>Prometheus endpoint exposure needs network controls.</x:v>
       </x:c>
@@ -2558,7 +2577,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refeebf71fa424451"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf039a2180b3b4562"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6d69c56f828b4204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R48178d1a0fd04284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R62d87e41330e464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R2a9c917b75224b4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rbc6b5d3751804d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf4509ff9c6bb4f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb5d67e7b6d524287"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R56bf03f088cd4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rdc4b60782d1b44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R75dba4a9abca4236"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Re919633c536c41b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0231def41e8d4059"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -820,10 +820,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="41" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="7.75" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="111.37999725341797" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="120" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -851,7 +851,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after payment sandbox UAT harness implementation.</x:v>
+        <x:v>Asia/Bangkok status after database release SQL workflow implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -859,13 +859,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/payment-sandbox-uat-harness</x:v>
+        <x:v>feature/database-release-sql-workflow</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds admin/devops UAT checklist endpoint for online payment sandbox validation.</x:v>
+        <x:v>Adds versioned SQL release folders, template, validator and deployment documentation without Flyway.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -873,13 +873,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge prometheus observability metrics</x:v>
+        <x:v>develop after merge payment sandbox UAT harness</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/observability-metrics is merged into develop; OTLP tracing branch is held unmerged.</x:v>
+        <x:v>feature/payment-sandbox-uat-harness is merged and pushed to develop; OTLP tracing branch is held unmerged.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -887,13 +887,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add payment sandbox uat harness</x:v>
+        <x:v>chore: add database release sql workflow</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Prepared on feature branch for user review before merge.</x:v>
+        <x:v>Prepared on feature branch for user review before commit/merge.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -901,13 +901,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>Full ./mvnw.cmd test: pass 354</x:v>
+        <x:v>DB release validator: pass</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>Full suite passed on 2026-06-30; targeted PaymentControllerTests and PaymentSandboxUatPlanServiceTests passed 8 tests.</x:v>
+        <x:v>validate-db-release.ps1 passed for db/releases/0000-template via -ReleasePath and -All. Full Maven suite pending because this branch changes docs/scripts only.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -954,30 +954,30 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
-        <x:v>Payment sandbox UAT harness</x:v>
+        <x:v>Database release SQL workflow</x:v>
       </x:c>
       <x:c r="B10" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
+        <x:v>db/releases + scripts/validate-db-release.ps1</x:v>
       </x:c>
       <x:c r="C10" s="29" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D10" s="29" t="str">
-        <x:v>Admin endpoint reports prerequisites, provider status, callback URLs, missing requirements, FE actions and backend checks without exposing secrets.</x:v>
+        <x:v>Adds manifest/precheck/apply/verify/rollback contract and validator for manual SQL releases without Flyway.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="29" t="str">
-        <x:v>Payment sandbox webhook contracts</x:v>
+        <x:v>Payment sandbox UAT harness</x:v>
       </x:c>
       <x:c r="B11" s="29" t="str">
-        <x:v>Service-level signed MoMo/VNPAY callback coverage</x:v>
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
       </x:c>
       <x:c r="C11" s="29" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D11" s="29" t="str">
-        <x:v>Real merchant sandbox callback UAT remains open.</x:v>
+        <x:v>Merged into develop; real merchant sandbox callback UAT remains open.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -1039,7 +1039,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95087947067b4cb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb15b9a30dde4329"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1052,7 +1052,7 @@
     <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="66.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="7.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="138.3800048828125" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="181" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -1650,10 +1650,27 @@
         <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements, FE actions and backend checks; real merchant sandbox UAT remains open.</x:v>
       </x:c>
     </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>Operations</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Database release SQL workflow without Flyway</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>db/releases, scripts/validate-db-release.ps1, docs/database-release-process.md</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>Adds manifest/precheck/apply/verify/rollback template, release README, deployment process docs and validator for required files, manifest fields, transactional apply SQL and destructive SQL review markers.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc466dce3424b4905"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83184e0ebac43c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1872,7 +1889,7 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="11" t="str">
-        <x:v>P1</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>Database release</x:v>
@@ -1881,13 +1898,13 @@
         <x:v>Define schema release SQL process without Flyway unless policy changes.</x:v>
       </x:c>
       <x:c r="D11" s="7" t="str">
-        <x:v>Release/deployment convention.</x:v>
+        <x:v>Release/deployment convention and db/releases template.</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>Schema changes are reproducible and documented per release.</x:v>
+        <x:v>Schema changes are reproducible through manifest, precheck, apply, verify and rollback SQL, validated before review/deploy.</x:v>
       </x:c>
       <x:c r="F11" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -2033,7 +2050,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b8c5ecacd0b488d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08488bc89e4a456f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2044,8 +2061,8 @@
   <x:cols>
     <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="221.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="174.3800048828125" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="232.1300048828125" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="196" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -2112,10 +2129,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting and Prometheus metrics implemented; log aggregation, distributed tracing, env profiles and release SQL strategy remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting, Prometheus metrics and SQL release workflow are implemented; log aggregation, distributed tracing and environment profiles remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, and operators can correlate failures across instances using request IDs.</x:v>
+        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, SQL releases are reviewable, and operators can correlate failures across instances using request IDs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -2149,7 +2166,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1107ea2189fe4f2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f8f5c85dc5941a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2416,10 +2433,24 @@
         <x:v>Ready for FE</x:v>
       </x:c>
     </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>Database release workflow</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>db/releases/* plus scripts/validate-db-release.ps1</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>No FE runtime API. Devops/backend creates a release folder for schema changes, runs precheck/apply/verify/rollback SQL and validates with the PowerShell script before review/deploy.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Ready for devops</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b291a9a9d404cd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6d05094a494442e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2574,10 +2605,24 @@
         <x:v>Open</x:v>
       </x:c>
     </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>Manual SQL releases can drift without discipline.</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Without Flyway, missed SQL folders or unverified manual changes can desynchronize environments.</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>Require a db/releases folder per schema change, run the validator, archive precheck/verify output and keep production ddl-auto non-mutating.</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>Mitigated</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf039a2180b3b4562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49819e0d517f461e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb5d67e7b6d524287"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R56bf03f088cd4e75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rdc4b60782d1b44bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R75dba4a9abca4236"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Re919633c536c41b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0231def41e8d4059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb459109b97c942cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rf44e7c580360448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R2a2d8d37f5d64602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re537a5cbf9f84e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Ra7c92cc5300e4845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rc9c71e2676144409"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E27" headerRowCount="1">
-  <x:autoFilter ref="A1:E27"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E28" headerRowCount="1">
+  <x:autoFilter ref="A1:E28"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -646,8 +646,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:D17" headerRowCount="1">
-  <x:autoFilter ref="A1:D17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="FrontendTable" displayName="FrontendTable" ref="A1:D20" headerRowCount="1">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -659,8 +658,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:D10" headerRowCount="1">
-  <x:autoFilter ref="A1:D10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="RisksTable" displayName="RisksTable" ref="A1:D12" headerRowCount="1">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -845,13 +843,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="C2" s="26" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after database release SQL workflow implementation.</x:v>
+        <x:v>Asia/Bangkok status after Cloudflare R2 storage provider implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -859,13 +857,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/database-release-sql-workflow</x:v>
+        <x:v>feature/upload-storage</x:v>
       </x:c>
       <x:c r="C3" s="28" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds versioned SQL release folders, template, validator and deployment documentation without Flyway.</x:v>
+        <x:v>Adds local upload storage plus Cloudflare R2/S3-compatible provider for staging/production uploads.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -873,13 +871,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge payment sandbox UAT harness</x:v>
+        <x:v>develop after merge database release SQL workflow</x:v>
       </x:c>
       <x:c r="C4" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/payment-sandbox-uat-harness is merged and pushed to develop; OTLP tracing branch is held unmerged.</x:v>
+        <x:v>feature/database-release-sql-workflow was merged locally into develop before this branch.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -887,7 +885,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>chore: add database release sql workflow</x:v>
+        <x:v>feat: add cloudflare r2 storage provider</x:v>
       </x:c>
       <x:c r="C5" s="96" t="str">
         <x:v>In review</x:v>
@@ -901,13 +899,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>DB release validator: pass</x:v>
+        <x:v>Full Maven suite: pass</x:v>
       </x:c>
       <x:c r="C6" s="26" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>validate-db-release.ps1 passed for db/releases/0000-template via -ReleasePath and -All. Full Maven suite pending because this branch changes docs/scripts only.</x:v>
+        <x:v>./mvnw.cmd test passed 366 tests, 0 failures, 0 errors after Cloudflare R2 provider. Targeted R2/local storage tests passed 8 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -921,7 +919,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Pass on 2026-06-30; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
+        <x:v>Pass on 2026-07-01 after R2 provider changes; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -929,13 +927,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>CodeRabbit CLI missing; remote installer rejected by approval policy</x:v>
+        <x:v>CodeRabbit CLI missing; remote installer needs explicit approval</x:v>
       </x:c>
       <x:c r="C8" s="99" t="str">
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>coderabbit is not in PATH; installer execution was rejected because it would install third-party software on the user machine without explicit approval.</x:v>
+        <x:v>coderabbit is not in PATH; installer execution requires explicit approval before installing third-party software.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -954,44 +952,44 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="29" t="str">
-        <x:v>Database release SQL workflow</x:v>
+        <x:v>Upload storage foundation</x:v>
       </x:c>
       <x:c r="B10" s="29" t="str">
-        <x:v>db/releases + scripts/validate-db-release.ps1</x:v>
+        <x:v>local uploads + Cloudflare R2 provider</x:v>
       </x:c>
       <x:c r="C10" s="29" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D10" s="29" t="str">
-        <x:v>Adds manifest/precheck/apply/verify/rollback contract and validator for manual SQL releases without Flyway.</x:v>
+        <x:v>Local/dev upload storage remains default; R2 provider uploads to Cloudflare when STORAGE_PROVIDER=r2 and CLOUDFLARE_R2_* env vars are set.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="29" t="str">
-        <x:v>Payment sandbox UAT harness</x:v>
+        <x:v>Database release SQL workflow</x:v>
       </x:c>
       <x:c r="B11" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
+        <x:v>db/releases + scripts/validate-db-release.ps1</x:v>
       </x:c>
       <x:c r="C11" s="29" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D11" s="29" t="str">
-        <x:v>Merged into develop; real merchant sandbox callback UAT remains open.</x:v>
+        <x:v>Merged locally into develop; new driver document URL schema change uses db/releases/20260630-driver-document-urls.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="29" t="str">
-        <x:v>Payment readiness diagnostics</x:v>
+        <x:v>Payment sandbox UAT harness</x:v>
       </x:c>
       <x:c r="B12" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/readiness</x:v>
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
       </x:c>
       <x:c r="C12" s="29" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="29" t="str">
-        <x:v>Readiness stays the gate for enabled/sandboxReady online providers.</x:v>
+        <x:v>Merged into develop; real merchant sandbox callback UAT remains open.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -1039,7 +1037,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb15b9a30dde4329"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec74420990347f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1516,19 +1514,19 @@
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="29" t="str">
-        <x:v>Testing</x:v>
+        <x:v>Upload storage</x:v>
       </x:c>
       <x:c r="B28" s="29" t="str">
-        <x:v>Trip completion, tracking fallback and cash payment integration flow</x:v>
+        <x:v>Local upload storage, Cloudflare R2/S3-compatible provider, user avatar upload, driver document upload and driver document URL metadata</x:v>
       </x:c>
       <x:c r="C28" s="29" t="str">
-        <x:v>BookingMatchingRoutingIntegrationTests</x:v>
+        <x:v>POST /api/users/me/avatar; POST /api/v1/uploads/driver-documents/{documentType}; STORAGE_PROVIDER=local|r2</x:v>
       </x:c>
       <x:c r="D28" s="29" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E28" s="29" t="str">
-        <x:v>Runs booking, matching, driver accept/arrived/start/complete, tracking REST fallback, final fare, payment detail/checkout, cash confirmation and driver heartbeat through Testcontainers.</x:v>
+        <x:v>Local/dev provider remains default. R2 provider uploads via S3 API and returns CLOUDFLARE_R2_PUBLIC_BASE_URL + objectKey; staging still needs bucket/API token/domain UAT.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -1670,7 +1668,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf83184e0ebac43c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ae17f6339e443ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1912,19 +1910,19 @@
         <x:v>P2</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Upload storage</x:v>
+        <x:v>Upload storage production UAT</x:v>
       </x:c>
       <x:c r="C12" s="7" t="str">
-        <x:v>Add driver document/avatar upload storage.</x:v>
+        <x:v>Provision Cloudflare R2 bucket/API token/public base URL, set deployment env vars and verify real avatar plus driver document upload/read access.</x:v>
       </x:c>
       <x:c r="D12" s="7" t="str">
-        <x:v>S3-compatible or local dev storage.</x:v>
+        <x:v>Cloudflare account, R2 bucket, API token, custom/public domain or signed URL policy, deployment secrets.</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>Drivers upload files; admins view secure document URLs.</x:v>
+        <x:v>Uploaded files survive redeploys and scale-out; credentials stay outside Git; failed R2 writes return FILE_STORAGE_ERROR; document privacy policy is decided before production.</x:v>
       </x:c>
       <x:c r="F12" s="13" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -2050,7 +2048,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08488bc89e4a456f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8485fa352e464819"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2157,16 +2155,16 @@
         <x:v>Product expansion</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Uploads, messaging, scheduled rides, surge, multi-city, analytics.</x:v>
+        <x:v>Local upload foundation and Cloudflare R2 provider are implemented; finish R2 bucket/domain/secret UAT, then messaging, scheduled rides, surge, multi-city and analytics.</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Roadmap features are ready for separate release planning.</x:v>
+        <x:v>Production upload storage is verified in staging with one avatar and one driver document, credentials are externalized, and document access policy is approved.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f8f5c85dc5941a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc570f667d00c41fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2214,10 +2212,10 @@
         <x:v>Passenger profile</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>/api/users/me</x:v>
+        <x:v>/api/users/me, POST /api/users/me/avatar</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Load/update current user profile.</x:v>
+        <x:v>Load/update current user profile; upload avatar with multipart file and use returned avatarUrl.</x:v>
       </x:c>
       <x:c r="D3" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -2228,10 +2226,10 @@
         <x:v>Driver onboarding</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>/api/v1/drivers/me/profile</x:v>
+        <x:v>POST /api/v1/uploads/driver-documents/{documentType}; /api/v1/drivers/me/profile</x:v>
       </x:c>
       <x:c r="C4" s="7" t="str">
-        <x:v>Submit driver profile/document metadata and show approval status.</x:v>
+        <x:v>Upload PORTRAIT/LICENSE/ID_CARD/VEHICLE_REGISTRATION first, then submit returned URLs in driver profile metadata and show approval status.</x:v>
       </x:c>
       <x:c r="D4" s="17" t="str">
         <x:v>Ready for FE</x:v>
@@ -2421,36 +2419,50 @@
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
-        <x:v>Driver offer cancellation</x:v>
+        <x:v>Upload storage</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>/user/queue/trip-requests</x:v>
+        <x:v>POST /api/users/me/avatar; POST /api/v1/uploads/driver-documents/{PORTRAIT|LICENSE|ID_CARD|VEHICLE_REGISTRATION}</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>On TRIP_CANCELLED/DISMISS: close modal, stop countdown.</x:v>
+        <x:v>Send multipart field file. Use returned avatarUrl/url in profile screens and driver onboarding payload; dev can use /uploads URLs, staging/prod should use returned R2 public-base URL; handle FILE_UPLOAD_INVALID and FILE_STORAGE_ERROR.</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>Ready for FE</x:v>
+        <x:v>Ready for FE/devops</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
+        <x:v>Driver offer cancellation</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>/user/queue/trip-requests</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>On TRIP_CANCELLED/DISMISS: close modal, stop countdown.</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
         <x:v>Database release workflow</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B20" t="str">
         <x:v>db/releases/* plus scripts/validate-db-release.ps1</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C20" t="str">
         <x:v>No FE runtime API. Devops/backend creates a release folder for schema changes, runs precheck/apply/verify/rollback SQL and validates with the PowerShell script before review/deploy.</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D20" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6d05094a494442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a2dee4b12614448"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2619,10 +2631,24 @@
         <x:v>Mitigated</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>R2 deployment config is not yet exercised.</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Upload code supports Cloudflare R2, but missing bucket/domain/API token config blocks startup when STORAGE_PROVIDER=r2 and document privacy policy is not finalized.</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Create R2 bucket/API token outside Git, set CLOUDFLARE_R2_* env vars, verify one avatar and one driver document in staging, and add signed URL/proxy access if documents must stay private.</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49819e0d517f461e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f0c57e7f1a4e68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rf027800bb47b4d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd5189a83f63a4b20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R883873bce04740a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R0e2d54e4b6d9446e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R65d4d2eca76e41a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rae12283ea7ad4df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6391d6b2480f4a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc9fbd1b2cd0d4717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rbffd401d6ba94817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R9790e2178e5c4b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R29bab0b3c73e4516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf355561b220548a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -764,8 +764,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D11" headerRowCount="1">
-  <x:autoFilter ref="A1:D11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D12" headerRowCount="1" totalsRowCount="0">
+  <x:autoFilter ref="A1:D12"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -777,8 +777,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E28" headerRowCount="1">
-  <x:autoFilter ref="A1:E28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:E29" headerRowCount="1" totalsRowCount="0">
+  <x:autoFilter ref="A1:E29"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -1020,13 +1020,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="C2" s="109" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after scheduled ride implementation.</x:v>
+        <x:v>Asia/Bangkok status after scheduled rides merge and payment sandbox evidence implementation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -1034,13 +1034,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/scheduled-rides</x:v>
+        <x:v>feature/payment-sandbox-e2e</x:v>
       </x:c>
       <x:c r="C3" s="110" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds future pickup scheduling and delayed dispatch into the existing matching flow.</x:v>
+        <x:v>Adds persisted sandbox UAT evidence and readyForFrontendExposure gating for online payment exposure.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
@@ -1048,13 +1048,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge in-trip messaging</x:v>
+        <x:v>develop after merge scheduled rides</x:v>
       </x:c>
       <x:c r="C4" s="111" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/in-trip-messaging was merged locally into develop before this branch.</x:v>
+        <x:v>feature/scheduled-rides was committed and merged locally into develop before this branch.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
@@ -1062,7 +1062,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add scheduled ride dispatch</x:v>
+        <x:v>feat: add payment sandbox uat evidence</x:v>
       </x:c>
       <x:c r="C5" s="112" t="str">
         <x:v>In review</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>./mvnw.cmd test passed 383 tests, 0 failures, 0 errors. Targeted scheduled ride tests passed 24 tests.</x:v>
+        <x:v>./mvnw.cmd test passed 390 tests, 0 failures, 0 errors. Context + payment targeted tests passed 22 tests.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
@@ -1096,7 +1096,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Pass on 2026-07-04 after scheduled rides changes; Git only reported LF/CRLF normalization warning on Windows.</x:v>
+        <x:v>Pass on 2026-07-05 after payment sandbox evidence changes; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
@@ -1110,7 +1110,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="7" t="str">
-        <x:v>coderabbit is not in PATH; official installer supports Linux/macOS and WSL cannot launch /bin/bash on this machine.</x:v>
+        <x:v>coderabbit is not in PATH; CLI review could not run in this environment.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
@@ -1157,16 +1157,16 @@
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="29" t="str">
-        <x:v>Payment sandbox UAT harness</x:v>
+        <x:v>Payment sandbox UAT evidence</x:v>
       </x:c>
       <x:c r="B12" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
+        <x:v>GET/PUT provider UAT result endpoints</x:v>
       </x:c>
       <x:c r="C12" s="117" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D12" s="29" t="str">
-        <x:v>Merged into develop; real merchant sandbox callback UAT remains open.</x:v>
+        <x:v>Admin can persist PASSED/BLOCKED/FAILED/NOT_RUN evidence; FE should expose online methods only when readyForFrontendExposure=true.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
@@ -1208,7 +1208,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>Backend harness is ready; external sandbox accounts and public callback URLs are still required.</x:v>
+        <x:v>Backend readiness, UAT plan and evidence gate are ready; external sandbox accounts and public callback URLs are still required.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1233,10 +1233,10 @@
         <x:v>future pickup time + dispatch scheduler</x:v>
       </x:c>
       <x:c r="C17" s="121" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D17" t="str">
-        <x:v>POST /api/v1/bookings accepts scheduledPickupTime; scheduler opens matching at configured lead time.</x:v>
+        <x:v>Committed as feat: add scheduled ride dispatch and merged locally into develop.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1247,16 +1247,16 @@
         <x:v>db/releases/20260704-scheduled-rides</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D18" t="str">
-        <x:v>Adds trips.scheduled_pickup_time and dispatch index with manifest/precheck/apply/verify/rollback.</x:v>
+        <x:v>Schema release was validated and merged with scheduled rides.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab89a6b8cc484055"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80825b3bc82941d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1753,19 +1753,19 @@
     </x:row>
     <x:row r="29" ht="15" customHeight="1">
       <x:c r="A29" t="str">
-        <x:v>Matching</x:v>
+        <x:v>Payment</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>Cancel dismisses active driver offer</x:v>
+        <x:v>Payment sandbox UAT evidence and FE exposure gate</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>/api/v1/bookings/{tripId}/cancel; /user/queue/trip-requests</x:v>
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-results; PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result</x:v>
       </x:c>
       <x:c r="D29" s="121" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Event clears Redis offer lock and sends TRIP_CANCELLED/DISMISS.</x:v>
+        <x:v>Persists admin sandbox evidence per provider; PASSED requires sandboxReady plus checkout, success, failure, replay and freshness checks.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" customHeight="1">
@@ -1864,10 +1864,10 @@
         <x:v>GET /api/v1/payments/providers/sandbox-uat-plan</x:v>
       </x:c>
       <x:c r="D35" s="121" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements, FE actions and backend checks; real merchant sandbox UAT remains open.</x:v>
+        <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements and scenarios.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" customHeight="1">
@@ -1898,10 +1898,10 @@
         <x:v>GET/POST /api/v1/trips/{tripId}/messages; SEND /app/trip.message; /topic/trip/{tripId}/messages</x:v>
       </x:c>
       <x:c r="D37" s="121" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>Only passenger and assigned driver can send during ACCEPTED/ARRIVED/IN_PROGRESS. Admin can view/subscribe for support. SQL release 20260701-trip-messages included.</x:v>
+        <x:v>Only passenger and assigned driver can send during ACCEPTED/ARRIVED/IN_PROGRESS. Admin can view/subscribe for support. SQL release 20260701-trip-messages is merged.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1915,16 +1915,16 @@
         <x:v>POST /api/v1/bookings; internal ScheduledRideDispatchScheduler</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E38" t="str">
-        <x:v>scheduledPickupTime creates SCHEDULED trips; scheduler moves them to SEARCHING at dispatch lead time, broadcasts status, and publishes BookingCreatedEvent for normal matching.</x:v>
+        <x:v>scheduledPickupTime creates SCHEDULED trips; scheduler moves them to SEARCHING at dispatch lead time, broadcasts status, and publishes BookingCreatedEvent for matching.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re66904ce97054c1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9af93d6903c432a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1971,13 +1971,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Finish real MoMo/VNPAY sandbox merchant UAT; backend readiness, sandbox UAT plan and service-level signed callback contract coverage are in place.</x:v>
+        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT; backend readiness, UAT plan, service-level signed callback coverage and persisted evidence gate are in place.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint and UAT plan endpoint.</x:v>
+        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint and UAT result endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Both providers return usable checkout URLs and real sandbox success/failure callbacks reconcile internal payment/trip state. Current backend harness/contract tests do not replace provider-hosted callback UAT.</x:v>
+        <x:v>Both providers return usable checkout URLs, real sandbox success/failure callbacks reconcile internal payment/trip state, and admin evidence is PASSED with all required checks.</x:v>
       </x:c>
       <x:c r="F2" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2031,13 +2031,13 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs; service-level success/failure/stale callback coverage and admin UAT plan are implemented.</x:v>
+        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs and persist evidence through the admin UAT result endpoint.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Sandbox callback examples, merchant test accounts and public HTTPS backend URL.</x:v>
+        <x:v>Sandbox callback examples, merchant test accounts, public HTTPS backend URL and provider webhook/IPN registration.</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; signed sandbox payloads map to internal payment states.</x:v>
+        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; success/failure/replay/freshness checks are marked passed.</x:v>
       </x:c>
       <x:c r="F5" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2200,7 +2200,7 @@
         <x:v>Only trip participants can send messages during ACCEPTED/ARRIVED/IN_PROGRESS; authorized users can load history and subscribe to /topic/trip/{tripId}/messages.</x:v>
       </x:c>
       <x:c r="F13" s="125" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
@@ -2220,7 +2220,7 @@
         <x:v>Passenger can create SCHEDULED ride; backend dispatches to SEARCHING at configured lead time; FE handles scheduled waiting state.</x:v>
       </x:c>
       <x:c r="F14" s="122" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
@@ -2306,7 +2306,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f8c8e301e8e4ba3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3ad02dea79b423c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2340,17 +2340,17 @@
       <x:c r="H1" s="137"/>
     </x:row>
     <x:row r="2" ht="15" customHeight="1">
-      <x:c r="A2" s="7" t="n">
+      <x:c r="A2" s="7" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Readiness diagnostics, admin sandbox UAT plan and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT and tune freshness windows if needed.</x:v>
+        <x:v>Readiness diagnostics, admin sandbox UAT plan, persisted UAT evidence and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Both providers report sandboxReady=true, UAT plan shows READY_FOR_SANDBOX_UAT, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
+        <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
@@ -2426,7 +2426,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80789db21e034990"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad7cf588158b44d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2548,10 +2548,10 @@
         <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="7" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Use readiness/UAT plan before exposing VNPAY/MoMo, open checkoutUrl only when enabled, then refresh payment detail after redirect/callback.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Expose VNPAY/MoMo only when method metadata is enabled and UAT result readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D8" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2632,13 +2632,13 @@
         <x:v>Payment sandbox UAT handoff</x:v>
       </x:c>
       <x:c r="B14" s="29" t="str">
-        <x:v>GET /api/v1/payments/providers/readiness, GET /api/v1/payments/providers/sandbox-uat-plan plus provider webhook callbacks</x:v>
+        <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result</x:v>
       </x:c>
       <x:c r="C14" s="29" t="str">
-        <x:v>Before exposing MoMo/VNPAY to testers, confirm sandboxReady=true and UAT plan status READY_FOR_SANDBOX_UAT, register the returned webhook/IPN URL with the provider, create checkout, complete/cancel in sandbox, then refresh payment detail after redirect/callback.</x:v>
+        <x:v>Admin/devops records sandbox evidence after testing checkout URL, success/failure callbacks, duplicate replay and freshness rejection. FE/admin dashboard can gate online methods on readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D14" s="126" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Ready for FE/devops</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
@@ -2756,7 +2756,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6a16f85dcae49cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf556e2b216d643ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2794,10 +2794,10 @@
         <x:v>Online payment providers are not production-complete.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation.</x:v>
+        <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation evidence.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Keep CASH as MVP. Use readiness endpoint, sandbox UAT plan and service-level signed callback tests before UAT, then enable MoMo/VNPAY only after real sandbox callback validation.</x:v>
+        <x:v>Keep CASH as MVP. Use readiness, UAT plan, service-level signed callback tests and persisted UAT result records; expose MoMo/VNPAY only when readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D2" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2811,7 +2811,7 @@
         <x:v>The configurable 24-hour age and 5-minute future-skew defaults have not been validated against real merchant retries.</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
-        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox before tuning provider-specific freshness windows.</x:v>
+        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox and record freshness/replay evidence before tuning provider windows.</x:v>
       </x:c>
       <x:c r="D3" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2864,10 +2864,10 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, and GitHub Actions runs the suite on pushes/PRs; real provider sandbox regressions may still slip through.</x:v>
+        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, but real provider callbacks still need external UAT.</x:v>
       </x:c>
       <x:c r="C7" s="7" t="str">
-        <x:v>Reuse the Testcontainers base for provider flows, use the sandbox UAT plan as the handoff checklist, and validate real gateway callbacks before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for provider-adjacent checks, use readiness/UAT evidence endpoints as the handoff gate, and validate real gateway callbacks before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="123" t="str">
         <x:v>Partial</x:v>
@@ -2974,7 +2974,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c02254330a041f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84f3ca89d3f4521"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6391d6b2480f4a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rc9fbd1b2cd0d4717"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rbffd401d6ba94817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R9790e2178e5c4b1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R29bab0b3c73e4516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf355561b220548a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Radd229d7b9114a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R2985d2f482234045"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rcd00c768ec5b4743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R623f5dd3047e4303"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R43f47fd99f334e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R7a0b15acafb54c34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -764,8 +764,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D12" headerRowCount="1" totalsRowCount="0">
-  <x:autoFilter ref="A1:D12"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:D13" headerRowCount="1" totalsRowCount="0">
+  <x:autoFilter ref="A1:D13"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -1020,56 +1020,72 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="C2" s="109" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asia/Bangkok status after scheduled rides merge and payment sandbox evidence implementation.</x:v>
-      </x:c>
+        <x:v>Asia/Bangkok status after user review and local structured logging commit preparation.</x:v>
+      </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>feature/payment-sandbox-e2e</x:v>
+        <x:v>feature/structured-logging</x:v>
       </x:c>
       <x:c r="C3" s="110" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>Adds persisted sandbox UAT evidence and readyForFrontendExposure gating for online payment exposure.</x:v>
-      </x:c>
+        <x:v>Adds optional Spring Boot structured stdout logs plus request completion MDC fields for collector search/correlation.</x:v>
+      </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="7" t="str">
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>develop after merge scheduled rides</x:v>
+        <x:v>develop after merge payment sandbox evidence</x:v>
       </x:c>
       <x:c r="C4" s="111" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>feature/scheduled-rides was committed and merged locally into develop before this branch.</x:v>
-      </x:c>
+        <x:v>feature/payment-sandbox-e2e was committed and merged locally into develop before this branch.</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="7" t="str">
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>feat: add payment sandbox uat evidence</x:v>
+        <x:v>feat: add structured logging context</x:v>
       </x:c>
       <x:c r="C5" s="112" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Prepared on feature branch for user review before commit/merge.</x:v>
-      </x:c>
+        <x:v>User reviewed on 2026-07-07; commit is created locally on the feature branch before merge/push.</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -1082,8 +1098,12 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="7" t="str">
-        <x:v>./mvnw.cmd test passed 390 tests, 0 failures, 0 errors. Context + payment targeted tests passed 22 tests.</x:v>
-      </x:c>
+        <x:v>./mvnw.cmd test passed 391 tests, 0 failures, 0 errors. Targeted RequestCorrelationFilterTests passed 4 tests. LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash smoke passed 3 tests and produced JSON MDC logs.</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="7" t="str">
@@ -1096,8 +1116,12 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="7" t="str">
-        <x:v>Pass on 2026-07-05 after payment sandbox evidence changes; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
-      </x:c>
+        <x:v>Pass before commit; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="7" t="str">
@@ -1112,6 +1136,10 @@
       <x:c r="D8" s="7" t="str">
         <x:v>coderabbit is not in PATH; CLI review could not run in this environment.</x:v>
       </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="7" t="str">
@@ -1126,6 +1154,10 @@
       <x:c r="D9" s="7" t="str">
         <x:v>Keep environment-specific local changes uncommitted.</x:v>
       </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="29" t="str">
@@ -1140,6 +1172,10 @@
       <x:c r="D10" s="29" t="str">
         <x:v>Merged locally into develop via merge: upload storage cloudflare r2. R2 staging UAT still needs bucket/API token/domain.</x:v>
       </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="29" t="str">
@@ -1154,6 +1190,10 @@
       <x:c r="D11" s="29" t="str">
         <x:v>Merged locally into develop; scheduled ride schema change uses db/releases/20260704-scheduled-rides.</x:v>
       </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="29" t="str">
@@ -1163,11 +1203,15 @@
         <x:v>GET/PUT provider UAT result endpoints</x:v>
       </x:c>
       <x:c r="C12" s="117" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="29" t="str">
-        <x:v>Admin can persist PASSED/BLOCKED/FAILED/NOT_RUN evidence; FE should expose online methods only when readyForFrontendExposure=true.</x:v>
-      </x:c>
+        <x:v>Committed as feat: add payment sandbox UAT evidence and merged locally into develop via merge: payment sandbox uat evidence.</x:v>
+      </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" t="str">
@@ -1180,8 +1224,12 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D13" t="str">
-        <x:v>Merged into develop before this feature branch.</x:v>
-      </x:c>
+        <x:v>Merged into develop before structured logging branch.</x:v>
+      </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="A14" t="str">
@@ -1196,6 +1244,10 @@
       <x:c r="D14" t="str">
         <x:v>Implemented on a separate branch but intentionally not merged into develop yet.</x:v>
       </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
       <x:c r="A15" t="str">
@@ -1210,6 +1262,10 @@
       <x:c r="D15" t="str">
         <x:v>Backend readiness, UAT plan and evidence gate are ready; external sandbox accounts and public callback URLs are still required.</x:v>
       </x:c>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -1224,6 +1280,10 @@
       <x:c r="D16" t="str">
         <x:v>Merged locally into develop via merge: in-trip messaging.</x:v>
       </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -1238,6 +1298,10 @@
       <x:c r="D17" t="str">
         <x:v>Committed as feat: add scheduled ride dispatch and merged locally into develop.</x:v>
       </x:c>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -1252,11 +1316,15 @@
       <x:c r="D18" t="str">
         <x:v>Schema release was validated and merged with scheduled rides.</x:v>
       </x:c>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80825b3bc82941d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7d5984ef20f452c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1308,6 +1376,9 @@
       <x:c r="E2" s="7" t="str">
         <x:v>Ready for FE auth session flow.</x:v>
       </x:c>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="7" t="str">
@@ -1325,6 +1396,9 @@
       <x:c r="E3" s="7" t="str">
         <x:v>Supports profile page and admin account management.</x:v>
       </x:c>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -1342,6 +1416,9 @@
       <x:c r="E4" s="7" t="str">
         <x:v>Redis availability is integrated with matching.</x:v>
       </x:c>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -1359,6 +1436,9 @@
       <x:c r="E5" s="7" t="str">
         <x:v>Static configurable pricing is in place.</x:v>
       </x:c>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -1376,6 +1456,9 @@
       <x:c r="E6" s="7" t="str">
         <x:v>Passenger booking flow is wired to trip/matching.</x:v>
       </x:c>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="7" t="str">
@@ -1393,6 +1476,9 @@
       <x:c r="E7" s="7" t="str">
         <x:v>Final fare can use tracking history.</x:v>
       </x:c>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="7" t="str">
@@ -1410,6 +1496,9 @@
       <x:c r="E8" s="7" t="str">
         <x:v>Uses Redis GEO/availability data; passenger cancellation clears active matching state/driver lock and sends TRIP_CANCELLED/DISMISS to the offered driver.</x:v>
       </x:c>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="7" t="str">
@@ -1427,6 +1516,9 @@
       <x:c r="E9" s="7" t="str">
         <x:v>Trip subscriptions are protected.</x:v>
       </x:c>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="7" t="str">
@@ -1444,6 +1536,9 @@
       <x:c r="E10" s="7" t="str">
         <x:v>Latest location stored in Redis.</x:v>
       </x:c>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="7" t="str">
@@ -1461,6 +1556,9 @@
       <x:c r="E11" s="7" t="str">
         <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
       </x:c>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="7" t="str">
@@ -1478,6 +1576,9 @@
       <x:c r="E12" s="7" t="str">
         <x:v>FE can render CASH/MOMO/VNPAY availability; online methods require provider registration, enabled config, and provider-specific required fields.</x:v>
       </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" s="7" t="str">
@@ -1495,6 +1596,9 @@
       <x:c r="E13" s="7" t="str">
         <x:v>Prevents duplicate trip ratings.</x:v>
       </x:c>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="A14" s="7" t="str">
@@ -1512,6 +1616,9 @@
       <x:c r="E14" s="7" t="str">
         <x:v>FCM stays disabled by default; enabled deployments use ADC or mounted service-account file and fail startup clearly when credentials are invalid.</x:v>
       </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
       <x:c r="A15" s="7" t="str">
@@ -1529,6 +1636,9 @@
       <x:c r="E15" s="7" t="str">
         <x:v>Operational admin views can be built.</x:v>
       </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16" ht="15" customHeight="1">
       <x:c r="A16" s="7" t="str">
@@ -1546,6 +1656,9 @@
       <x:c r="E16" s="7" t="str">
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17" ht="15" customHeight="1">
       <x:c r="A17" s="29" t="str">
@@ -1563,6 +1676,9 @@
       <x:c r="E17" s="29" t="str">
         <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18" ht="15" customHeight="1">
       <x:c r="A18" s="71" t="str">
@@ -1580,6 +1696,9 @@
       <x:c r="E18" s="71" t="str">
         <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" s="29" t="str">
@@ -1597,6 +1716,9 @@
       <x:c r="E19" s="29" t="str">
         <x:v>Runs register, JWT-protected request, refresh rotation, logout revocation, and duplicate-phone rejection through HTTP, JPA, and Redis.</x:v>
       </x:c>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20" ht="15" customHeight="1">
       <x:c r="A20" s="55" t="str">
@@ -1614,6 +1736,9 @@
       <x:c r="E20" s="55" t="str">
         <x:v>Validates assigned driver and trip status; returns destination, distance/duration, GeoJSON LineString, and OSRM maneuver steps.</x:v>
       </x:c>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21" ht="15" customHeight="1">
       <x:c r="A21" s="81" t="str">
@@ -1631,6 +1756,9 @@
       <x:c r="E21" s="81" t="str">
         <x:v>Refreshes GEO/meta/status TTL without overwriting BUSY; scheduled batch marks stale database profiles offline.</x:v>
       </x:c>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22" ht="15" customHeight="1">
       <x:c r="A22" s="29" t="str">
@@ -1648,23 +1776,29 @@
       <x:c r="E22" s="29" t="str">
         <x:v>Runs booking creation, Redis offer matching, driver acceptance, pickup route, arrival transition, and dropoff route through HTTP/JWT/PostGIS/Redis with a local OSRM boundary.</x:v>
       </x:c>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
     </x:row>
     <x:row r="23" ht="15" customHeight="1">
       <x:c r="A23" s="29" t="str">
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="B23" s="29" t="str">
-        <x:v>HTTP request correlation and centralized error logging</x:v>
+        <x:v>HTTP request correlation, structured stdout logging and centralized error logging</x:v>
       </x:c>
       <x:c r="C23" s="29" t="str">
-        <x:v>X-Request-Id on all REST endpoints</x:v>
+        <x:v>X-Request-Id, LOGGING_STRUCTURED_FORMAT_CONSOLE, APP_ENV, APP_VERSION</x:v>
       </x:c>
       <x:c r="D23" s="117" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E23" s="29" t="str">
-        <x:v>Returns request ID in header/error body; logs method, path, status, duration, error code, and 5xx stack traces without bodies or secrets.</x:v>
-      </x:c>
+        <x:v>Completion logs include requestId, http.request.method, url.path, http.response.status_code and event.duration_ms; JSON stdout verified via LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash smoke test.</x:v>
+      </x:c>
+      <x:c r="F23"/>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
     </x:row>
     <x:row r="24" ht="15" customHeight="1">
       <x:c r="A24" s="29" t="str">
@@ -1682,6 +1816,9 @@
       <x:c r="E24" s="29" t="str">
         <x:v>Covers signed MoMo success, signed VNPAY failure, and stale callback rejection through the service dispatch layer.</x:v>
       </x:c>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
     </x:row>
     <x:row r="25" ht="15" customHeight="1">
       <x:c r="A25" s="29" t="str">
@@ -1699,6 +1836,9 @@
       <x:c r="E25" s="29" t="str">
         <x:v>Initial no-candidate booking remains SEARCHING; driver online/heartbeat retries unmatched searching trips and dispatches offer when a candidate is available.</x:v>
       </x:c>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
     </x:row>
     <x:row r="26" ht="15" customHeight="1">
       <x:c r="A26" s="29" t="str">
@@ -1716,6 +1856,9 @@
       <x:c r="E26" s="29" t="str">
         <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds. Merged before current branch.</x:v>
       </x:c>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
     </x:row>
     <x:row r="27" ht="15" customHeight="1">
       <x:c r="A27" s="29" t="str">
@@ -1733,6 +1876,9 @@
       <x:c r="E27" s="29" t="str">
         <x:v>Exposes standard HTTP metrics, common application tag, request histogram config, and custom rate-limit allowed/rejected counters plus bucket gauge. Merged into develop.</x:v>
       </x:c>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
     </x:row>
     <x:row r="28" ht="15" customHeight="1">
       <x:c r="A28" s="29" t="str">
@@ -1750,6 +1896,9 @@
       <x:c r="E28" s="29" t="str">
         <x:v>Local/dev provider remains default. R2 provider uploads via S3 API and returns CLOUDFLARE_R2_PUBLIC_BASE_URL + objectKey; staging still needs bucket/API token/domain UAT.</x:v>
       </x:c>
+      <x:c r="F28"/>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
     </x:row>
     <x:row r="29" ht="15" customHeight="1">
       <x:c r="A29" t="str">
@@ -1762,11 +1911,14 @@
         <x:v>GET /api/v1/payments/providers/sandbox-uat-results; PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result</x:v>
       </x:c>
       <x:c r="D29" s="121" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Persists admin sandbox evidence per provider; PASSED requires sandboxReady plus checkout, success, failure, replay and freshness checks.</x:v>
-      </x:c>
+        <x:v>Persists admin sandbox evidence per provider; PASSED requires sandboxReady plus checkout, success, failure, replay and freshness checks. Merged into develop.</x:v>
+      </x:c>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
     </x:row>
     <x:row r="30" ht="15" customHeight="1">
       <x:c r="A30" t="str">
@@ -1784,6 +1936,9 @@
       <x:c r="E30" t="str">
         <x:v>Registers user, verifies Redis token CRUD, lists inbox, marks read.</x:v>
       </x:c>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
     </x:row>
     <x:row r="31" ht="15" customHeight="1">
       <x:c r="A31" t="str">
@@ -1801,6 +1956,9 @@
       <x:c r="E31" t="str">
         <x:v>Covers forbidden passenger access, pending driver approval, pricing CRUD, admin trips and dashboard.</x:v>
       </x:c>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
     </x:row>
     <x:row r="32" ht="15" customHeight="1">
       <x:c r="A32" s="102" t="str">
@@ -1818,6 +1976,9 @@
       <x:c r="E32" s="102" t="str">
         <x:v>Runs on push to main/develop/feature branches and PRs to main/develop using Java 17, Maven cache, Docker check and ./mvnw test.</x:v>
       </x:c>
+      <x:c r="F32"/>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
     </x:row>
     <x:row r="33" ht="15" customHeight="1">
       <x:c r="A33" s="105" t="str">
@@ -1835,6 +1996,9 @@
       <x:c r="E33" s="105" t="str">
         <x:v>Endpoints are public; readiness includes readinessState, db and redis; liveness includes livenessState only; health details are hidden.</x:v>
       </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
     </x:row>
     <x:row r="34" ht="15" customHeight="1">
       <x:c r="A34" s="108" t="str">
@@ -1852,6 +2016,9 @@
       <x:c r="E34" s="108" t="str">
         <x:v>Defaults allow common localhost origins; production can override origins/patterns, methods, headers, exposed headers, credentials and max-age via env vars.</x:v>
       </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
     </x:row>
     <x:row r="35" ht="15" customHeight="1">
       <x:c r="A35" t="str">
@@ -1869,6 +2036,9 @@
       <x:c r="E35" t="str">
         <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements and scenarios.</x:v>
       </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35"/>
+      <x:c r="H35"/>
     </x:row>
     <x:row r="36" ht="15" customHeight="1">
       <x:c r="A36" t="str">
@@ -1886,6 +2056,9 @@
       <x:c r="E36" t="str">
         <x:v>Adds manifest/precheck/apply/verify/rollback template, release README, deployment process docs and validator for required files, manifest fields, transactional apply SQL and destructive SQL review markers.</x:v>
       </x:c>
+      <x:c r="F36"/>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str">
@@ -1903,6 +2076,9 @@
       <x:c r="E37" t="str">
         <x:v>Only passenger and assigned driver can send during ACCEPTED/ARRIVED/IN_PROGRESS. Admin can view/subscribe for support. SQL release 20260701-trip-messages is merged.</x:v>
       </x:c>
+      <x:c r="F37"/>
+      <x:c r="G37"/>
+      <x:c r="H37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str">
@@ -1920,11 +2096,14 @@
       <x:c r="E38" t="str">
         <x:v>scheduledPickupTime creates SCHEDULED trips; scheduler moves them to SEARCHING at dispatch lead time, broadcasts status, and publishes BookingCreatedEvent for matching.</x:v>
       </x:c>
+      <x:c r="F38"/>
+      <x:c r="G38"/>
+      <x:c r="H38"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9af93d6903c432a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2581740a00044f2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1982,6 +2161,8 @@
       <x:c r="F2" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="116" t="str">
@@ -2002,6 +2183,8 @@
       <x:c r="F3" s="116" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="114" t="str">
@@ -2022,6 +2205,8 @@
       <x:c r="F4" s="114" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="122" t="str">
@@ -2042,6 +2227,8 @@
       <x:c r="F5" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="114" t="str">
@@ -2062,6 +2249,8 @@
       <x:c r="F6" s="114" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="114" t="str">
@@ -2082,6 +2271,8 @@
       <x:c r="F7" s="114" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="114" t="str">
@@ -2102,6 +2293,8 @@
       <x:c r="F8" s="114" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="123" t="str">
@@ -2122,6 +2315,8 @@
       <x:c r="F9" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="123" t="str">
@@ -2131,7 +2326,7 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="7" t="str">
-        <x:v>Request correlation, centralized error logging, configurable CORS, health/readiness, basic rate limiting and Prometheus metrics are implemented; add centralized log shipping plus distributed tracing backend.</x:v>
+        <x:v>Request correlation, structured stdout logging, centralized error logging, configurable CORS, health/readiness, basic rate limiting and Prometheus metrics are implemented; add deployment collector dashboards plus distributed tracing backend.</x:v>
       </x:c>
       <x:c r="D10" s="7" t="str">
         <x:v>Deployment platform, log aggregation and tracing/observability stack.</x:v>
@@ -2142,6 +2337,8 @@
       <x:c r="F10" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="116" t="str">
@@ -2162,6 +2359,8 @@
       <x:c r="F11" s="116" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="124" t="str">
@@ -2182,6 +2381,8 @@
       <x:c r="F12" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" s="116" t="str">
@@ -2202,6 +2403,8 @@
       <x:c r="F13" s="125" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="A14" s="124" t="str">
@@ -2222,6 +2425,8 @@
       <x:c r="F14" s="122" t="str">
         <x:v>Done</x:v>
       </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
       <x:c r="A15" s="124" t="str">
@@ -2242,6 +2447,8 @@
       <x:c r="F15" s="122" t="str">
         <x:v>Open</x:v>
       </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16" ht="15" customHeight="1">
       <x:c r="A16" s="124" t="str">
@@ -2262,6 +2469,8 @@
       <x:c r="F16" s="122" t="str">
         <x:v>Open</x:v>
       </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17" ht="15" customHeight="1">
       <x:c r="A17" s="124" t="str">
@@ -2282,6 +2491,8 @@
       <x:c r="F17" s="122" t="str">
         <x:v>Open</x:v>
       </x:c>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18" ht="15" customHeight="1">
       <x:c r="A18" s="126" t="str">
@@ -2302,11 +2513,13 @@
       <x:c r="F18" s="126" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3ad02dea79b423c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d815ff47a93414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2352,6 +2565,10 @@
       <x:c r="D2" s="7" t="str">
         <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
       </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="7" t="str">
@@ -2366,6 +2583,10 @@
       <x:c r="D3" s="7" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -2380,6 +2601,10 @@
       <x:c r="D4" s="7" t="str">
         <x:v>Stale drivers are excluded from matching and database online state is cleaned in configured batches.</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -2389,11 +2614,15 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting, Prometheus metrics and SQL release workflow are implemented; log aggregation, distributed tracing and environment profiles remain.</x:v>
+        <x:v>Firebase secure credential loading, HTTP request correlation, structured stdout logging, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting, Prometheus metrics and SQL release workflow are implemented; collector dashboards, distributed tracing and environment profiles remain.</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, SQL releases are reviewable, and operators can correlate failures across instances using request IDs.</x:v>
-      </x:c>
+        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, SQL releases are reviewable, and operators can search request IDs across structured logs.</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -2408,6 +2637,10 @@
       <x:c r="D6" s="7" t="str">
         <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="7" t="str">
@@ -2422,11 +2655,15 @@
       <x:c r="D7" s="7" t="str">
         <x:v>Production upload storage is verified in staging; scheduled rides dispatch reliably at lead time; remaining expansion items are prioritized separately.</x:v>
       </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad7cf588158b44d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30eaa216fcf14860"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2472,6 +2709,10 @@
       <x:c r="D2" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="7" t="str">
@@ -2486,6 +2727,10 @@
       <x:c r="D3" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -2500,6 +2745,10 @@
       <x:c r="D4" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -2514,6 +2763,10 @@
       <x:c r="D5" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -2528,6 +2781,10 @@
       <x:c r="D6" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="7" t="str">
@@ -2542,6 +2799,10 @@
       <x:c r="D7" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="7" t="str">
@@ -2556,6 +2817,10 @@
       <x:c r="D8" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="7" t="str">
@@ -2570,6 +2835,10 @@
       <x:c r="D9" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="7" t="str">
@@ -2584,6 +2853,10 @@
       <x:c r="D10" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" s="7" t="str">
@@ -2598,6 +2871,10 @@
       <x:c r="D11" s="116" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12" ht="15" customHeight="1">
       <x:c r="A12" s="81" t="str">
@@ -2612,6 +2889,10 @@
       <x:c r="D12" s="127" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13" ht="15" customHeight="1">
       <x:c r="A13" s="29" t="str">
@@ -2626,6 +2907,10 @@
       <x:c r="D13" s="117" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14" ht="15" customHeight="1">
       <x:c r="A14" s="29" t="str">
@@ -2640,6 +2925,10 @@
       <x:c r="D14" s="126" t="str">
         <x:v>Ready for FE/devops</x:v>
       </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
     <x:row r="15" ht="15" customHeight="1">
       <x:c r="A15" s="29" t="str">
@@ -2654,6 +2943,10 @@
       <x:c r="D15" s="117" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
     </x:row>
     <x:row r="16" ht="15" customHeight="1">
       <x:c r="A16" s="29" t="str">
@@ -2668,20 +2961,28 @@
       <x:c r="D16" s="117" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
     </x:row>
     <x:row r="17" ht="15" customHeight="1">
       <x:c r="A17" s="29" t="str">
         <x:v>Observability smoke</x:v>
       </x:c>
       <x:c r="B17" s="29" t="str">
-        <x:v>/actuator, /actuator/metrics, /actuator/prometheus</x:v>
+        <x:v>/actuator, /actuator/metrics, /actuator/prometheus, stdout logs with LOGGING_STRUCTURED_FORMAT_CONSOLE</x:v>
       </x:c>
       <x:c r="C17" s="29" t="str">
-        <x:v>Devops scrapes Prometheus and checks http.server.requests, goride.rate.limit.requests and goride.rate.limit.buckets; keep endpoints behind trusted network controls in production.</x:v>
+        <x:v>Devops scrapes Prometheus and checks http.server.requests, goride.rate.limit.*, and JSON logs with requestId/http.request.method/url.path/http.response.status_code/event.duration_ms when LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash|ecs|gelf.</x:v>
       </x:c>
       <x:c r="D17" s="117" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
     </x:row>
     <x:row r="18" ht="15" customHeight="1">
       <x:c r="A18" t="str">
@@ -2696,6 +2997,10 @@
       <x:c r="D18" s="118" t="str">
         <x:v>Ready for FE/devops</x:v>
       </x:c>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
     </x:row>
     <x:row r="19" ht="15" customHeight="1">
       <x:c r="A19" t="str">
@@ -2710,6 +3015,10 @@
       <x:c r="D19" s="118" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str">
@@ -2724,6 +3033,10 @@
       <x:c r="D20" s="118" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str">
@@ -2738,6 +3051,10 @@
       <x:c r="D21" s="118" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str">
@@ -2752,11 +3069,15 @@
       <x:c r="D22" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf556e2b216d643ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc086c4f5ea4c4a35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2802,6 +3123,10 @@
       <x:c r="D2" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="7" t="str">
@@ -2816,6 +3141,10 @@
       <x:c r="D3" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+      <x:c r="G3"/>
+      <x:c r="H3"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
       <x:c r="A4" s="7" t="str">
@@ -2830,6 +3159,10 @@
       <x:c r="D4" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
     </x:row>
     <x:row r="5" ht="15" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -2844,6 +3177,10 @@
       <x:c r="D5" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
     </x:row>
     <x:row r="6" ht="15" customHeight="1">
       <x:c r="A6" s="7" t="str">
@@ -2858,6 +3195,10 @@
       <x:c r="D6" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
     </x:row>
     <x:row r="7" ht="15" customHeight="1">
       <x:c r="A7" s="7" t="str">
@@ -2872,20 +3213,28 @@
       <x:c r="D7" s="123" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
     </x:row>
     <x:row r="8" ht="15" customHeight="1">
       <x:c r="A8" s="29" t="str">
         <x:v>Logs and metrics are still per-instance until deployment wiring is added.</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
-        <x:v>Request IDs, health probes, Prometheus metrics and 429 throttling improve diagnosis, but logs/metrics can still be fragmented across replicas.</x:v>
+        <x:v>Structured JSON stdout logs, request IDs, health probes, Prometheus metrics and 429 throttling improve diagnosis, but data can still be fragmented across replicas without a collector.</x:v>
       </x:c>
       <x:c r="C8" s="29" t="str">
-        <x:v>Ship stdout logs centrally, scrape each instance from Prometheus or the platform collector, and add retention/search/alert dashboards before production scaling.</x:v>
+        <x:v>Enable LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash or platform-preferred format, ship stdout centrally, scrape each instance and add retention/search/alert dashboards before production scaling.</x:v>
       </x:c>
       <x:c r="D8" s="128" t="str">
-        <x:v>Open</x:v>
-      </x:c>
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
     </x:row>
     <x:row r="9" ht="15" customHeight="1">
       <x:c r="A9" s="29" t="str">
@@ -2900,6 +3249,10 @@
       <x:c r="D9" s="128" t="str">
         <x:v>Open</x:v>
       </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="29" t="str">
@@ -2914,6 +3267,10 @@
       <x:c r="D10" s="128" t="str">
         <x:v>Open</x:v>
       </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
     </x:row>
     <x:row r="11" ht="15" customHeight="1">
       <x:c r="A11" t="str">
@@ -2928,6 +3285,10 @@
       <x:c r="D11" t="str">
         <x:v>Mitigated</x:v>
       </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -2942,6 +3303,10 @@
       <x:c r="D12" s="120" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -2956,6 +3321,10 @@
       <x:c r="D13" s="120" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -2970,11 +3339,15 @@
       <x:c r="D14" t="str">
         <x:v>Partial</x:v>
       </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84f3ca89d3f4521"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51e1c39a7f094821"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6d9462b1382d4875"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R73644f8695e3407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R45fcd0bf543047a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rd4634d9b1c4d47dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R2a72d1c8f82f4b4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R62f49b9383e24a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2873ee8366cf4d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rf640d7a74ad348ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R00c4dbf25ad94b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1149aca96e024552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6747c739cf5d419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb1ccde8ed80a4359"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -393,8 +393,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H39" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H39"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H40"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -444,8 +444,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H24"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -461,8 +461,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H16"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -701,13 +701,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Asia/Bangkok status after structured logging merge and surge pricing implementation on feature branch.</x:v>
+        <x:v>Feature freeze and product-readiness hardening snapshot for APP_ENV production startup guardrails.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -719,13 +719,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/surge-pricing-rules</x:v>
+        <x:v>hardening/product-readiness-guardrails</x:v>
       </x:c>
       <x:c r="C3" s="66" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>User reviewed on 2026-07-08; ready to commit locally as feat: add surge pricing rules.</x:v>
+        <x:v>No new product feature development; branch focuses on go-product backend readiness.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -737,13 +737,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>develop after merge structured logging context</x:v>
+        <x:v>develop at 78cc0a9 merge: surge pricing rules</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>feature/structured-logging was reviewed, committed and merged locally into develop via merge: structured logging context.</x:v>
+        <x:v>develop includes backend implementation through surge pricing; service-area WIP is paused in stash.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -755,13 +755,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add surge pricing rules</x:v>
+        <x:v>chore: add production readiness guardrails</x:v>
       </x:c>
       <x:c r="C5" s="66" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Created after user review on 2026-07-08; not merged to develop yet.</x:v>
+        <x:v>Awaiting user review before commit/merge; not pushed.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -773,13 +773,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted surge pricing suite: pass</x:v>
+        <x:v>Full Maven suite: pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>./mvnw.cmd "-Dtest=BookingServiceTests,SurgePricingServiceTests,TripCompletionFareServiceTests,PricingConfigTests" test passed 23 tests; db release validator passed.</x:v>
+        <x:v>./mvnw.cmd test passed 403 tests; targeted ProductionReadinessValidatorTests passed 6 tests; context-test repair suite passed 7 tests after clean.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -797,7 +797,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Pass after docs/workbook updates; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
+        <x:v>Pass after code/docs/workbook updates; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -1005,7 +1005,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22c7be056b9a4725"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec04f970f0c4b4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1801,10 +1801,30 @@
       <x:c r="G39" s="27" t="str"/>
       <x:c r="H39" s="28" t="str"/>
     </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>Production readiness</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Startup guardrails for unsafe production config</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>APP_ENV/app.environment, JWT_SECRET, CORS_ALLOWED_ORIGINS, STORAGE_PROVIDER, spring.jpa.hibernate.ddl-auto</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>Fails startup when production still uses dev JWT secret, mutating Hibernate DDL, local storage, localhost/wildcard CORS or incomplete R2 config.</x:v>
+      </x:c>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf4f810005604255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5aaf762f800440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2027,13 +2047,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>Request correlation, structured stdout logging, centralized error logging, configurable CORS, health/readiness, basic rate limiting and Prometheus metrics are implemented; add deployment collector dashboards plus distributed tracing backend.</x:v>
+        <x:v>Startup guardrails are in review; finish deployment collector dashboards, alerts, distributed tracing decision and staging env validation.</x:v>
       </x:c>
       <x:c r="D10" s="24" t="str">
-        <x:v>Deployment platform, log aggregation and tracing/observability stack.</x:v>
+        <x:v>Deployment platform, log aggregation, tracing/observability stack and staging secret/config management.</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>Logs, metrics and traces are correlated across instances; dashboards and alerts cover health, latency, 5xx, throttling and dependency readiness.</x:v>
+        <x:v>APP_ENV=production starts only with safe secrets/CORS/storage/DDL config; logs/metrics/probes are centrally visible with actionable alerts.</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2220,7 +2240,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53e2eaa0f92d4285"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbef06a52f044b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2315,10 +2335,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Firebase secure credential loading, HTTP request correlation, structured stdout logging, centralized application error logging, configurable CORS allowlist, Actuator health/readiness, basic API rate limiting, Prometheus metrics and SQL release workflow are implemented; collector dashboards, distributed tracing and environment profiles remain.</x:v>
+        <x:v>Firebase secure credential loading, request correlation, structured stdout logging, centralized error logging, CORS allowlist, rate limiting, Prometheus metrics, Actuator probes, SQL release workflow and startup guardrails are implemented; finish collector dashboards, tracing decision and staging env UAT.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Staging loads secrets safely, FE origins are allowlisted, probes report readiness, abusive bursts return documented 429 responses, Prometheus scrapes app metrics, SQL releases are reviewable, and operators can search request IDs across structured logs.</x:v>
+        <x:v>Staging boots with APP_ENV=production using safe secrets, R2, non-mutating DDL and production FE/admin origins; probes/metrics/logs are monitored and unsafe config fails before traffic.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -2364,7 +2384,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e99d62f2854c4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ae7becda7e45c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2793,10 +2813,28 @@
       <x:c r="G23" s="27" t="str"/>
       <x:c r="H23" s="28" t="str"/>
     </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>Production startup guardrails</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>No FE runtime API; deployment env uses APP_ENV, JWT_SECRET, CORS_ALLOWED_ORIGINS, STORAGE_PROVIDER, CLOUDFLARE_R2_* and ddl-auto</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>FE does not change request contracts. Web/admin production origins must be in CORS allowlist; if backend fails startup with Production readiness check failed, fix deployment env before FE smoke.</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>Ready for devops</x:v>
+      </x:c>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb686c7e738414776"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec0cb2e99964341"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3081,10 +3119,28 @@
       <x:c r="G15" s="27" t="str"/>
       <x:c r="H15" s="28" t="str"/>
     </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Unsafe production config blocks startup.</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Deployments using APP_ENV=production with local JWT secret, ddl-auto update/create, local uploads, localhost/wildcard CORS or incomplete R2 config will fail before serving traffic.</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>Prepare env vars in staging first, keep APP_ENV=local for dev, and use the startup failure message as a deployment checklist.</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>Mitigated in review</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8561bbf1f72d44c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2d257f84b4143e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2873ee8366cf4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rf640d7a74ad348ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R00c4dbf25ad94b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R1149aca96e024552"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R6747c739cf5d419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb1ccde8ed80a4359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfac2c4bd90d74b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R1a817aec81b74c04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R6829d08ae4fb4402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re2d5491e8ade4e07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb223bbd1495d4fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rfe1b3e7625d14158"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -185,7 +185,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -367,6 +367,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -393,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H41"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -444,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H25"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -461,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H17"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -701,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Feature freeze and product-readiness hardening snapshot for APP_ENV production startup guardrails.</x:v>
+        <x:v>Product-feature completion snapshot for service area / multi-city foundation.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -719,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>hardening/product-readiness-guardrails</x:v>
-      </x:c>
-      <x:c r="C3" s="66" t="str">
+        <x:v>feature/service-area-zones</x:v>
+      </x:c>
+      <x:c r="C3" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>No new product feature development; branch focuses on go-product backend readiness.</x:v>
+        <x:v>Feature branch focuses on service area polygons and booking geofence validation; production API docs hardening is paused in stash.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -737,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>develop at 78cc0a9 merge: surge pricing rules</x:v>
+        <x:v>develop at 10e5159 merge: production readiness guardrails</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>develop includes backend implementation through surge pricing; service-area WIP is paused in stash.</x:v>
+        <x:v>develop includes backend implementation through production readiness guardrails; merged into this feature branch.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -755,9 +758,9 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>chore: add production readiness guardrails</x:v>
-      </x:c>
-      <x:c r="C5" s="66" t="str">
+        <x:v>feat: add service area zones</x:v>
+      </x:c>
+      <x:c r="C5" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -779,7 +782,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>./mvnw.cmd test passed 403 tests; targeted ProductionReadinessValidatorTests passed 6 tests; context-test repair suite passed 7 tests after clean.</x:v>
+        <x:v>./mvnw.cmd test passed 416 tests; targeted ServiceAreaServiceTests + BookingServiceTests passed 25 tests; SQL release validator passed.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -791,13 +794,13 @@
         <x:v>Diff hygiene</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>git diff --check: pass</x:v>
-      </x:c>
-      <x:c r="C7" s="65" t="str">
+        <x:v>git diff --cached --check: pass</x:v>
+      </x:c>
+      <x:c r="C7" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Pass after code/docs/workbook updates; Git only reported LF/CRLF normalization warnings on Windows.</x:v>
+        <x:v>Staged diff hygiene passed after docs/workbook update; local application.yml remains intentionally uncommitted.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -815,7 +818,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>coderabbit is not in PATH; CLI review could not run in this environment.</x:v>
+        <x:v>coderabbit is not in PATH; local review fallback used.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1005,7 +1008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ec04f970f0c4b4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b514ebacf341e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1037,9 +1040,9 @@
       <x:c r="E1" s="39" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="F1" s="39" t="str"/>
-      <x:c r="G1" s="39" t="str"/>
-      <x:c r="H1" s="40" t="str"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="40"/>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="23" t="str">
@@ -1057,9 +1060,9 @@
       <x:c r="E2" s="24" t="str">
         <x:v>Ready for FE auth session flow.</x:v>
       </x:c>
-      <x:c r="F2" s="24" t="str"/>
-      <x:c r="G2" s="24" t="str"/>
-      <x:c r="H2" s="25" t="str"/>
+      <x:c r="F2" s="24"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="25"/>
     </x:row>
     <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="23" t="str">
@@ -1077,9 +1080,9 @@
       <x:c r="E3" s="24" t="str">
         <x:v>Supports profile page and admin account management.</x:v>
       </x:c>
-      <x:c r="F3" s="24" t="str"/>
-      <x:c r="G3" s="24" t="str"/>
-      <x:c r="H3" s="25" t="str"/>
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="25"/>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="23" t="str">
@@ -1097,9 +1100,9 @@
       <x:c r="E4" s="24" t="str">
         <x:v>Redis availability is integrated with matching.</x:v>
       </x:c>
-      <x:c r="F4" s="24" t="str"/>
-      <x:c r="G4" s="24" t="str"/>
-      <x:c r="H4" s="25" t="str"/>
+      <x:c r="F4" s="24"/>
+      <x:c r="G4" s="24"/>
+      <x:c r="H4" s="25"/>
     </x:row>
     <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="23" t="str">
@@ -1111,15 +1114,15 @@
       <x:c r="C5" s="24" t="str">
         <x:v>/api/v1/bookings/estimate, /api/v1/pricing, /api/v1/admin/pricing, /api/v1/admin/pricing/surge-rules, /api/v1/admin/pricing/surge-status</x:v>
       </x:c>
-      <x:c r="D5" s="66" t="str">
+      <x:c r="D5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str">
         <x:v>Reviewed by user; demand/supply surge rules, baseFare/surgeAmount multipliers and fareSurgeMultiplier snapshot are ready on feature branch.</x:v>
       </x:c>
-      <x:c r="F5" s="24" t="str"/>
-      <x:c r="G5" s="24" t="str"/>
-      <x:c r="H5" s="25" t="str"/>
+      <x:c r="F5" s="24"/>
+      <x:c r="G5" s="24"/>
+      <x:c r="H5" s="25"/>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="23" t="str">
@@ -1137,9 +1140,9 @@
       <x:c r="E6" s="24" t="str">
         <x:v>Passenger booking flow is wired to trip/matching.</x:v>
       </x:c>
-      <x:c r="F6" s="24" t="str"/>
-      <x:c r="G6" s="24" t="str"/>
-      <x:c r="H6" s="25" t="str"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="25"/>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="23" t="str">
@@ -1157,9 +1160,9 @@
       <x:c r="E7" s="24" t="str">
         <x:v>Final fare can use tracking history.</x:v>
       </x:c>
-      <x:c r="F7" s="24" t="str"/>
-      <x:c r="G7" s="24" t="str"/>
-      <x:c r="H7" s="25" t="str"/>
+      <x:c r="F7" s="24"/>
+      <x:c r="G7" s="24"/>
+      <x:c r="H7" s="25"/>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="23" t="str">
@@ -1177,9 +1180,9 @@
       <x:c r="E8" s="24" t="str">
         <x:v>Uses Redis GEO/availability data; passenger cancellation clears active matching state/driver lock and sends TRIP_CANCELLED/DISMISS to the offered driver.</x:v>
       </x:c>
-      <x:c r="F8" s="24" t="str"/>
-      <x:c r="G8" s="24" t="str"/>
-      <x:c r="H8" s="25" t="str"/>
+      <x:c r="F8" s="24"/>
+      <x:c r="G8" s="24"/>
+      <x:c r="H8" s="25"/>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="23" t="str">
@@ -1197,9 +1200,9 @@
       <x:c r="E9" s="24" t="str">
         <x:v>Trip subscriptions are protected.</x:v>
       </x:c>
-      <x:c r="F9" s="24" t="str"/>
-      <x:c r="G9" s="24" t="str"/>
-      <x:c r="H9" s="25" t="str"/>
+      <x:c r="F9" s="24"/>
+      <x:c r="G9" s="24"/>
+      <x:c r="H9" s="25"/>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="23" t="str">
@@ -1217,9 +1220,9 @@
       <x:c r="E10" s="24" t="str">
         <x:v>Latest location stored in Redis.</x:v>
       </x:c>
-      <x:c r="F10" s="24" t="str"/>
-      <x:c r="G10" s="24" t="str"/>
-      <x:c r="H10" s="25" t="str"/>
+      <x:c r="F10" s="24"/>
+      <x:c r="G10" s="24"/>
+      <x:c r="H10" s="25"/>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="23" t="str">
@@ -1237,9 +1240,9 @@
       <x:c r="E11" s="24" t="str">
         <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
       </x:c>
-      <x:c r="F11" s="24" t="str"/>
-      <x:c r="G11" s="24" t="str"/>
-      <x:c r="H11" s="25" t="str"/>
+      <x:c r="F11" s="24"/>
+      <x:c r="G11" s="24"/>
+      <x:c r="H11" s="25"/>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="23" t="str">
@@ -1257,9 +1260,9 @@
       <x:c r="E12" s="24" t="str">
         <x:v>FE can render CASH/MOMO/VNPAY availability; online methods require provider registration, enabled config, and provider-specific required fields.</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="str"/>
-      <x:c r="G12" s="24" t="str"/>
-      <x:c r="H12" s="25" t="str"/>
+      <x:c r="F12" s="24"/>
+      <x:c r="G12" s="24"/>
+      <x:c r="H12" s="25"/>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="23" t="str">
@@ -1277,9 +1280,9 @@
       <x:c r="E13" s="24" t="str">
         <x:v>Prevents duplicate trip ratings.</x:v>
       </x:c>
-      <x:c r="F13" s="24" t="str"/>
-      <x:c r="G13" s="24" t="str"/>
-      <x:c r="H13" s="25" t="str"/>
+      <x:c r="F13" s="24"/>
+      <x:c r="G13" s="24"/>
+      <x:c r="H13" s="25"/>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="23" t="str">
@@ -1297,9 +1300,9 @@
       <x:c r="E14" s="24" t="str">
         <x:v>FCM stays disabled by default; enabled deployments use ADC or mounted service-account file and fail startup clearly when credentials are invalid.</x:v>
       </x:c>
-      <x:c r="F14" s="24" t="str"/>
-      <x:c r="G14" s="24" t="str"/>
-      <x:c r="H14" s="25" t="str"/>
+      <x:c r="F14" s="24"/>
+      <x:c r="G14" s="24"/>
+      <x:c r="H14" s="25"/>
     </x:row>
     <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="23" t="str">
@@ -1317,9 +1320,9 @@
       <x:c r="E15" s="24" t="str">
         <x:v>Operational admin views can be built.</x:v>
       </x:c>
-      <x:c r="F15" s="24" t="str"/>
-      <x:c r="G15" s="24" t="str"/>
-      <x:c r="H15" s="25" t="str"/>
+      <x:c r="F15" s="24"/>
+      <x:c r="G15" s="24"/>
+      <x:c r="H15" s="25"/>
     </x:row>
     <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="23" t="str">
@@ -1337,9 +1340,9 @@
       <x:c r="E16" s="24" t="str">
         <x:v>Docs track backend delivery and FE contracts.</x:v>
       </x:c>
-      <x:c r="F16" s="24" t="str"/>
-      <x:c r="G16" s="24" t="str"/>
-      <x:c r="H16" s="25" t="str"/>
+      <x:c r="F16" s="24"/>
+      <x:c r="G16" s="24"/>
+      <x:c r="H16" s="25"/>
     </x:row>
     <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="23" t="str">
@@ -1357,9 +1360,9 @@
       <x:c r="E17" s="24" t="str">
         <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
-      <x:c r="F17" s="24" t="str"/>
-      <x:c r="G17" s="24" t="str"/>
-      <x:c r="H17" s="25" t="str"/>
+      <x:c r="F17" s="24"/>
+      <x:c r="G17" s="24"/>
+      <x:c r="H17" s="25"/>
     </x:row>
     <x:row r="18" ht="46" customHeight="1">
       <x:c r="A18" s="23" t="str">
@@ -1377,9 +1380,9 @@
       <x:c r="E18" s="24" t="str">
         <x:v>Uses routed meter/second values for estimates, configurable timeout and Haversine fallback; final fare remains based on actual tracking history.</x:v>
       </x:c>
-      <x:c r="F18" s="24" t="str"/>
-      <x:c r="G18" s="24" t="str"/>
-      <x:c r="H18" s="25" t="str"/>
+      <x:c r="F18" s="24"/>
+      <x:c r="G18" s="24"/>
+      <x:c r="H18" s="25"/>
     </x:row>
     <x:row r="19" ht="46" customHeight="1">
       <x:c r="A19" s="23" t="str">
@@ -1397,9 +1400,9 @@
       <x:c r="E19" s="24" t="str">
         <x:v>Runs register, JWT-protected request, refresh rotation, logout revocation, and duplicate-phone rejection through HTTP, JPA, and Redis.</x:v>
       </x:c>
-      <x:c r="F19" s="24" t="str"/>
-      <x:c r="G19" s="24" t="str"/>
-      <x:c r="H19" s="25" t="str"/>
+      <x:c r="F19" s="24"/>
+      <x:c r="G19" s="24"/>
+      <x:c r="H19" s="25"/>
     </x:row>
     <x:row r="20" ht="46" customHeight="1">
       <x:c r="A20" s="23" t="str">
@@ -1417,9 +1420,9 @@
       <x:c r="E20" s="24" t="str">
         <x:v>Validates assigned driver and trip status; returns destination, distance/duration, GeoJSON LineString, and OSRM maneuver steps.</x:v>
       </x:c>
-      <x:c r="F20" s="24" t="str"/>
-      <x:c r="G20" s="24" t="str"/>
-      <x:c r="H20" s="25" t="str"/>
+      <x:c r="F20" s="24"/>
+      <x:c r="G20" s="24"/>
+      <x:c r="H20" s="25"/>
     </x:row>
     <x:row r="21" ht="46" customHeight="1">
       <x:c r="A21" s="23" t="str">
@@ -1437,9 +1440,9 @@
       <x:c r="E21" s="24" t="str">
         <x:v>Refreshes GEO/meta/status TTL without overwriting BUSY; scheduled batch marks stale database profiles offline.</x:v>
       </x:c>
-      <x:c r="F21" s="24" t="str"/>
-      <x:c r="G21" s="24" t="str"/>
-      <x:c r="H21" s="25" t="str"/>
+      <x:c r="F21" s="24"/>
+      <x:c r="G21" s="24"/>
+      <x:c r="H21" s="25"/>
     </x:row>
     <x:row r="22" ht="46" customHeight="1">
       <x:c r="A22" s="23" t="str">
@@ -1457,9 +1460,9 @@
       <x:c r="E22" s="24" t="str">
         <x:v>Runs booking creation, Redis offer matching, driver acceptance, pickup route, arrival transition, and dropoff route through HTTP/JWT/PostGIS/Redis with a local OSRM boundary.</x:v>
       </x:c>
-      <x:c r="F22" s="24" t="str"/>
-      <x:c r="G22" s="24" t="str"/>
-      <x:c r="H22" s="25" t="str"/>
+      <x:c r="F22" s="24"/>
+      <x:c r="G22" s="24"/>
+      <x:c r="H22" s="25"/>
     </x:row>
     <x:row r="23" ht="46" customHeight="1">
       <x:c r="A23" s="23" t="str">
@@ -1477,9 +1480,9 @@
       <x:c r="E23" s="24" t="str">
         <x:v>Completion logs include requestId, http.request.method, url.path, http.response.status_code and event.duration_ms; JSON stdout verified via LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash smoke test.</x:v>
       </x:c>
-      <x:c r="F23" s="24" t="str"/>
-      <x:c r="G23" s="24" t="str"/>
-      <x:c r="H23" s="25" t="str"/>
+      <x:c r="F23" s="24"/>
+      <x:c r="G23" s="24"/>
+      <x:c r="H23" s="25"/>
     </x:row>
     <x:row r="24" ht="46" customHeight="1">
       <x:c r="A24" s="23" t="str">
@@ -1497,9 +1500,9 @@
       <x:c r="E24" s="24" t="str">
         <x:v>Covers signed MoMo success, signed VNPAY failure, and stale callback rejection through the service dispatch layer.</x:v>
       </x:c>
-      <x:c r="F24" s="24" t="str"/>
-      <x:c r="G24" s="24" t="str"/>
-      <x:c r="H24" s="25" t="str"/>
+      <x:c r="F24" s="24"/>
+      <x:c r="G24" s="24"/>
+      <x:c r="H24" s="25"/>
     </x:row>
     <x:row r="25" ht="46" customHeight="1">
       <x:c r="A25" s="23" t="str">
@@ -1517,9 +1520,9 @@
       <x:c r="E25" s="24" t="str">
         <x:v>Initial no-candidate booking remains SEARCHING; driver online/heartbeat retries unmatched searching trips and dispatches offer when a candidate is available.</x:v>
       </x:c>
-      <x:c r="F25" s="24" t="str"/>
-      <x:c r="G25" s="24" t="str"/>
-      <x:c r="H25" s="25" t="str"/>
+      <x:c r="F25" s="24"/>
+      <x:c r="G25" s="24"/>
+      <x:c r="H25" s="25"/>
     </x:row>
     <x:row r="26" ht="46" customHeight="1">
       <x:c r="A26" s="23" t="str">
@@ -1537,9 +1540,9 @@
       <x:c r="E26" s="24" t="str">
         <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds. Merged before current branch.</x:v>
       </x:c>
-      <x:c r="F26" s="24" t="str"/>
-      <x:c r="G26" s="24" t="str"/>
-      <x:c r="H26" s="25" t="str"/>
+      <x:c r="F26" s="24"/>
+      <x:c r="G26" s="24"/>
+      <x:c r="H26" s="25"/>
     </x:row>
     <x:row r="27" ht="46" customHeight="1">
       <x:c r="A27" s="23" t="str">
@@ -1557,9 +1560,9 @@
       <x:c r="E27" s="24" t="str">
         <x:v>Exposes standard HTTP metrics, common application tag, request histogram config, and custom rate-limit allowed/rejected counters plus bucket gauge. Merged into develop.</x:v>
       </x:c>
-      <x:c r="F27" s="24" t="str"/>
-      <x:c r="G27" s="24" t="str"/>
-      <x:c r="H27" s="25" t="str"/>
+      <x:c r="F27" s="24"/>
+      <x:c r="G27" s="24"/>
+      <x:c r="H27" s="25"/>
     </x:row>
     <x:row r="28" ht="46" customHeight="1">
       <x:c r="A28" s="23" t="str">
@@ -1577,9 +1580,9 @@
       <x:c r="E28" s="24" t="str">
         <x:v>Local/dev provider remains default. R2 provider uploads via S3 API and returns CLOUDFLARE_R2_PUBLIC_BASE_URL + objectKey; staging still needs bucket/API token/domain UAT.</x:v>
       </x:c>
-      <x:c r="F28" s="24" t="str"/>
-      <x:c r="G28" s="24" t="str"/>
-      <x:c r="H28" s="25" t="str"/>
+      <x:c r="F28" s="24"/>
+      <x:c r="G28" s="24"/>
+      <x:c r="H28" s="25"/>
     </x:row>
     <x:row r="29" ht="46" customHeight="1">
       <x:c r="A29" s="23" t="str">
@@ -1597,9 +1600,9 @@
       <x:c r="E29" s="24" t="str">
         <x:v>Persists admin sandbox evidence per provider; PASSED requires sandboxReady plus checkout, success, failure, replay and freshness checks. Merged into develop.</x:v>
       </x:c>
-      <x:c r="F29" s="24" t="str"/>
-      <x:c r="G29" s="24" t="str"/>
-      <x:c r="H29" s="25" t="str"/>
+      <x:c r="F29" s="24"/>
+      <x:c r="G29" s="24"/>
+      <x:c r="H29" s="25"/>
     </x:row>
     <x:row r="30" ht="46" customHeight="1">
       <x:c r="A30" s="23" t="str">
@@ -1617,9 +1620,9 @@
       <x:c r="E30" s="24" t="str">
         <x:v>Registers user, verifies Redis token CRUD, lists inbox, marks read.</x:v>
       </x:c>
-      <x:c r="F30" s="24" t="str"/>
-      <x:c r="G30" s="24" t="str"/>
-      <x:c r="H30" s="25" t="str"/>
+      <x:c r="F30" s="24"/>
+      <x:c r="G30" s="24"/>
+      <x:c r="H30" s="25"/>
     </x:row>
     <x:row r="31" ht="46" customHeight="1">
       <x:c r="A31" s="23" t="str">
@@ -1637,9 +1640,9 @@
       <x:c r="E31" s="24" t="str">
         <x:v>Covers forbidden passenger access, pending driver approval, pricing CRUD, admin trips and dashboard.</x:v>
       </x:c>
-      <x:c r="F31" s="24" t="str"/>
-      <x:c r="G31" s="24" t="str"/>
-      <x:c r="H31" s="25" t="str"/>
+      <x:c r="F31" s="24"/>
+      <x:c r="G31" s="24"/>
+      <x:c r="H31" s="25"/>
     </x:row>
     <x:row r="32" ht="46" customHeight="1">
       <x:c r="A32" s="23" t="str">
@@ -1657,9 +1660,9 @@
       <x:c r="E32" s="24" t="str">
         <x:v>Runs on push to main/develop/feature branches and PRs to main/develop using Java 17, Maven cache, Docker check and ./mvnw test.</x:v>
       </x:c>
-      <x:c r="F32" s="24" t="str"/>
-      <x:c r="G32" s="24" t="str"/>
-      <x:c r="H32" s="25" t="str"/>
+      <x:c r="F32" s="24"/>
+      <x:c r="G32" s="24"/>
+      <x:c r="H32" s="25"/>
     </x:row>
     <x:row r="33" ht="46" customHeight="1">
       <x:c r="A33" s="23" t="str">
@@ -1677,9 +1680,9 @@
       <x:c r="E33" s="24" t="str">
         <x:v>Endpoints are public; readiness includes readinessState, db and redis; liveness includes livenessState only; health details are hidden.</x:v>
       </x:c>
-      <x:c r="F33" s="24" t="str"/>
-      <x:c r="G33" s="24" t="str"/>
-      <x:c r="H33" s="25" t="str"/>
+      <x:c r="F33" s="24"/>
+      <x:c r="G33" s="24"/>
+      <x:c r="H33" s="25"/>
     </x:row>
     <x:row r="34" ht="46" customHeight="1">
       <x:c r="A34" s="23" t="str">
@@ -1697,9 +1700,9 @@
       <x:c r="E34" s="24" t="str">
         <x:v>Defaults allow common localhost origins; production can override origins/patterns, methods, headers, exposed headers, credentials and max-age via env vars.</x:v>
       </x:c>
-      <x:c r="F34" s="24" t="str"/>
-      <x:c r="G34" s="24" t="str"/>
-      <x:c r="H34" s="25" t="str"/>
+      <x:c r="F34" s="24"/>
+      <x:c r="G34" s="24"/>
+      <x:c r="H34" s="25"/>
     </x:row>
     <x:row r="35" ht="46" customHeight="1">
       <x:c r="A35" s="23" t="str">
@@ -1717,9 +1720,9 @@
       <x:c r="E35" s="24" t="str">
         <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements and scenarios.</x:v>
       </x:c>
-      <x:c r="F35" s="24" t="str"/>
-      <x:c r="G35" s="24" t="str"/>
-      <x:c r="H35" s="25" t="str"/>
+      <x:c r="F35" s="24"/>
+      <x:c r="G35" s="24"/>
+      <x:c r="H35" s="25"/>
     </x:row>
     <x:row r="36" ht="46" customHeight="1">
       <x:c r="A36" s="23" t="str">
@@ -1737,9 +1740,9 @@
       <x:c r="E36" s="24" t="str">
         <x:v>Adds manifest/precheck/apply/verify/rollback template, release README, deployment process docs and validator for required files, manifest fields, transactional apply SQL and destructive SQL review markers.</x:v>
       </x:c>
-      <x:c r="F36" s="24" t="str"/>
-      <x:c r="G36" s="24" t="str"/>
-      <x:c r="H36" s="25" t="str"/>
+      <x:c r="F36" s="24"/>
+      <x:c r="G36" s="24"/>
+      <x:c r="H36" s="25"/>
     </x:row>
     <x:row r="37" ht="46" customHeight="1">
       <x:c r="A37" s="23" t="str">
@@ -1757,9 +1760,9 @@
       <x:c r="E37" s="24" t="str">
         <x:v>Only passenger and assigned driver can send during ACCEPTED/ARRIVED/IN_PROGRESS. Admin can view/subscribe for support. SQL release 20260701-trip-messages is merged.</x:v>
       </x:c>
-      <x:c r="F37" s="24" t="str"/>
-      <x:c r="G37" s="24" t="str"/>
-      <x:c r="H37" s="25" t="str"/>
+      <x:c r="F37" s="24"/>
+      <x:c r="G37" s="24"/>
+      <x:c r="H37" s="25"/>
     </x:row>
     <x:row r="38" ht="46" customHeight="1">
       <x:c r="A38" s="23" t="str">
@@ -1777,9 +1780,9 @@
       <x:c r="E38" s="24" t="str">
         <x:v>scheduledPickupTime creates SCHEDULED trips; scheduler moves them to SEARCHING at dispatch lead time, broadcasts status, and publishes BookingCreatedEvent for matching.</x:v>
       </x:c>
-      <x:c r="F38" s="24" t="str"/>
-      <x:c r="G38" s="24" t="str"/>
-      <x:c r="H38" s="25" t="str"/>
+      <x:c r="F38" s="24"/>
+      <x:c r="G38" s="24"/>
+      <x:c r="H38" s="25"/>
     </x:row>
     <x:row r="39" ht="46" customHeight="1">
       <x:c r="A39" s="26" t="str">
@@ -1791,40 +1794,60 @@
       <x:c r="C39" s="27" t="str">
         <x:v>db/releases/20260707-surge-pricing-rules</x:v>
       </x:c>
-      <x:c r="D39" s="67" t="str">
+      <x:c r="D39" s="58" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E39" s="27" t="str">
         <x:v>Reviewed by user; adds trips.fare_surge_multiplier plus surge_pricing_rules with validated precheck/apply/verify/rollback files.</x:v>
       </x:c>
-      <x:c r="F39" s="27" t="str"/>
-      <x:c r="G39" s="27" t="str"/>
-      <x:c r="H39" s="28" t="str"/>
+      <x:c r="F39" s="27"/>
+      <x:c r="G39" s="27"/>
+      <x:c r="H39" s="28"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" t="str">
+      <x:c r="A40" s="68" t="str">
         <x:v>Production readiness</x:v>
       </x:c>
-      <x:c r="B40" t="str">
+      <x:c r="B40" s="68" t="str">
         <x:v>Startup guardrails for unsafe production config</x:v>
       </x:c>
-      <x:c r="C40" t="str">
+      <x:c r="C40" s="68" t="str">
         <x:v>APP_ENV/app.environment, JWT_SECRET, CORS_ALLOWED_ORIGINS, STORAGE_PROVIDER, spring.jpa.hibernate.ddl-auto</x:v>
       </x:c>
-      <x:c r="D40" t="str">
+      <x:c r="D40" s="68" t="str">
         <x:v>In review</x:v>
       </x:c>
-      <x:c r="E40" t="str">
+      <x:c r="E40" s="68" t="str">
         <x:v>Fails startup when production still uses dev JWT secret, mutating Hibernate DDL, local storage, localhost/wildcard CORS or incomplete R2 config.</x:v>
       </x:c>
-      <x:c r="F40"/>
-      <x:c r="G40"/>
-      <x:c r="H40"/>
+      <x:c r="F40" s="68"/>
+      <x:c r="G40" s="68"/>
+      <x:c r="H40" s="68"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="68" t="str">
+        <x:v>Service areas</x:v>
+      </x:c>
+      <x:c r="B41" s="68" t="str">
+        <x:v>Public active service area list, admin CRUD/deactivate and booking geofence validation</x:v>
+      </x:c>
+      <x:c r="C41" s="68" t="str">
+        <x:v>GET /api/v1/service-areas; /api/v1/admin/service-areas; /api/v1/bookings/estimate; /api/v1/bookings</x:v>
+      </x:c>
+      <x:c r="D41" s="68" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="E41" s="68" t="str">
+        <x:v>No active service areas keeps rollout open; once active zones exist pickup/dropoff must share at least one active area or backend returns LOCATION_OUT_OF_SERVICE_AREA. Overlapping/nested zones are resolved by common active area.</x:v>
+      </x:c>
+      <x:c r="F41" s="68"/>
+      <x:c r="G41" s="68"/>
+      <x:c r="H41" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5aaf762f800440d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68ec0cba93345c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2179,16 +2202,16 @@
         <x:v>Multi-city</x:v>
       </x:c>
       <x:c r="C16" s="24" t="str">
-        <x:v>Add service area/city configuration.</x:v>
+        <x:v>Service area backend foundation is in review; add real launch-city polygons, staging UAT and optional seed/import tooling.</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
-        <x:v>Geofence data and admin controls.</x:v>
+        <x:v>Geofence data, admin operations policy and staging validation.</x:v>
       </x:c>
       <x:c r="E16" s="24" t="str">
-        <x:v>Bookings outside service zones are handled according to policy.</x:v>
+        <x:v>Active service zones are configured for launch cities; common pickup/dropoff pairs are validated on devices; FE displays boundaries and handles LOCATION_OUT_OF_SERVICE_AREA clearly.</x:v>
       </x:c>
       <x:c r="F16" s="49" t="str">
-        <x:v>Open</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="G16" s="24" t="str"/>
       <x:c r="H16" s="25" t="str"/>
@@ -2240,7 +2263,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbef06a52f044b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ccaf8f7b2d340c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2371,10 +2394,10 @@
         <x:v>Product expansion</x:v>
       </x:c>
       <x:c r="C7" s="27" t="str">
-        <x:v>Local upload foundation, Cloudflare R2 provider, in-trip messaging, scheduled rides and surge pricing rules are implemented; finish R2 deployment UAT, surge threshold tuning, multi-city and analytics.</x:v>
+        <x:v>Local upload foundation, Cloudflare R2 provider, in-trip messaging, scheduled rides, surge pricing rules and service area zones are implemented/in review; finish R2 deployment UAT, surge tuning, real zone data and analytics.</x:v>
       </x:c>
       <x:c r="D7" s="27" t="str">
-        <x:v>Production upload storage is verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated with acceptance/cancellation data.</x:v>
+        <x:v>Production upload storage is verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated; launch-city service polygons are validated with common pickup/dropoff pairs.</x:v>
       </x:c>
       <x:c r="E7" s="27" t="str"/>
       <x:c r="F7" s="27" t="str"/>
@@ -2384,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2ae7becda7e45c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8a5e0408554b8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2412,10 +2435,10 @@
       <x:c r="D1" s="39" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="E1" s="39" t="str"/>
-      <x:c r="F1" s="39" t="str"/>
-      <x:c r="G1" s="39" t="str"/>
-      <x:c r="H1" s="40" t="str"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="40"/>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="23" t="str">
@@ -2430,10 +2453,10 @@
       <x:c r="D2" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E2" s="24" t="str"/>
-      <x:c r="F2" s="24" t="str"/>
-      <x:c r="G2" s="24" t="str"/>
-      <x:c r="H2" s="25" t="str"/>
+      <x:c r="E2" s="24"/>
+      <x:c r="F2" s="24"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="25"/>
     </x:row>
     <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="23" t="str">
@@ -2448,10 +2471,10 @@
       <x:c r="D3" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E3" s="24" t="str"/>
-      <x:c r="F3" s="24" t="str"/>
-      <x:c r="G3" s="24" t="str"/>
-      <x:c r="H3" s="25" t="str"/>
+      <x:c r="E3" s="24"/>
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="25"/>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="23" t="str">
@@ -2466,10 +2489,10 @@
       <x:c r="D4" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E4" s="24" t="str"/>
-      <x:c r="F4" s="24" t="str"/>
-      <x:c r="G4" s="24" t="str"/>
-      <x:c r="H4" s="25" t="str"/>
+      <x:c r="E4" s="24"/>
+      <x:c r="F4" s="24"/>
+      <x:c r="G4" s="24"/>
+      <x:c r="H4" s="25"/>
     </x:row>
     <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="23" t="str">
@@ -2484,10 +2507,10 @@
       <x:c r="D5" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str"/>
-      <x:c r="F5" s="24" t="str"/>
-      <x:c r="G5" s="24" t="str"/>
-      <x:c r="H5" s="25" t="str"/>
+      <x:c r="E5" s="24"/>
+      <x:c r="F5" s="24"/>
+      <x:c r="G5" s="24"/>
+      <x:c r="H5" s="25"/>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="23" t="str">
@@ -2502,10 +2525,10 @@
       <x:c r="D6" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E6" s="24" t="str"/>
-      <x:c r="F6" s="24" t="str"/>
-      <x:c r="G6" s="24" t="str"/>
-      <x:c r="H6" s="25" t="str"/>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="25"/>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="23" t="str">
@@ -2520,10 +2543,10 @@
       <x:c r="D7" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E7" s="24" t="str"/>
-      <x:c r="F7" s="24" t="str"/>
-      <x:c r="G7" s="24" t="str"/>
-      <x:c r="H7" s="25" t="str"/>
+      <x:c r="E7" s="24"/>
+      <x:c r="F7" s="24"/>
+      <x:c r="G7" s="24"/>
+      <x:c r="H7" s="25"/>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="23" t="str">
@@ -2538,10 +2561,10 @@
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="E8" s="24" t="str"/>
-      <x:c r="F8" s="24" t="str"/>
-      <x:c r="G8" s="24" t="str"/>
-      <x:c r="H8" s="25" t="str"/>
+      <x:c r="E8" s="24"/>
+      <x:c r="F8" s="24"/>
+      <x:c r="G8" s="24"/>
+      <x:c r="H8" s="25"/>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="23" t="str">
@@ -2556,10 +2579,10 @@
       <x:c r="D9" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E9" s="24" t="str"/>
-      <x:c r="F9" s="24" t="str"/>
-      <x:c r="G9" s="24" t="str"/>
-      <x:c r="H9" s="25" t="str"/>
+      <x:c r="E9" s="24"/>
+      <x:c r="F9" s="24"/>
+      <x:c r="G9" s="24"/>
+      <x:c r="H9" s="25"/>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="23" t="str">
@@ -2574,10 +2597,10 @@
       <x:c r="D10" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E10" s="24" t="str"/>
-      <x:c r="F10" s="24" t="str"/>
-      <x:c r="G10" s="24" t="str"/>
-      <x:c r="H10" s="25" t="str"/>
+      <x:c r="E10" s="24"/>
+      <x:c r="F10" s="24"/>
+      <x:c r="G10" s="24"/>
+      <x:c r="H10" s="25"/>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="23" t="str">
@@ -2592,10 +2615,10 @@
       <x:c r="D11" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E11" s="24" t="str"/>
-      <x:c r="F11" s="24" t="str"/>
-      <x:c r="G11" s="24" t="str"/>
-      <x:c r="H11" s="25" t="str"/>
+      <x:c r="E11" s="24"/>
+      <x:c r="F11" s="24"/>
+      <x:c r="G11" s="24"/>
+      <x:c r="H11" s="25"/>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="23" t="str">
@@ -2610,10 +2633,10 @@
       <x:c r="D12" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E12" s="24" t="str"/>
-      <x:c r="F12" s="24" t="str"/>
-      <x:c r="G12" s="24" t="str"/>
-      <x:c r="H12" s="25" t="str"/>
+      <x:c r="E12" s="24"/>
+      <x:c r="F12" s="24"/>
+      <x:c r="G12" s="24"/>
+      <x:c r="H12" s="25"/>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="23" t="str">
@@ -2628,10 +2651,10 @@
       <x:c r="D13" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E13" s="24" t="str"/>
-      <x:c r="F13" s="24" t="str"/>
-      <x:c r="G13" s="24" t="str"/>
-      <x:c r="H13" s="25" t="str"/>
+      <x:c r="E13" s="24"/>
+      <x:c r="F13" s="24"/>
+      <x:c r="G13" s="24"/>
+      <x:c r="H13" s="25"/>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="23" t="str">
@@ -2646,10 +2669,10 @@
       <x:c r="D14" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
       </x:c>
-      <x:c r="E14" s="24" t="str"/>
-      <x:c r="F14" s="24" t="str"/>
-      <x:c r="G14" s="24" t="str"/>
-      <x:c r="H14" s="25" t="str"/>
+      <x:c r="E14" s="24"/>
+      <x:c r="F14" s="24"/>
+      <x:c r="G14" s="24"/>
+      <x:c r="H14" s="25"/>
     </x:row>
     <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="23" t="str">
@@ -2664,10 +2687,10 @@
       <x:c r="D15" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E15" s="24" t="str"/>
-      <x:c r="F15" s="24" t="str"/>
-      <x:c r="G15" s="24" t="str"/>
-      <x:c r="H15" s="25" t="str"/>
+      <x:c r="E15" s="24"/>
+      <x:c r="F15" s="24"/>
+      <x:c r="G15" s="24"/>
+      <x:c r="H15" s="25"/>
     </x:row>
     <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="23" t="str">
@@ -2682,10 +2705,10 @@
       <x:c r="D16" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E16" s="24" t="str"/>
-      <x:c r="F16" s="24" t="str"/>
-      <x:c r="G16" s="24" t="str"/>
-      <x:c r="H16" s="25" t="str"/>
+      <x:c r="E16" s="24"/>
+      <x:c r="F16" s="24"/>
+      <x:c r="G16" s="24"/>
+      <x:c r="H16" s="25"/>
     </x:row>
     <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="23" t="str">
@@ -2700,10 +2723,10 @@
       <x:c r="D17" s="43" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
-      <x:c r="E17" s="24" t="str"/>
-      <x:c r="F17" s="24" t="str"/>
-      <x:c r="G17" s="24" t="str"/>
-      <x:c r="H17" s="25" t="str"/>
+      <x:c r="E17" s="24"/>
+      <x:c r="F17" s="24"/>
+      <x:c r="G17" s="24"/>
+      <x:c r="H17" s="25"/>
     </x:row>
     <x:row r="18" ht="46" customHeight="1">
       <x:c r="A18" s="23" t="str">
@@ -2718,10 +2741,10 @@
       <x:c r="D18" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
       </x:c>
-      <x:c r="E18" s="24" t="str"/>
-      <x:c r="F18" s="24" t="str"/>
-      <x:c r="G18" s="24" t="str"/>
-      <x:c r="H18" s="25" t="str"/>
+      <x:c r="E18" s="24"/>
+      <x:c r="F18" s="24"/>
+      <x:c r="G18" s="24"/>
+      <x:c r="H18" s="25"/>
     </x:row>
     <x:row r="19" ht="46" customHeight="1">
       <x:c r="A19" s="23" t="str">
@@ -2736,10 +2759,10 @@
       <x:c r="D19" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E19" s="24" t="str"/>
-      <x:c r="F19" s="24" t="str"/>
-      <x:c r="G19" s="24" t="str"/>
-      <x:c r="H19" s="25" t="str"/>
+      <x:c r="E19" s="24"/>
+      <x:c r="F19" s="24"/>
+      <x:c r="G19" s="24"/>
+      <x:c r="H19" s="25"/>
     </x:row>
     <x:row r="20" ht="46" customHeight="1">
       <x:c r="A20" s="23" t="str">
@@ -2754,10 +2777,10 @@
       <x:c r="D20" s="43" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
-      <x:c r="E20" s="24" t="str"/>
-      <x:c r="F20" s="24" t="str"/>
-      <x:c r="G20" s="24" t="str"/>
-      <x:c r="H20" s="25" t="str"/>
+      <x:c r="E20" s="24"/>
+      <x:c r="F20" s="24"/>
+      <x:c r="G20" s="24"/>
+      <x:c r="H20" s="25"/>
     </x:row>
     <x:row r="21" ht="46" customHeight="1">
       <x:c r="A21" s="23" t="str">
@@ -2772,10 +2795,10 @@
       <x:c r="D21" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E21" s="24" t="str"/>
-      <x:c r="F21" s="24" t="str"/>
-      <x:c r="G21" s="24" t="str"/>
-      <x:c r="H21" s="25" t="str"/>
+      <x:c r="E21" s="24"/>
+      <x:c r="F21" s="24"/>
+      <x:c r="G21" s="24"/>
+      <x:c r="H21" s="25"/>
     </x:row>
     <x:row r="22" ht="46" customHeight="1">
       <x:c r="A22" s="23" t="str">
@@ -2790,10 +2813,10 @@
       <x:c r="D22" s="43" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E22" s="24" t="str"/>
-      <x:c r="F22" s="24" t="str"/>
-      <x:c r="G22" s="24" t="str"/>
-      <x:c r="H22" s="25" t="str"/>
+      <x:c r="E22" s="24"/>
+      <x:c r="F22" s="24"/>
+      <x:c r="G22" s="24"/>
+      <x:c r="H22" s="25"/>
     </x:row>
     <x:row r="23" ht="46" customHeight="1">
       <x:c r="A23" s="26" t="str">
@@ -2808,33 +2831,51 @@
       <x:c r="D23" s="58" t="str">
         <x:v>Ready for FE/admin</x:v>
       </x:c>
-      <x:c r="E23" s="27" t="str"/>
-      <x:c r="F23" s="27" t="str"/>
-      <x:c r="G23" s="27" t="str"/>
-      <x:c r="H23" s="28" t="str"/>
+      <x:c r="E23" s="27"/>
+      <x:c r="F23" s="27"/>
+      <x:c r="G23" s="27"/>
+      <x:c r="H23" s="28"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" t="str">
+      <x:c r="A24" s="68" t="str">
         <x:v>Production startup guardrails</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B24" s="68" t="str">
         <x:v>No FE runtime API; deployment env uses APP_ENV, JWT_SECRET, CORS_ALLOWED_ORIGINS, STORAGE_PROVIDER, CLOUDFLARE_R2_* and ddl-auto</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C24" s="68" t="str">
         <x:v>FE does not change request contracts. Web/admin production origins must be in CORS allowlist; if backend fails startup with Production readiness check failed, fix deployment env before FE smoke.</x:v>
       </x:c>
-      <x:c r="D24" t="str">
+      <x:c r="D24" s="68" t="str">
         <x:v>Ready for devops</x:v>
       </x:c>
-      <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
+      <x:c r="E24" s="68"/>
+      <x:c r="F24" s="68"/>
+      <x:c r="G24" s="68"/>
+      <x:c r="H24" s="68"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="68" t="str">
+        <x:v>Service area zones</x:v>
+      </x:c>
+      <x:c r="B25" s="68" t="str">
+        <x:v>GET /api/v1/service-areas; GET/POST/PATCH /api/v1/admin/service-areas; LOCATION_OUT_OF_SERVICE_AREA</x:v>
+      </x:c>
+      <x:c r="C25" s="68" t="str">
+        <x:v>Draw active polygons on booking/admin maps, do not hardcode them, let backend validate estimate/create, handle LOCATION_OUT_OF_SERVICE_AREA, and do not infer rejection from the first polygon when zones overlap.</x:v>
+      </x:c>
+      <x:c r="D25" s="68" t="str">
+        <x:v>Ready for FE/admin</x:v>
+      </x:c>
+      <x:c r="E25" s="68"/>
+      <x:c r="F25" s="68"/>
+      <x:c r="G25" s="68"/>
+      <x:c r="H25" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec0cb2e99964341"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b97d19883e4a94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3120,27 +3161,45 @@
       <x:c r="H15" s="28" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="str">
+      <x:c r="A16" s="68" t="str">
         <x:v>Unsafe production config blocks startup.</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="68" t="str">
         <x:v>Deployments using APP_ENV=production with local JWT secret, ddl-auto update/create, local uploads, localhost/wildcard CORS or incomplete R2 config will fail before serving traffic.</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="68" t="str">
         <x:v>Prepare env vars in staging first, keep APP_ENV=local for dev, and use the startup failure message as a deployment checklist.</x:v>
       </x:c>
-      <x:c r="D16" t="str">
+      <x:c r="D16" s="68" t="str">
         <x:v>Mitigated in review</x:v>
       </x:c>
-      <x:c r="E16"/>
-      <x:c r="F16"/>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
+      <x:c r="E16" s="68"/>
+      <x:c r="F16" s="68"/>
+      <x:c r="G16" s="68"/>
+      <x:c r="H16" s="68"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="68" t="str">
+        <x:v>Service area polygons can block valid trips if drawn poorly.</x:v>
+      </x:c>
+      <x:c r="B17" s="68" t="str">
+        <x:v>Once active zones exist, estimate/create booking reject trips outside a single active polygon.</x:v>
+      </x:c>
+      <x:c r="C17" s="68" t="str">
+        <x:v>Start with broad launch-city polygons, test common pickup/dropoff pairs on real devices, keep no active zones until admin data is verified, and expose boundaries to FE for clear guidance.</x:v>
+      </x:c>
+      <x:c r="D17" s="68" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="E17" s="68"/>
+      <x:c r="F17" s="68"/>
+      <x:c r="G17" s="68"/>
+      <x:c r="H17" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2d257f84b4143e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c916184f60248cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfac2c4bd90d74b2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R1a817aec81b74c04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R6829d08ae4fb4402"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re2d5491e8ade4e07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb223bbd1495d4fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rfe1b3e7625d14158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8bbcacf79c854aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6612af11ef65435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R30bb2dc8b0ea47da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4d71e06869194a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rfd9ad6cfa3b64d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R21b87836a6074331"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Product-feature completion snapshot for service area / multi-city foundation.</x:v>
+        <x:v>Post-merge product-readiness snapshot after service area zones were merged into develop.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/service-area-zones</x:v>
+        <x:v>develop</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Feature branch focuses on service area polygons and booking geofence validation; production API docs hardening is paused in stash.</x:v>
+        <x:v>develop now contains feature/service-area-zones locally.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>develop at 10e5159 merge: production readiness guardrails</x:v>
+        <x:v>af2583a merge: service area zones</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>develop includes backend implementation through production readiness guardrails; merged into this feature branch.</x:v>
+        <x:v>Service area feature commit 54e8a3e was merged with --no-ff.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add service area zones</x:v>
+        <x:v>docs: mark service area merged</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Awaiting user review before commit/merge; not pushed.</x:v>
+        <x:v>Docs-only tracking commit after merge; no code changes.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -782,7 +782,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>./mvnw.cmd test passed 416 tests; targeted ServiceAreaServiceTests + BookingServiceTests passed 25 tests; SQL release validator passed.</x:v>
+        <x:v>Last full ./mvnw.cmd test passed 416 tests; targeted ServiceAreaServiceTests + BookingServiceTests passed 25 tests; SQL release validator passed.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -794,13 +794,13 @@
         <x:v>Diff hygiene</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>git diff --cached --check: pass</x:v>
+        <x:v>git diff --check: pass</x:v>
       </x:c>
       <x:c r="C7" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Staged diff hygiene passed after docs/workbook update; local application.yml remains intentionally uncommitted.</x:v>
+        <x:v>Post-merge docs/workbook diff hygiene passed; Windows only reports LF/CRLF warnings.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -1008,7 +1008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b514ebacf341e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R030bf9176cd6409c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1835,10 +1835,10 @@
         <x:v>GET /api/v1/service-areas; /api/v1/admin/service-areas; /api/v1/bookings/estimate; /api/v1/bookings</x:v>
       </x:c>
       <x:c r="D41" s="68" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E41" s="68" t="str">
-        <x:v>No active service areas keeps rollout open; once active zones exist pickup/dropoff must share at least one active area or backend returns LOCATION_OUT_OF_SERVICE_AREA. Overlapping/nested zones are resolved by common active area.</x:v>
+        <x:v>Merged into develop. No active service areas keeps rollout open; once active zones exist pickup/dropoff must share at least one active area or backend returns LOCATION_OUT_OF_SERVICE_AREA. Overlapping/nested zones resolve by common active area.</x:v>
       </x:c>
       <x:c r="F41" s="68"/>
       <x:c r="G41" s="68"/>
@@ -1847,7 +1847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra68ec0cba93345c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf605296926fc4057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1883,8 +1883,8 @@
       <x:c r="F1" s="39" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="G1" s="39" t="str"/>
-      <x:c r="H1" s="40" t="str"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="40"/>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="23" t="str">
@@ -1905,8 +1905,8 @@
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G2" s="24" t="str"/>
-      <x:c r="H2" s="25" t="str"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="25"/>
     </x:row>
     <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="23" t="str">
@@ -1927,8 +1927,8 @@
       <x:c r="F3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G3" s="24" t="str"/>
-      <x:c r="H3" s="25" t="str"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="25"/>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="23" t="str">
@@ -1949,8 +1949,8 @@
       <x:c r="F4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G4" s="24" t="str"/>
-      <x:c r="H4" s="25" t="str"/>
+      <x:c r="G4" s="24"/>
+      <x:c r="H4" s="25"/>
     </x:row>
     <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="23" t="str">
@@ -1971,8 +1971,8 @@
       <x:c r="F5" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G5" s="24" t="str"/>
-      <x:c r="H5" s="25" t="str"/>
+      <x:c r="G5" s="24"/>
+      <x:c r="H5" s="25"/>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="23" t="str">
@@ -1993,8 +1993,8 @@
       <x:c r="F6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G6" s="24" t="str"/>
-      <x:c r="H6" s="25" t="str"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="25"/>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="23" t="str">
@@ -2015,8 +2015,8 @@
       <x:c r="F7" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G7" s="24" t="str"/>
-      <x:c r="H7" s="25" t="str"/>
+      <x:c r="G7" s="24"/>
+      <x:c r="H7" s="25"/>
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="23" t="str">
@@ -2037,8 +2037,8 @@
       <x:c r="F8" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G8" s="24" t="str"/>
-      <x:c r="H8" s="25" t="str"/>
+      <x:c r="G8" s="24"/>
+      <x:c r="H8" s="25"/>
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="23" t="str">
@@ -2059,8 +2059,8 @@
       <x:c r="F9" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G9" s="24" t="str"/>
-      <x:c r="H9" s="25" t="str"/>
+      <x:c r="G9" s="24"/>
+      <x:c r="H9" s="25"/>
     </x:row>
     <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="23" t="str">
@@ -2081,8 +2081,8 @@
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G10" s="24" t="str"/>
-      <x:c r="H10" s="25" t="str"/>
+      <x:c r="G10" s="24"/>
+      <x:c r="H10" s="25"/>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="23" t="str">
@@ -2103,8 +2103,8 @@
       <x:c r="F11" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G11" s="24" t="str"/>
-      <x:c r="H11" s="25" t="str"/>
+      <x:c r="G11" s="24"/>
+      <x:c r="H11" s="25"/>
     </x:row>
     <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="23" t="str">
@@ -2125,8 +2125,8 @@
       <x:c r="F12" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G12" s="24" t="str"/>
-      <x:c r="H12" s="25" t="str"/>
+      <x:c r="G12" s="24"/>
+      <x:c r="H12" s="25"/>
     </x:row>
     <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="23" t="str">
@@ -2147,8 +2147,8 @@
       <x:c r="F13" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G13" s="24" t="str"/>
-      <x:c r="H13" s="25" t="str"/>
+      <x:c r="G13" s="24"/>
+      <x:c r="H13" s="25"/>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="23" t="str">
@@ -2169,8 +2169,8 @@
       <x:c r="F14" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
-      <x:c r="G14" s="24" t="str"/>
-      <x:c r="H14" s="25" t="str"/>
+      <x:c r="G14" s="24"/>
+      <x:c r="H14" s="25"/>
     </x:row>
     <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="23" t="str">
@@ -2191,8 +2191,8 @@
       <x:c r="F15" s="55" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G15" s="24" t="str"/>
-      <x:c r="H15" s="25" t="str"/>
+      <x:c r="G15" s="24"/>
+      <x:c r="H15" s="25"/>
     </x:row>
     <x:row r="16" ht="46" customHeight="1">
       <x:c r="A16" s="23" t="str">
@@ -2202,7 +2202,7 @@
         <x:v>Multi-city</x:v>
       </x:c>
       <x:c r="C16" s="24" t="str">
-        <x:v>Service area backend foundation is in review; add real launch-city polygons, staging UAT and optional seed/import tooling.</x:v>
+        <x:v>Service area backend foundation is merged; add real launch-city polygons, staging UAT and optional seed/import tooling.</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
         <x:v>Geofence data, admin operations policy and staging validation.</x:v>
@@ -2213,8 +2213,8 @@
       <x:c r="F16" s="49" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G16" s="24" t="str"/>
-      <x:c r="H16" s="25" t="str"/>
+      <x:c r="G16" s="24"/>
+      <x:c r="H16" s="25"/>
     </x:row>
     <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="23" t="str">
@@ -2235,8 +2235,8 @@
       <x:c r="F17" s="49" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="G17" s="24" t="str"/>
-      <x:c r="H17" s="25" t="str"/>
+      <x:c r="G17" s="24"/>
+      <x:c r="H17" s="25"/>
     </x:row>
     <x:row r="18" ht="46" customHeight="1">
       <x:c r="A18" s="26" t="str">
@@ -2257,13 +2257,13 @@
       <x:c r="F18" s="64" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G18" s="27" t="str"/>
-      <x:c r="H18" s="28" t="str"/>
+      <x:c r="G18" s="27"/>
+      <x:c r="H18" s="28"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ccaf8f7b2d340c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra529173623a14868"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2291,10 +2291,10 @@
       <x:c r="D1" s="39" t="str">
         <x:v>Exit Criteria</x:v>
       </x:c>
-      <x:c r="E1" s="39" t="str"/>
-      <x:c r="F1" s="39" t="str"/>
-      <x:c r="G1" s="39" t="str"/>
-      <x:c r="H1" s="40" t="str"/>
+      <x:c r="E1" s="39"/>
+      <x:c r="F1" s="39"/>
+      <x:c r="G1" s="39"/>
+      <x:c r="H1" s="40"/>
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="23" t="str">
@@ -2309,10 +2309,10 @@
       <x:c r="D2" s="24" t="str">
         <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
       </x:c>
-      <x:c r="E2" s="24" t="str"/>
-      <x:c r="F2" s="24" t="str"/>
-      <x:c r="G2" s="24" t="str"/>
-      <x:c r="H2" s="25" t="str"/>
+      <x:c r="E2" s="24"/>
+      <x:c r="F2" s="24"/>
+      <x:c r="G2" s="24"/>
+      <x:c r="H2" s="25"/>
     </x:row>
     <x:row r="3" ht="46" customHeight="1">
       <x:c r="A3" s="23" t="str">
@@ -2327,10 +2327,10 @@
       <x:c r="D3" s="24" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
       </x:c>
-      <x:c r="E3" s="24" t="str"/>
-      <x:c r="F3" s="24" t="str"/>
-      <x:c r="G3" s="24" t="str"/>
-      <x:c r="H3" s="25" t="str"/>
+      <x:c r="E3" s="24"/>
+      <x:c r="F3" s="24"/>
+      <x:c r="G3" s="24"/>
+      <x:c r="H3" s="25"/>
     </x:row>
     <x:row r="4" ht="46" customHeight="1">
       <x:c r="A4" s="23" t="str">
@@ -2345,10 +2345,10 @@
       <x:c r="D4" s="24" t="str">
         <x:v>Stale drivers are excluded from matching and database online state is cleaned in configured batches.</x:v>
       </x:c>
-      <x:c r="E4" s="24" t="str"/>
-      <x:c r="F4" s="24" t="str"/>
-      <x:c r="G4" s="24" t="str"/>
-      <x:c r="H4" s="25" t="str"/>
+      <x:c r="E4" s="24"/>
+      <x:c r="F4" s="24"/>
+      <x:c r="G4" s="24"/>
+      <x:c r="H4" s="25"/>
     </x:row>
     <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="23" t="str">
@@ -2363,10 +2363,10 @@
       <x:c r="D5" s="24" t="str">
         <x:v>Staging boots with APP_ENV=production using safe secrets, R2, non-mutating DDL and production FE/admin origins; probes/metrics/logs are monitored and unsafe config fails before traffic.</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str"/>
-      <x:c r="F5" s="24" t="str"/>
-      <x:c r="G5" s="24" t="str"/>
-      <x:c r="H5" s="25" t="str"/>
+      <x:c r="E5" s="24"/>
+      <x:c r="F5" s="24"/>
+      <x:c r="G5" s="24"/>
+      <x:c r="H5" s="25"/>
     </x:row>
     <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="23" t="str">
@@ -2381,10 +2381,10 @@
       <x:c r="D6" s="24" t="str">
         <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
       </x:c>
-      <x:c r="E6" s="24" t="str"/>
-      <x:c r="F6" s="24" t="str"/>
-      <x:c r="G6" s="24" t="str"/>
-      <x:c r="H6" s="25" t="str"/>
+      <x:c r="E6" s="24"/>
+      <x:c r="F6" s="24"/>
+      <x:c r="G6" s="24"/>
+      <x:c r="H6" s="25"/>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="26" t="str">
@@ -2399,15 +2399,15 @@
       <x:c r="D7" s="27" t="str">
         <x:v>Production upload storage is verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated; launch-city service polygons are validated with common pickup/dropoff pairs.</x:v>
       </x:c>
-      <x:c r="E7" s="27" t="str"/>
-      <x:c r="F7" s="27" t="str"/>
-      <x:c r="G7" s="27" t="str"/>
-      <x:c r="H7" s="28" t="str"/>
+      <x:c r="E7" s="27"/>
+      <x:c r="F7" s="27"/>
+      <x:c r="G7" s="27"/>
+      <x:c r="H7" s="28"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8a5e0408554b8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f714953bf3f4885"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2875,7 +2875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b97d19883e4a94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1cfc132b09d43cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3199,7 +3199,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c916184f60248cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb673dabbd9304de5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8bbcacf79c854aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6612af11ef65435c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R30bb2dc8b0ea47da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4d71e06869194a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rfd9ad6cfa3b64d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R21b87836a6074331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5830f11373a545d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R808e4f076c3b4117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R563c9c539c1c4c99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R14e8e8294cf040fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rcefd880fb6a94f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Raed1deaff593476e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Post-merge product-readiness snapshot after service area zones were merged into develop.</x:v>
+        <x:v>Task #1 product-readiness implementation completed and reviewed on the payment sandbox E2E feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>develop</x:v>
+        <x:v>feature/payment-sandbox-e2e-uat</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>develop now contains feature/service-area-zones locally.</x:v>
+        <x:v>Adds session-level MoMo/VNPAY sandbox evidence workflow; user review completed, not merged to develop yet.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>af2583a merge: service area zones</x:v>
+        <x:v>77f83a4 docs: mark service area merged</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Service area feature commit 54e8a3e was merged with --no-ff.</x:v>
+        <x:v>Feature branch starts from develop after service-area tracking commit.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>docs: mark service area merged</x:v>
+        <x:v>feat: add payment sandbox e2e evidence</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Docs-only tracking commit after merge; no code changes.</x:v>
+        <x:v>User review completed; feature commit created by this snapshot. src/main/resources/application.yml remains local-only.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Full Maven suite: pass</x:v>
+        <x:v>Targeted payment tests: pass; SQL validator: pass; full Maven suite: pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Last full ./mvnw.cmd test passed 416 tests; targeted ServiceAreaServiceTests + BookingServiceTests passed 25 tests; SQL release validator passed.</x:v>
+        <x:v>Targeted payment sandbox E2E/session tests passed 22 tests; SQL release 20260710 validator passed; full ./mvnw.cmd test passed 423 tests.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Post-merge docs/workbook diff hygiene passed; Windows only reports LF/CRLF warnings.</x:v>
+        <x:v>Passed after docs/workbook update; Windows only reports LF/CRLF warnings.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>CodeRabbit CLI unavailable on this Windows/WSL setup</x:v>
+        <x:v>Manual review: pass; CodeRabbit CLI blocked</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
-        <x:v>Blocked</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>coderabbit is not in PATH; local review fallback used.</x:v>
+        <x:v>Manual diff review found no blocker. CodeRabbit remains unavailable: command missing, WSL installer blocked, and unsafe external installer escalation rejected.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -884,13 +884,13 @@
         <x:v>Payment sandbox UAT evidence</x:v>
       </x:c>
       <x:c r="B12" s="24" t="str">
-        <x:v>GET/PUT provider UAT result endpoints</x:v>
+        <x:v>GET/PUT UAT result + GET/POST sandbox E2E session endpoints</x:v>
       </x:c>
       <x:c r="C12" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
-        <x:v>Committed as feat: add payment sandbox UAT evidence and merged locally into develop via merge: payment sandbox uat evidence.</x:v>
+        <x:v>Session API records checkout URL, success/failure payment refs, replay ref and freshness evidence, then syncs aggregate readyForFrontendExposure. User review completed.</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str"/>
       <x:c r="F12" s="24" t="str"/>
@@ -944,7 +944,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
-        <x:v>Backend readiness, UAT plan and evidence gate are ready; external sandbox accounts and public callback URLs are still required.</x:v>
+        <x:v>Backend evidence workflow is ready; real merchant accounts, public HTTPS callbacks and provider test apps are still required.</x:v>
       </x:c>
       <x:c r="E15" s="24" t="str"/>
       <x:c r="F15" s="24" t="str"/>
@@ -1008,7 +1008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R030bf9176cd6409c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87dc0ae7997a4879"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1589,16 +1589,16 @@
         <x:v>Payment</x:v>
       </x:c>
       <x:c r="B29" s="24" t="str">
-        <x:v>Payment sandbox UAT evidence and FE exposure gate</x:v>
+        <x:v>Payment sandbox UAT evidence, session history and FE exposure gate</x:v>
       </x:c>
       <x:c r="C29" s="24" t="str">
-        <x:v>GET /api/v1/payments/providers/sandbox-uat-results; PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result</x:v>
+        <x:v>GET /api/v1/payments/providers/sandbox-uat-results; PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result; GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions</x:v>
       </x:c>
       <x:c r="D29" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" s="24" t="str">
-        <x:v>Persists admin sandbox evidence per provider; PASSED requires sandboxReady plus checkout, success, failure, replay and freshness checks. Merged into develop.</x:v>
+        <x:v>Reviewed by user. Adds auditable sandbox E2E sessions; PASSED validates sandboxReady, HTTPS checkout URL, COMPLETED/FAILED provider payments, transaction refs, replay ref and freshness evidence before syncing aggregate result.</x:v>
       </x:c>
       <x:c r="F29" s="24"/>
       <x:c r="G29" s="24"/>
@@ -1718,7 +1718,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E35" s="24" t="str">
-        <x:v>Admin/devops endpoint summarizes prerequisites, provider readiness-derived status, checkout/webhook endpoints, configured return/IPN URLs, missing requirements and scenarios.</x:v>
+        <x:v>Reviewed by user. UAT plan points admin/devops to the sandbox E2E session endpoint after real checkout/callback/replay/freshness tests.</x:v>
       </x:c>
       <x:c r="F35" s="24"/>
       <x:c r="G35" s="24"/>
@@ -1847,7 +1847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf605296926fc4057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9176d834cbad4541"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1894,13 +1894,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT; backend readiness, UAT plan, service-level signed callback coverage and persisted evidence gate are in place.</x:v>
+        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT; backend readiness, UAT plan, service-level signed callback coverage, aggregate UAT evidence and session-level E2E evidence API are in place.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint and UAT result endpoint.</x:v>
+        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint, UAT result endpoint and sandbox E2E session endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Both providers return usable checkout URLs, real sandbox success/failure callbacks reconcile internal payment/trip state, and admin evidence is PASSED with all required checks.</x:v>
+        <x:v>Both providers return usable checkout URLs, real sandbox success/failure callbacks reconcile internal payment/trip state, and admin records PASSED aggregate evidence plus at least one complete sandbox E2E session per provider.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -1960,13 +1960,13 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs and persist evidence through the admin UAT result endpoint.</x:v>
+        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs and persist session evidence through the admin sandbox E2E endpoint.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Sandbox callback examples, merchant test accounts, public HTTPS backend URL and provider webhook/IPN registration.</x:v>
+        <x:v>Sandbox callback examples, merchant test accounts, public HTTPS backend URL, provider webhook/IPN registration and sandbox E2E session API.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str">
-        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; success/failure/replay/freshness checks are marked passed.</x:v>
+        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; success/failure/replay/freshness checks are recorded in session and aggregate evidence.</x:v>
       </x:c>
       <x:c r="F5" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2048,13 +2048,13 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="24" t="str">
-        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow, admin flow and CI wiring are covered; add provider sandbox E2E flow.</x:v>
+        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow, admin flow and CI wiring are covered; backend session evidence workflow is implemented, real provider sandbox automation remains.</x:v>
       </x:c>
       <x:c r="D9" s="24" t="str">
         <x:v>Existing Testcontainers PostGIS/Redis base and sandbox merchant accounts.</x:v>
       </x:c>
       <x:c r="E9" s="24" t="str">
-        <x:v>Provider sandbox happy paths run in CI/staging against database/Redis-compatible services and real provider sandbox callbacks are validated.</x:v>
+        <x:v>Provider sandbox happy paths run in CI/staging where secrets/callback infrastructure are available, and real provider callbacks are validated before online payment exposure.</x:v>
       </x:c>
       <x:c r="F9" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2263,7 +2263,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra529173623a14868"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1326e2d4a2d644e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2304,10 +2304,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Readiness diagnostics, admin sandbox UAT plan, persisted UAT evidence and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
+        <x:v>Readiness diagnostics, admin sandbox UAT plan, aggregate UAT evidence, session-level sandbox E2E evidence API and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
+        <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, at least one complete E2E session is recorded per provider, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2376,7 +2376,7 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="24" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token, admin flows and backend CI workflow are implemented; provider sandbox E2E remains.</x:v>
+        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token, admin flows and backend CI workflow are implemented; real provider sandbox E2E automation remains.</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
         <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f714953bf3f4885"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2304f65628bf47e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2553,10 +2553,10 @@
         <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Expose VNPAY/MoMo only when method metadata is enabled and UAT result readyForFrontendExposure=true.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Expose VNPAY/MoMo only when method metadata is enabled and aggregate UAT result readyForFrontendExposure=true; session endpoint is for admin/devops evidence only.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2661,10 +2661,10 @@
         <x:v>Payment sandbox UAT handoff</x:v>
       </x:c>
       <x:c r="B14" s="24" t="str">
-        <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result</x:v>
+        <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result; GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions</x:v>
       </x:c>
       <x:c r="C14" s="24" t="str">
-        <x:v>Admin/devops records sandbox evidence after testing checkout URL, success/failure callbacks, duplicate replay and freshness rejection. FE/admin dashboard can gate online methods on readyForFrontendExposure=true.</x:v>
+        <x:v>Admin/devops records real sandbox session evidence after testing checkout URL, success/failure callbacks, duplicate replay and freshness rejection. FE/admin dashboard gates online methods on aggregate readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
@@ -2875,7 +2875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1cfc132b09d43cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2083a5899352447b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2916,7 +2916,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation evidence.</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Keep CASH as MVP. Use readiness, UAT plan, service-level signed callback tests and persisted UAT result records; expose MoMo/VNPAY only when readyForFrontendExposure=true.</x:v>
+        <x:v>Keep CASH as MVP. Use readiness, UAT plan, service-level signed callback tests, persisted UAT result records and sandbox E2E session records; expose MoMo/VNPAY only when readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2934,7 +2934,7 @@
         <x:v>The configurable 24-hour age and 5-minute future-skew defaults have not been validated against real merchant retries.</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox and record freshness/replay evidence before tuning provider windows.</x:v>
+        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox and record freshness/replay evidence through sandbox E2E sessions before tuning provider windows.</x:v>
       </x:c>
       <x:c r="D3" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3006,7 +3006,7 @@
         <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, but real provider callbacks still need external UAT.</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>Reuse the Testcontainers base for provider-adjacent checks, use readiness/UAT evidence endpoints as the handoff gate, and validate real gateway callbacks before release candidate.</x:v>
+        <x:v>Reuse the Testcontainers base for provider-adjacent checks, use readiness/UAT evidence/session endpoints as the handoff gate, and validate real gateway callbacks before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3199,7 +3199,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb673dabbd9304de5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc538599a87724563"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5830f11373a545d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R808e4f076c3b4117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R563c9c539c1c4c99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R14e8e8294cf040fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rcefd880fb6a94f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Raed1deaff593476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc47f1b48574f4ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R60181373ab2f44e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rc766cb2d7db24250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R6c93657edf98403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd31cf0b1f2af4cad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R9f7c9a6efe424804"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-11</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Task #1 product-readiness implementation completed and reviewed on the payment sandbox E2E feature branch.</x:v>
+        <x:v>Payment sandbox follow-up completed and reviewed on the feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -728,7 +728,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Adds session-level MoMo/VNPAY sandbox evidence workflow; user review completed, not merged to develop yet.</x:v>
+        <x:v>Aggregate readyForFrontendExposure remains the FE gate; historical sessions use stable sessionEvidencePassed.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add payment sandbox e2e evidence</x:v>
+        <x:v>fix: clarify sandbox session evidence and enforce foreign keys</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>User review completed; feature commit created by this snapshot. src/main/resources/application.yml remains local-only.</x:v>
+        <x:v>User review completed; follow-up commit created by this snapshot. src/main/resources/application.yml remains local-only.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted payment tests: pass; SQL validator: pass; full Maven suite: pass</x:v>
+        <x:v>Targeted payment tests: 23 pass; SQL validator: pass; full Maven suite: 424 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Targeted payment sandbox E2E/session tests passed 22 tests; SQL release 20260710 validator passed; full ./mvnw.cmd test passed 423 tests.</x:v>
+        <x:v>Payment sandbox targeted suite passed 23 tests; SQL release validator passed; full ./mvnw.cmd test passed 424 tests.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Passed after docs/workbook update; Windows only reports LF/CRLF warnings.</x:v>
+        <x:v>Passed after code and Markdown updates; Windows only reports LF/CRLF warnings.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Manual review: pass; CodeRabbit CLI blocked</x:v>
+        <x:v>Manual review: pass; CodeRabbit CLI unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Manual diff review found no blocker. CodeRabbit remains unavailable: command missing, WSL installer blocked, and unsafe external installer escalation rejected.</x:v>
+        <x:v>Manual review found no blocker in the response contract, regression coverage, FK creation guards or SQL verification.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -890,7 +890,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
-        <x:v>Session API records checkout URL, success/failure payment refs, replay ref and freshness evidence, then syncs aggregate readyForFrontendExposure. User review completed.</x:v>
+        <x:v>Reviewed: aggregate readyForFrontendExposure is the FE gate, session history uses sessionEvidencePassed, and evidence references have ON DELETE RESTRICT foreign keys.</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str"/>
       <x:c r="F12" s="24" t="str"/>
@@ -1008,7 +1008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87dc0ae7997a4879"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03a86423cdc42d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1598,7 +1598,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" s="24" t="str">
-        <x:v>Reviewed by user. Adds auditable sandbox E2E sessions; PASSED validates sandboxReady, HTTPS checkout URL, COMPLETED/FAILED provider payments, transaction refs, replay ref and freshness evidence before syncing aggregate result.</x:v>
+        <x:v>Reviewed by user. Session response uses stable sessionEvidencePassed while aggregate readyForFrontendExposure remains the FE gate; payment/user evidence references have verified ON DELETE RESTRICT foreign keys.</x:v>
       </x:c>
       <x:c r="F29" s="24"/>
       <x:c r="G29" s="24"/>
@@ -1847,7 +1847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9176d834cbad4541"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063104f4620248b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1894,13 +1894,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT; backend readiness, UAT plan, service-level signed callback coverage, aggregate UAT evidence and session-level E2E evidence API are in place.</x:v>
+        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT. Aggregate readyForFrontendExposure is the FE gate; sessionEvidencePassed is historical evidence only, with payment/user references protected by foreign keys.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
         <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint, UAT result endpoint and sandbox E2E session endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Both providers return usable checkout URLs, real sandbox success/failure callbacks reconcile internal payment/trip state, and admin records PASSED aggregate evidence plus at least one complete sandbox E2E session per provider.</x:v>
+        <x:v>Both providers return usable checkout URLs, real callbacks reconcile payment state, aggregate evidence is PASSED, and at least one complete sessionEvidencePassed=true record exists per provider.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2263,7 +2263,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1326e2d4a2d644e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R074d2db930074c1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2304,10 +2304,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Readiness diagnostics, admin sandbox UAT plan, aggregate UAT evidence, session-level sandbox E2E evidence API and service-level signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
+        <x:v>Backend readiness, aggregate UAT gate, stable sessionEvidencePassed history, verified evidence foreign keys and signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Both providers report sandboxReady=true, UAT evidence is PASSED with all checks, at least one complete E2E session is recorded per provider, readyForFrontendExposure=true, and real sandbox payments complete/fail with correct internal reconciliation.</x:v>
+        <x:v>Both providers report sandboxReady=true, aggregate readyForFrontendExposure=true, at least one complete sessionEvidencePassed=true record exists per provider, and real sandbox callbacks reconcile correctly.</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2304f65628bf47e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b011828f7fa4c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2556,7 +2556,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false; show cash collection and driver payment-confirm. Expose VNPAY/MoMo only when method metadata is enabled and aggregate UAT result readyForFrontendExposure=true; session endpoint is for admin/devops evidence only.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false. Expose VNPAY/MoMo only when method metadata is enabled and aggregate UAT readyForFrontendExposure=true; do not use per-session sessionEvidencePassed as the consumer gate.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2664,7 +2664,7 @@
         <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result; GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions</x:v>
       </x:c>
       <x:c r="C14" s="24" t="str">
-        <x:v>Admin/devops records real sandbox session evidence after testing checkout URL, success/failure callbacks, duplicate replay and freshness rejection. FE/admin dashboard gates online methods on aggregate readyForFrontendExposure=true.</x:v>
+        <x:v>Admin/devops records and audits sessionEvidencePassed after real checkout/callback/replay/freshness tests. FE/admin dashboard gates online methods only on aggregate readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
@@ -2875,7 +2875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2083a5899352447b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2952d23d6544cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2916,7 +2916,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation evidence.</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Keep CASH as MVP. Use readiness, UAT plan, service-level signed callback tests, persisted UAT result records and sandbox E2E session records; expose MoMo/VNPAY only when readyForFrontendExposure=true.</x:v>
+        <x:v>Keep CASH as MVP. Expose MoMo/VNPAY only when aggregate readyForFrontendExposure=true; use sessionEvidencePassed records for audit, not as the current FE gate.</x:v>
       </x:c>
       <x:c r="D2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3199,7 +3199,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc538599a87724563"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58574d9c762f413a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc47f1b48574f4ed1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R60181373ab2f44e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rc766cb2d7db24250"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R6c93657edf98403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd31cf0b1f2af4cad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R9f7c9a6efe424804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd1507fee9b1b422d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R2f855f43163f4446"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rae065790450e4e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Raa8ed649f29b463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3399adee61f146f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd362283b74ff42c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Payment sandbox follow-up completed and reviewed on the feature branch.</x:v>
+        <x:v>User review completed; commit is being created from the reviewed patch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/payment-sandbox-e2e-uat</x:v>
+        <x:v>feature/payment-uat-actor-foreign-key</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Aggregate readyForFrontendExposure remains the FE gate; historical sessions use stable sessionEvidencePassed.</x:v>
+        <x:v>Actor FK release passed review and is ready to merge after commit.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>77f83a4 docs: mark service area merged</x:v>
+        <x:v>d9b2d98 merge: payment sandbox e2e evidence</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts from develop after service-area tracking commit.</x:v>
+        <x:v>Feature branch starts from develop after payment sandbox E2E merge.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>fix: clarify sandbox session evidence and enforce foreign keys</x:v>
+        <x:v>fix: enforce payment sandbox uat actor foreign key</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>User review completed; follow-up commit created by this snapshot. src/main/resources/application.yml remains local-only.</x:v>
+        <x:v>No review blocker; release validates actor ownership and orphan safety.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted payment tests: 23 pass; SQL validator: pass; full Maven suite: 424 pass</x:v>
+        <x:v>SQL validator: pass; full Maven suite: 424 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Payment sandbox targeted suite passed 23 tests; SQL release validator passed; full ./mvnw.cmd test passed 424 tests.</x:v>
+        <x:v>Release 20260711 validator passed; full ./mvnw.cmd test passed 424 tests on merge base d9b2d98.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Passed after code and Markdown updates; Windows only reports LF/CRLF warnings.</x:v>
+        <x:v>Passed after code, docs and workbook update; Windows only reports LF/CRLF warnings.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -818,7 +818,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Manual review found no blocker in the response contract, regression coverage, FK creation guards or SQL verification.</x:v>
+        <x:v>No blocker found in orphan guard, exact FK definition, release ordering or data-safe rollback.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -872,7 +872,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D11" s="24" t="str">
-        <x:v>Merged locally into develop; scheduled ride schema change uses db/releases/20260704-scheduled-rides.</x:v>
+        <x:v>FK release reviewed; staging must still run precheck/apply/verify in order.</x:v>
       </x:c>
       <x:c r="E11" s="24" t="str"/>
       <x:c r="F11" s="24" t="str"/>
@@ -890,7 +890,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
-        <x:v>Reviewed: aggregate readyForFrontendExposure is the FE gate, session history uses sessionEvidencePassed, and evidence references have ON DELETE RESTRICT foreign keys.</x:v>
+        <x:v>Documentation and workbook status updated after user review.</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str"/>
       <x:c r="F12" s="24" t="str"/>
@@ -1008,7 +1008,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd03a86423cdc42d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3e3ff266574dac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1598,7 +1598,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" s="24" t="str">
-        <x:v>Reviewed by user. Session response uses stable sessionEvidencePassed while aggregate readyForFrontendExposure remains the FE gate; payment/user evidence references have verified ON DELETE RESTRICT foreign keys.</x:v>
+        <x:v>Sandbox UAT aggregate actor FK reviewed; staging execution remains an environment task.</x:v>
       </x:c>
       <x:c r="F29" s="24"/>
       <x:c r="G29" s="24"/>
@@ -1735,10 +1735,10 @@
         <x:v>db/releases, scripts/validate-db-release.ps1, docs/database-release-process.md</x:v>
       </x:c>
       <x:c r="D36" s="46" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E36" s="24" t="str">
-        <x:v>Adds manifest/precheck/apply/verify/rollback template, release README, deployment process docs and validator for required files, manifest fields, transactional apply SQL and destructive SQL review markers.</x:v>
+        <x:v>Versioned actor FK release reviewed with orphan precheck, exact verification and data-safe rollback.</x:v>
       </x:c>
       <x:c r="F36" s="24"/>
       <x:c r="G36" s="24"/>
@@ -1847,7 +1847,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063104f4620248b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra730bdb28d7a4644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1894,13 +1894,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run and record real MoMo/VNPAY sandbox merchant UAT. Aggregate readyForFrontendExposure is the FE gate; sessionEvidencePassed is historical evidence only, with payment/user references protected by foreign keys.</x:v>
+        <x:v>Run real MoMo/VNPAY merchant UAT. Aggregate actor FK hardening is in review and must deploy after the sandbox E2E session release.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
         <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint, UAT result endpoint and sandbox E2E session endpoint.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Both providers return usable checkout URLs, real callbacks reconcile payment state, aggregate evidence is PASSED, and at least one complete sessionEvidencePassed=true record exists per provider.</x:v>
+        <x:v>Providers pass real callbacks, aggregate evidence is PASSED, testedByUserId references a real user, and complete session evidence exists per provider.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2263,7 +2263,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R074d2db930074c1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R631c3a013c294c1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2304,10 +2304,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Backend readiness, aggregate UAT gate, stable sessionEvidencePassed history, verified evidence foreign keys and signed callback coverage are implemented; finish real MoMo/VNPAY sandbox checkout/callback UAT.</x:v>
+        <x:v>Payment sandbox backend is merged; aggregate tested-by user FK release is in review. Finish its staging deploy, then real MoMo/VNPAY checkout/callback UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Both providers report sandboxReady=true, aggregate readyForFrontendExposure=true, at least one complete sessionEvidencePassed=true record exists per provider, and real sandbox callbacks reconcile correctly.</x:v>
+        <x:v>FK precheck reports zero orphans, apply/verify pass, both providers reach aggregate readyForFrontendExposure=true, and real callbacks reconcile correctly.</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2407,7 +2407,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b011828f7fa4c2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2245d7909a7843c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2664,7 +2664,7 @@
         <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result; GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions</x:v>
       </x:c>
       <x:c r="C14" s="24" t="str">
-        <x:v>Admin/devops records and audits sessionEvidencePassed after real checkout/callback/replay/freshness tests. FE/admin dashboard gates online methods only on aggregate readyForFrontendExposure=true.</x:v>
+        <x:v>Admin/devops records session evidence; aggregate testedByUserId must reference a real user after release 20260711. FE gating remains aggregate readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
@@ -2772,7 +2772,7 @@
         <x:v>db/releases/* plus scripts/validate-db-release.ps1</x:v>
       </x:c>
       <x:c r="C20" s="24" t="str">
-        <x:v>No FE runtime API. Devops/backend creates a release folder for schema changes, runs precheck/apply/verify/rollback SQL and validates with the PowerShell script before review/deploy.</x:v>
+        <x:v>No FE runtime API. Deploy payment SQL in order 20260705 -&gt; 20260710 -&gt; 20260711; confirm orphaned_tested_by_user_rows=0 before applying the actor FK.</x:v>
       </x:c>
       <x:c r="D20" s="43" t="str">
         <x:v>Ready for devops</x:v>
@@ -2875,7 +2875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2952d23d6544cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d194c0fb9c4cd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3078,7 +3078,7 @@
         <x:v>Without Flyway, missed SQL folders or unverified manual changes can desynchronize environments.</x:v>
       </x:c>
       <x:c r="C11" s="24" t="str">
-        <x:v>Require a db/releases folder per schema change, run the validator, archive precheck/verify output and keep production ddl-auto non-mutating.</x:v>
+        <x:v>Require a release folder per schema change. For payment UAT actor FK, archive precheck orphan count, apply output and verify output before promotion.</x:v>
       </x:c>
       <x:c r="D11" s="43" t="str">
         <x:v>Mitigated</x:v>
@@ -3199,7 +3199,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58574d9c762f413a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R929a56fb88d2443d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd1507fee9b1b422d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R2f855f43163f4446"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rae065790450e4e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Raa8ed649f29b463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3399adee61f146f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd362283b74ff42c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4ac91a1cf1414a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R477741f0252d4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R5627bc01923b4dd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rb781dc6f521d47fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3fe5e265d0b1469f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0b6b62f6a8934d52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -379,8 +379,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H19"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -396,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H41"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H42"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -464,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H18"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>User review completed; commit is being created from the reviewed patch.</x:v>
+        <x:v>User review completed; staging smoke commit is being created from the reviewed patch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/payment-uat-actor-foreign-key</x:v>
+        <x:v>feature/staging-readiness-smoke</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Actor FK release passed review and is ready to merge after commit.</x:v>
+        <x:v>Staging smoke script, workflow and deployment evidence contract passed user review.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>d9b2d98 merge: payment sandbox e2e evidence</x:v>
+        <x:v>1596826 merge: payment sandbox uat actor foreign key</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts from develop after payment sandbox E2E merge.</x:v>
+        <x:v>Feature branch starts after the reviewed actor FK release merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>fix: enforce payment sandbox uat actor foreign key</x:v>
+        <x:v>chore: add staging readiness smoke gate</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>No review blocker; release validates actor ownership and orphan safety.</x:v>
+        <x:v>Reviewed commit is ready to merge into develop after creation.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>SQL validator: pass; full Maven suite: 424 pass</x:v>
+        <x:v>PowerShell/mock smoke + full Maven: pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Release 20260711 validator passed; full ./mvnw.cmd test passed 424 tests on merge base d9b2d98.</x:v>
+        <x:v>Strict mock passed 13 checks, missing-token fail-safe passed and Maven passed 424 tests.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Passed after code, docs and workbook update; Windows only reports LF/CRLF warnings.</x:v>
+        <x:v>Passed after final code, workflow, docs and workbook updates.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -818,7 +818,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>No blocker found in orphan guard, exact FK definition, release ordering or data-safe rollback.</x:v>
+        <x:v>No blocker remains; workflow inputs are isolated through environment variables and token is not persisted.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -872,7 +872,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D11" s="24" t="str">
-        <x:v>FK release reviewed; staging must still run precheck/apply/verify in order.</x:v>
+        <x:v>Actor FK release is merged; staging still must execute releases in order.</x:v>
       </x:c>
       <x:c r="E11" s="24" t="str"/>
       <x:c r="F11" s="24" t="str"/>
@@ -1005,10 +1005,28 @@
       <x:c r="G18" s="27" t="str"/>
       <x:c r="H18" s="28" t="str"/>
     </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Staging readiness smoke</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>scripts/test-staging-readiness.ps1 + GitHub workflow</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Reviewed strict gates cover service areas, online payment readiness/UAT evidence and JSON deployment reporting.</x:v>
+      </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f3e3ff266574dac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c38109cef214bbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1844,10 +1862,30 @@
       <x:c r="G41" s="68"/>
       <x:c r="H41" s="68"/>
     </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>Operations</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Staging readiness smoke gate and JSON deployment evidence</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>scripts/test-staging-readiness.ps1; .github/workflows/staging-readiness-smoke.yml</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>User reviewed the probes, strict rollout gates, secret handling and JSON deployment evidence workflow.</x:v>
+      </x:c>
+      <x:c r="F42"/>
+      <x:c r="G42"/>
+      <x:c r="H42"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra730bdb28d7a4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f51077f9f34d11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1894,13 +1932,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run real MoMo/VNPAY merchant UAT. Aggregate actor FK hardening is in review and must deploy after the sandbox E2E session release.</x:v>
+        <x:v>Run real MoMo/VNPAY merchant UAT; actor FK release is merged and ready for ordered staging execution.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Sandbox merchant accounts, callback URLs, provider test apps, readiness endpoint, UAT plan endpoint, UAT result endpoint and sandbox E2E session endpoint.</x:v>
+        <x:v>Sandbox merchant accounts, public callback URLs, provider test apps and applied payment UAT SQL releases.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Providers pass real callbacks, aggregate evidence is PASSED, testedByUserId references a real user, and complete session evidence exists per provider.</x:v>
+        <x:v>Providers pass real callbacks, aggregate evidence is PASSED, testedByUserId remains referentially valid and strict staging smoke passes.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2070,13 +2108,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>Startup guardrails are in review; finish deployment collector dashboards, alerts, distributed tracing decision and staging env validation.</x:v>
+        <x:v>Run the new strict staging smoke workflow on a reachable release candidate; add collector dashboards and distributed tracing.</x:v>
       </x:c>
       <x:c r="D10" s="24" t="str">
-        <x:v>Deployment platform, log aggregation, tracing/observability stack and staging secret/config management.</x:v>
+        <x:v>Staging URL, GORIDE_STAGING_ADMIN_TOKEN secret, deployment platform, log collector and tracing backend.</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>APP_ENV=production starts only with safe secrets/CORS/storage/DDL config; logs/metrics/probes are centrally visible with actionable alerts.</x:v>
+        <x:v>Strict report passes and is archived; logs/metrics/traces are centrally searchable with release correlation.</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2263,7 +2301,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R631c3a013c294c1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f15b37d77324ff9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2304,10 +2342,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Payment sandbox backend is merged; aggregate tested-by user FK release is in review. Finish its staging deploy, then real MoMo/VNPAY checkout/callback UAT.</x:v>
+        <x:v>Payment sandbox backend and actor FK releases are merged; execute ordered SQL releases and real merchant UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>FK precheck reports zero orphans, apply/verify pass, both providers reach aggregate readyForFrontendExposure=true, and real callbacks reconcile correctly.</x:v>
+        <x:v>FK precheck reports zero orphans, apply/verify pass, both providers reach aggregate readyForFrontendExposure=true and strict smoke passes.</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2358,10 +2396,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Firebase secure credential loading, request correlation, structured stdout logging, centralized error logging, CORS allowlist, rate limiting, Prometheus metrics, Actuator probes, SQL release workflow and startup guardrails are implemented; finish collector dashboards, tracing decision and staging env UAT.</x:v>
+        <x:v>Startup guardrails, probes, metrics, structured logs, SQL workflow and staging smoke automation are implemented; real environment execution and observability backends remain.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Staging boots with APP_ENV=production using safe secrets, R2, non-mutating DDL and production FE/admin origins; probes/metrics/logs are monitored and unsafe config fails before traffic.</x:v>
+        <x:v>Strict staging smoke passes for the release candidate and collector dashboards/tracing are operational.</x:v>
       </x:c>
       <x:c r="E5" s="24"/>
       <x:c r="F5" s="24"/>
@@ -2407,7 +2445,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2245d7909a7843c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ab6831751054591"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2715,10 +2753,10 @@
         <x:v>Observability smoke</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>/actuator, /actuator/metrics, /actuator/prometheus, stdout logs with LOGGING_STRUCTURED_FORMAT_CONSOLE</x:v>
+        <x:v>scripts/test-staging-readiness.ps1; Staging Readiness Smoke workflow; Actuator/payment/service-area endpoints</x:v>
       </x:c>
       <x:c r="C17" s="24" t="str">
-        <x:v>Devops scrapes Prometheus and checks http.server.requests, goride.rate.limit.*, and JSON logs with requestId/http.request.method/url.path/http.response.status_code/event.duration_ms when LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash|ecs|gelf.</x:v>
+        <x:v>Devops runs basic or strict smoke, archives the JSON report and blocks release on failed probes, missing zones or payment exposure inconsistency.</x:v>
       </x:c>
       <x:c r="D17" s="43" t="str">
         <x:v>Ready for devops</x:v>
@@ -2875,7 +2913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31d194c0fb9c4cd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refe7e2a395974327"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3196,10 +3234,26 @@
       <x:c r="G17" s="68"/>
       <x:c r="H17" s="68"/>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Smoke runner cannot reach a private staging backend.</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Workflow fails before validating application readiness, leaving no reliable release evidence.</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>Use a self-hosted runner or trusted network path; keep the admin JWT in GORIDE_STAGING_ADMIN_TOKEN and never place it in workflow inputs.</x:v>
+      </x:c>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R929a56fb88d2443d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47adc5eb4d374543"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R4ac91a1cf1414a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R477741f0252d4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R5627bc01923b4dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rb781dc6f521d47fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R3fe5e265d0b1469f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0b6b62f6a8934d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Raf967f6a643e4cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R438a0f1527d14638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R86f4caf207534411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5133cce553714fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Re2736de4abf64f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R593895d7cddc433f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -447,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H26"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>User review completed; staging smoke commit is being created from the reviewed patch.</x:v>
+        <x:v>User review completed; production API docs guardrail commit is being created.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/staging-readiness-smoke</x:v>
+        <x:v>feature/production-api-docs-guardrails</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Staging smoke script, workflow and deployment evidence contract passed user review.</x:v>
+        <x:v>Production OpenAPI and Swagger UI startup policy passed user review.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>1596826 merge: payment sandbox uat actor foreign key</x:v>
+        <x:v>3ea7317 merge: staging readiness smoke gate</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after the reviewed actor FK release merged into develop.</x:v>
+        <x:v>Feature branch starts after staging smoke merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,7 +758,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>chore: add staging readiness smoke gate</x:v>
+        <x:v>chore: enforce production api docs guardrails</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>PowerShell/mock smoke + full Maven: pass</x:v>
+        <x:v>Targeted 9 + full Maven 427: pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Strict mock passed 13 checks, missing-token fail-safe passed and Maven passed 424 tests.</x:v>
+        <x:v>Production guardrail coverage and full backend suite passed with zero failures.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Passed after final code, workflow, docs and workbook updates.</x:v>
+        <x:v>Passed after final code, docs and workbook updates.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -818,7 +818,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>No blocker remains; workflow inputs are isolated through environment variables and token is not persisted.</x:v>
+        <x:v>No blocker remains in production detection, independent flags or local/staging behavior.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1026,7 +1026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c38109cef214bbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca39cacaeb774cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1827,16 +1827,16 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="B40" s="68" t="str">
-        <x:v>Startup guardrails for unsafe production config</x:v>
+        <x:v>Startup guardrails including production OpenAPI and Swagger UI shutdown</x:v>
       </x:c>
       <x:c r="C40" s="68" t="str">
-        <x:v>APP_ENV/app.environment, JWT_SECRET, CORS_ALLOWED_ORIGINS, STORAGE_PROVIDER, spring.jpa.hibernate.ddl-auto</x:v>
+        <x:v>APP_ENV, SPRINGDOC_API_DOCS_ENABLED, SPRINGDOC_SWAGGER_UI_ENABLED and existing production config</x:v>
       </x:c>
       <x:c r="D40" s="68" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E40" s="68" t="str">
-        <x:v>Fails startup when production still uses dev JWT secret, mutating Hibernate DDL, local storage, localhost/wildcard CORS or incomplete R2 config.</x:v>
+        <x:v>User reviewed production-only enforcement, independent flags, local/staging defaults and deployment environment contract.</x:v>
       </x:c>
       <x:c r="F40" s="68"/>
       <x:c r="G40" s="68"/>
@@ -1885,7 +1885,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f51077f9f34d11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ac868683ef34afe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2108,13 +2108,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>Run the new strict staging smoke workflow on a reachable release candidate; add collector dashboards and distributed tracing.</x:v>
+        <x:v>Run strict staging smoke, deploy production with both Springdoc flags disabled, then add collector dashboards and distributed tracing.</x:v>
       </x:c>
       <x:c r="D10" s="24" t="str">
-        <x:v>Staging URL, GORIDE_STAGING_ADMIN_TOKEN secret, deployment platform, log collector and tracing backend.</x:v>
+        <x:v>Deployment env, reachable staging URL, admin token secret, log collector and tracing backend.</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>Strict report passes and is archived; logs/metrics/traces are centrally searchable with release correlation.</x:v>
+        <x:v>Production starts only with API docs/Swagger disabled; strict smoke passes and observability is centrally correlated.</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2301,7 +2301,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f15b37d77324ff9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radf48d979010412a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2396,10 +2396,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Startup guardrails, probes, metrics, structured logs, SQL workflow and staging smoke automation are implemented; real environment execution and observability backends remain.</x:v>
+        <x:v>Startup guardrails now cover API docs/Swagger shutdown; probes, metrics, structured logs, SQL workflow and staging smoke are implemented.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Strict staging smoke passes for the release candidate and collector dashboards/tracing are operational.</x:v>
+        <x:v>Production boots with both Springdoc flags false; strict staging smoke passes and collector dashboards/tracing are operational.</x:v>
       </x:c>
       <x:c r="E5" s="24"/>
       <x:c r="F5" s="24"/>
@@ -2445,7 +2445,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ab6831751054591"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab754834c4be4888"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2910,10 +2910,26 @@
       <x:c r="G25" s="68"/>
       <x:c r="H25" s="68"/>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>API documentation</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>/v3/api-docs, /swagger-ui.html (local/staging only)</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Use trusted local/staging docs for integration; do not depend on these endpoints in production because startup policy requires them disabled.</x:v>
+      </x:c>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refe7e2a395974327"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R727423b844db407c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3203,10 +3219,10 @@
         <x:v>Unsafe production config blocks startup.</x:v>
       </x:c>
       <x:c r="B16" s="68" t="str">
-        <x:v>Deployments using APP_ENV=production with local JWT secret, ddl-auto update/create, local uploads, localhost/wildcard CORS or incomplete R2 config will fail before serving traffic.</x:v>
+        <x:v>Production now also refuses startup while OpenAPI JSON or Swagger UI remains enabled.</x:v>
       </x:c>
       <x:c r="C16" s="68" t="str">
-        <x:v>Prepare env vars in staging first, keep APP_ENV=local for dev, and use the startup failure message as a deployment checklist.</x:v>
+        <x:v>Set SPRINGDOC_API_DOCS_ENABLED=false and SPRINGDOC_SWAGGER_UI_ENABLED=false with the existing safe production env before deployment.</x:v>
       </x:c>
       <x:c r="D16" s="68" t="str">
         <x:v>Mitigated in review</x:v>
@@ -3253,7 +3269,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47adc5eb4d374543"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd36ab9b93d654a61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Raf967f6a643e4cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R438a0f1527d14638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R86f4caf207534411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R5133cce553714fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Re2736de4abf64f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R593895d7cddc433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb774c41460104743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R44a18f7130e145ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R1d04f450bba74bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R8ea11423c6bd475a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb7135748a4d94677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R70e0e40b8a404fa1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -379,8 +379,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SummaryTable" displayName="SummaryTable" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H20"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Field"/>
     <x:tableColumn id="2" name="Value"/>
@@ -710,7 +710,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>User review completed; production API docs guardrail commit is being created.</x:v>
+        <x:v>Redis-backed distributed rate limiting is implemented and waiting for user review.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/production-api-docs-guardrails</x:v>
+        <x:v>feature/redis-rate-limit-store</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Production OpenAPI and Swagger UI startup policy passed user review.</x:v>
+        <x:v>Atomic Redis token bucket shares one quota across application replicas.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>3ea7317 merge: staging readiness smoke gate</x:v>
+        <x:v>bea0201 merge: production api docs guardrails</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after staging smoke merged into develop.</x:v>
+        <x:v>Feature branch starts after API docs guardrails merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>chore: enforce production api docs guardrails</x:v>
+        <x:v>feat: add redis-backed distributed rate limiting</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Reviewed commit is ready to merge into develop after creation.</x:v>
+        <x:v>Draft code/tests/docs commit; not committed or merged.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 9 + full Maven 427: pass</x:v>
+        <x:v>Targeted 19 pass; full 436 run: 426 pass, 10 Docker/Testcontainers startup errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Production guardrail coverage and full backend suite passed with zero failures.</x:v>
+        <x:v>Includes Redis 7 shared bucket, refill, bean wiring, HTTP 429 and store-failure 503 coverage; full suite pending.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -800,7 +800,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Passed after final code, docs and workbook updates.</x:v>
+        <x:v>Run after final updates.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Manual review: pass; CodeRabbit CLI unavailable</x:v>
+        <x:v>Manual + user review: pass; CodeRabbit CLI unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>No blocker remains in production detection, independent flags or local/staging behavior.</x:v>
+        <x:v>Review Lua atomicity, TTL, hashed keys, fail-closed contract and production guardrail.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1023,10 +1023,28 @@
       <x:c r="G19"/>
       <x:c r="H19"/>
     </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>Redis distributed rate limiting</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>RATE_LIMIT_STORE=redis + atomic Lua token bucket</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>In review</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>Production shared quota, hashed client keys, idle TTL, 429 compatibility and structured 503 store-failure contract.</x:v>
+      </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca39cacaeb774cbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5f97022c75a4db6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1547,16 +1565,16 @@
         <x:v>Security/Operations</x:v>
       </x:c>
       <x:c r="B26" s="24" t="str">
-        <x:v>In-memory API rate limiting policy</x:v>
+        <x:v>Configurable memory/Redis distributed API rate limiting</x:v>
       </x:c>
       <x:c r="C26" s="24" t="str">
-        <x:v>All REST endpoints; Retry-After and X-RateLimit-* headers</x:v>
+        <x:v>All REST endpoints; Retry-After, X-RateLimit-* and RATE_LIMIT_STORE_UNAVAILABLE</x:v>
       </x:c>
       <x:c r="D26" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E26" s="24" t="str">
-        <x:v>Token-bucket per client IP; actuator/docs/WebSocket paths excluded by config; HTTP 429 returns RATE_LIMIT_EXCEEDED with retryAfterSeconds. Merged before current branch.</x:v>
+        <x:v>Memory remains local/test default; Redis Lua shares quota across replicas and production guardrail requires Redis when enabled.</x:v>
       </x:c>
       <x:c r="F26" s="24"/>
       <x:c r="G26" s="24"/>
@@ -1885,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ac868683ef34afe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redd87c0c4a484275"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2108,13 +2126,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>Run strict staging smoke, deploy production with both Springdoc flags disabled, then add collector dashboards and distributed tracing.</x:v>
+        <x:v>Configure managed Redis rate limiting on multi-replica staging, soak test shared quota/store latency, then add collector dashboards and tracing.</x:v>
       </x:c>
       <x:c r="D10" s="24" t="str">
-        <x:v>Deployment env, reachable staging URL, admin token secret, log collector and tracing backend.</x:v>
+        <x:v>Managed Redis, multi-replica staging, load test, log collector and tracing backend.</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>Production starts only with API docs/Swagger disabled; strict smoke passes and observability is centrally correlated.</x:v>
+        <x:v>No quota drift, unexpected 503 or store_error spikes; strict smoke passes and observability is centrally correlated.</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2301,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radf48d979010412a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf97481cbd7b949dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2396,10 +2414,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Startup guardrails now cover API docs/Swagger shutdown; probes, metrics, structured logs, SQL workflow and staging smoke are implemented.</x:v>
+        <x:v>Production API docs shutdown and Redis distributed rate limiting are code-ready; real environment soak test and observability backends remain.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Production boots with both Springdoc flags false; strict staging smoke passes and collector dashboards/tracing are operational.</x:v>
+        <x:v>Production uses Redis shared buckets, strict smoke passes, store_error remains healthy and collector dashboards/tracing are operational.</x:v>
       </x:c>
       <x:c r="E5" s="24"/>
       <x:c r="F5" s="24"/>
@@ -2445,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab754834c4be4888"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e15addc490440b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2735,10 +2753,10 @@
         <x:v>Rate limit handling</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>All REST endpoints except configured diagnostics/docs/WebSocket paths; Retry-After and X-RateLimit-* headers</x:v>
+        <x:v>All REST endpoints; Retry-After; X-RateLimit-*; RATE_LIMIT_EXCEEDED; RATE_LIMIT_STORE_UNAVAILABLE</x:v>
       </x:c>
       <x:c r="C16" s="24" t="str">
-        <x:v>On HTTP 429/RATE_LIMIT_EXCEEDED, stop immediate retries, disable the action temporarily, schedule retry after Retry-After and keep requestId for support.</x:v>
+        <x:v>Back off on 429 using Retry-After. On 503 store outage, wait at least one second, avoid retry storms and preserve requestId for support.</x:v>
       </x:c>
       <x:c r="D16" s="43" t="str">
         <x:v>Ready for FE</x:v>
@@ -2929,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R727423b844db407c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7b9b9aca9dd404c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3090,13 +3108,13 @@
     </x:row>
     <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="23" t="str">
-        <x:v>In-memory rate limiting is per application instance.</x:v>
+        <x:v>Redis rate limiting is a synchronous request-path dependency.</x:v>
       </x:c>
       <x:c r="B9" s="24" t="str">
-        <x:v>Multiple replicas each keep their own token buckets, so total traffic allowed may exceed the configured per-instance limit.</x:v>
+        <x:v>Redis outage or latency rejects protected requests with HTTP 503; memory fallback would break global quota guarantees.</x:v>
       </x:c>
       <x:c r="C9" s="24" t="str">
-        <x:v>Use conservative MVP defaults now; move bucket state to Redis or enforce limits at the API gateway if production needs global quotas.</x:v>
+        <x:v>Use managed HA Redis, readiness and alerts on outcome=store_error; keep explicit fail-closed behavior and retry guidance.</x:v>
       </x:c>
       <x:c r="D9" s="49" t="str">
         <x:v>Open</x:v>
@@ -3269,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd36ab9b93d654a61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f2f4aecba24e11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rb774c41460104743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R44a18f7130e145ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R1d04f450bba74bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R8ea11423c6bd475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb7135748a4d94677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R70e0e40b8a404fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3c6ec0d6195d4cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6b703a1a05604a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R0073534190794752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rcc8eba8218ef4e50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R5a2784811f4c4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Recf6ef4879804aa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -722,7 +722,7 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/redis-rate-limit-store</x:v>
+        <x:v>feature/payment-sandbox-e2e-automation</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
@@ -740,7 +740,7 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>bea0201 merge: production api docs guardrails</x:v>
+        <x:v>aed76ed merge: redis-backed distributed rate limiting</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
@@ -758,7 +758,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add redis-backed distributed rate limiting</x:v>
+        <x:v>ci: automate payment sandbox callback verification</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Done</x:v>
@@ -776,7 +776,7 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 19 pass; full 436 run: 426 pass, 10 Docker/Testcontainers startup errors</x:v>
+        <x:v>Static + targeted payment 26 pass; full 436: 426 pass, 10 Docker startup errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Partial</x:v>
@@ -812,7 +812,7 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Manual + user review: pass; CodeRabbit CLI unavailable</x:v>
+        <x:v>Manual + user review: pass; Actionlint/CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Partial</x:v>
@@ -884,7 +884,7 @@
         <x:v>Payment sandbox UAT evidence</x:v>
       </x:c>
       <x:c r="B12" s="24" t="str">
-        <x:v>GET/PUT UAT result + GET/POST sandbox E2E session endpoints</x:v>
+        <x:v>UAT/session APIs + protected signed-callback staging workflow</x:v>
       </x:c>
       <x:c r="C12" s="43" t="str">
         <x:v>Done</x:v>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5f97022c75a4db6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4beab3d640374e0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1634,7 +1634,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E29" s="24" t="str">
-        <x:v>Sandbox UAT aggregate actor FK reviewed; staging execution remains an environment task.</x:v>
+        <x:v>Evidence APIs and actor FK are done; protected callback replay workflow is in review, while real wallet/bank-app merchant UAT remains open.</x:v>
       </x:c>
       <x:c r="F29" s="24"/>
       <x:c r="G29" s="24"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redd87c0c4a484275"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R699b591eaf694282"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1950,13 +1950,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run real MoMo/VNPAY merchant UAT; actor FK release is merged and ready for ordered staging execution.</x:v>
+        <x:v>Run protected callback automation for MoMo/VNPAY, then complete real merchant wallet/bank-app UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Sandbox merchant accounts, public callback URLs, provider test apps and applied payment UAT SQL releases.</x:v>
+        <x:v>Sandbox merchant accounts, public callback URLs, fresh signed Base64 payload secrets, two pending payments per run and applied payment UAT SQL releases.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Providers pass real callbacks, aggregate evidence is PASSED, testedByUserId remains referentially valid and strict staging smoke passes.</x:v>
+        <x:v>Workflow and real merchant checkout both pass; aggregate evidence is PASSED and strict staging smoke passes.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2016,13 +2016,13 @@
         <x:v>Webhook sandbox</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Run real MoMo/VNPAY sandbox callbacks against public callback URLs and persist session evidence through the admin sandbox E2E endpoint.</x:v>
+        <x:v>Run the protected signed-callback workflow for both providers and separately validate gateway-originated callbacks.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Sandbox callback examples, merchant test accounts, public HTTPS backend URL, provider webhook/IPN registration and sandbox E2E session API.</x:v>
+        <x:v>Protected staging environment, fresh signed payloads tied to the selected payments, merchant test apps and public HTTPS backend URL.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str">
-        <x:v>Real provider callback acknowledgements match MoMo HTTP 204 and VNPay RspCode contracts; success/failure/replay/freshness checks are recorded in session and aggregate evidence.</x:v>
+        <x:v>Automation verifies success/failure/replay/freshness without leaking payloads; real MoMo HTTP 204 and VNPay RspCode acknowledgements are reviewed.</x:v>
       </x:c>
       <x:c r="F5" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2104,13 +2104,13 @@
         <x:v>Testing</x:v>
       </x:c>
       <x:c r="C9" s="24" t="str">
-        <x:v>Auth, booking/matching/routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token flow, admin flow and CI wiring are covered; backend session evidence workflow is implemented, real provider sandbox automation remains.</x:v>
+        <x:v>Core backend CI and protected payment callback automation are implemented; execute staging runs and retain real merchant evidence.</x:v>
       </x:c>
       <x:c r="D9" s="24" t="str">
-        <x:v>Existing Testcontainers PostGIS/Redis base and sandbox merchant accounts.</x:v>
+        <x:v>Existing Testcontainers base, staging secrets, two pending payments per provider run and sandbox merchant accounts.</x:v>
       </x:c>
       <x:c r="E9" s="24" t="str">
-        <x:v>Provider sandbox happy paths run in CI/staging where secrets/callback infrastructure are available, and real provider callbacks are validated before online payment exposure.</x:v>
+        <x:v>MoMo/VNPAY workflow artifacts are sanitized and pass; separate real provider checkout/callback evidence is approved before exposure.</x:v>
       </x:c>
       <x:c r="F9" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf97481cbd7b949dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9950b8d847ca408a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2360,10 +2360,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Payment sandbox backend and actor FK releases are merged; execute ordered SQL releases and real merchant UAT.</x:v>
+        <x:v>Payment backend, actor FK and protected callback workflow are code-ready; execute SQL releases, automation and real merchant UAT.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>FK precheck reports zero orphans, apply/verify pass, both providers reach aggregate readyForFrontendExposure=true and strict smoke passes.</x:v>
+        <x:v>FK verification, both provider workflow runs, real wallet/bank-app callbacks and aggregate readyForFrontendExposure=true all pass.</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2432,10 +2432,10 @@
         <x:v>Integration confidence</x:v>
       </x:c>
       <x:c r="C6" s="24" t="str">
-        <x:v>Testcontainers PostGIS/Redis foundation, auth, booking/routing, trip completion/payment, notification inbox/FCM token, admin flows and backend CI workflow are implemented; real provider sandbox E2E automation remains.</x:v>
+        <x:v>Core Testcontainers/HTTP flows and protected payment callback workflow are implemented; staging execution and real merchant UAT remain.</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Critical passenger/driver/admin happy paths run in CI; provider sandbox callback UAT passes before online payment launch.</x:v>
+        <x:v>Critical flows run in CI, sanitized provider callback automation passes, and gateway-originated callbacks are approved before launch.</x:v>
       </x:c>
       <x:c r="E6" s="24"/>
       <x:c r="F6" s="24"/>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72e15addc490440b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc274ae681a844241"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2720,7 +2720,7 @@
         <x:v>GET /api/v1/payments/providers/readiness; GET /api/v1/payments/providers/sandbox-uat-plan; GET/PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result; GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions</x:v>
       </x:c>
       <x:c r="C14" s="24" t="str">
-        <x:v>Admin/devops records session evidence; aggregate testedByUserId must reference a real user after release 20260711. FE gating remains aggregate readyForFrontendExposure=true.</x:v>
+        <x:v>Admin/devops runs the protected staging workflow and reviews sanitized evidence; FE still gates only on aggregate readyForFrontendExposure=true, never on one session or workflow artifact.</x:v>
       </x:c>
       <x:c r="D14" s="43" t="str">
         <x:v>Ready for FE/devops</x:v>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7b9b9aca9dd404c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R004d447aa92a492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2988,7 +2988,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation evidence.</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Keep CASH as MVP. Expose MoMo/VNPAY only when aggregate readyForFrontendExposure=true; use sessionEvidencePassed records for audit, not as the current FE gate.</x:v>
+        <x:v>Keep CASH as MVP. Run protected signed-callback automation plus separate real wallet/bank-app UAT; expose online methods only when aggregate readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="D2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3006,7 +3006,7 @@
         <x:v>The configurable 24-hour age and 5-minute future-skew defaults have not been validated against real merchant retries.</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Service-level tests cover signed success/failure/stale callbacks; validate real gateway retry timing in sandbox and record freshness/replay evidence through sandbox E2E sessions before tuning provider windows.</x:v>
+        <x:v>Use the protected workflow to verify stale/replay behavior, then compare against real gateway retry timing before tuning provider freshness windows.</x:v>
       </x:c>
       <x:c r="D3" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3075,10 +3075,10 @@
         <x:v>Integration coverage is partial.</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>Auth, booking/matching/driver-routing, trip completion, tracking fallback, cash payment confirmation, notification inbox/FCM token and admin flow run through HTTP/JWT/JPA/Redis, but real provider callbacks still need external UAT.</x:v>
+        <x:v>Core backend flows and signed-callback automation exist, but staging secrets and real gateway callbacks still require external UAT.</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>Reuse the Testcontainers base for provider-adjacent checks, use readiness/UAT evidence/session endpoints as the handoff gate, and validate real gateway callbacks before release candidate.</x:v>
+        <x:v>Run the protected workflow for each provider, retain sanitized artifacts, and separately validate gateway-originated callbacks before release candidate.</x:v>
       </x:c>
       <x:c r="D7" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f2f4aecba24e11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbce364ea54b4deb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3c6ec0d6195d4cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R6b703a1a05604a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R0073534190794752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rcc8eba8218ef4e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R5a2784811f4c4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Recf6ef4879804aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9cdaa2ac7e6542cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R16d6baa3185341c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R3505978be316433d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R34ea632469c34328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd9a2f9bbf68845cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb747f99d0ad64c6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-11</x:v>
+        <x:v>2026-07-19</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Redis-backed distributed rate limiting is implemented and waiting for user review.</x:v>
+        <x:v>Production OTLP tracing wiring is reviewed and committed on the feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/payment-sandbox-e2e-automation</x:v>
+        <x:v>feature/production-observability-wiring</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Committed</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Atomic Redis token bucket shares one quota across application replicas.</x:v>
+        <x:v>Micrometer/OpenTelemetry OTLP tracing, safe actuator info flags and production startup/smoke guardrails.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>aed76ed merge: redis-backed distributed rate limiting</x:v>
+        <x:v>4e96274 merge: payment sandbox callback automation</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after API docs guardrails merged into develop.</x:v>
+        <x:v>Feature branch starts after payment sandbox callback automation merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>ci: automate payment sandbox callback verification</x:v>
+        <x:v>feat: wire production otlp tracing</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Draft code/tests/docs commit; not committed or merged.</x:v>
+        <x:v>Committed on feature branch; not merged or pushed yet.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Static + targeted payment 26 pass; full 436: 426 pass, 10 Docker startup errors</x:v>
+        <x:v>Targeted 24 pass; full Maven 445 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Includes Redis 7 shared bucket, refill, bean wiring, HTTP 429 and store-failure 503 coverage; full suite pending.</x:v>
+        <x:v>Covers typed actuator info booleans, no endpoint leak, production tracing guardrails and CORS header exposure.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -794,13 +794,13 @@
         <x:v>Diff hygiene</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>git diff --check: pass</x:v>
+        <x:v>PowerShell parse + workflow run-block check + git diff --check: pass</x:v>
       </x:c>
       <x:c r="C7" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Run after final updates.</x:v>
+        <x:v>git diff --check reports only Windows CRLF conversion warnings.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Manual + user review: pass; Actionlint/CodeRabbit unavailable</x:v>
+        <x:v>Manual + user review passed; Actionlint/CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Review Lua atomicity, TTL, hashed keys, fail-closed contract and production guardrail.</x:v>
+        <x:v>User review completed on 2026-07-19. No blocker found in OTLP endpoint validation, production opt-out semantics, safe actuator info or smoke gate wiring.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -920,13 +920,13 @@
         <x:v>OTLP tracing config</x:v>
       </x:c>
       <x:c r="B14" s="24" t="str">
-        <x:v>feature/otlp-tracing-config</x:v>
+        <x:v>feature/production-observability-wiring</x:v>
       </x:c>
       <x:c r="C14" s="52" t="str">
-        <x:v>Held</x:v>
+        <x:v>Committed</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
-        <x:v>Implemented on a separate branch but intentionally not merged into develop yet.</x:v>
+        <x:v>Ported and hardened from held feature/otlp-tracing-config; local/test disabled, production guarded and user-reviewed.</x:v>
       </x:c>
       <x:c r="E14" s="24" t="str"/>
       <x:c r="F14" s="24" t="str"/>
@@ -1013,10 +1013,10 @@
         <x:v>scripts/test-staging-readiness.ps1 + GitHub workflow</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Done</x:v>
+        <x:v>Committed</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>Reviewed strict gates cover service areas, online payment readiness/UAT evidence and JSON deployment reporting.</x:v>
+        <x:v>Adds optional -RequireTracing gate for typed tracing/export flags while keeping collector details private.</x:v>
       </x:c>
       <x:c r="E19"/>
       <x:c r="F19"/>
@@ -1031,10 +1031,10 @@
         <x:v>RATE_LIMIT_STORE=redis + atomic Lua token bucket</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>Production shared quota, hashed client keys, idle TTL, 429 compatibility and structured 503 store-failure contract.</x:v>
+        <x:v>Merged into develop before payment sandbox automation; production still needs managed Redis soak and alerts.</x:v>
       </x:c>
       <x:c r="E20"/>
       <x:c r="F20"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4beab3d640374e0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc867510b29d94dd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1505,16 +1505,16 @@
         <x:v>Observability</x:v>
       </x:c>
       <x:c r="B23" s="24" t="str">
-        <x:v>HTTP request correlation, structured stdout logging and centralized error logging</x:v>
+        <x:v>HTTP request correlation, structured stdout logging and OTLP tracing</x:v>
       </x:c>
       <x:c r="C23" s="24" t="str">
-        <x:v>X-Request-Id, LOGGING_STRUCTURED_FORMAT_CONSOLE, APP_ENV, APP_VERSION</x:v>
+        <x:v>X-Request-Id, traceId/spanId, TRACING_*, OTLP_TRACING_*, /actuator/info</x:v>
       </x:c>
       <x:c r="D23" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E23" s="24" t="str">
-        <x:v>Completion logs include requestId, http.request.method, url.path, http.response.status_code and event.duration_ms; JSON stdout verified via LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash smoke test.</x:v>
+        <x:v>Request IDs are added to spans as request.id, plain logs include trace/span IDs, and info exposes only tracing/export booleans.</x:v>
       </x:c>
       <x:c r="F23" s="24"/>
       <x:c r="G23" s="24"/>
@@ -1571,7 +1571,7 @@
         <x:v>All REST endpoints; Retry-After, X-RateLimit-* and RATE_LIMIT_STORE_UNAVAILABLE</x:v>
       </x:c>
       <x:c r="D26" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="E26" s="24" t="str">
         <x:v>Memory remains local/test default; Redis Lua shares quota across replicas and production guardrail requires Redis when enabled.</x:v>
@@ -1888,13 +1888,13 @@
         <x:v>Staging readiness smoke gate and JSON deployment evidence</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>scripts/test-staging-readiness.ps1; .github/workflows/staging-readiness-smoke.yml</x:v>
+        <x:v>scripts/test-staging-readiness.ps1; .github/workflows/staging-readiness-smoke.yml; /actuator/info</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E42" t="str">
-        <x:v>User reviewed the probes, strict rollout gates, secret handling and JSON deployment evidence workflow.</x:v>
+        <x:v>Adds optional strict tracing/export checks through -RequireTracing while preserving sanitized JSON evidence and secret handling.</x:v>
       </x:c>
       <x:c r="F42"/>
       <x:c r="G42"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R699b591eaf694282"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R930917766e444d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2126,13 +2126,13 @@
         <x:v>Production hardening</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>Configure managed Redis rate limiting on multi-replica staging, soak test shared quota/store latency, then add collector dashboards and tracing.</x:v>
+        <x:v>OTLP exporter/config/startup/smoke gates and Redis rate limiting are code-ready; deploy collector/log shipping/dashboards and soak-test multi-replica staging.</x:v>
       </x:c>
       <x:c r="D10" s="24" t="str">
-        <x:v>Managed Redis, multi-replica staging, load test, log collector and tracing backend.</x:v>
+        <x:v>Managed Redis, OTLP collector/backend, log collector, Prometheus/Grafana-equivalent dashboards and multi-replica staging.</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>No quota drift, unexpected 503 or store_error spikes; strict smoke passes and observability is centrally correlated.</x:v>
+        <x:v>Traces correlate with requestId/traceId, logs and metrics are centralized, shared quota remains correct and strict smoke passes without store/exporter errors.</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9950b8d847ca408a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b0d5113c784df4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2414,10 +2414,10 @@
         <x:v>Production readiness</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Production API docs shutdown and Redis distributed rate limiting are code-ready; real environment soak test and observability backends remain.</x:v>
+        <x:v>Firebase config, structured logs, Redis rate limits, Prometheus/Actuator, OTLP tracing config/correlation/startup/smoke gates and SQL release guards are implemented; collector deployment, dashboards, soak tests and final UAT remain.</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Production uses Redis shared buckets, strict smoke passes, store_error remains healthy and collector dashboards/tracing are operational.</x:v>
+        <x:v>Production uses Redis shared buckets, strict smoke including -RequireTracing passes, requestId-to-trace search works, store_error/exporter signals stay healthy, and dashboards are operational.</x:v>
       </x:c>
       <x:c r="E5" s="24"/>
       <x:c r="F5" s="24"/>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc274ae681a844241"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R951c40ac8e8e4b99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2768,13 +2768,13 @@
     </x:row>
     <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="23" t="str">
-        <x:v>Observability smoke</x:v>
+        <x:v>Observability/devops smoke</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>scripts/test-staging-readiness.ps1; Staging Readiness Smoke workflow; Actuator/payment/service-area endpoints</x:v>
+        <x:v>scripts/test-staging-readiness.ps1; Staging Readiness Smoke workflow; /actuator/info; /actuator/prometheus</x:v>
       </x:c>
       <x:c r="C17" s="24" t="str">
-        <x:v>Devops runs basic or strict smoke, archives the JSON report and blocks release on failed probes, missing zones or payment exposure inconsistency.</x:v>
+        <x:v>Devops can add -RequireTracing for strict staging promotion, archive JSON evidence, then verify traces/logs/metrics in the external collector stack; FE should keep X-Request-Id for support correlation.</x:v>
       </x:c>
       <x:c r="D17" s="43" t="str">
         <x:v>Ready for devops</x:v>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R004d447aa92a492a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fe6c92e30474536"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3090,13 +3090,13 @@
     </x:row>
     <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="23" t="str">
-        <x:v>Logs and metrics are still per-instance until deployment wiring is added.</x:v>
+        <x:v>Collector infrastructure is not deployed by this repository.</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Structured JSON stdout logs, request IDs, health probes, Prometheus metrics and 429 throttling improve diagnosis, but data can still be fragmented across replicas without a collector.</x:v>
+        <x:v>Backend can emit correlated OTLP traces, structured logs and Prometheus metrics, but data remains fragmented until external collectors/backends are provisioned.</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>Enable LOGGING_STRUCTURED_FORMAT_CONSOLE=logstash or platform-preferred format, ship stdout centrally, scrape each instance and add retention/search/alert dashboards before production scaling.</x:v>
+        <x:v>Configure a non-loopback OTLP collector, centralized stdout shipping and Prometheus dashboards/alerts; enable strict tracing smoke and verify requestId-to-trace search before scaling.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbce364ea54b4deb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb0d565c200a414f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9cdaa2ac7e6542cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R16d6baa3185341c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R3505978be316433d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R34ea632469c34328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd9a2f9bbf68845cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rb747f99d0ad64c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R42f24c219b734e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rfafede56bc9b4380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R48d7af9d7b544249"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R6baaf0e87af746b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R8cf895c645764e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rbd1028a2b8894f6d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,10 +707,10 @@
         <x:v>2026-07-19</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Production OTLP tracing wiring is reviewed and committed on the feature branch.</x:v>
+        <x:v>Online payment exposure gate and driver lifecycle polish are implemented on feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/production-observability-wiring</x:v>
+        <x:v>feature/online-payment-production-gate</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>Committed</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Micrometer/OpenTelemetry OTLP tracing, safe actuator info flags and production startup/smoke guardrails.</x:v>
+        <x:v>Adds /payments/methods consumerEnabled plus online pending driver release after trip completion.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>4e96274 merge: payment sandbox callback automation</x:v>
+        <x:v>e6aba60 merge: production observability wiring</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after payment sandbox callback automation merged into develop.</x:v>
+        <x:v>Feature branch starts after production observability wiring merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: wire production otlp tracing</x:v>
+        <x:v>feat: complete online payment exposure gate</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Committed on feature branch; not merged or pushed yet.</x:v>
+        <x:v>User review completed on 2026-07-19; commit created on feature branch, not merged or pushed yet.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 24 pass; full Maven 445 pass</x:v>
+        <x:v>Targeted 14 pass; full Maven 450 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Covers typed actuator info booleans, no endpoint leak, production tracing guardrails and CORS header exposure.</x:v>
+        <x:v>PaymentMethodServiceTests, TripPaymentServiceTests, PaymentCompletionWorkflowTests and full ./mvnw.cmd test pass.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -794,13 +794,13 @@
         <x:v>Diff hygiene</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>PowerShell parse + workflow run-block check + git diff --check: pass</x:v>
+        <x:v>git diff --check: pass</x:v>
       </x:c>
       <x:c r="C7" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>git diff --check reports only Windows CRLF conversion warnings.</x:v>
+        <x:v>Only Windows CRLF conversion warnings are reported by Git.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Manual + user review passed; Actionlint/CodeRabbit unavailable</x:v>
+        <x:v>User review completed; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>User review completed on 2026-07-19. No blocker found in OTLP endpoint validation, production opt-out semantics, safe actuator info or smoke gate wiring.</x:v>
+        <x:v>User review completed on 2026-07-19; coderabbit command is not available in PATH.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc867510b29d94dd3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f19fffaf924a56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1274,7 +1274,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E11" s="24" t="str">
-        <x:v>CASH works; online provider registry and shared checkout/webhook foundations exist.</x:v>
+        <x:v>CASH works; online provider registry, signed checkout and shared webhook foundations exist. Online pending payment now releases the driver after trip completion.</x:v>
       </x:c>
       <x:c r="F11" s="24"/>
       <x:c r="G11" s="24"/>
@@ -1294,7 +1294,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str">
-        <x:v>FE can render CASH/MOMO/VNPAY availability; online methods require provider registration, enabled config, and provider-specific required fields.</x:v>
+        <x:v>FE should use consumerEnabled to render passenger payment methods. enabled remains backend/UAT checkout availability; online consumer exposure requires aggregate readyForFrontendExposure=true.</x:v>
       </x:c>
       <x:c r="F12" s="24"/>
       <x:c r="G12" s="24"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R930917766e444d3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b36c240df184cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1950,13 +1950,13 @@
         <x:v>Payment providers</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Run protected callback automation for MoMo/VNPAY, then complete real merchant wallet/bank-app UAT.</x:v>
+        <x:v>Run protected callback automation for MoMo/VNPAY, then complete real merchant wallet/bank-app UAT and confirm /payments/methods consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
         <x:v>Sandbox merchant accounts, public callback URLs, fresh signed Base64 payload secrets, two pending payments per run and applied payment UAT SQL releases.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Workflow and real merchant checkout both pass; aggregate evidence is PASSED and strict staging smoke passes.</x:v>
+        <x:v>Workflow and real merchant checkout both pass; aggregate evidence is PASSED; /api/v1/payments/methods returns consumerEnabled=true for the provider.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -1972,13 +1972,13 @@
         <x:v>Payment methods</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Expose supported payment methods/provider metadata to FE.</x:v>
+        <x:v>Expose supported payment methods/provider metadata to FE, including consumerEnabled and readyForFrontendExposure.</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Provider enabled flags, registry support, booking guard.</x:v>
+        <x:v>Provider enabled flags, registry support, checkout/webhook readiness and aggregate sandbox UAT evidence.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str">
-        <x:v>GET /api/v1/payments/methods returns CASH/MOMO/VNPAY metadata and booking rejects disabled methods.</x:v>
+        <x:v>GET /api/v1/payments/methods returns CASH/MOMO/VNPAY metadata; FE renders passenger options only when consumerEnabled=true; booking still rejects disabled methods.</x:v>
       </x:c>
       <x:c r="F3" s="43" t="str">
         <x:v>Done</x:v>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b0d5113c784df4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R102f8cfe9b854281"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2360,10 +2360,10 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Payment backend, actor FK and protected callback workflow are code-ready; execute SQL releases, automation and real merchant UAT.</x:v>
+        <x:v>MoMo/VNPAY signed checkout/webhook, UAT/session APIs, protected callback workflow and /methods consumerEnabled gate are code-ready; run real merchant sandbox checkout/callback and record evidence.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>FK verification, both provider workflow runs, real wallet/bank-app callbacks and aggregate readyForFrontendExposure=true all pass.</x:v>
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="E2" s="24"/>
       <x:c r="F2" s="24"/>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R951c40ac8e8e4b99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bcf7b7349fe4084"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2594,7 +2594,7 @@
         <x:v>/api/v1/payments/methods</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>Render payment method options from backend; allow only enabled methods.</x:v>
+        <x:v>Render payment method options from backend; passenger UI should allow only consumerEnabled=true. enabled=true means backend/UAT checkout availability, not public exposure by itself.</x:v>
       </x:c>
       <x:c r="D7" s="43" t="str">
         <x:v>Ready for FE</x:v>
@@ -2612,7 +2612,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false. Expose VNPAY/MoMo only when method metadata is enabled and aggregate UAT readyForFrontendExposure=true; do not use per-session sessionEvidencePassed as the consumer gate.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false. Expose VNPAY/MoMo only when /payments/methods consumerEnabled=true; after redirect/callback, poll payment detail until status is terminal.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fe6c92e30474536"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e7b52b2d4146d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2982,13 +2982,13 @@
     </x:row>
     <x:row r="2" ht="46" customHeight="1">
       <x:c r="A2" s="23" t="str">
-        <x:v>Online payment providers are not production-complete.</x:v>
+        <x:v>Online payment providers still need real merchant UAT.</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>Frontend should not expose MoMo/VNPAY in production without real sandbox/UAT validation evidence.</x:v>
+        <x:v>Frontend should not expose MoMo/VNPAY publicly until sandbox/UAT validation evidence is recorded and /payments/methods returns consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Keep CASH as MVP. Run protected signed-callback automation plus separate real wallet/bank-app UAT; expose online methods only when aggregate readyForFrontendExposure=true.</x:v>
+        <x:v>Keep CASH as fallback. Run protected signed-callback automation plus separate real wallet/bank-app UAT; expose online methods from FE only via consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="D2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb0d565c200a414f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c74a8120f0a47bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R42f24c219b734e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rfafede56bc9b4380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R48d7af9d7b544249"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R6baaf0e87af746b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R8cf895c645764e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rbd1028a2b8894f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rba1f4d63f843476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rfbf825602ba8428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rff591199f78842e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Ra9b4e983c8ef42e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R2f0c255a40e74aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R98045a2119db415b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Online payment exposure gate and driver lifecycle polish are implemented on feature branch.</x:v>
+        <x:v>Payment checkout POST endpoint is implemented on feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/online-payment-production-gate</x:v>
+        <x:v>feature/payment-checkout-post-endpoint</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Adds /payments/methods consumerEnabled plus online pending driver release after trip completion.</x:v>
+        <x:v>Adds canonical POST checkout endpoint while keeping GET /checkout as a compatibility alias.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>e6aba60 merge: production observability wiring</x:v>
+        <x:v>6284ce5 merge: online payment exposure gate</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after production observability wiring merged into develop.</x:v>
+        <x:v>Feature branch starts after online payment exposure gate merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,7 +758,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: complete online payment exposure gate</x:v>
+        <x:v>feat: add payment checkout post endpoint</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 14 pass; full Maven 450 pass</x:v>
+        <x:v>Targeted 17 pass; full Maven 452 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>PaymentMethodServiceTests, TripPaymentServiceTests, PaymentCompletionWorkflowTests and full ./mvnw.cmd test pass.</x:v>
+        <x:v>PaymentControllerTests, PaymentCheckoutServiceTests, PaymentSandboxUatPlanServiceTests and full ./mvnw.cmd test pass.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9f19fffaf924a56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8571e33201bd4186"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1268,13 +1268,13 @@
         <x:v>Cash payment, detail, checkout/webhook/config foundations</x:v>
       </x:c>
       <x:c r="C11" s="24" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
+        <x:v>/api/v1/payments/trips/{tripId}, POST /api/v1/payments/trips/{tripId}/checkout (GET legacy), /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="D11" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E11" s="24" t="str">
-        <x:v>CASH works; online provider registry, signed checkout and shared webhook foundations exist. Online pending payment now releases the driver after trip completion.</x:v>
+        <x:v>CASH works; online provider registry, signed checkout and shared webhook foundations exist. POST checkout is canonical for FE/provider checkout creation; GET remains compatibility. Online pending payment releases the driver after trip completion.</x:v>
       </x:c>
       <x:c r="F11" s="24"/>
       <x:c r="G11" s="24"/>
@@ -1388,13 +1388,13 @@
         <x:v>MoMo signed checkout and signature-verified IPN</x:v>
       </x:c>
       <x:c r="C17" s="24" t="str">
-        <x:v>/api/v1/payments/trips/{tripId}/checkout, /api/v1/payments/providers/momo/webhook</x:v>
+        <x:v>POST /api/v1/payments/trips/{tripId}/checkout (GET legacy), /api/v1/payments/providers/momo/webhook</x:v>
       </x:c>
       <x:c r="D17" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E17" s="24" t="str">
-        <x:v>Creates verified captureWallet checkout; IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
+        <x:v>Creates verified captureWallet checkout through the canonical POST checkout API; GET remains a legacy alias. IPN verifies HMAC/payment data, enforces freshness, maps state idempotently, runs completion once, and returns HTTP 204.</x:v>
       </x:c>
       <x:c r="F17" s="24"/>
       <x:c r="G17" s="24"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b36c240df184cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5b162ff891346a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R102f8cfe9b854281"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree211c0d560a4899"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2360,7 +2360,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>MoMo/VNPAY signed checkout/webhook, UAT/session APIs, protected callback workflow and /methods consumerEnabled gate are code-ready; run real merchant sandbox checkout/callback and record evidence.</x:v>
+        <x:v>MoMo/VNPAY signed checkout/webhook, canonical POST checkout contract, UAT/session APIs, protected callback workflow and /methods consumerEnabled gate are code-ready; run real merchant sandbox checkout/callback and record evidence.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
         <x:v>In progress</x:v>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bcf7b7349fe4084"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb5ca23aca3d495a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2609,10 +2609,10 @@
         <x:v>Payment checkout/callback</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, /checkout, /providers/{providerName}/webhook</x:v>
+        <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, POST /api/v1/payments/trips/{tripId}/checkout (GET legacy), /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false. Expose VNPAY/MoMo only when /payments/methods consumerEnabled=true; after redirect/callback, poll payment detail until status is terminal.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false. For online providers, call POST checkout after trip completion/payment PENDING, open checkoutUrl, then poll payment detail after redirect/callback. Expose VNPAY/MoMo only when /payments/methods consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e7b52b2d4146d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198dbc013e7f4b71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c74a8120f0a47bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e3526fffc24969"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rba1f4d63f843476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rfbf825602ba8428d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rff591199f78842e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Ra9b4e983c8ef42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R2f0c255a40e74aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R98045a2119db415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R26a13ad2372d49c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R71298d1d7df64155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R9d755ad2eede4184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf2d79f15b1774a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb599927a617f41be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd7e3b1fdbbeb44f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -710,7 +710,7 @@
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Payment checkout POST endpoint is implemented on feature branch.</x:v>
+        <x:v>Payment production exposure gate fix is implemented on feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/payment-checkout-post-endpoint</x:v>
+        <x:v>feature/payment-production-exposure-gate</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Adds canonical POST checkout endpoint while keeping GET /checkout as a compatibility alias.</x:v>
+        <x:v>Allows consumerEnabled=true after UAT evidence passes even when provider sandbox=false in production mode.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>6284ce5 merge: online payment exposure gate</x:v>
+        <x:v>39fb871 merge: payment checkout post endpoint</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after online payment exposure gate merged into develop.</x:v>
+        <x:v>Feature branch starts after checkout POST endpoint was merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,7 +758,7 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add payment checkout post endpoint</x:v>
+        <x:v>fix: allow production payment exposure after uat</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 17 pass; full Maven 452 pass</x:v>
+        <x:v>Targeted 11 pass; full Maven 454 pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>PaymentControllerTests, PaymentCheckoutServiceTests, PaymentSandboxUatPlanServiceTests and full ./mvnw.cmd test pass.</x:v>
+        <x:v>PaymentMethodServiceTests, PaymentSandboxUatResultServiceTests and full ./mvnw.cmd test pass.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8571e33201bd4186"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R947eb1263e2f46fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1294,7 +1294,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str">
-        <x:v>FE should use consumerEnabled to render passenger payment methods. enabled remains backend/UAT checkout availability; online consumer exposure requires aggregate readyForFrontendExposure=true.</x:v>
+        <x:v>FE should use consumerEnabled to render passenger payment methods. enabled remains backend/UAT checkout availability; online consumer exposure requires checkout+webhook readiness and aggregate readyForFrontendExposure=true, not current sandbox=true.</x:v>
       </x:c>
       <x:c r="F12" s="24"/>
       <x:c r="G12" s="24"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5b162ff891346a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61cab9027d3f411f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1956,7 +1956,7 @@
         <x:v>Sandbox merchant accounts, public callback URLs, fresh signed Base64 payload secrets, two pending payments per run and applied payment UAT SQL releases.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str">
-        <x:v>Workflow and real merchant checkout both pass; aggregate evidence is PASSED; /api/v1/payments/methods returns consumerEnabled=true for the provider.</x:v>
+        <x:v>Workflow and real merchant checkout both pass; aggregate evidence is PASSED; /api/v1/payments/methods returns consumerEnabled=true in sandbox and after switching provider config to production sandbox=false.</x:v>
       </x:c>
       <x:c r="F2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree211c0d560a4899"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3f2a772c4b434e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2360,7 +2360,7 @@
         <x:v>Payment provider completion</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>MoMo/VNPAY signed checkout/webhook, canonical POST checkout contract, UAT/session APIs, protected callback workflow and /methods consumerEnabled gate are code-ready; run real merchant sandbox checkout/callback and record evidence.</x:v>
+        <x:v>MoMo/VNPAY signed checkout/webhook, canonical POST checkout contract, UAT/session APIs, protected callback workflow and /methods consumerEnabled production gate are code-ready; run real merchant sandbox checkout/callback and record evidence.</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
         <x:v>In progress</x:v>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb5ca23aca3d495a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04f69c27d79d4522"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2594,7 +2594,7 @@
         <x:v>/api/v1/payments/methods</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>Render payment method options from backend; passenger UI should allow only consumerEnabled=true. enabled=true means backend/UAT checkout availability, not public exposure by itself.</x:v>
+        <x:v>Render payment method options from backend; passenger UI should allow only consumerEnabled=true. enabled=true means backend/UAT checkout availability, and sandbox=false in production must not hide a method when consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="D7" s="43" t="str">
         <x:v>Ready for FE</x:v>
@@ -2612,7 +2612,7 @@
         <x:v>/api/v1/payments/methods, /api/v1/payments/providers/readiness, /api/v1/payments/providers/sandbox-uat-plan, /api/v1/payments/providers/sandbox-uat-results, PUT /api/v1/payments/providers/{providerName}/sandbox-uat-result, GET/POST /api/v1/payments/providers/{providerName}/sandbox-e2e-sessions, /api/v1/payments/trips/{tripId}, POST /api/v1/payments/trips/{tripId}/checkout (GET legacy), /providers/{providerName}/webhook</x:v>
       </x:c>
       <x:c r="C8" s="24" t="str">
-        <x:v>For CASH, do not open a webview when checkoutRequired=false. For online providers, call POST checkout after trip completion/payment PENDING, open checkoutUrl, then poll payment detail after redirect/callback. Expose VNPAY/MoMo only when /payments/methods consumerEnabled=true.</x:v>
+        <x:v>For CASH, do not open a webview when checkoutRequired=false. For online providers, call POST checkout after trip completion/payment PENDING, open checkoutUrl, then poll payment detail after redirect/callback. Expose VNPAY/MoMo only when /payments/methods consumerEnabled=true, including production mode after UAT evidence passes.</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
         <x:v>Partial</x:v>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R198dbc013e7f4b71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab16318bbc74cb7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2988,7 +2988,7 @@
         <x:v>Frontend should not expose MoMo/VNPAY publicly until sandbox/UAT validation evidence is recorded and /payments/methods returns consumerEnabled=true.</x:v>
       </x:c>
       <x:c r="C2" s="24" t="str">
-        <x:v>Keep CASH as fallback. Run protected signed-callback automation plus separate real wallet/bank-app UAT; expose online methods from FE only via consumerEnabled=true.</x:v>
+        <x:v>Keep CASH as fallback. Run protected signed-callback automation plus separate real wallet/bank-app UAT; expose online methods from FE only via consumerEnabled=true and do not block solely because sandbox=false in production.</x:v>
       </x:c>
       <x:c r="D2" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28e3526fffc24969"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6e9cc843ae4272"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R26a13ad2372d49c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R71298d1d7df64155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R9d755ad2eede4184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf2d79f15b1774a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rb599927a617f41be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rd7e3b1fdbbeb44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5d4cc163cda047d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd3434667d6d240b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R642de77b5638411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R54e60b2846864614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R29ab6f8a273b4a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R928773c795b94396"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-19</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Payment production exposure gate fix is implemented on feature branch.</x:v>
+        <x:v>Driver location bootstrap is implemented on the feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/payment-production-exposure-gate</x:v>
+        <x:v>feature/driver-location-bootstrap</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Allows consumerEnabled=true after UAT evidence passes even when provider sandbox=false in production mode.</x:v>
+        <x:v>Maps the latest valid online heartbeat location to the trip immediately after offer acceptance.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>39fb871 merge: payment checkout post endpoint</x:v>
+        <x:v>eee3359 merge: harden trip startup and offer access</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature branch starts after checkout POST endpoint was merged into develop.</x:v>
+        <x:v>Current feature starts after the reviewed startup and active-offer access fixes were merged into develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>fix: allow production payment exposure after uat</x:v>
+        <x:v>feat: bootstrap driver location after offer accept</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>Committed</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>User review completed on 2026-07-19; commit created on feature branch, not merged or pushed yet.</x:v>
+        <x:v>Prepared on the feature branch for user review; not merged or pushed.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 11 pass; full Maven 454 pass</x:v>
+        <x:v>Targeted 26 pass; full Maven 460 pass + 10 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>PaymentMethodServiceTests, PaymentSandboxUatResultServiceTests and full ./mvnw.cmd test pass.</x:v>
+        <x:v>All unit/service tests pass. Ten Testcontainers integration tests cannot initialize because Docker access is unavailable; no assertion failures.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>User review completed; CodeRabbit unavailable</x:v>
+        <x:v>Internal review complete; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>User review completed on 2026-07-19; coderabbit command is not available in PATH.</x:v>
+        <x:v>Code and FE contract were reviewed; coderabbit command is not available in PATH.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R947eb1263e2f46fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa27419e79754d08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1245,16 +1245,16 @@
         <x:v>Tracking</x:v>
       </x:c>
       <x:c r="B10" s="24" t="str">
-        <x:v>Realtime driver location plus REST fallback</x:v>
+        <x:v>Realtime driver location, accept-time heartbeat bootstrap and REST fallback</x:v>
       </x:c>
       <x:c r="C10" s="24" t="str">
-        <x:v>/api/v1/tracking/trips/{tripId}/driver-location and WS channel</x:v>
+        <x:v>/api/v1/tracking/trips/{tripId}/driver-location and /topic/trip/{tripId}/location</x:v>
       </x:c>
       <x:c r="D10" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>Latest location stored in Redis.</x:v>
+        <x:v>After ACCEPTED, backend maps the latest valid Redis GEO heartbeat to the trip, caches it and broadcasts it before the first trip-scoped driver update; bearing/speed remain null until live tracking starts.</x:v>
       </x:c>
       <x:c r="F10" s="24"/>
       <x:c r="G10" s="24"/>
@@ -1903,7 +1903,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61cab9027d3f411f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R025aab06421d4e2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2060,13 +2060,13 @@
         <x:v>Driver availability</x:v>
       </x:c>
       <x:c r="C7" s="24" t="str">
-        <x:v>Add driver heartbeat and automatic offline timeout.</x:v>
+        <x:v>Driver heartbeat, automatic offline timeout and accept-time trip location bootstrap are implemented; production interval tuning remains.</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Redis TTL policy and scheduled cleanup/job behavior.</x:v>
+        <x:v>Redis TTL policy, scheduled cleanup/job behavior and mobile heartbeat cadence.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str">
-        <x:v>Stale drivers become unavailable for matching without manual offline action.</x:v>
+        <x:v>Stale drivers leave matching, accepted trips receive the latest valid heartbeat location immediately, and database online state is cleaned in configured batches.</x:v>
       </x:c>
       <x:c r="F7" s="43" t="str">
         <x:v>Done</x:v>
@@ -2319,7 +2319,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd3f2a772c4b434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64f6d8a74ebf4616"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2396,10 +2396,10 @@
         <x:v>Driver availability reliability</x:v>
       </x:c>
       <x:c r="C4" s="24" t="str">
-        <x:v>Heartbeat API, Redis TTL refresh and scheduled database offline timeout implemented; production interval tuning remains.</x:v>
+        <x:v>Heartbeat API, Redis TTL refresh, scheduled database offline timeout and accept-time trip location bootstrap are implemented; production interval and Redis/database soak tuning remain.</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Stale drivers are excluded from matching and database online state is cleaned in configured batches.</x:v>
+        <x:v>Stale drivers are excluded from matching; accepted trips expose a valid heartbeat location immediately; database online state is cleaned in configured batches.</x:v>
       </x:c>
       <x:c r="E4" s="24"/>
       <x:c r="F4" s="24"/>
@@ -2463,7 +2463,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04f69c27d79d4522"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a51fb28de9d441c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2735,13 +2735,13 @@
         <x:v>Passenger matching/tracking</x:v>
       </x:c>
       <x:c r="B15" s="24" t="str">
-        <x:v>Trip status topic and GET /api/v1/tracking/trips/{tripId}/driver-location</x:v>
+        <x:v>Trip status topic; GET /api/v1/tracking/trips/{tripId}/driver-location; /topic/trip/{tripId}/location</x:v>
       </x:c>
       <x:c r="C15" s="24" t="str">
-        <x:v>Handle SEARCHING as waiting-for-driver; once assigned, subscribe/poll location during ACCEPTED, ARRIVED, and IN_PROGRESS. Driver approach location is realtime before trip start.</x:v>
+        <x:v>Handle SEARCHING as waiting-for-driver. On ACCEPTED, call REST once to hydrate the bootstrapped heartbeat location, then continue WebSocket updates during ACCEPTED/ARRIVED/IN_PROGRESS. bearing/speed can be null in the bootstrap payload; DRIVER_LOCATION_NOT_FOUND is a temporary waiting state and must not cancel the trip.</x:v>
       </x:c>
       <x:c r="D15" s="43" t="str">
-        <x:v>Ready for FE</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E15" s="24"/>
       <x:c r="F15" s="24"/>
@@ -2947,7 +2947,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ab16318bbc74cb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd508afac75f41e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3039,10 +3039,10 @@
         <x:v>Heartbeat intervals are not production-calibrated.</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>Aggressive intervals may cause reconnect churn; loose intervals delay database cleanup.</x:v>
+        <x:v>Aggressive intervals may cause reconnect churn; loose intervals delay database cleanup and can make accept-time bootstrapped coordinates older.</x:v>
       </x:c>
       <x:c r="C5" s="24" t="str">
-        <x:v>Start with 20-second client heartbeat and 60-second timeout, then tune using staging disconnect and scheduler metrics.</x:v>
+        <x:v>Start with a 20-second client heartbeat and 60-second timeout, then tune using staging disconnect, location-age and scheduler metrics.</x:v>
       </x:c>
       <x:c r="D5" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3287,7 +3287,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6e9cc843ae4272"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3054887040a24a86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5d4cc163cda047d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rd3434667d6d240b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R642de77b5638411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R54e60b2846864614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R29ab6f8a273b4a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R928773c795b94396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R938be022bd90447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Ref6f932e18e94bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R48a9569f719b46da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4b03f5dd1edf4bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R35e6d08919534116"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R726ffa63237f4cc5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -396,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H43"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -413,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H19"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
@@ -447,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="FrontendTable" displayName="FrontendTable" ref="A1:H27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H27"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Screen / Flow"/>
     <x:tableColumn id="2" name="Backend Endpoint / Channel"/>
@@ -464,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H18"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H19"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -704,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Driver location bootstrap is implemented on the feature branch.</x:v>
+        <x:v>Three-word mobile location gateway completed after pre-merge review.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>feature/driver-location-bootstrap</x:v>
+        <x:v>codex/word-location-mobile</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Maps the latest valid online heartbeat location to the trip immediately after offer acceptance.</x:v>
+        <x:v>Authenticated GoRide APIs wrap the custom Python coordinate/three-word provider for passenger and driver mobile flows.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>eee3359 merge: harden trip startup and offer access</x:v>
+        <x:v>5b941d6 merge: driver location bootstrap</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Current feature starts after the reviewed startup and active-offer access fixes were merged into develop.</x:v>
+        <x:v>Feature starts from the latest reviewed develop commit.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: bootstrap driver location after offer accept</x:v>
+        <x:v>feat: integrate three-word mobile location lookup</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>In review</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Prepared on the feature branch for user review; not merged or pushed.</x:v>
+        <x:v>Review findings resolved and feature approved for merge into develop.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 26 pass; full Maven 460 pass + 10 Docker errors</x:v>
+        <x:v>Targeted 32 pass; full Maven 485 pass + 10 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>All unit/service tests pass. Ten Testcontainers integration tests cannot initialize because Docker access is unavailable; no assertion failures.</x:v>
+        <x:v>Feature/security tests pass. Ten Testcontainers tests cannot initialize because Docker access is unavailable; no assertion failures.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Internal review complete; CodeRabbit unavailable</x:v>
+        <x:v>Internal review findings resolved; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Code and FE contract were reviewed; coderabbit command is not available in PATH.</x:v>
+        <x:v>Default-disable config, address consistency and cell-bounds validation were fixed before commit.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -836,7 +836,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D9" s="24" t="str">
-        <x:v>Keep environment-specific local changes uncommitted.</x:v>
+        <x:v>Keep environment-specific local changes uncommitted during commit and merge.</x:v>
       </x:c>
       <x:c r="E9" s="24" t="str"/>
       <x:c r="F9" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa27419e79754d08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f8af05d7004d7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1900,10 +1900,30 @@
       <x:c r="G42"/>
       <x:c r="H42"/>
     </x:row>
+    <x:row r="43" ht="54" customHeight="1">
+      <x:c r="A43" s="68" t="str">
+        <x:v>Location</x:v>
+      </x:c>
+      <x:c r="B43" s="68" t="str">
+        <x:v>Three-word coordinate conversion gateway and mobile contract</x:v>
+      </x:c>
+      <x:c r="C43" s="68" t="str">
+        <x:v>GET /api/v1/locations/to-words; GET /api/v1/locations/to-coordinate</x:v>
+      </x:c>
+      <x:c r="D43" s="68" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E43" s="68" t="str">
+        <x:v>JWT roles PASSENGER/DRIVER; provider disabled by default; validates normalized address, WGS84 coordinates and ordered cell bounds.</x:v>
+      </x:c>
+      <x:c r="F43"/>
+      <x:c r="G43"/>
+      <x:c r="H43"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R025aab06421d4e2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611f9b9a3b6a41a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2316,10 +2336,32 @@
       <x:c r="G18" s="27"/>
       <x:c r="H18" s="28"/>
     </x:row>
+    <x:row r="19" ht="72" customHeight="1">
+      <x:c r="A19" s="68" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="B19" s="68" t="str">
+        <x:v>Three-word provider UAT</x:v>
+      </x:c>
+      <x:c r="C19" s="68" t="str">
+        <x:v>Deploy the custom Python provider and validate both conversion directions from real mobile devices.</x:v>
+      </x:c>
+      <x:c r="D19" s="68" t="str">
+        <x:v>Reachable provider hostname, production dictionary/map data and THREE_WORD_LOCATION_* environment settings.</x:v>
+      </x:c>
+      <x:c r="E19" s="68" t="str">
+        <x:v>Passenger pin lookup and driver address preview return consistent coordinates/bounds; provider outage never blocks booking or trip navigation.</x:v>
+      </x:c>
+      <x:c r="F19" s="68" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64f6d8a74ebf4616"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729846d4e7de43aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2450,10 +2492,10 @@
         <x:v>Product expansion</x:v>
       </x:c>
       <x:c r="C7" s="27" t="str">
-        <x:v>Local upload foundation, Cloudflare R2 provider, in-trip messaging, scheduled rides, surge pricing rules and service area zones are implemented/in review; finish R2 deployment UAT, surge tuning, real zone data and analytics.</x:v>
+        <x:v>Local upload foundation, Cloudflare R2 provider, in-trip messaging, scheduled rides, surge pricing rules, service area zones and three-word mobile location gateway are implemented/in review; finish provider/R2 deployment UAT, surge tuning, real zone data and analytics.</x:v>
       </x:c>
       <x:c r="D7" s="27" t="str">
-        <x:v>Production upload storage is verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated; launch-city service polygons are validated with common pickup/dropoff pairs.</x:v>
+        <x:v>Production upload and three-word providers are verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated; launch-city service polygons are validated.</x:v>
       </x:c>
       <x:c r="E7" s="27"/>
       <x:c r="F7" s="27"/>
@@ -2463,7 +2505,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a51fb28de9d441c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a13f9905ad4d88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2944,10 +2986,28 @@
       <x:c r="G26"/>
       <x:c r="H26"/>
     </x:row>
+    <x:row r="27" ht="72" customHeight="1">
+      <x:c r="A27" s="68" t="str">
+        <x:v>Three-word location lookup</x:v>
+      </x:c>
+      <x:c r="B27" s="68" t="str">
+        <x:v>GET /api/v1/locations/to-words?lat=&amp;lng=; GET /api/v1/locations/to-coordinate?address=</x:v>
+      </x:c>
+      <x:c r="C27" s="68" t="str">
+        <x:v>Passenger resolves a selected pin on demand; driver previews returned marker/bounds and confirms before navigation. Keep lat/lng and street address as booking source of truth.</x:v>
+      </x:c>
+      <x:c r="D27" s="68" t="str">
+        <x:v>Ready for FE</x:v>
+      </x:c>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd508afac75f41e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48cd8730721149eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3284,10 +3344,28 @@
       <x:c r="G18"/>
       <x:c r="H18"/>
     </x:row>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="68" t="str">
+        <x:v>Custom three-word provider is an external runtime dependency.</x:v>
+      </x:c>
+      <x:c r="B19" s="68" t="str">
+        <x:v>If the Python service, dictionary or supported map is unavailable, optional lookup returns 502/503.</x:v>
+      </x:c>
+      <x:c r="C19" s="68" t="str">
+        <x:v>Keep provider disabled by default, deploy it on a reachable private hostname, monitor failures and preserve coordinate/street-address fallback in mobile flows.</x:v>
+      </x:c>
+      <x:c r="D19" s="68" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3054887040a24a86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc272e0665e4c45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R938be022bd90447a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Ref6f932e18e94bc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R48a9569f719b46da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="R4b03f5dd1edf4bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R35e6d08919534116"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R726ffa63237f4cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R71ac023c16174024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R8788818833dd4a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rb04df3dbad9a4454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf39a64472dd2487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R68fd69eaf159415f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0e6a9e71b5a4404b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,13 +704,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Three-word mobile location gateway completed after pre-merge review.</x:v>
+        <x:v>Driver routing fallback was approved and committed on the feature branch.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +722,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>codex/word-location-mobile</x:v>
+        <x:v>codex/driver-routing-fallback</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Authenticated GoRide APIs wrap the custom Python coordinate/three-word provider for passenger and driver mobile flows.</x:v>
+        <x:v>User review completed; assigned-driver routing has a labeled straight-line fallback.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +740,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>5b941d6 merge: driver location bootstrap</x:v>
+        <x:v>ae3dac2 merge admin-v2</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature starts from the latest reviewed develop commit.</x:v>
+        <x:v>Feature starts from current origin/develop.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +758,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: integrate three-word mobile location lookup</x:v>
+        <x:v>feat: add driver routing fallback</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Review findings resolved and feature approved for merge into develop.</x:v>
+        <x:v>Feature commit completed locally and awaits merge into develop.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +776,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted 32 pass; full Maven 485 pass + 10 Docker errors</x:v>
+        <x:v>Targeted routing/controller: 10 pass; full Maven: 3 failures + 18 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
-        <x:v>Partial</x:v>
+        <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Feature/security tests pass. Ten Testcontainers tests cannot initialize because Docker access is unavailable; no assertion failures.</x:v>
+        <x:v>Routing fallback cases pass; full-suite failures are baseline config/location assertions and unavailable Docker.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -812,13 +812,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Internal review findings resolved; CodeRabbit unavailable</x:v>
+        <x:v>Internal review complete; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Default-disable config, address consistency and cell-bounds validation were fixed before commit.</x:v>
+        <x:v>Manual and user review completed with no remaining routing fallback issue; CodeRabbit is not installed in PATH.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1044,7 +1044,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f8af05d7004d7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8164e898c0a249fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1454,7 +1454,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E20" s="24" t="str">
-        <x:v>Validates assigned driver and trip status; returns destination, distance/duration, GeoJSON LineString, and OSRM maneuver steps.</x:v>
+        <x:v>Validates assigned driver and trip status; returns provider distance/duration, GeoJSON LineString and maneuvers when available. ROUTING_PROVIDER_ERROR can degrade to a labeled straight-line LineString with steps=[] when configured.</x:v>
       </x:c>
       <x:c r="F20" s="24"/>
       <x:c r="G20" s="24"/>
@@ -1923,7 +1923,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611f9b9a3b6a41a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b124f31611249db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2322,13 +2322,13 @@
         <x:v>Routing UAT</x:v>
       </x:c>
       <x:c r="C18" s="27" t="str">
-        <x:v>Validate driver navigation against a controlled production/self-hosted routing endpoint and add request-rate controls.</x:v>
+        <x:v>Validate driver navigation against a controlled production/self-hosted routing endpoint, monitor fallback frequency and add request-rate controls.</x:v>
       </x:c>
       <x:c r="D18" s="27" t="str">
-        <x:v>OSRM-compatible endpoint, staging GPS routes, metrics/rate-limit policy.</x:v>
+        <x:v>OSRM-compatible endpoint, staging GPS routes, fallback metrics and rate-limit policy.</x:v>
       </x:c>
       <x:c r="E18" s="27" t="str">
-        <x:v>Vietnam routes are accurate enough, latency/error rate is measured, and FE re-route requests are debounced or rate-limited.</x:v>
+        <x:v>Vietnam routes are accurate enough, latency/error/fallback rates are measured, and FE re-route requests are debounced or rate-limited.</x:v>
       </x:c>
       <x:c r="F18" s="64" t="str">
         <x:v>Partial</x:v>
@@ -2361,7 +2361,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729846d4e7de43aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806b9a8d0bb64b67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2420,7 +2420,7 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Fare estimation and assigned-driver pickup/dropoff GeoJSON routing implemented; production endpoint UAT, request-rate control, monitoring, and timeout tuning remain.</x:v>
+        <x:v>Fare estimation, pickup/dropoff GeoJSON routing and labeled straight-line driver fallback are implemented; production endpoint UAT, request-rate control, fallback monitoring and timeout tuning remain.</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
@@ -2505,7 +2505,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3a13f9905ad4d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15942cd629ef4b90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2726,7 +2726,7 @@
         <x:v>POST /api/v1/drivers/trips/{tripId}/route</x:v>
       </x:c>
       <x:c r="C12" s="24" t="str">
-        <x:v>Send current GPS; draw GeoJSON LineString to pickup while ACCEPTED and dropoff after ARRIVED; debounce re-route and handle provider fallback to external maps.</x:v>
+        <x:v>Send current GPS and inspect routeSource. For PROVIDER, draw route and maneuvers. For STRAIGHT_LINE_FALLBACK, show degraded guidance, hide turn-by-turn steps and offer external navigation. Debounce re-route calls.</x:v>
       </x:c>
       <x:c r="D12" s="43" t="str">
         <x:v>Ready for FE</x:v>
@@ -3007,7 +3007,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48cd8730721149eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f217b4920f74a77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3081,10 +3081,10 @@
         <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>Fare estimates and driver navigation geometry are implemented, but endpoint capacity, request rate, latency, and Vietnamese road quality are not validated.</x:v>
+        <x:v>Driver routing now remains available as labeled straight-line guidance during provider failure, but endpoint capacity, fallback frequency, request rate, latency and Vietnamese road quality are not validated.</x:v>
       </x:c>
       <x:c r="C4" s="24" t="str">
-        <x:v>Use a controlled OSRM-compatible endpoint, debounce/re-route on FE, add rate/latency metrics, and tune profile/timeout before launch.</x:v>
+        <x:v>Use a controlled OSRM-compatible endpoint, debounce/re-route on FE, monitor STRAIGHT_LINE_FALLBACK frequency, add rate/latency metrics and tune profile/timeout before launch.</x:v>
       </x:c>
       <x:c r="D4" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3365,7 +3365,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bc272e0665e4c45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb38e6edce2d4c1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R71ac023c16174024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R8788818833dd4a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rb04df3dbad9a4454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf39a64472dd2487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R68fd69eaf159415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R0e6a9e71b5a4404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdda40accdd194b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R09d93273ab2b4261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf025225c206a4b04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rd5842a4a34ae42f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd3313357f6c84705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R286363e4d63b492d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -40,8 +40,20 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF274E13"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C5700"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -86,6 +98,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -185,7 +207,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="69">
+  <x:cellXfs count="82">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -370,6 +392,37 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -396,8 +449,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H44"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -413,8 +466,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H20"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
@@ -464,8 +517,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H20"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -704,13 +757,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Driver routing fallback was approved and committed on the feature branch.</x:v>
+        <x:v>GPS filtering for actual fare was approved by the user.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -722,13 +775,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>codex/driver-routing-fallback</x:v>
+        <x:v>codex/gps-fare-filtering</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>User review completed; assigned-driver routing has a labeled straight-line fallback.</x:v>
+        <x:v>Approved feature is included in commit feat: filter gps distance for actual fare.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -740,13 +793,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>ae3dac2 merge admin-v2</x:v>
+        <x:v>a687c1d merge: driver routing fallback</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature starts from current origin/develop.</x:v>
+        <x:v>Feature starts from the latest local develop merge.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -758,13 +811,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: add driver routing fallback</x:v>
+        <x:v>feat: filter gps distance for actual fare</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Feature commit completed locally and awaits merge into develop.</x:v>
+        <x:v>Reviewed implementation and tracking documents are committed together before merge to develop.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -776,13 +829,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted routing/controller: 10 pass; full Maven: 3 failures + 18 Docker errors</x:v>
+        <x:v>Targeted suite: 29 pass; full Maven: 572 tests, 3 baseline failures + 18 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Routing fallback cases pass; full-suite failures are baseline config/location assertions and unavailable Docker.</x:v>
+        <x:v>GPS filtering tests pass; full-suite failures are existing local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -812,13 +865,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>Internal review complete; CodeRabbit unavailable</x:v>
+        <x:v>User and internal review complete; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>Manual and user review completed with no remaining routing fallback issue; CodeRabbit is not installed in PATH.</x:v>
+        <x:v>No blocking issue found; CodeRabbit is not installed in PATH.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1044,7 +1097,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8164e898c0a249fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R481cc70dd6344729"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1920,10 +1973,30 @@
       <x:c r="G43"/>
       <x:c r="H43"/>
     </x:row>
+    <x:row r="44" ht="72" customHeight="1">
+      <x:c r="A44" s="74" t="str">
+        <x:v>Payment</x:v>
+      </x:c>
+      <x:c r="B44" s="74" t="str">
+        <x:v>GPS-filtered completed-trip actual distance</x:v>
+      </x:c>
+      <x:c r="C44" s="74" t="str">
+        <x:v>TripCompletionFareService / trip completion</x:v>
+      </x:c>
+      <x:c r="D44" s="75" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E44" s="74" t="str">
+        <x:v>Filters sub-5m jitter, implausible speed, non-increasing timestamps and distance across long tracking gaps. Long gaps rebase the anchor; when no segment remains valid, final fare uses the trip estimate. No API or schema change.</x:v>
+      </x:c>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b124f31611249db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf04f40bbde7d4288"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2358,10 +2431,32 @@
       <x:c r="G19"/>
       <x:c r="H19"/>
     </x:row>
+    <x:row r="20" ht="84" customHeight="1">
+      <x:c r="A20" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B20" s="74" t="str">
+        <x:v>GPS fare filtering calibration</x:v>
+      </x:c>
+      <x:c r="C20" s="74" t="str">
+        <x:v>Tune jitter, speed and tracking-gap thresholds against real device traces; add rejected-segment and estimate-fallback metrics.</x:v>
+      </x:c>
+      <x:c r="D20" s="74" t="str">
+        <x:v>Staging trips across device models and vehicle types, GPS traces, fare reconciliation samples and monitoring.</x:v>
+      </x:c>
+      <x:c r="E20" s="74" t="str">
+        <x:v>Spike/noise scenarios do not overcharge; legitimate route distance stays within agreed tolerance; rejected-segment and estimate-fallback rates are observable.</x:v>
+      </x:c>
+      <x:c r="F20" s="81" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R806b9a8d0bb64b67"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47b48a897ae4d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2420,7 +2515,7 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Fare estimation, pickup/dropoff GeoJSON routing and labeled straight-line driver fallback are implemented; production endpoint UAT, request-rate control, fallback monitoring and timeout tuning remain.</x:v>
+        <x:v>Fare estimation, pickup/dropoff GeoJSON routing, labeled straight-line driver fallback and GPS-filtered completed-trip distance are implemented; controlled endpoint UAT, request-rate control, fallback monitoring and real-device GPS threshold calibration remain.</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
@@ -2505,7 +2600,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15942cd629ef4b90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363f4b95649f440e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2780,7 +2875,7 @@
         <x:v>Trip status topic; GET /api/v1/tracking/trips/{tripId}/driver-location; /topic/trip/{tripId}/location</x:v>
       </x:c>
       <x:c r="C15" s="24" t="str">
-        <x:v>Handle SEARCHING as waiting-for-driver. On ACCEPTED, call REST once to hydrate the bootstrapped heartbeat location, then continue WebSocket updates during ACCEPTED/ARRIVED/IN_PROGRESS. bearing/speed can be null in the bootstrap payload; DRIVER_LOCATION_NOT_FOUND is a temporary waiting state and must not cancel the trip.</x:v>
+        <x:v>Handle SEARCHING as waiting-for-driver. On ACCEPTED, call REST once to hydrate the bootstrapped heartbeat location, then continue WebSocket updates during ACCEPTED/ARRIVED/IN_PROGRESS. bearing/speed can be null in the bootstrap payload; DRIVER_LOCATION_NOT_FOUND is a temporary waiting state and must not cancel the trip. After completion, display backend finalFare/actualDistanceKm and do not recalculate fare from raw location points.</x:v>
       </x:c>
       <x:c r="D15" s="43" t="str">
         <x:v>In review</x:v>
@@ -3007,7 +3102,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f217b4920f74a77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd88d19b0e4e14ceb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3362,10 +3457,28 @@
       <x:c r="G19"/>
       <x:c r="H19"/>
     </x:row>
+    <x:row r="20" ht="84" customHeight="1">
+      <x:c r="A20" s="74" t="str">
+        <x:v>GPS fare thresholds are not production-calibrated.</x:v>
+      </x:c>
+      <x:c r="B20" s="74" t="str">
+        <x:v>Thresholds that are too strict can undercount legitimate travel; thresholds that are too loose can retain noise and inflate final fare.</x:v>
+      </x:c>
+      <x:c r="C20" s="74" t="str">
+        <x:v>Replay real-device traces in staging, reconcile against routed/odometer samples, monitor rejection and estimate-fallback rates, then tune environment settings without a code release.</x:v>
+      </x:c>
+      <x:c r="D20" s="81" t="str">
+        <x:v>Partial</x:v>
+      </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb38e6edce2d4c1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83668811fb30478c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rdda40accdd194b20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R09d93273ab2b4261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="Rf025225c206a4b04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rd5842a4a34ae42f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Rd3313357f6c84705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R286363e4d63b492d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R51e3f76dee774d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Ra2db3047cb094949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R2f90ba02a4ac466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re269f58012e0484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R848a4623cc0649df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf7e5e84e49d94992"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -52,8 +52,14 @@
       <x:color rgb="FF9C5700"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF990000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="12">
+  <x:fills count="16">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -108,6 +114,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -207,7 +233,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="82">
+  <x:cellXfs count="98">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -423,6 +449,46 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -449,8 +515,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H44"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTable" displayName="CompletedTable" ref="A1:H46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H46"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Module"/>
     <x:tableColumn id="2" name="Feature"/>
@@ -466,8 +532,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H22"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
@@ -763,7 +829,7 @@
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>GPS filtering for actual fare was approved by the user.</x:v>
+        <x:v>Redis routing estimate cache was approved by the user.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -775,13 +841,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>codex/gps-fare-filtering</x:v>
+        <x:v>codex/routing-estimate-cache</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Approved feature is included in commit feat: filter gps distance for actual fare.</x:v>
+        <x:v>Approved feature is included in commit perf: cache routing estimates.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -793,13 +859,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>a687c1d merge: driver routing fallback</x:v>
+        <x:v>caf3cd1 merge: gps fare filtering</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature starts from the latest local develop merge.</x:v>
+        <x:v>Feature starts after the reviewed GPS filtering merge.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -811,13 +877,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: filter gps distance for actual fare</x:v>
+        <x:v>perf: cache routing estimates</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Reviewed implementation and tracking documents are committed together before merge to develop.</x:v>
+        <x:v>Reviewed implementation and documentation are committed before the develop merge.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -829,13 +895,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted suite: 29 pass; full Maven: 572 tests, 3 baseline failures + 18 Docker errors</x:v>
+        <x:v>Targeted suite: 22 pass; full Maven: 584 tests, 3 baseline failures + 18 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>GPS filtering tests pass; full-suite failures are existing local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
+        <x:v>Routing cache tests pass; full-suite failures are existing local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -1097,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R481cc70dd6344729"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096d6029693145f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1993,10 +2059,50 @@
       <x:c r="G44"/>
       <x:c r="H44"/>
     </x:row>
+    <x:row r="45" ht="78" customHeight="1">
+      <x:c r="A45" s="74" t="str">
+        <x:v>Routing</x:v>
+      </x:c>
+      <x:c r="B45" s="74" t="str">
+        <x:v>Redis cache for successful route estimates</x:v>
+      </x:c>
+      <x:c r="C45" s="74" t="str">
+        <x:v>/api/v1/bookings/estimate; POST /api/v1/bookings</x:v>
+      </x:c>
+      <x:c r="D45" s="94" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E45" s="74" t="str">
+        <x:v>Caches successful provider distance/duration JSON for five minutes using routing profile and pickup/dropoff rounded to four decimals. Redis failures are non-blocking; malformed entries are evicted; fallback estimates are not cached. No FE contract change.</x:v>
+      </x:c>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>Routing</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Redis cache for successful route estimates</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>/api/v1/bookings/estimate; POST /api/v1/bookings</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Caches successful provider distance/duration JSON for five minutes using routing profile and pickup/dropoff rounded to four decimals. Redis failures are non-blocking; malformed entries are evicted; fallback estimates are not cached. No FE contract change.</x:v>
+      </x:c>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf04f40bbde7d4288"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78ed17144c7c4dff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2453,10 +2559,54 @@
       <x:c r="G20"/>
       <x:c r="H20"/>
     </x:row>
+    <x:row r="21" ht="84" customHeight="1">
+      <x:c r="A21" s="74" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B21" s="74" t="str">
+        <x:v>Route-ETA driver ranking</x:v>
+      </x:c>
+      <x:c r="C21" s="74" t="str">
+        <x:v>Use Redis GEO for the nearby shortlist, include driver coordinates and rank a bounded top N by provider route ETA with distance-order fallback.</x:v>
+      </x:c>
+      <x:c r="D21" s="74" t="str">
+        <x:v>Controlled routing provider, candidate coordinates, Redis GEO and matching latency/rate metrics.</x:v>
+      </x:c>
+      <x:c r="E21" s="74" t="str">
+        <x:v>Matching chooses the fastest reachable driver from a bounded shortlist; provider/cache failure preserves existing Redis-distance ordering and offer flow.</x:v>
+      </x:c>
+      <x:c r="F21" s="96" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Route-ETA driver ranking</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Use Redis GEO for the nearby shortlist, include driver coordinates and rank a bounded top N by provider route ETA with distance-order fallback.</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Controlled routing provider, candidate coordinates, Redis GEO and matching latency/rate metrics.</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Matching chooses the fastest reachable driver from a bounded shortlist; provider/cache failure preserves existing Redis-distance ordering and offer flow.</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47b48a897ae4d61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re027290c40744110"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2515,7 +2665,7 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Fare estimation, pickup/dropoff GeoJSON routing, labeled straight-line driver fallback and GPS-filtered completed-trip distance are implemented; controlled endpoint UAT, request-rate control, fallback monitoring and real-device GPS threshold calibration remain.</x:v>
+        <x:v>Fare estimation, Redis estimate cache, pickup/dropoff GeoJSON routing, labeled straight-line fallback and GPS-filtered completed-trip distance are implemented; route-ETA candidate ranking, controlled endpoint UAT, cache/fallback metrics and threshold tuning remain.</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
@@ -2600,7 +2750,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363f4b95649f440e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02f574da0c44c5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2713,7 +2863,7 @@
         <x:v>/api/v1/bookings/estimate</x:v>
       </x:c>
       <x:c r="C6" s="24" t="str">
-        <x:v>Show distance/duration plus baseFare, surgeAmount, pricing/dynamic/effective multipliers and a surge badge when surge.surgeApplied=true. FE never recalculates fare; refresh estimate before final confirm if user waits.</x:v>
+        <x:v>Show distance/duration plus baseFare, surgeAmount, pricing/dynamic/effective multipliers and a surge badge when surge.surgeApplied=true. FE never recalculates fare; refresh estimate before final confirm if user waits. Backend cache hits are transparent, but FE should still debounce calls while the map pin moves.</x:v>
       </x:c>
       <x:c r="D6" s="43" t="str">
         <x:v>Ready for FE</x:v>
@@ -3102,7 +3252,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd88d19b0e4e14ceb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b7ebc511dc4c4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3176,10 +3326,10 @@
         <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>Driver routing now remains available as labeled straight-line guidance during provider failure, but endpoint capacity, fallback frequency, request rate, latency and Vietnamese road quality are not validated.</x:v>
+        <x:v>Redis caching reduces repeated successful estimate calls, but endpoint capacity, cache hit rate, route request rate, latency and Vietnamese road quality are not validated.</x:v>
       </x:c>
       <x:c r="C4" s="24" t="str">
-        <x:v>Use a controlled OSRM-compatible endpoint, debounce/re-route on FE, monitor STRAIGHT_LINE_FALLBACK frequency, add rate/latency metrics and tune profile/timeout before launch.</x:v>
+        <x:v>Use a controlled OSRM-compatible endpoint, monitor cache hit/miss and STRAIGHT_LINE_FALLBACK frequency, debounce FE requests, add rate/latency metrics and tune cache precision/TTL plus provider timeout before launch.</x:v>
       </x:c>
       <x:c r="D4" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3478,7 +3628,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83668811fb30478c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9be178c2a5b04dea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R51e3f76dee774d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Ra2db3047cb094949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R2f90ba02a4ac466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Re269f58012e0484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R848a4623cc0649df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Rf7e5e84e49d94992"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R794dc18ae47e4f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R527cfae65a1d44b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R175c3a37890540ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf659e5668c094556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R79420e9a0d334bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Ra94422769f884fbd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -58,8 +58,14 @@
       <x:color rgb="FF990000"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F6000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="16">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -129,6 +135,31 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAD3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -233,7 +264,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="98">
+  <x:cellXfs count="118">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -488,6 +519,58 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -823,13 +906,13 @@
         <x:v>Generated date</x:v>
       </x:c>
       <x:c r="B2" s="24" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Redis routing estimate cache was approved by the user.</x:v>
+        <x:v>Bounded Redis GEO route-ETA matching was approved by the user.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -841,13 +924,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>codex/routing-estimate-cache</x:v>
+        <x:v>codex/matching-route-eta-ranking</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
         <x:v>Reviewed</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Approved feature is included in commit perf: cache routing estimates.</x:v>
+        <x:v>Approved feature is included in commit feat: rank matching candidates by route eta.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -859,13 +942,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>caf3cd1 merge: gps fare filtering</x:v>
+        <x:v>ffe9964 merge: routing estimate cache</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature starts after the reviewed GPS filtering merge.</x:v>
+        <x:v>Feature starts after the reviewed routing cache merge.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -877,13 +960,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>perf: cache routing estimates</x:v>
+        <x:v>feat: rank matching candidates by route eta</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
         <x:v>Committed</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Reviewed implementation and documentation are committed before the develop merge.</x:v>
+        <x:v>Reviewed implementation and documentation are committed on the feature branch.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -895,13 +978,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted suite: 22 pass; full Maven: 584 tests, 3 baseline failures + 18 Docker errors</x:v>
+        <x:v>Targeted suite: 41 pass; Spring context pass; full Maven: 597 tests, 3 baseline failures + 18 Docker errors</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Routing cache tests pass; full-suite failures are existing local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
+        <x:v>Route-ETA tests pass; full-suite failures remain local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -919,7 +1002,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>Only Windows CRLF conversion warnings are reported by Git.</x:v>
+        <x:v>No whitespace error is reported.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -1163,7 +1246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R096d6029693145f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf190ec02cf3469c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2079,21 +2162,21 @@
       <x:c r="G45"/>
       <x:c r="H45"/>
     </x:row>
-    <x:row r="46">
-      <x:c r="A46" t="str">
-        <x:v>Routing</x:v>
-      </x:c>
-      <x:c r="B46" t="str">
-        <x:v>Redis cache for successful route estimates</x:v>
-      </x:c>
-      <x:c r="C46" t="str">
-        <x:v>/api/v1/bookings/estimate; POST /api/v1/bookings</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="E46" t="str">
-        <x:v>Caches successful provider distance/duration JSON for five minutes using routing profile and pickup/dropoff rounded to four decimals. Redis failures are non-blocking; malformed entries are evicted; fallback estimates are not cached. No FE contract change.</x:v>
+    <x:row r="46" ht="88" customHeight="1">
+      <x:c r="A46" s="74" t="str">
+        <x:v>Matching</x:v>
+      </x:c>
+      <x:c r="B46" s="74" t="str">
+        <x:v>Redis GEO shortlist with opt-in route-ETA ranking</x:v>
+      </x:c>
+      <x:c r="C46" s="74" t="str">
+        <x:v>Internal matching flow; Redis GEO; OSRM-compatible route estimate/cache</x:v>
+      </x:c>
+      <x:c r="D46" s="112" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="E46" s="74" t="str">
+        <x:v>Includes driver coordinates, ranks a bounded top N by provider duration/route distance using concurrent no-queue execution, and atomically falls back to Redis-distance order on any incomplete result. FE offer contract is unchanged.</x:v>
       </x:c>
       <x:c r="F46"/>
       <x:c r="G46"/>
@@ -2102,7 +2185,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78ed17144c7c4dff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39c783e3e11c4371"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2559,45 +2642,45 @@
       <x:c r="G20"/>
       <x:c r="H20"/>
     </x:row>
-    <x:row r="21" ht="84" customHeight="1">
+    <x:row r="21" ht="88" customHeight="1">
       <x:c r="A21" s="74" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="B21" s="74" t="str">
-        <x:v>Route-ETA driver ranking</x:v>
+        <x:v>Route-ETA ranking UAT</x:v>
       </x:c>
       <x:c r="C21" s="74" t="str">
-        <x:v>Use Redis GEO for the nearby shortlist, include driver coordinates and rank a bounded top N by provider route ETA with distance-order fallback.</x:v>
+        <x:v>Enable the implemented bounded route-ETA ranking in staging and validate fastest-route selection, latency and fallback behavior.</x:v>
       </x:c>
       <x:c r="D21" s="74" t="str">
-        <x:v>Controlled routing provider, candidate coordinates, Redis GEO and matching latency/rate metrics.</x:v>
+        <x:v>Controlled/self-hosted routing provider, real driver GPS, matching latency and fallback metrics.</x:v>
       </x:c>
       <x:c r="E21" s="74" t="str">
-        <x:v>Matching chooses the fastest reachable driver from a bounded shortlist; provider/cache failure preserves existing Redis-distance ordering and offer flow.</x:v>
-      </x:c>
-      <x:c r="F21" s="96" t="str">
-        <x:v>Open</x:v>
+        <x:v>Real-road tests select the fastest reachable candidate, matching latency stays within target, and failures preserve Redis-distance offer order.</x:v>
+      </x:c>
+      <x:c r="F21" s="114" t="str">
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="G21"/>
       <x:c r="H21"/>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
+    <x:row r="22" ht="88" customHeight="1">
+      <x:c r="A22" s="74" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="B22" t="str">
-        <x:v>Route-ETA driver ranking</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>Use Redis GEO for the nearby shortlist, include driver coordinates and rank a bounded top N by provider route ETA with distance-order fallback.</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>Controlled routing provider, candidate coordinates, Redis GEO and matching latency/rate metrics.</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>Matching chooses the fastest reachable driver from a bounded shortlist; provider/cache failure preserves existing Redis-distance ordering and offer flow.</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
+      <x:c r="B22" s="74" t="str">
+        <x:v>Routing and matching observability</x:v>
+      </x:c>
+      <x:c r="C22" s="74" t="str">
+        <x:v>Add cache hit/miss, provider latency/error, route-ETA fallback and executor saturation metrics before production enablement.</x:v>
+      </x:c>
+      <x:c r="D22" s="74" t="str">
+        <x:v>Metrics backend, controlled routing endpoint and staging load profile.</x:v>
+      </x:c>
+      <x:c r="E22" s="74" t="str">
+        <x:v>Dashboards show provider/cache/executor health and alerts identify elevated matching fallback or latency before passengers are affected.</x:v>
+      </x:c>
+      <x:c r="F22" s="116" t="str">
         <x:v>Open</x:v>
       </x:c>
       <x:c r="G22"/>
@@ -2606,7 +2689,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re027290c40744110"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0b11e9797f84c1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2665,7 +2748,7 @@
         <x:v>Real-world routing</x:v>
       </x:c>
       <x:c r="C3" s="24" t="str">
-        <x:v>Fare estimation, Redis estimate cache, pickup/dropoff GeoJSON routing, labeled straight-line fallback and GPS-filtered completed-trip distance are implemented; route-ETA candidate ranking, controlled endpoint UAT, cache/fallback metrics and threshold tuning remain.</x:v>
+        <x:v>Fare estimation/cache, pickup/dropoff routing/fallback, GPS-filtered actual distance and opt-in bounded route-ETA matching are implemented; controlled endpoint UAT, matching/routing metrics and timeout/executor tuning remain.</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
         <x:v>Controlled endpoint returns stable Vietnamese routes and driver re-route traffic stays within operational limits.</x:v>
@@ -2750,7 +2833,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd02f574da0c44c5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08eadd966bb24050"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3025,7 +3108,7 @@
         <x:v>Trip status topic; GET /api/v1/tracking/trips/{tripId}/driver-location; /topic/trip/{tripId}/location</x:v>
       </x:c>
       <x:c r="C15" s="24" t="str">
-        <x:v>Handle SEARCHING as waiting-for-driver. On ACCEPTED, call REST once to hydrate the bootstrapped heartbeat location, then continue WebSocket updates during ACCEPTED/ARRIVED/IN_PROGRESS. bearing/speed can be null in the bootstrap payload; DRIVER_LOCATION_NOT_FOUND is a temporary waiting state and must not cancel the trip. After completion, display backend finalFare/actualDistanceKm and do not recalculate fare from raw location points.</x:v>
+        <x:v>Handle SEARCHING as waiting-for-driver. Route-ETA selection is backend-only and does not change offer or trip payloads. On ACCEPTED, call REST once to hydrate the bootstrapped heartbeat location, then continue WebSocket updates during ACCEPTED/ARRIVED/IN_PROGRESS. bearing/speed can be null in the bootstrap payload; DRIVER_LOCATION_NOT_FOUND is temporary and must not cancel the trip. Display backend finalFare/actualDistanceKm after completion.</x:v>
       </x:c>
       <x:c r="D15" s="43" t="str">
         <x:v>In review</x:v>
@@ -3252,7 +3335,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b7ebc511dc4c4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4705ec9e9bb4321"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3326,10 +3409,10 @@
         <x:v>Routing endpoint is not production-calibrated.</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>Redis caching reduces repeated successful estimate calls, but endpoint capacity, cache hit rate, route request rate, latency and Vietnamese road quality are not validated.</x:v>
+        <x:v>Redis caching and bounded no-queue route-ETA execution control load, but endpoint capacity, matching latency, cache hit rate, fallback frequency and Vietnamese road quality are not validated.</x:v>
       </x:c>
       <x:c r="C4" s="24" t="str">
-        <x:v>Use a controlled OSRM-compatible endpoint, monitor cache hit/miss and STRAIGHT_LINE_FALLBACK frequency, debounce FE requests, add rate/latency metrics and tune cache precision/TTL plus provider timeout before launch.</x:v>
+        <x:v>Keep route-ETA disabled by default, use a controlled OSRM-compatible endpoint, monitor cache/provider/executor metrics, load-test concurrent matching and tune candidate count, threads, cache and timeout before enablement.</x:v>
       </x:c>
       <x:c r="D4" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3628,7 +3711,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9be178c2a5b04dea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0906b0330a8b4d52"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/pland.xlsx
+++ b/docs/pland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R794dc18ae47e4f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="R527cfae65a1d44b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R175c3a37890540ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Rf659e5668c094556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="R79420e9a0d334bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="Ra94422769f884fbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7b0e945cf66a49e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completed" sheetId="2" r:id="Rcc706d291c6d487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Remaining" sheetId="3" r:id="R080e6bd3a4684d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="4" r:id="Ra3e1d4bfc9c4450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontend" sheetId="5" r:id="Re916cce6d8824ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risks" sheetId="6" r:id="R7348e351c5c444da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65,7 +65,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -160,6 +160,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -264,7 +269,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="118">
+  <x:cellXfs count="123">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -572,6 +577,21 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -615,8 +635,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RemainingTable" displayName="RemainingTable" ref="A1:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H23"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Priority"/>
     <x:tableColumn id="2" name="Area"/>
@@ -666,8 +686,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:H20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="RisksTable" displayName="RisksTable" ref="A1:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:H21"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Risk"/>
     <x:tableColumn id="2" name="Impact"/>
@@ -909,10 +929,10 @@
         <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="C2" s="43" t="str">
-        <x:v>Reviewed</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D2" s="24" t="str">
-        <x:v>Bounded Redis GEO route-ETA matching was approved by the user.</x:v>
+        <x:v>Reliable trip messaging backend is complete and awaiting user review.</x:v>
       </x:c>
       <x:c r="E2" s="24" t="str"/>
       <x:c r="F2" s="24" t="str"/>
@@ -924,13 +944,13 @@
         <x:v>Current feature</x:v>
       </x:c>
       <x:c r="B3" s="24" t="str">
-        <x:v>codex/matching-route-eta-ranking</x:v>
+        <x:v>codex/trip-messaging-production</x:v>
       </x:c>
       <x:c r="C3" s="43" t="str">
-        <x:v>Reviewed</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D3" s="24" t="str">
-        <x:v>Approved feature is included in commit feat: rank matching candidates by route eta.</x:v>
+        <x:v>Feature branch created from develop after merging route-ETA matching ranking.</x:v>
       </x:c>
       <x:c r="E3" s="24" t="str"/>
       <x:c r="F3" s="24" t="str"/>
@@ -942,13 +962,13 @@
         <x:v>Develop base</x:v>
       </x:c>
       <x:c r="B4" s="24" t="str">
-        <x:v>ffe9964 merge: routing estimate cache</x:v>
+        <x:v>develop after merge: route eta matching ranking</x:v>
       </x:c>
       <x:c r="C4" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D4" s="24" t="str">
-        <x:v>Feature starts after the reviewed routing cache merge.</x:v>
+        <x:v>Chat work starts from the latest reviewed local develop state.</x:v>
       </x:c>
       <x:c r="E4" s="24" t="str"/>
       <x:c r="F4" s="24" t="str"/>
@@ -960,13 +980,13 @@
         <x:v>Feature commit</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>feat: rank matching candidates by route eta</x:v>
+        <x:v>planned: feat: complete reliable trip messaging</x:v>
       </x:c>
       <x:c r="C5" s="43" t="str">
-        <x:v>Committed</x:v>
+        <x:v>Uncommitted</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
-        <x:v>Reviewed implementation and documentation are committed on the feature branch.</x:v>
+        <x:v>Implementation and docs remain uncommitted for user review.</x:v>
       </x:c>
       <x:c r="E5" s="24" t="str"/>
       <x:c r="F5" s="24" t="str"/>
@@ -978,13 +998,13 @@
         <x:v>Test status</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Targeted suite: 41 pass; Spring context pass; full Maven: 597 tests, 3 baseline failures + 18 Docker errors</x:v>
+        <x:v>Full Maven: 616 pass; chat flow + SQL release integration pass</x:v>
       </x:c>
       <x:c r="C6" s="43" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D6" s="24" t="str">
-        <x:v>Route-ETA tests pass; full-suite failures remain local application.yml assertions, location messages and unavailable Docker/Testcontainers.</x:v>
+        <x:v>Docker-backed PostgreSQL/PostGIS and Redis integration tests passed.</x:v>
       </x:c>
       <x:c r="E6" s="24" t="str"/>
       <x:c r="F6" s="24" t="str"/>
@@ -1002,7 +1022,7 @@
         <x:v>Done</x:v>
       </x:c>
       <x:c r="D7" s="24" t="str">
-        <x:v>No whitespace error is reported.</x:v>
+        <x:v>No whitespace error after code, docs and workbook updates.</x:v>
       </x:c>
       <x:c r="E7" s="24" t="str"/>
       <x:c r="F7" s="24" t="str"/>
@@ -1014,13 +1034,13 @@
         <x:v>Code review</x:v>
       </x:c>
       <x:c r="B8" s="24" t="str">
-        <x:v>User and internal review complete; CodeRabbit unavailable</x:v>
+        <x:v>Internal review complete; user review pending; CodeRabbit unavailable</x:v>
       </x:c>
       <x:c r="C8" s="49" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D8" s="24" t="str">
-        <x:v>No blocking issue found; CodeRabbit is not installed in PATH.</x:v>
+        <x:v>No chat blocker found; coderabbit command is not installed in PATH.</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str"/>
       <x:c r="F8" s="24" t="str"/>
@@ -1032,13 +1052,13 @@
         <x:v>Local config</x:v>
       </x:c>
       <x:c r="B9" s="24" t="str">
-        <x:v>src/main/resources/application.yml</x:v>
+        <x:v>src/main/resources/application.yml + docs/images/</x:v>
       </x:c>
       <x:c r="C9" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>Protected</x:v>
       </x:c>
       <x:c r="D9" s="24" t="str">
-        <x:v>Keep environment-specific local changes uncommitted during commit and merge.</x:v>
+        <x:v>Tracked YAML uses env defaults; environment-specific local override and images remain outside the feature commit.</x:v>
       </x:c>
       <x:c r="E9" s="24" t="str"/>
       <x:c r="F9" s="24" t="str"/>
@@ -1158,13 +1178,13 @@
         <x:v>In-trip messaging</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>REST + STOMP trip chat</x:v>
+        <x:v>Idempotent REST/STOMP chat + cursor sync + read state + unread + FCM</x:v>
       </x:c>
       <x:c r="C16" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
-        <x:v>Merged locally into develop via merge: in-trip messaging.</x:v>
+        <x:v>Backend complete for single WebSocket replica; FE contract is documented. Broker relay remains a scale-out task.</x:v>
       </x:c>
       <x:c r="E16" s="24" t="str"/>
       <x:c r="F16" s="24" t="str"/>
@@ -1208,45 +1228,45 @@
       <x:c r="H18" s="28" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" t="str">
+      <x:c r="A19" s="68" t="str">
         <x:v>Staging readiness smoke</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B19" s="68" t="str">
         <x:v>scripts/test-staging-readiness.ps1 + GitHub workflow</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C19" s="68" t="str">
         <x:v>Committed</x:v>
       </x:c>
-      <x:c r="D19" t="str">
+      <x:c r="D19" s="68" t="str">
         <x:v>Adds optional -RequireTracing gate for typed tracing/export flags while keeping collector details private.</x:v>
       </x:c>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="E19" s="68"/>
+      <x:c r="F19" s="68"/>
+      <x:c r="G19" s="68"/>
+      <x:c r="H19" s="68"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" t="str">
+      <x:c r="A20" s="68" t="str">
         <x:v>Redis distributed rate limiting</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="68" t="str">
         <x:v>RATE_LIMIT_STORE=redis + atomic Lua token bucket</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
+      <x:c r="C20" s="68" t="str">
+        <x:v>Done</x:v>
+      </x:c>
+      <x:c r="D20" s="68" t="str">
         <x:v>Merged into develop before payment sandbox automation; production still needs managed Redis soak and alerts.</x:v>
       </x:c>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="E20" s="68"/>
+      <x:c r="F20" s="68"/>
+      <x:c r="G20" s="68"/>
+      <x:c r="H20" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf190ec02cf3469c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a0ee78f75c746ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1987,16 +2007,16 @@
         <x:v>Messaging</x:v>
       </x:c>
       <x:c r="B37" s="24" t="str">
-        <x:v>Passenger-driver in-trip messaging with persisted history, REST fallback and STOMP realtime fan-out</x:v>
+        <x:v>Reliable passenger-driver trip messaging with idempotency, reconnect sync, read state, unread count, push and rate limiting</x:v>
       </x:c>
       <x:c r="C37" s="24" t="str">
-        <x:v>GET/POST /api/v1/trips/{tripId}/messages; SEND /app/trip.message; /topic/trip/{tripId}/messages</x:v>
+        <x:v>GET/POST /api/v1/trips/{tripId}/messages; /messages/sync; /messages/read-state; /messages/unread-count; STOMP message/read topics and user ACK/error queues</x:v>
       </x:c>
       <x:c r="D37" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="E37" s="24" t="str">
-        <x:v>Only passenger and assigned driver can send during ACCEPTED/ARRIVED/IN_PROGRESS. Admin can view/subscribe for support. SQL release 20260701-trip-messages is merged.</x:v>
+        <x:v>FE-generated clientMessageId prevents duplicate retries. PostgreSQL/Redis flow and SQL release apply/verify/rollback pass; ready for FE integration review.</x:v>
       </x:c>
       <x:c r="F37" s="24"/>
       <x:c r="G37" s="24"/>
@@ -2083,24 +2103,24 @@
       <x:c r="H41" s="68"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" t="str">
+      <x:c r="A42" s="68" t="str">
         <x:v>Operations</x:v>
       </x:c>
-      <x:c r="B42" t="str">
+      <x:c r="B42" s="68" t="str">
         <x:v>Staging readiness smoke gate and JSON deployment evidence</x:v>
       </x:c>
-      <x:c r="C42" t="str">
+      <x:c r="C42" s="68" t="str">
         <x:v>scripts/test-staging-readiness.ps1; .github/workflows/staging-readiness-smoke.yml; /actuator/info</x:v>
       </x:c>
-      <x:c r="D42" t="str">
+      <x:c r="D42" s="68" t="str">
         <x:v>In review</x:v>
       </x:c>
-      <x:c r="E42" t="str">
+      <x:c r="E42" s="68" t="str">
         <x:v>Adds optional strict tracing/export checks through -RequireTracing while preserving sanitized JSON evidence and secret handling.</x:v>
       </x:c>
-      <x:c r="F42"/>
-      <x:c r="G42"/>
-      <x:c r="H42"/>
+      <x:c r="F42" s="68"/>
+      <x:c r="G42" s="68"/>
+      <x:c r="H42" s="68"/>
     </x:row>
     <x:row r="43" ht="54" customHeight="1">
       <x:c r="A43" s="68" t="str">
@@ -2118,9 +2138,9 @@
       <x:c r="E43" s="68" t="str">
         <x:v>JWT roles PASSENGER/DRIVER; provider disabled by default; validates normalized address, WGS84 coordinates and ordered cell bounds.</x:v>
       </x:c>
-      <x:c r="F43"/>
-      <x:c r="G43"/>
-      <x:c r="H43"/>
+      <x:c r="F43" s="68"/>
+      <x:c r="G43" s="68"/>
+      <x:c r="H43" s="68"/>
     </x:row>
     <x:row r="44" ht="72" customHeight="1">
       <x:c r="A44" s="74" t="str">
@@ -2132,15 +2152,15 @@
       <x:c r="C44" s="74" t="str">
         <x:v>TripCompletionFareService / trip completion</x:v>
       </x:c>
-      <x:c r="D44" s="75" t="str">
+      <x:c r="D44" s="118" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E44" s="74" t="str">
         <x:v>Filters sub-5m jitter, implausible speed, non-increasing timestamps and distance across long tracking gaps. Long gaps rebase the anchor; when no segment remains valid, final fare uses the trip estimate. No API or schema change.</x:v>
       </x:c>
-      <x:c r="F44"/>
-      <x:c r="G44"/>
-      <x:c r="H44"/>
+      <x:c r="F44" s="68"/>
+      <x:c r="G44" s="68"/>
+      <x:c r="H44" s="68"/>
     </x:row>
     <x:row r="45" ht="78" customHeight="1">
       <x:c r="A45" s="74" t="str">
@@ -2152,15 +2172,15 @@
       <x:c r="C45" s="74" t="str">
         <x:v>/api/v1/bookings/estimate; POST /api/v1/bookings</x:v>
       </x:c>
-      <x:c r="D45" s="94" t="str">
+      <x:c r="D45" s="118" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E45" s="74" t="str">
         <x:v>Caches successful provider distance/duration JSON for five minutes using routing profile and pickup/dropoff rounded to four decimals. Redis failures are non-blocking; malformed entries are evicted; fallback estimates are not cached. No FE contract change.</x:v>
       </x:c>
-      <x:c r="F45"/>
-      <x:c r="G45"/>
-      <x:c r="H45"/>
+      <x:c r="F45" s="68"/>
+      <x:c r="G45" s="68"/>
+      <x:c r="H45" s="68"/>
     </x:row>
     <x:row r="46" ht="88" customHeight="1">
       <x:c r="A46" s="74" t="str">
@@ -2172,20 +2192,20 @@
       <x:c r="C46" s="74" t="str">
         <x:v>Internal matching flow; Redis GEO; OSRM-compatible route estimate/cache</x:v>
       </x:c>
-      <x:c r="D46" s="112" t="str">
+      <x:c r="D46" s="118" t="str">
         <x:v>Done</x:v>
       </x:c>
       <x:c r="E46" s="74" t="str">
         <x:v>Includes driver coordinates, ranks a bounded top N by provider duration/route distance using concurrent no-queue execution, and atomically falls back to Redis-distance order on any incomplete result. FE offer contract is unchanged.</x:v>
       </x:c>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46"/>
+      <x:c r="F46" s="68"/>
+      <x:c r="G46" s="68"/>
+      <x:c r="H46" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39c783e3e11c4371"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R566ca76a775f4cc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2474,16 +2494,16 @@
         <x:v>Messaging</x:v>
       </x:c>
       <x:c r="C13" s="24" t="str">
-        <x:v>Add passenger-driver in-trip messaging with persisted history, REST fallback and STOMP realtime topic.</x:v>
+        <x:v>Complete reliable passenger-driver chat: idempotent sends, cursor reconnect, read state/unread, ACK/error, FCM and per-user rate limit.</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
-        <x:v>Trip topic authorization, trip participant checks and trip_messages SQL release.</x:v>
+        <x:v>Trip authorization, PostgreSQL release, Redis rate-limit store and existing WebSocket security.</x:v>
       </x:c>
       <x:c r="E13" s="24" t="str">
-        <x:v>Only trip participants can send messages during ACCEPTED/ARRIVED/IN_PROGRESS; authorized users can load history and subscribe to /topic/trip/{tripId}/messages.</x:v>
+        <x:v>616 backend tests pass; FE can sync/send/reconnect/read without duplicate messages; user review remains before merge.</x:v>
       </x:c>
       <x:c r="F13" s="43" t="str">
-        <x:v>Done</x:v>
+        <x:v>In review</x:v>
       </x:c>
       <x:c r="G13" s="24"/>
       <x:c r="H13" s="25"/>
@@ -2617,8 +2637,8 @@
       <x:c r="F19" s="68" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="G19" s="68"/>
+      <x:c r="H19" s="68"/>
     </x:row>
     <x:row r="20" ht="84" customHeight="1">
       <x:c r="A20" s="74" t="str">
@@ -2636,11 +2656,11 @@
       <x:c r="E20" s="74" t="str">
         <x:v>Spike/noise scenarios do not overcharge; legitimate route distance stays within agreed tolerance; rejected-segment and estimate-fallback rates are observable.</x:v>
       </x:c>
-      <x:c r="F20" s="81" t="str">
+      <x:c r="F20" s="119" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="G20" s="68"/>
+      <x:c r="H20" s="68"/>
     </x:row>
     <x:row r="21" ht="88" customHeight="1">
       <x:c r="A21" s="74" t="str">
@@ -2658,11 +2678,11 @@
       <x:c r="E21" s="74" t="str">
         <x:v>Real-road tests select the fastest reachable candidate, matching latency stays within target, and failures preserve Redis-distance offer order.</x:v>
       </x:c>
-      <x:c r="F21" s="114" t="str">
+      <x:c r="F21" s="120" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
+      <x:c r="G21" s="68"/>
+      <x:c r="H21" s="68"/>
     </x:row>
     <x:row r="22" ht="88" customHeight="1">
       <x:c r="A22" s="74" t="str">
@@ -2680,16 +2700,38 @@
       <x:c r="E22" s="74" t="str">
         <x:v>Dashboards show provider/cache/executor health and alerts identify elevated matching fallback or latency before passengers are affected.</x:v>
       </x:c>
-      <x:c r="F22" s="116" t="str">
+      <x:c r="F22" s="121" t="str">
         <x:v>Open</x:v>
       </x:c>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
+      <x:c r="G22" s="68"/>
+      <x:c r="H22" s="68"/>
+    </x:row>
+    <x:row r="23" ht="48" customHeight="1">
+      <x:c r="A23" s="68" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="B23" s="68" t="str">
+        <x:v>Chat horizontal scaling</x:v>
+      </x:c>
+      <x:c r="C23" s="68" t="str">
+        <x:v>Replace Spring Simple Broker or keep one WebSocket replica before scaling chat horizontally.</x:v>
+      </x:c>
+      <x:c r="D23" s="68" t="str">
+        <x:v>Managed STOMP broker relay or shared realtime fan-out plus multi-replica staging.</x:v>
+      </x:c>
+      <x:c r="E23" s="68" t="str">
+        <x:v>A message persisted on one backend replica reaches clients connected to another; REST afterId sync recovers broker interruption.</x:v>
+      </x:c>
+      <x:c r="F23" s="122" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="G23" s="68"/>
+      <x:c r="H23" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0b11e9797f84c1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R386ac433c834480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2820,10 +2862,10 @@
         <x:v>Product expansion</x:v>
       </x:c>
       <x:c r="C7" s="27" t="str">
-        <x:v>Local upload foundation, Cloudflare R2 provider, in-trip messaging, scheduled rides, surge pricing rules, service area zones and three-word mobile location gateway are implemented/in review; finish provider/R2 deployment UAT, surge tuning, real zone data and analytics.</x:v>
+        <x:v>R2 upload, reliable in-trip messaging, scheduled rides, surge pricing, service areas and three-word gateway are implemented/in review; finish FE chat integration, broker relay before multi-replica scale, provider/R2 UAT, surge tuning, real zone data and analytics.</x:v>
       </x:c>
       <x:c r="D7" s="27" t="str">
-        <x:v>Production upload and three-word providers are verified in staging; scheduled rides dispatch reliably; surge thresholds are calibrated; launch-city service polygons are validated.</x:v>
+        <x:v>FE chat passes two-device reconnect/read/unread tests; production upload and three-word providers are verified; scheduled rides, surge thresholds and launch zones pass staging UAT.</x:v>
       </x:c>
       <x:c r="E7" s="27"/>
       <x:c r="F7" s="27"/>
@@ -2833,7 +2875,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08eadd966bb24050"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52cf168c0701428d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3213,13 +3255,13 @@
         <x:v>In-trip messaging</x:v>
       </x:c>
       <x:c r="B21" s="24" t="str">
-        <x:v>GET/POST /api/v1/trips/{tripId}/messages; SEND /app/trip.message; /topic/trip/{tripId}/messages</x:v>
+        <x:v>POST /messages; GET /messages/sync; PUT /messages/read-state; GET /messages/unread-count; /topic/trip/{tripId}/messages; /message-read; user ACK/error queues</x:v>
       </x:c>
       <x:c r="C21" s="24" t="str">
-        <x:v>Load history on trip detail, subscribe to realtime messages, send text while trip status is ACCEPTED/ARRIVED/IN_PROGRESS, de-dupe by id and disable input on TRIP_MESSAGE_NOT_AVAILABLE.</x:v>
+        <x:v>Subscribe topics first, initial-sync second; send stable UUID clientMessageId via REST; de-duplicate by id/client id; reconnect with afterId; debounce read-state; handle 429 and FCM deep-link.</x:v>
       </x:c>
       <x:c r="D21" s="43" t="str">
-        <x:v>Ready for FE</x:v>
+        <x:v>Ready for FE review</x:v>
       </x:c>
       <x:c r="E21" s="24"/>
       <x:c r="F21" s="24"/>
@@ -3299,20 +3341,20 @@
       <x:c r="H25" s="68"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" t="str">
+      <x:c r="A26" s="68" t="str">
         <x:v>API documentation</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B26" s="68" t="str">
         <x:v>/v3/api-docs, /swagger-ui.html (local/staging only)</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C26" s="68" t="str">
         <x:v>Use trusted local/staging docs for integration; do not depend on these endpoints in production because startup policy requires them disabled.</x:v>
       </x:c>
-      <x:c r="D26"/>
-      <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
+      <x:c r="D26" s="68"/>
+      <x:c r="E26" s="68"/>
+      <x:c r="F26" s="68"/>
+      <x:c r="G26" s="68"/>
+      <x:c r="H26" s="68"/>
     </x:row>
     <x:row r="27" ht="72" customHeight="1">
       <x:c r="A27" s="68" t="str">
@@ -3327,15 +3369,15 @@
       <x:c r="D27" s="68" t="str">
         <x:v>Ready for FE</x:v>
       </x:c>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
+      <x:c r="E27" s="68"/>
+      <x:c r="F27" s="68"/>
+      <x:c r="G27" s="68"/>
+      <x:c r="H27" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4705ec9e9bb4321"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra669fd9cae704427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3571,10 +3613,10 @@
         <x:v>Chat moderation and retention policy is not production-defined.</x:v>
       </x:c>
       <x:c r="B13" s="24" t="str">
-        <x:v>Text chat is stored and visible to trip participants/admin support, but no moderation, deletion workflow, attachment support, read receipts or retention policy exists yet.</x:v>
+        <x:v>Text chat now has reliable history, read receipts and admin support visibility, but moderation, deletion/retention policy and attachments are not defined.</x:v>
       </x:c>
       <x:c r="C13" s="24" t="str">
-        <x:v>Keep MVP to text-only trip messages, document privacy/support access, and add moderation/retention/read receipt requirements before broad production launch if needed.</x:v>
+        <x:v>Keep launch scope text-only, document privacy/support access and retention, then add moderation/attachment requirements only after the core flow is stable.</x:v>
       </x:c>
       <x:c r="D13" s="55" t="str">
         <x:v>Partial</x:v>
@@ -3657,20 +3699,20 @@
       <x:c r="H17" s="68"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" t="str">
+      <x:c r="A18" s="68" t="str">
         <x:v>Smoke runner cannot reach a private staging backend.</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B18" s="68" t="str">
         <x:v>Workflow fails before validating application readiness, leaving no reliable release evidence.</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C18" s="68" t="str">
         <x:v>Use a self-hosted runner or trusted network path; keep the admin JWT in GORIDE_STAGING_ADMIN_TOKEN and never place it in workflow inputs.</x:v>
       </x:c>
-      <x:c r="D18"/>
-      <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
+      <x:c r="D18" s="68"/>
+      <x:c r="E18" s="68"/>
+      <x:c r="F18" s="68"/>
+      <x:c r="G18" s="68"/>
+      <x:c r="H18" s="68"/>
     </x:row>
     <x:row r="19" ht="60" customHeight="1">
       <x:c r="A19" s="68" t="str">
@@ -3685,10 +3727,10 @@
       <x:c r="D19" s="68" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
+      <x:c r="E19" s="68"/>
+      <x:c r="F19" s="68"/>
+      <x:c r="G19" s="68"/>
+      <x:c r="H19" s="68"/>
     </x:row>
     <x:row r="20" ht="84" customHeight="1">
       <x:c r="A20" s="74" t="str">
@@ -3700,18 +3742,36 @@
       <x:c r="C20" s="74" t="str">
         <x:v>Replay real-device traces in staging, reconcile against routed/odometer samples, monitor rejection and estimate-fallback rates, then tune environment settings without a code release.</x:v>
       </x:c>
-      <x:c r="D20" s="81" t="str">
+      <x:c r="D20" s="119" t="str">
         <x:v>Partial</x:v>
       </x:c>
-      <x:c r="E20"/>
-      <x:c r="F20"/>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
+      <x:c r="E20" s="68"/>
+      <x:c r="F20" s="68"/>
+      <x:c r="G20" s="68"/>
+      <x:c r="H20" s="68"/>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="68" t="str">
+        <x:v>Spring Simple Broker is single-instance realtime infrastructure.</x:v>
+      </x:c>
+      <x:c r="B21" s="68" t="str">
+        <x:v>With multiple WebSocket backend replicas, a message broadcast on one process may not reach clients connected to another process.</x:v>
+      </x:c>
+      <x:c r="C21" s="68" t="str">
+        <x:v>Run one WebSocket replica for MVP or add a managed STOMP broker relay/shared fan-out; keep REST afterId cursor sync as delivery recovery.</x:v>
+      </x:c>
+      <x:c r="D21" s="122" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="E21" s="68"/>
+      <x:c r="F21" s="68"/>
+      <x:c r="G21" s="68"/>
+      <x:c r="H21" s="68"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0906b0330a8b4d52"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R652294efcc2341af"/>
   </x:tableParts>
 </x:worksheet>
 </file>